--- a/sources_S158/2.0.0/S-158_102_Validation_Checks_2_0_0.xlsx
+++ b/sources_S158/2.0.0/S-158_102_Validation_Checks_2_0_0.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\S-102PT25\1.2_ValidationChecks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\004_IHO_GIT_Repos\S-102\sources_S158\2.0.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="362" documentId="13_ncr:1_{04A3D6D0-B112-4BC0-8C1E-6246B02D4764}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FEB75717-0E32-49CB-9052-CC34A5BDA0D9}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBC4B8FE-F92D-4646-A3F9-C4642D98445A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{D500D42E-56ED-44C2-B321-3F3845968AA3}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="1" xr2:uid="{D500D42E-56ED-44C2-B321-3F3845968AA3}"/>
   </bookViews>
   <sheets>
     <sheet name="S100ValiSpec metadata" sheetId="11" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="Legend+Tracking (internal)" sheetId="14" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">S102Checks!$A$1:$O$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">S102Checks!$A$1:$O$30</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -36,6 +36,9 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -46,7 +49,7 @@
     <author>Raphael Malyankar</author>
   </authors>
   <commentList>
-    <comment ref="E113" authorId="0" shapeId="0" xr:uid="{D6896438-96A9-4B35-AF6A-EB04B70F8003}">
+    <comment ref="E93" authorId="0" shapeId="0" xr:uid="{D6896438-96A9-4B35-AF6A-EB04B70F8003}">
       <text>
         <r>
           <rPr>
@@ -75,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="573" uniqueCount="347">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="236">
   <si>
     <t>Metadata of S-100 Validation Check Specification</t>
   </si>
@@ -288,91 +291,10 @@
     <t>Add missing attribute</t>
   </si>
   <si>
-    <t>102_Dev1004</t>
-  </si>
-  <si>
-    <t>102_1004</t>
-  </si>
-  <si>
-    <t>Wrong type for General Metadata attribute</t>
-  </si>
-  <si>
-    <t>FOR EACH attribute of the root group, WHERE the type does not match the type in the PS</t>
-  </si>
-  <si>
-    <t>Correct attribute type</t>
-  </si>
-  <si>
     <t>Table 10-2 (Root group attributes)</t>
   </si>
   <si>
-    <t>102_Dev1005</t>
-  </si>
-  <si>
-    <t>102_1005</t>
-  </si>
-  <si>
     <t>Error</t>
-  </si>
-  <si>
-    <t>Wrong format for data or time</t>
-  </si>
-  <si>
-    <r>
-      <t>FOR attributes [</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>issueDate</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>issueTime</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>], WHERE the format of the value does not match the specified pattern.</t>
-    </r>
-  </si>
-  <si>
-    <t>Correct value string</t>
-  </si>
-  <si>
-    <t>Table 10-2 (Root group attributes), 5.4</t>
-  </si>
-  <si>
-    <t>102_Dev1006</t>
-  </si>
-  <si>
-    <t>102_1006</t>
-  </si>
-  <si>
-    <t>Wrong value for General Metadata attribute</t>
-  </si>
-  <si>
-    <t>FOR EACH mandatory or conditionally mandatory attribute of the root group, WHERE the value does not match the specified range or required value (if any) in the PS</t>
   </si>
   <si>
     <t>Correct attribute value</t>
@@ -488,154 +410,9 @@
     <t>Table 5-1 (S-102 Coordinate Reference Systems), Table 10-2 (Root group attributes)</t>
   </si>
   <si>
-    <t>102_Dev1020</t>
-  </si>
-  <si>
-    <t>102_1010</t>
-  </si>
-  <si>
-    <t>Attribute verticalCS must be the EPSG code 6498</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">IF attribute </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>verticalCS</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> ≠</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.9"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 6498</t>
-    </r>
-  </si>
-  <si>
-    <t>Correct vertical coordinate system</t>
-  </si>
-  <si>
-    <t>Table 10-2</t>
-  </si>
-  <si>
-    <t>102_Dev1022</t>
-  </si>
-  <si>
-    <t>102_1011</t>
-  </si>
-  <si>
-    <t>Bathymetry data feature missing from featureCode array</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">IF </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Group_F.featureCode</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> DOES NOT contain an entry for </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>BathymetryCoverage</t>
-    </r>
-  </si>
-  <si>
-    <t>Add entry to featureCode</t>
-  </si>
-  <si>
-    <t>4, 10.2.2</t>
-  </si>
-  <si>
-    <t>102_Dev1026</t>
-  </si>
-  <si>
-    <t>102_1012</t>
-  </si>
-  <si>
-    <t>No feature instances for feature type</t>
-  </si>
-  <si>
-    <t>FOR EACH feature type, IF the root group does not contain a group member of the same name</t>
-  </si>
-  <si>
-    <t>Confirm omission of instances of the specified feature type from the dataset</t>
-  </si>
-  <si>
-    <t>10.2, Table 10-1 (Overview of S-102 Data Product), Figure 10-2 (Hierarchy of S-102 Data Product)</t>
-  </si>
-  <si>
-    <t>102_Dev1027</t>
-  </si>
-  <si>
-    <t>102_1013</t>
-  </si>
-  <si>
-    <t>Feature information dataset component type error</t>
-  </si>
-  <si>
-    <t>FOR EACH &lt;FIDS&gt;, IF the compound type or values are different from the PS</t>
-  </si>
-  <si>
-    <t>Correct structure and/or values of feature information dataset</t>
-  </si>
-  <si>
-    <t>Table 10-3 (Sample contents of the BathymetryCoverage and QualityOfBathymetryCoverage arrays)</t>
-  </si>
-  <si>
-    <t>102_Dev1028</t>
-  </si>
-  <si>
-    <t>102_1014</t>
-  </si>
-  <si>
-    <t>Extra element in root group</t>
-  </si>
-  <si>
     <t>IF there are attributes, datasets, or groups other than those allowed in the product specification</t>
   </si>
   <si>
-    <t>Remove or rename extra attribute, dataset, or group</t>
-  </si>
-  <si>
-    <t>4, 10.2.1</t>
-  </si>
-  <si>
-    <t>Completeness / Commission</t>
-  </si>
-  <si>
     <t>102_Dev1029</t>
   </si>
   <si>
@@ -657,27 +434,9 @@
     <t>Gateway to next phase</t>
   </si>
   <si>
-    <t>102_Dev2001</t>
-  </si>
-  <si>
-    <t>102_2001</t>
-  </si>
-  <si>
-    <t>Missing or invalid HDF attribute in container group</t>
-  </si>
-  <si>
-    <t>IF the HDF attributes of the respective group do not conform to the multiplicities, names, types, and values in the PS</t>
-  </si>
-  <si>
-    <t>Correct attribute</t>
-  </si>
-  <si>
     <t>Table 10-4 (Attributes of BathymetryCoverage feature container group), 10.2.8 (para. 1)</t>
   </si>
   <si>
-    <t>Logical Consistency / Format Consistency OR Conceptual Consistency</t>
-  </si>
-  <si>
     <t>102_Dev2002</t>
   </si>
   <si>
@@ -693,24 +452,6 @@
     <t>Correct attributes</t>
   </si>
   <si>
-    <t>102_Dev2003</t>
-  </si>
-  <si>
-    <t>102_2003</t>
-  </si>
-  <si>
-    <t>Feature container group does not have the axisNames dataset, or the axisNames dataset does not have the correct dimensions</t>
-  </si>
-  <si>
-    <t>IF dataset axisNames is not found or does not have the correct rank and datatype, or has length ≠ 2</t>
-  </si>
-  <si>
-    <t>Add or correct the axisNames dataset</t>
-  </si>
-  <si>
-    <t>Table 10-1 (Overview of S-102 Data Product), Figure 10-2 (Hierarchy of S-102 Data Product)</t>
-  </si>
-  <si>
     <t>102_Dev2004</t>
   </si>
   <si>
@@ -729,57 +470,6 @@
     <t>4.2.1.1.1.9, 4.2.1.1.3.5</t>
   </si>
   <si>
-    <t>102_Dev2005</t>
-  </si>
-  <si>
-    <t>102_2005</t>
-  </si>
-  <si>
-    <t>No feature attribute table in quality feature</t>
-  </si>
-  <si>
-    <t>IF &lt;QTYPE&gt; is present and the featureAttributeTable dataset does not exist</t>
-  </si>
-  <si>
-    <t>Add feature attribute table</t>
-  </si>
-  <si>
-    <t>Table 10-1 (Overview of S-102 Data Product), Figure 10-2 (Hierarchy of S-102 Data Product), 10.2.8</t>
-  </si>
-  <si>
-    <t>102_Dev2006</t>
-  </si>
-  <si>
-    <t>102_2006</t>
-  </si>
-  <si>
-    <t>Feature attribute table does not conform to PS</t>
-  </si>
-  <si>
-    <t>IF the  featureAttributeTable dataset does not have  the structure, components, and types described in the PS</t>
-  </si>
-  <si>
-    <t>Correct structure, components, and types</t>
-  </si>
-  <si>
-    <t>Table 10-8 (Elements of featureAttributeTable compound datatype)</t>
-  </si>
-  <si>
-    <t>102_Dev2009</t>
-  </si>
-  <si>
-    <t>102_2007</t>
-  </si>
-  <si>
-    <t>No instance groups in quality coverage</t>
-  </si>
-  <si>
-    <t>IF &lt;QTYPE&gt; is present and there are no groups named &lt;QTYPE&gt;.N</t>
-  </si>
-  <si>
-    <t>Add instance groups to quality coverage</t>
-  </si>
-  <si>
     <t>102_Dev2010</t>
   </si>
   <si>
@@ -813,40 +503,6 @@
     <t>Table 10-4 (Attributes of BathymetryCoverage feature container group)</t>
   </si>
   <si>
-    <t>102_Dev2012</t>
-  </si>
-  <si>
-    <t>102_2010</t>
-  </si>
-  <si>
-    <t>Extra element in container</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>Thematic Accuracy / ThematicClassificationCorrectness OR
-LogicalConsistency / Format Consistency</t>
-  </si>
-  <si>
-    <t>102_Dev2014</t>
-  </si>
-  <si>
-    <t>102_2011</t>
-  </si>
-  <si>
-    <t>&lt;QTYPE&gt; must be encoded as Feature oriented Regular Grid</t>
-  </si>
-  <si>
-    <t>IF &lt;QTYPE&gt; is present and the data coding format is not 9 (Feature oriented Regular Grid)</t>
-  </si>
-  <si>
-    <t>Encode &lt;QTYPE&gt; as  Feature oriented Regular Grid</t>
-  </si>
-  <si>
-    <t>10.2.8</t>
-  </si>
-  <si>
     <t>100_0214</t>
   </si>
   <si>
@@ -914,23 +570,6 @@
   </si>
   <si>
     <t>Correct error in bounding box attributes</t>
-  </si>
-  <si>
-    <t>102_Dev3003</t>
-  </si>
-  <si>
-    <t>102_3003</t>
-  </si>
-  <si>
-    <t>Inconsistent bounding box coordinates in   instance group</t>
-  </si>
-  <si>
-    <t>IF the bounding box attributes are inconsistent:
-(eastBoundLongitude &lt;= westBoundLongitude)
-OR (northBoundLatitude &lt;= southBoundLatitude)</t>
-  </si>
-  <si>
-    <t>6.2.1</t>
   </si>
   <si>
     <t>102_Dev3004</t>
@@ -966,60 +605,12 @@
     <t>6.2.1, 10.2.5, Table 10-6 (Attributes of BathymetryCoverage feature instance group)</t>
   </si>
   <si>
-    <t>102_Dev3006</t>
-  </si>
-  <si>
-    <t>102_3006</t>
-  </si>
-  <si>
-    <t>Grid spacing attribute in instance group has value out of range</t>
-  </si>
-  <si>
-    <t>IF attributes gridSpacingLongitudinal &lt;= 0 OR gridSpacingLatitudinal &lt;= 0</t>
-  </si>
-  <si>
-    <t>Correct value</t>
-  </si>
-  <si>
-    <t>6.2.3, Table 10-6 (Attributes of BathymetryCoverage feature instance group)</t>
-  </si>
-  <si>
-    <t>102_Dev3007</t>
-  </si>
-  <si>
-    <t>102_3007</t>
-  </si>
-  <si>
-    <t>Value of gridSpacingLongitudinal or gridSpacingLatitudinal in instance group too high</t>
-  </si>
-  <si>
-    <t>IF
-attribute gridSpacingLongitudinal &gt;  (eastBoundLongitude - westBoundLongitude)
-OR
-attribute gridSpacingLatitudinal &gt; (northBoundLatitude - southBoundLatitude)</t>
-  </si>
-  <si>
-    <t>Correct value of attribute</t>
-  </si>
-  <si>
-    <t>102_Dev3015</t>
-  </si>
-  <si>
-    <t>102_3008</t>
-  </si>
-  <si>
-    <t>Extra element in  instance group</t>
-  </si>
-  <si>
     <t>Remove or rename extra attribute, dataset, or group, or confirm its permissibility</t>
   </si>
   <si>
     <t>10.2.5, 10.2.9</t>
   </si>
   <si>
-    <t>Thematic Accuracy / ThematicClassificationCorrectness OR Logical Consistency / Format Consistency</t>
-  </si>
-  <si>
     <t>102_Dev3017</t>
   </si>
   <si>
@@ -1033,26 +624,6 @@
   </si>
   <si>
     <t>Correct attributes of quality instance group</t>
-  </si>
-  <si>
-    <t>102_Dev3018</t>
-  </si>
-  <si>
-    <t>102_3010</t>
-  </si>
-  <si>
-    <t>Grid resolution out of range</t>
-  </si>
-  <si>
-    <t>IF ABS(((numPointsLongitudinal - 1) * gridSpacingLongitudinal) - (eastBoundLongitude - westBoundLongitude)) 
-&gt; (0.5 * gridSpacingLongitudinal) OR ABS(((numPointsLatitudinal - 1) * gridSpacingLatitudinal) - (northBoundLatitude - southBoundLatitude)) &gt; (0.5 * gridSpacingLatitudinal)</t>
-  </si>
-  <si>
-    <t>Ensure that grid has correct resolution</t>
-  </si>
-  <si>
-    <t>there is a tolerance of +/- (0.5*grid spacing)
- when doing the comparison, as noted in the logical check description</t>
   </si>
   <si>
     <t>102_Dev3019</t>
@@ -1306,7 +877,7 @@
     <numFmt numFmtId="164" formatCode="yyyy"/>
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="33">
+  <fonts count="30" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1442,12 +1013,6 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
@@ -1502,17 +1067,6 @@
     <font>
       <b/>
       <sz val="9"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9.9"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
@@ -1582,7 +1136,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="18">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -1715,15 +1269,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
@@ -1778,7 +1323,7 @@
     <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="105">
+  <cellXfs count="101">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1872,22 +1417,22 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="10" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="10" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="32" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="29" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1933,8 +1478,98 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="25" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="26" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -1947,108 +1582,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="23" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="23" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="26" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="22" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="23" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="27" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -2713,8 +2246,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F44E654-AC6C-49C1-9073-99ADE8895A1C}" name="Tabelle1" displayName="Tabelle1" ref="A1:O50" totalsRowShown="0" headerRowDxfId="17" dataDxfId="16" tableBorderDxfId="15">
-  <autoFilter ref="A1:O50" xr:uid="{C4482FDF-CCC7-4CB2-82A2-40975B0659F0}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F44E654-AC6C-49C1-9073-99ADE8895A1C}" name="Tabelle1" displayName="Tabelle1" ref="A1:O30" totalsRowShown="0" headerRowDxfId="17" dataDxfId="16" tableBorderDxfId="15">
+  <autoFilter ref="A1:O30" xr:uid="{C4482FDF-CCC7-4CB2-82A2-40975B0659F0}"/>
   <tableColumns count="15">
     <tableColumn id="1" xr3:uid="{6B215FFE-658C-4C88-A9B1-399C1329F8AB}" name="Dev ID " dataDxfId="14"/>
     <tableColumn id="2" xr3:uid="{5DB5C3CF-C2D9-4A25-8D85-BC6186A89833}" name="Check ID" dataDxfId="13"/>
@@ -2737,9 +2270,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 – 2022-Design">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 – 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2777,7 +2310,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 – 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2883,7 +2416,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 – 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3025,7 +2558,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -3034,7 +2567,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5259F99A-ECF4-40F3-98D1-0270DF8F1219}">
   <dimension ref="B1:H20"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.85546875" customWidth="1"/>
     <col min="2" max="2" width="20.85546875" style="4" customWidth="1"/>
@@ -3044,19 +2577,19 @@
     <col min="7" max="7" width="6.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="15" thickBot="1"/>
-    <row r="2" spans="2:8" ht="33.6" customHeight="1">
-      <c r="B2" s="68" t="s">
+    <row r="1" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:8" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="98" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="69"/>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69"/>
-      <c r="F2" s="69"/>
-      <c r="G2" s="70"/>
+      <c r="C2" s="99"/>
+      <c r="D2" s="99"/>
+      <c r="E2" s="99"/>
+      <c r="F2" s="99"/>
+      <c r="G2" s="100"/>
       <c r="H2" s="7"/>
     </row>
-    <row r="3" spans="2:8" s="6" customFormat="1" ht="20.45" customHeight="1">
+    <row r="3" spans="2:8" s="6" customFormat="1" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="19" t="s">
         <v>1</v>
       </c>
@@ -3068,7 +2601,7 @@
       <c r="F3" s="8"/>
       <c r="G3" s="9"/>
     </row>
-    <row r="4" spans="2:8" s="6" customFormat="1" ht="20.45" customHeight="1">
+    <row r="4" spans="2:8" s="6" customFormat="1" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="19" t="s">
         <v>3</v>
       </c>
@@ -3080,7 +2613,7 @@
       <c r="F4" s="8"/>
       <c r="G4" s="9"/>
     </row>
-    <row r="5" spans="2:8" s="6" customFormat="1" ht="20.45" customHeight="1">
+    <row r="5" spans="2:8" s="6" customFormat="1" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="19" t="s">
         <v>5</v>
       </c>
@@ -3092,7 +2625,7 @@
       <c r="F5" s="8"/>
       <c r="G5" s="9"/>
     </row>
-    <row r="6" spans="2:8" s="6" customFormat="1" ht="20.45" customHeight="1">
+    <row r="6" spans="2:8" s="6" customFormat="1" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="19" t="s">
         <v>7</v>
       </c>
@@ -3104,7 +2637,7 @@
       <c r="F6" s="8"/>
       <c r="G6" s="9"/>
     </row>
-    <row r="7" spans="2:8" s="6" customFormat="1" ht="20.45" customHeight="1">
+    <row r="7" spans="2:8" s="6" customFormat="1" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="19" t="s">
         <v>9</v>
       </c>
@@ -3116,7 +2649,7 @@
       <c r="F7" s="8"/>
       <c r="G7" s="9"/>
     </row>
-    <row r="8" spans="2:8" s="6" customFormat="1" ht="20.45" customHeight="1">
+    <row r="8" spans="2:8" s="6" customFormat="1" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="19" t="s">
         <v>11</v>
       </c>
@@ -3128,7 +2661,7 @@
       <c r="F8" s="8"/>
       <c r="G8" s="9"/>
     </row>
-    <row r="9" spans="2:8" s="6" customFormat="1" ht="20.45" customHeight="1">
+    <row r="9" spans="2:8" s="6" customFormat="1" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="19" t="s">
         <v>12</v>
       </c>
@@ -3141,7 +2674,7 @@
       <c r="F9" s="8"/>
       <c r="G9" s="9"/>
     </row>
-    <row r="10" spans="2:8" s="6" customFormat="1" ht="20.45" customHeight="1">
+    <row r="10" spans="2:8" s="6" customFormat="1" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="19" t="s">
         <v>13</v>
       </c>
@@ -3153,7 +2686,7 @@
       <c r="F10" s="8"/>
       <c r="G10" s="9"/>
     </row>
-    <row r="11" spans="2:8" s="6" customFormat="1" ht="20.45" customHeight="1">
+    <row r="11" spans="2:8" s="6" customFormat="1" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="19" t="s">
         <v>15</v>
       </c>
@@ -3165,7 +2698,7 @@
       <c r="F11" s="8"/>
       <c r="G11" s="9"/>
     </row>
-    <row r="12" spans="2:8" s="6" customFormat="1" ht="15" customHeight="1">
+    <row r="12" spans="2:8" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="20"/>
       <c r="C12" s="16" t="s">
         <v>3</v>
@@ -3179,8 +2712,8 @@
       <c r="F12" s="18"/>
       <c r="G12" s="9"/>
     </row>
-    <row r="13" spans="2:8" s="6" customFormat="1" ht="20.45" customHeight="1">
-      <c r="B13" s="67" t="s">
+    <row r="13" spans="2:8" s="6" customFormat="1" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="97" t="s">
         <v>19</v>
       </c>
       <c r="C13" s="24" t="s">
@@ -3193,8 +2726,8 @@
       <c r="F13" s="29"/>
       <c r="G13" s="9"/>
     </row>
-    <row r="14" spans="2:8" s="6" customFormat="1" ht="20.45" customHeight="1">
-      <c r="B14" s="67"/>
+    <row r="14" spans="2:8" s="6" customFormat="1" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="97"/>
       <c r="C14" s="30" t="s">
         <v>22</v>
       </c>
@@ -3205,39 +2738,39 @@
       <c r="F14" s="32"/>
       <c r="G14" s="9"/>
     </row>
-    <row r="15" spans="2:8" s="6" customFormat="1" ht="20.45" customHeight="1">
-      <c r="B15" s="67"/>
+    <row r="15" spans="2:8" s="6" customFormat="1" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="97"/>
       <c r="C15" s="33"/>
       <c r="D15" s="28"/>
       <c r="E15" s="29"/>
       <c r="F15" s="31"/>
       <c r="G15" s="9"/>
     </row>
-    <row r="16" spans="2:8" s="6" customFormat="1" ht="20.45" customHeight="1">
-      <c r="B16" s="67"/>
+    <row r="16" spans="2:8" s="6" customFormat="1" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="97"/>
       <c r="C16" s="22"/>
       <c r="D16" s="8"/>
       <c r="E16" s="21"/>
       <c r="F16" s="21"/>
       <c r="G16" s="9"/>
     </row>
-    <row r="17" spans="2:7" s="6" customFormat="1" ht="20.45" customHeight="1">
-      <c r="B17" s="67"/>
+    <row r="17" spans="2:7" s="6" customFormat="1" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="97"/>
       <c r="C17" s="23"/>
       <c r="D17" s="21"/>
       <c r="E17" s="21"/>
       <c r="F17" s="21"/>
       <c r="G17" s="9"/>
     </row>
-    <row r="18" spans="2:7" s="6" customFormat="1" ht="20.45" customHeight="1">
-      <c r="B18" s="67"/>
+    <row r="18" spans="2:7" s="6" customFormat="1" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="97"/>
       <c r="C18" s="13"/>
       <c r="D18" s="8"/>
       <c r="E18" s="8"/>
       <c r="F18" s="8"/>
       <c r="G18" s="9"/>
     </row>
-    <row r="19" spans="2:7" s="6" customFormat="1" ht="20.45" customHeight="1" thickBot="1">
+    <row r="19" spans="2:7" s="6" customFormat="1" ht="20.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B19" s="10"/>
       <c r="C19" s="14"/>
       <c r="D19" s="11"/>
@@ -3245,7 +2778,7 @@
       <c r="F19" s="11"/>
       <c r="G19" s="12"/>
     </row>
-    <row r="20" spans="2:7" s="6" customFormat="1" ht="20.45" customHeight="1">
+    <row r="20" spans="2:7" s="6" customFormat="1" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="5"/>
       <c r="C20" s="15"/>
     </row>
@@ -3266,8 +2799,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4482FDF-CCC7-4CB2-82A2-40975B0659F0}">
-  <dimension ref="A1:O460"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12.75" customHeight="1"/>
+  <dimension ref="A1:O440"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.85546875" style="1" customWidth="1"/>
@@ -3287,7 +2820,7 @@
     <col min="16" max="16384" width="8.7109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="37.5" customHeight="1">
+    <row r="1" spans="1:15" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="46" t="s">
         <v>23</v>
       </c>
@@ -3334,1885 +2867,1342 @@
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="48.75" customHeight="1">
-      <c r="A2" s="77" t="s">
+    <row r="2" spans="1:15" ht="48.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="73" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="72" t="s">
+      <c r="B2" s="68" t="s">
         <v>39</v>
       </c>
-      <c r="C2" s="78" t="s">
+      <c r="C2" s="74" t="s">
         <v>40</v>
       </c>
-      <c r="D2" s="75" t="s">
+      <c r="D2" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="E2" s="75" t="s">
+      <c r="E2" s="71" t="s">
         <v>42</v>
       </c>
-      <c r="F2" s="75" t="s">
+      <c r="F2" s="71" t="s">
         <v>43</v>
       </c>
-      <c r="G2" s="75" t="s">
+      <c r="G2" s="71" t="s">
         <v>44</v>
       </c>
-      <c r="H2" s="79" t="s">
+      <c r="H2" s="75" t="s">
         <v>45</v>
       </c>
       <c r="I2" s="66" t="s">
         <v>46</v>
       </c>
-      <c r="J2" s="72" t="s">
+      <c r="J2" s="68" t="s">
         <v>21</v>
       </c>
-      <c r="K2" s="72"/>
-      <c r="L2" s="72"/>
-      <c r="M2" s="72"/>
-      <c r="N2" s="72"/>
-      <c r="O2" s="76"/>
-    </row>
-    <row r="3" spans="1:15" ht="36" customHeight="1">
-      <c r="A3" s="71" t="s">
+      <c r="K2" s="68"/>
+      <c r="L2" s="68"/>
+      <c r="M2" s="68"/>
+      <c r="N2" s="68"/>
+      <c r="O2" s="72"/>
+    </row>
+    <row r="3" spans="1:15" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="67" t="s">
         <v>47</v>
       </c>
-      <c r="B3" s="72" t="s">
+      <c r="B3" s="68" t="s">
         <v>48</v>
       </c>
-      <c r="C3" s="73" t="s">
+      <c r="C3" s="69" t="s">
         <v>49</v>
       </c>
-      <c r="D3" s="73" t="s">
+      <c r="D3" s="69" t="s">
         <v>50</v>
       </c>
-      <c r="E3" s="74" t="s">
+      <c r="E3" s="70" t="s">
         <v>51</v>
       </c>
-      <c r="F3" s="73" t="s">
+      <c r="F3" s="69" t="s">
         <v>52</v>
       </c>
-      <c r="G3" s="75" t="s">
+      <c r="G3" s="71" t="s">
         <v>44</v>
       </c>
-      <c r="H3" s="73">
+      <c r="H3" s="69">
         <v>10.199999999999999</v>
       </c>
-      <c r="I3" s="73" t="s">
+      <c r="I3" s="69" t="s">
         <v>53</v>
       </c>
-      <c r="J3" s="72" t="s">
+      <c r="J3" s="68" t="s">
         <v>21</v>
       </c>
-      <c r="K3" s="72"/>
-      <c r="L3" s="72"/>
-      <c r="M3" s="72"/>
-      <c r="N3" s="72" t="s">
+      <c r="K3" s="68"/>
+      <c r="L3" s="68"/>
+      <c r="M3" s="68"/>
+      <c r="N3" s="68" t="s">
         <v>54</v>
       </c>
-      <c r="O3" s="76"/>
-    </row>
-    <row r="4" spans="1:15" ht="40.5">
-      <c r="A4" s="71" t="s">
+      <c r="O3" s="72"/>
+    </row>
+    <row r="4" spans="1:15" ht="48" x14ac:dyDescent="0.2">
+      <c r="A4" s="67" t="s">
         <v>55</v>
       </c>
-      <c r="B4" s="72" t="s">
+      <c r="B4" s="68" t="s">
         <v>56</v>
       </c>
-      <c r="C4" s="73" t="s">
+      <c r="C4" s="69" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="73" t="s">
+      <c r="D4" s="69" t="s">
         <v>57</v>
       </c>
-      <c r="E4" s="80" t="s">
+      <c r="E4" s="76" t="s">
         <v>58</v>
       </c>
-      <c r="F4" s="73" t="s">
+      <c r="F4" s="69" t="s">
         <v>59</v>
       </c>
-      <c r="G4" s="75" t="s">
+      <c r="G4" s="71" t="s">
         <v>44</v>
       </c>
-      <c r="H4" s="81" t="s">
+      <c r="H4" s="77" t="s">
         <v>60</v>
       </c>
-      <c r="I4" s="73" t="s">
+      <c r="I4" s="69" t="s">
         <v>53</v>
       </c>
-      <c r="J4" s="72" t="s">
+      <c r="J4" s="68" t="s">
         <v>21</v>
       </c>
-      <c r="K4" s="82"/>
-      <c r="L4" s="82"/>
-      <c r="M4" s="82"/>
-      <c r="N4" s="72" t="s">
+      <c r="K4" s="78"/>
+      <c r="L4" s="78"/>
+      <c r="M4" s="78"/>
+      <c r="N4" s="68" t="s">
         <v>54</v>
       </c>
-      <c r="O4" s="76"/>
-    </row>
-    <row r="5" spans="1:15" ht="40.5">
-      <c r="A5" s="71" t="s">
+      <c r="O4" s="72"/>
+    </row>
+    <row r="5" spans="1:15" ht="48" x14ac:dyDescent="0.2">
+      <c r="A5" s="67" t="s">
         <v>61</v>
       </c>
-      <c r="B5" s="72" t="s">
+      <c r="B5" s="68" t="s">
         <v>62</v>
       </c>
-      <c r="C5" s="73" t="s">
+      <c r="C5" s="69" t="s">
         <v>49</v>
       </c>
-      <c r="D5" s="73" t="s">
+      <c r="D5" s="69" t="s">
         <v>63</v>
       </c>
-      <c r="E5" s="80" t="s">
+      <c r="E5" s="76" t="s">
         <v>64</v>
       </c>
-      <c r="F5" s="73" t="s">
+      <c r="F5" s="69" t="s">
         <v>65</v>
       </c>
-      <c r="G5" s="75" t="s">
+      <c r="G5" s="71" t="s">
         <v>44</v>
       </c>
-      <c r="H5" s="81" t="s">
+      <c r="H5" s="77" t="s">
         <v>60</v>
       </c>
-      <c r="I5" s="73" t="s">
+      <c r="I5" s="69" t="s">
         <v>53</v>
       </c>
-      <c r="J5" s="72" t="s">
+      <c r="J5" s="68" t="s">
         <v>21</v>
       </c>
-      <c r="K5" s="82"/>
-      <c r="L5" s="82"/>
-      <c r="M5" s="82"/>
-      <c r="N5" s="72" t="s">
+      <c r="K5" s="78"/>
+      <c r="L5" s="78"/>
+      <c r="M5" s="78"/>
+      <c r="N5" s="68" t="s">
         <v>54</v>
       </c>
-      <c r="O5" s="76"/>
-    </row>
-    <row r="6" spans="1:15" ht="36" customHeight="1">
-      <c r="A6" s="71" t="s">
+      <c r="O5" s="72"/>
+    </row>
+    <row r="6" spans="1:15" ht="24" x14ac:dyDescent="0.2">
+      <c r="A6" s="67" t="s">
+        <v>70</v>
+      </c>
+      <c r="B6" s="68" t="s">
+        <v>71</v>
+      </c>
+      <c r="C6" s="69" t="s">
+        <v>40</v>
+      </c>
+      <c r="D6" s="69" t="s">
+        <v>72</v>
+      </c>
+      <c r="E6" s="69" t="s">
+        <v>73</v>
+      </c>
+      <c r="F6" s="69" t="s">
+        <v>68</v>
+      </c>
+      <c r="G6" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="H6" s="76" t="s">
         <v>66</v>
       </c>
-      <c r="B6" s="72" t="s">
+      <c r="I6" s="69" t="s">
+        <v>69</v>
+      </c>
+      <c r="J6" s="68" t="s">
+        <v>21</v>
+      </c>
+      <c r="K6" s="78"/>
+      <c r="L6" s="78"/>
+      <c r="M6" s="78"/>
+      <c r="N6" s="78"/>
+      <c r="O6" s="72"/>
+    </row>
+    <row r="7" spans="1:15" ht="36" x14ac:dyDescent="0.2">
+      <c r="A7" s="67" t="s">
+        <v>74</v>
+      </c>
+      <c r="B7" s="68" t="s">
+        <v>75</v>
+      </c>
+      <c r="C7" s="69" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7" s="69" t="s">
+        <v>76</v>
+      </c>
+      <c r="E7" s="69" t="s">
+        <v>77</v>
+      </c>
+      <c r="F7" s="69" t="s">
+        <v>78</v>
+      </c>
+      <c r="G7" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="H7" s="69" t="s">
+        <v>79</v>
+      </c>
+      <c r="I7" s="69" t="s">
+        <v>69</v>
+      </c>
+      <c r="J7" s="68" t="s">
+        <v>21</v>
+      </c>
+      <c r="K7" s="79"/>
+      <c r="L7" s="78"/>
+      <c r="M7" s="78"/>
+      <c r="N7" s="78"/>
+      <c r="O7" s="72"/>
+    </row>
+    <row r="8" spans="1:15" ht="74.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="67" t="s">
+        <v>80</v>
+      </c>
+      <c r="B8" s="68" t="s">
+        <v>81</v>
+      </c>
+      <c r="C8" s="69" t="s">
+        <v>49</v>
+      </c>
+      <c r="D8" s="76" t="s">
+        <v>82</v>
+      </c>
+      <c r="E8" s="70" t="s">
+        <v>83</v>
+      </c>
+      <c r="F8" s="69" t="s">
+        <v>84</v>
+      </c>
+      <c r="G8" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="H8" s="76" t="s">
+        <v>85</v>
+      </c>
+      <c r="I8" s="69" t="s">
+        <v>69</v>
+      </c>
+      <c r="J8" s="68" t="s">
+        <v>21</v>
+      </c>
+      <c r="K8" s="68"/>
+      <c r="L8" s="68"/>
+      <c r="M8" s="68"/>
+      <c r="N8" s="68"/>
+      <c r="O8" s="72"/>
+    </row>
+    <row r="9" spans="1:15" ht="36" x14ac:dyDescent="0.2">
+      <c r="A9" s="67" t="s">
+        <v>87</v>
+      </c>
+      <c r="B9" s="68" t="s">
+        <v>88</v>
+      </c>
+      <c r="C9" s="80" t="s">
+        <v>49</v>
+      </c>
+      <c r="D9" s="69" t="s">
+        <v>89</v>
+      </c>
+      <c r="E9" s="69" t="s">
+        <v>90</v>
+      </c>
+      <c r="F9" s="69" t="s">
+        <v>91</v>
+      </c>
+      <c r="G9" s="71" t="s">
+        <v>92</v>
+      </c>
+      <c r="H9" s="69" t="s">
+        <v>92</v>
+      </c>
+      <c r="I9" s="69"/>
+      <c r="J9" s="68"/>
+      <c r="K9" s="68"/>
+      <c r="L9" s="68"/>
+      <c r="M9" s="68"/>
+      <c r="N9" s="68"/>
+      <c r="O9" s="72" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" ht="100.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="67" t="s">
+        <v>95</v>
+      </c>
+      <c r="B10" s="95" t="s">
+        <v>96</v>
+      </c>
+      <c r="C10" s="74" t="s">
         <v>67</v>
       </c>
-      <c r="C6" s="73" t="s">
+      <c r="D10" s="71" t="s">
+        <v>97</v>
+      </c>
+      <c r="E10" s="71" t="s">
+        <v>98</v>
+      </c>
+      <c r="F10" s="71" t="s">
+        <v>99</v>
+      </c>
+      <c r="G10" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="H10" s="81" t="s">
+        <v>94</v>
+      </c>
+      <c r="I10" s="69" t="s">
+        <v>69</v>
+      </c>
+      <c r="J10" s="68" t="s">
+        <v>21</v>
+      </c>
+      <c r="K10" s="68"/>
+      <c r="L10" s="68"/>
+      <c r="M10" s="68"/>
+      <c r="N10" s="68" t="s">
+        <v>54</v>
+      </c>
+      <c r="O10" s="72"/>
+    </row>
+    <row r="11" spans="1:15" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A11" s="67" t="s">
+        <v>100</v>
+      </c>
+      <c r="B11" s="95" t="s">
+        <v>101</v>
+      </c>
+      <c r="C11" s="74" t="s">
+        <v>67</v>
+      </c>
+      <c r="D11" s="71" t="s">
+        <v>102</v>
+      </c>
+      <c r="E11" s="71" t="s">
+        <v>103</v>
+      </c>
+      <c r="F11" s="71" t="s">
+        <v>104</v>
+      </c>
+      <c r="G11" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="H11" s="81" t="s">
+        <v>105</v>
+      </c>
+      <c r="I11" s="69" t="s">
+        <v>69</v>
+      </c>
+      <c r="J11" s="68" t="s">
+        <v>21</v>
+      </c>
+      <c r="K11" s="83"/>
+      <c r="L11" s="83"/>
+      <c r="M11" s="68"/>
+      <c r="N11" s="83"/>
+      <c r="O11" s="72"/>
+    </row>
+    <row r="12" spans="1:15" s="44" customFormat="1" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A12" s="67" t="s">
+        <v>106</v>
+      </c>
+      <c r="B12" s="95" t="s">
+        <v>107</v>
+      </c>
+      <c r="C12" s="74" t="s">
+        <v>40</v>
+      </c>
+      <c r="D12" s="71" t="s">
+        <v>108</v>
+      </c>
+      <c r="E12" s="71" t="s">
+        <v>109</v>
+      </c>
+      <c r="F12" s="45" t="s">
+        <v>110</v>
+      </c>
+      <c r="G12" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="H12" s="81" t="s">
+        <v>92</v>
+      </c>
+      <c r="I12" s="69" t="s">
+        <v>53</v>
+      </c>
+      <c r="J12" s="68" t="s">
+        <v>21</v>
+      </c>
+      <c r="K12" s="83"/>
+      <c r="L12" s="83"/>
+      <c r="M12" s="68" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="N12" s="83"/>
+      <c r="O12" s="72"/>
+    </row>
+    <row r="13" spans="1:15" ht="72.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="67" t="s">
+        <v>111</v>
+      </c>
+      <c r="B13" s="95" t="s">
+        <v>112</v>
+      </c>
+      <c r="C13" s="74" t="s">
+        <v>40</v>
+      </c>
+      <c r="D13" s="71" t="s">
+        <v>113</v>
+      </c>
+      <c r="E13" s="71" t="s">
+        <v>114</v>
+      </c>
+      <c r="F13" s="45" t="s">
+        <v>115</v>
+      </c>
+      <c r="G13" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="H13" s="81" t="s">
+        <v>116</v>
+      </c>
+      <c r="I13" s="69" t="s">
+        <v>69</v>
+      </c>
+      <c r="J13" s="68" t="s">
+        <v>21</v>
+      </c>
+      <c r="K13" s="83"/>
+      <c r="L13" s="83"/>
+      <c r="M13" s="68" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="N13" s="83"/>
+      <c r="O13" s="72"/>
+    </row>
+    <row r="14" spans="1:15" ht="24" x14ac:dyDescent="0.2">
+      <c r="A14" s="67" t="s">
+        <v>118</v>
+      </c>
+      <c r="B14" s="95" t="s">
+        <v>119</v>
+      </c>
+      <c r="C14" s="74" t="s">
         <v>49</v>
       </c>
-      <c r="D6" s="73" t="s">
-        <v>68</v>
-      </c>
-      <c r="E6" s="73" t="s">
+      <c r="D14" s="84" t="s">
+        <v>120</v>
+      </c>
+      <c r="E14" s="85" t="s">
+        <v>121</v>
+      </c>
+      <c r="F14" s="71" t="s">
+        <v>122</v>
+      </c>
+      <c r="G14" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="H14" s="81" t="s">
+        <v>123</v>
+      </c>
+      <c r="I14" s="69" t="s">
+        <v>53</v>
+      </c>
+      <c r="J14" s="68" t="s">
+        <v>21</v>
+      </c>
+      <c r="K14" s="68"/>
+      <c r="L14" s="68"/>
+      <c r="M14" s="84" t="s">
+        <v>117</v>
+      </c>
+      <c r="N14" s="68" t="s">
+        <v>54</v>
+      </c>
+      <c r="O14" s="72"/>
+    </row>
+    <row r="15" spans="1:15" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A15" s="67" t="s">
+        <v>124</v>
+      </c>
+      <c r="B15" s="95" t="s">
+        <v>125</v>
+      </c>
+      <c r="C15" s="74" t="s">
+        <v>49</v>
+      </c>
+      <c r="D15" s="71" t="s">
+        <v>126</v>
+      </c>
+      <c r="E15" s="71" t="s">
+        <v>127</v>
+      </c>
+      <c r="F15" s="45" t="s">
+        <v>128</v>
+      </c>
+      <c r="G15" s="71" t="s">
+        <v>92</v>
+      </c>
+      <c r="H15" s="81" t="s">
+        <v>92</v>
+      </c>
+      <c r="I15" s="69"/>
+      <c r="J15" s="68"/>
+      <c r="K15" s="83"/>
+      <c r="L15" s="83"/>
+      <c r="M15" s="68"/>
+      <c r="N15" s="83"/>
+      <c r="O15" s="72" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" ht="63.75" x14ac:dyDescent="0.2">
+      <c r="A16" s="86" t="s">
+        <v>129</v>
+      </c>
+      <c r="B16" s="95" t="s">
+        <v>130</v>
+      </c>
+      <c r="C16" s="74" t="s">
+        <v>49</v>
+      </c>
+      <c r="D16" s="71" t="s">
+        <v>131</v>
+      </c>
+      <c r="E16" s="71" t="s">
+        <v>132</v>
+      </c>
+      <c r="F16" s="71" t="s">
+        <v>133</v>
+      </c>
+      <c r="G16" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="H16" s="81" t="s">
+        <v>134</v>
+      </c>
+      <c r="I16" s="69" t="s">
+        <v>53</v>
+      </c>
+      <c r="J16" s="68" t="s">
+        <v>21</v>
+      </c>
+      <c r="K16" s="83"/>
+      <c r="L16" s="83"/>
+      <c r="M16" s="68"/>
+      <c r="N16" s="83"/>
+      <c r="O16" s="82"/>
+    </row>
+    <row r="17" spans="1:15" ht="63.75" x14ac:dyDescent="0.2">
+      <c r="A17" s="86" t="s">
+        <v>135</v>
+      </c>
+      <c r="B17" s="95" t="s">
+        <v>136</v>
+      </c>
+      <c r="C17" s="74" t="s">
+        <v>67</v>
+      </c>
+      <c r="D17" s="71" t="s">
+        <v>137</v>
+      </c>
+      <c r="E17" s="68" t="s">
+        <v>138</v>
+      </c>
+      <c r="F17" s="71" t="s">
+        <v>139</v>
+      </c>
+      <c r="G17" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="H17" s="77" t="s">
+        <v>60</v>
+      </c>
+      <c r="I17" s="69" t="s">
         <v>69</v>
       </c>
-      <c r="F6" s="73" t="s">
-        <v>70</v>
-      </c>
-      <c r="G6" s="75" t="s">
+      <c r="J17" s="68" t="s">
+        <v>21</v>
+      </c>
+      <c r="K17" s="83"/>
+      <c r="L17" s="83"/>
+      <c r="M17" s="68"/>
+      <c r="N17" s="83"/>
+      <c r="O17" s="72"/>
+    </row>
+    <row r="18" spans="1:15" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A18" s="86" t="s">
+        <v>140</v>
+      </c>
+      <c r="B18" s="95" t="s">
+        <v>141</v>
+      </c>
+      <c r="C18" s="74" t="s">
+        <v>67</v>
+      </c>
+      <c r="D18" s="71" t="s">
+        <v>142</v>
+      </c>
+      <c r="E18" s="71" t="s">
+        <v>143</v>
+      </c>
+      <c r="F18" s="71" t="s">
+        <v>139</v>
+      </c>
+      <c r="G18" s="71" t="s">
         <v>44</v>
       </c>
-      <c r="H6" s="80" t="s">
-        <v>71</v>
-      </c>
-      <c r="I6" s="73" t="s">
+      <c r="H18" s="81" t="s">
+        <v>66</v>
+      </c>
+      <c r="I18" s="69" t="s">
+        <v>69</v>
+      </c>
+      <c r="J18" s="68" t="s">
+        <v>21</v>
+      </c>
+      <c r="K18" s="83"/>
+      <c r="L18" s="83"/>
+      <c r="M18" s="68"/>
+      <c r="N18" s="83"/>
+      <c r="O18" s="72"/>
+    </row>
+    <row r="19" spans="1:15" ht="93" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="86" t="s">
+        <v>144</v>
+      </c>
+      <c r="B19" s="95" t="s">
+        <v>145</v>
+      </c>
+      <c r="C19" s="74" t="s">
+        <v>67</v>
+      </c>
+      <c r="D19" s="45" t="s">
+        <v>146</v>
+      </c>
+      <c r="E19" s="45" t="s">
+        <v>147</v>
+      </c>
+      <c r="F19" s="45" t="s">
+        <v>148</v>
+      </c>
+      <c r="G19" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="H19" s="81" t="s">
+        <v>149</v>
+      </c>
+      <c r="I19" s="69" t="s">
+        <v>69</v>
+      </c>
+      <c r="J19" s="68" t="s">
+        <v>21</v>
+      </c>
+      <c r="K19" s="83"/>
+      <c r="L19" s="83"/>
+      <c r="M19" s="68"/>
+      <c r="N19" s="83"/>
+      <c r="O19" s="72"/>
+    </row>
+    <row r="20" spans="1:15" ht="63.75" x14ac:dyDescent="0.2">
+      <c r="A20" s="86" t="s">
+        <v>152</v>
+      </c>
+      <c r="B20" s="95" t="s">
+        <v>153</v>
+      </c>
+      <c r="C20" s="74" t="s">
+        <v>67</v>
+      </c>
+      <c r="D20" s="71" t="s">
+        <v>154</v>
+      </c>
+      <c r="E20" s="71" t="s">
+        <v>155</v>
+      </c>
+      <c r="F20" s="71" t="s">
+        <v>156</v>
+      </c>
+      <c r="G20" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="H20" s="81" t="s">
+        <v>151</v>
+      </c>
+      <c r="I20" s="69" t="s">
         <v>53</v>
       </c>
-      <c r="J6" s="72" t="s">
+      <c r="J20" s="68" t="s">
         <v>21</v>
       </c>
-      <c r="K6" s="82"/>
-      <c r="L6" s="82"/>
-      <c r="M6" s="82"/>
-      <c r="N6" s="72" t="s">
+      <c r="K20" s="83"/>
+      <c r="L20" s="83"/>
+      <c r="M20" s="68"/>
+      <c r="N20" s="83"/>
+      <c r="O20" s="72"/>
+    </row>
+    <row r="21" spans="1:15" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A21" s="86" t="s">
+        <v>157</v>
+      </c>
+      <c r="B21" s="95" t="s">
+        <v>158</v>
+      </c>
+      <c r="C21" s="74" t="s">
+        <v>49</v>
+      </c>
+      <c r="D21" s="71" t="s">
+        <v>159</v>
+      </c>
+      <c r="E21" s="71" t="s">
+        <v>160</v>
+      </c>
+      <c r="F21" s="71" t="s">
+        <v>161</v>
+      </c>
+      <c r="G21" s="71" t="s">
+        <v>92</v>
+      </c>
+      <c r="H21" s="81" t="s">
+        <v>92</v>
+      </c>
+      <c r="I21" s="45"/>
+      <c r="J21" s="81"/>
+      <c r="K21" s="83"/>
+      <c r="L21" s="83"/>
+      <c r="M21" s="68"/>
+      <c r="N21" s="83"/>
+      <c r="O21" s="72" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A22" s="86" t="s">
+        <v>162</v>
+      </c>
+      <c r="B22" s="95" t="s">
+        <v>163</v>
+      </c>
+      <c r="C22" s="74" t="s">
+        <v>49</v>
+      </c>
+      <c r="D22" s="71" t="s">
+        <v>164</v>
+      </c>
+      <c r="E22" s="71" t="s">
+        <v>165</v>
+      </c>
+      <c r="F22" s="71" t="s">
+        <v>166</v>
+      </c>
+      <c r="G22" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="H22" s="81" t="s">
+        <v>167</v>
+      </c>
+      <c r="I22" s="71" t="s">
+        <v>53</v>
+      </c>
+      <c r="J22" s="68" t="s">
+        <v>21</v>
+      </c>
+      <c r="K22" s="83"/>
+      <c r="L22" s="83"/>
+      <c r="M22" s="68"/>
+      <c r="N22" s="83"/>
+      <c r="O22" s="72"/>
+    </row>
+    <row r="23" spans="1:15" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A23" s="86" t="s">
+        <v>168</v>
+      </c>
+      <c r="B23" s="95" t="s">
+        <v>169</v>
+      </c>
+      <c r="C23" s="74" t="s">
+        <v>40</v>
+      </c>
+      <c r="D23" s="71" t="s">
+        <v>170</v>
+      </c>
+      <c r="E23" s="71" t="s">
+        <v>171</v>
+      </c>
+      <c r="F23" s="71" t="s">
+        <v>172</v>
+      </c>
+      <c r="G23" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="H23" s="87" t="s">
+        <v>173</v>
+      </c>
+      <c r="I23" s="87" t="s">
+        <v>174</v>
+      </c>
+      <c r="J23" s="87" t="s">
+        <v>21</v>
+      </c>
+      <c r="K23" s="83"/>
+      <c r="L23" s="83"/>
+      <c r="M23" s="68"/>
+      <c r="N23" s="83"/>
+      <c r="O23" s="72"/>
+    </row>
+    <row r="24" spans="1:15" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A24" s="86" t="s">
+        <v>175</v>
+      </c>
+      <c r="B24" s="95" t="s">
+        <v>176</v>
+      </c>
+      <c r="C24" s="74" t="s">
+        <v>40</v>
+      </c>
+      <c r="D24" s="71" t="s">
+        <v>177</v>
+      </c>
+      <c r="E24" s="71" t="s">
+        <v>86</v>
+      </c>
+      <c r="F24" s="71" t="s">
+        <v>150</v>
+      </c>
+      <c r="G24" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="H24" s="81" t="s">
+        <v>178</v>
+      </c>
+      <c r="I24" s="71" t="s">
+        <v>53</v>
+      </c>
+      <c r="J24" s="68" t="s">
+        <v>21</v>
+      </c>
+      <c r="K24" s="83"/>
+      <c r="L24" s="83"/>
+      <c r="M24" s="68"/>
+      <c r="N24" s="83"/>
+      <c r="O24" s="72"/>
+    </row>
+    <row r="25" spans="1:15" ht="150" x14ac:dyDescent="0.2">
+      <c r="A25" s="86" t="s">
+        <v>179</v>
+      </c>
+      <c r="B25" s="95" t="s">
+        <v>180</v>
+      </c>
+      <c r="C25" s="74" t="s">
+        <v>67</v>
+      </c>
+      <c r="D25" s="96" t="s">
+        <v>181</v>
+      </c>
+      <c r="E25" s="96" t="s">
+        <v>182</v>
+      </c>
+      <c r="F25" s="83" t="s">
+        <v>183</v>
+      </c>
+      <c r="G25" s="71" t="s">
+        <v>92</v>
+      </c>
+      <c r="H25" s="81" t="s">
+        <v>92</v>
+      </c>
+      <c r="I25" s="87" t="s">
+        <v>46</v>
+      </c>
+      <c r="J25" s="87" t="s">
+        <v>21</v>
+      </c>
+      <c r="K25" s="83"/>
+      <c r="L25" s="83"/>
+      <c r="M25" s="68"/>
+      <c r="N25" s="83" t="s">
         <v>54</v>
       </c>
-      <c r="O6" s="76"/>
-    </row>
-    <row r="7" spans="1:15" ht="40.5" customHeight="1">
-      <c r="A7" s="71" t="s">
-        <v>72</v>
-      </c>
-      <c r="B7" s="72" t="s">
-        <v>73</v>
-      </c>
-      <c r="C7" s="73" t="s">
-        <v>74</v>
-      </c>
-      <c r="D7" s="73" t="s">
-        <v>75</v>
-      </c>
-      <c r="E7" s="73" t="s">
-        <v>76</v>
-      </c>
-      <c r="F7" s="73" t="s">
-        <v>77</v>
-      </c>
-      <c r="G7" s="75" t="s">
+      <c r="O25" s="72" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" ht="135" x14ac:dyDescent="0.2">
+      <c r="A26" s="86" t="s">
+        <v>185</v>
+      </c>
+      <c r="B26" s="95" t="s">
+        <v>186</v>
+      </c>
+      <c r="C26" s="74" t="s">
+        <v>67</v>
+      </c>
+      <c r="D26" s="45" t="s">
+        <v>187</v>
+      </c>
+      <c r="E26" s="96" t="s">
+        <v>188</v>
+      </c>
+      <c r="F26" s="83" t="s">
+        <v>183</v>
+      </c>
+      <c r="G26" s="71" t="s">
+        <v>92</v>
+      </c>
+      <c r="H26" s="81" t="s">
+        <v>92</v>
+      </c>
+      <c r="I26" s="87" t="s">
+        <v>46</v>
+      </c>
+      <c r="J26" s="68" t="s">
+        <v>21</v>
+      </c>
+      <c r="K26" s="83"/>
+      <c r="L26" s="83"/>
+      <c r="M26" s="68"/>
+      <c r="N26" s="83" t="s">
+        <v>54</v>
+      </c>
+      <c r="O26" s="96" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" ht="51" x14ac:dyDescent="0.2">
+      <c r="A27" s="73" t="s">
+        <v>190</v>
+      </c>
+      <c r="B27" s="95" t="s">
+        <v>191</v>
+      </c>
+      <c r="C27" s="74" t="s">
+        <v>49</v>
+      </c>
+      <c r="D27" s="71" t="s">
+        <v>192</v>
+      </c>
+      <c r="E27" s="71" t="s">
+        <v>193</v>
+      </c>
+      <c r="F27" s="71" t="s">
+        <v>194</v>
+      </c>
+      <c r="G27" s="71" t="s">
         <v>44</v>
       </c>
-      <c r="H7" s="80" t="s">
-        <v>78</v>
-      </c>
-      <c r="I7" s="73" t="s">
+      <c r="H27" s="71" t="s">
+        <v>195</v>
+      </c>
+      <c r="I27" s="71" t="s">
+        <v>196</v>
+      </c>
+      <c r="J27" s="71" t="s">
+        <v>21</v>
+      </c>
+      <c r="K27" s="83"/>
+      <c r="L27" s="83"/>
+      <c r="M27" s="68"/>
+      <c r="N27" s="83"/>
+      <c r="O27" s="72"/>
+    </row>
+    <row r="28" spans="1:15" ht="51" x14ac:dyDescent="0.2">
+      <c r="A28" s="73" t="s">
+        <v>197</v>
+      </c>
+      <c r="B28" s="95" t="s">
+        <v>198</v>
+      </c>
+      <c r="C28" s="74" t="s">
+        <v>67</v>
+      </c>
+      <c r="D28" s="71" t="s">
+        <v>199</v>
+      </c>
+      <c r="E28" s="88" t="s">
+        <v>200</v>
+      </c>
+      <c r="F28" s="88" t="s">
+        <v>201</v>
+      </c>
+      <c r="G28" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="H28" s="75" t="s">
+        <v>202</v>
+      </c>
+      <c r="I28" s="71" t="s">
+        <v>196</v>
+      </c>
+      <c r="J28" s="68" t="s">
+        <v>21</v>
+      </c>
+      <c r="K28" s="83"/>
+      <c r="L28" s="83"/>
+      <c r="M28" s="68"/>
+      <c r="N28" s="83"/>
+      <c r="O28" s="72"/>
+    </row>
+    <row r="29" spans="1:15" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A29" s="73" t="s">
+        <v>203</v>
+      </c>
+      <c r="B29" s="95" t="s">
+        <v>204</v>
+      </c>
+      <c r="C29" s="74" t="s">
+        <v>67</v>
+      </c>
+      <c r="D29" s="71" t="s">
+        <v>205</v>
+      </c>
+      <c r="E29" s="71" t="s">
+        <v>206</v>
+      </c>
+      <c r="F29" s="71" t="s">
+        <v>207</v>
+      </c>
+      <c r="G29" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="H29" s="71" t="s">
+        <v>208</v>
+      </c>
+      <c r="I29" s="71" t="s">
+        <v>196</v>
+      </c>
+      <c r="J29" s="71" t="s">
+        <v>21</v>
+      </c>
+      <c r="K29" s="83"/>
+      <c r="L29" s="83"/>
+      <c r="M29" s="68"/>
+      <c r="N29" s="83"/>
+      <c r="O29" s="72"/>
+    </row>
+    <row r="30" spans="1:15" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A30" s="89" t="s">
+        <v>209</v>
+      </c>
+      <c r="B30" s="95" t="s">
+        <v>210</v>
+      </c>
+      <c r="C30" s="90" t="s">
+        <v>40</v>
+      </c>
+      <c r="D30" s="91" t="s">
+        <v>211</v>
+      </c>
+      <c r="E30" s="91" t="s">
+        <v>212</v>
+      </c>
+      <c r="F30" s="91" t="s">
+        <v>183</v>
+      </c>
+      <c r="G30" s="91" t="s">
+        <v>44</v>
+      </c>
+      <c r="H30" s="92" t="s">
+        <v>213</v>
+      </c>
+      <c r="I30" s="91" t="s">
         <v>53</v>
       </c>
-      <c r="J7" s="72" t="s">
+      <c r="J30" s="93" t="s">
         <v>21</v>
       </c>
-      <c r="K7" s="82"/>
-      <c r="L7" s="82"/>
-      <c r="M7" s="82"/>
-      <c r="N7" s="82"/>
-      <c r="O7" s="76"/>
-    </row>
-    <row r="8" spans="1:15" ht="37.5">
-      <c r="A8" s="71" t="s">
-        <v>79</v>
-      </c>
-      <c r="B8" s="72" t="s">
-        <v>80</v>
-      </c>
-      <c r="C8" s="73" t="s">
-        <v>49</v>
-      </c>
-      <c r="D8" s="73" t="s">
-        <v>81</v>
-      </c>
-      <c r="E8" s="73" t="s">
-        <v>82</v>
-      </c>
-      <c r="F8" s="73" t="s">
-        <v>83</v>
-      </c>
-      <c r="G8" s="75" t="s">
-        <v>44</v>
-      </c>
-      <c r="H8" s="80" t="s">
-        <v>71</v>
-      </c>
-      <c r="I8" s="73" t="s">
-        <v>84</v>
-      </c>
-      <c r="J8" s="72" t="s">
-        <v>21</v>
-      </c>
-      <c r="K8" s="82"/>
-      <c r="L8" s="82"/>
-      <c r="M8" s="82"/>
-      <c r="N8" s="75" t="s">
-        <v>54</v>
-      </c>
-      <c r="O8" s="76"/>
-    </row>
-    <row r="9" spans="1:15" ht="24.75">
-      <c r="A9" s="71" t="s">
-        <v>85</v>
-      </c>
-      <c r="B9" s="72" t="s">
-        <v>86</v>
-      </c>
-      <c r="C9" s="73" t="s">
-        <v>40</v>
-      </c>
-      <c r="D9" s="73" t="s">
-        <v>87</v>
-      </c>
-      <c r="E9" s="73" t="s">
-        <v>88</v>
-      </c>
-      <c r="F9" s="73" t="s">
-        <v>83</v>
-      </c>
-      <c r="G9" s="75" t="s">
-        <v>44</v>
-      </c>
-      <c r="H9" s="80" t="s">
-        <v>71</v>
-      </c>
-      <c r="I9" s="73" t="s">
-        <v>84</v>
-      </c>
-      <c r="J9" s="72" t="s">
-        <v>21</v>
-      </c>
-      <c r="K9" s="82"/>
-      <c r="L9" s="82"/>
-      <c r="M9" s="82"/>
-      <c r="N9" s="82"/>
-      <c r="O9" s="76"/>
-    </row>
-    <row r="10" spans="1:15" ht="37.5">
-      <c r="A10" s="71" t="s">
-        <v>89</v>
-      </c>
-      <c r="B10" s="72" t="s">
-        <v>90</v>
-      </c>
-      <c r="C10" s="73" t="s">
-        <v>40</v>
-      </c>
-      <c r="D10" s="73" t="s">
-        <v>91</v>
-      </c>
-      <c r="E10" s="73" t="s">
-        <v>92</v>
-      </c>
-      <c r="F10" s="73" t="s">
-        <v>93</v>
-      </c>
-      <c r="G10" s="75" t="s">
-        <v>44</v>
-      </c>
-      <c r="H10" s="73" t="s">
-        <v>94</v>
-      </c>
-      <c r="I10" s="73" t="s">
-        <v>84</v>
-      </c>
-      <c r="J10" s="72" t="s">
-        <v>21</v>
-      </c>
-      <c r="K10" s="83"/>
-      <c r="L10" s="82"/>
-      <c r="M10" s="82"/>
-      <c r="N10" s="82"/>
-      <c r="O10" s="76"/>
-    </row>
-    <row r="11" spans="1:15" ht="74.25" customHeight="1">
-      <c r="A11" s="71" t="s">
-        <v>95</v>
-      </c>
-      <c r="B11" s="72" t="s">
-        <v>96</v>
-      </c>
-      <c r="C11" s="73" t="s">
-        <v>49</v>
-      </c>
-      <c r="D11" s="80" t="s">
-        <v>97</v>
-      </c>
-      <c r="E11" s="74" t="s">
-        <v>98</v>
-      </c>
-      <c r="F11" s="73" t="s">
-        <v>99</v>
-      </c>
-      <c r="G11" s="75" t="s">
-        <v>44</v>
-      </c>
-      <c r="H11" s="80" t="s">
-        <v>100</v>
-      </c>
-      <c r="I11" s="73" t="s">
-        <v>84</v>
-      </c>
-      <c r="J11" s="72" t="s">
-        <v>21</v>
-      </c>
-      <c r="K11" s="72"/>
-      <c r="L11" s="72"/>
-      <c r="M11" s="72"/>
-      <c r="N11" s="72"/>
-      <c r="O11" s="76"/>
-    </row>
-    <row r="12" spans="1:15" ht="24.75">
-      <c r="A12" s="71" t="s">
-        <v>101</v>
-      </c>
-      <c r="B12" s="72" t="s">
-        <v>102</v>
-      </c>
-      <c r="C12" s="73" t="s">
-        <v>49</v>
-      </c>
-      <c r="D12" s="73" t="s">
-        <v>103</v>
-      </c>
-      <c r="E12" s="73" t="s">
-        <v>104</v>
-      </c>
-      <c r="F12" s="73" t="s">
-        <v>105</v>
-      </c>
-      <c r="G12" s="75" t="s">
-        <v>44</v>
-      </c>
-      <c r="H12" s="80" t="s">
-        <v>106</v>
-      </c>
-      <c r="I12" s="73" t="s">
-        <v>84</v>
-      </c>
-      <c r="J12" s="72" t="s">
-        <v>21</v>
-      </c>
-      <c r="K12" s="72"/>
-      <c r="L12" s="72"/>
-      <c r="M12" s="72"/>
-      <c r="N12" s="72"/>
-      <c r="O12" s="76"/>
-    </row>
-    <row r="13" spans="1:15" ht="24.75">
-      <c r="A13" s="71" t="s">
-        <v>107</v>
-      </c>
-      <c r="B13" s="72" t="s">
-        <v>108</v>
-      </c>
-      <c r="C13" s="73" t="s">
-        <v>49</v>
-      </c>
-      <c r="D13" s="73" t="s">
-        <v>109</v>
-      </c>
-      <c r="E13" s="73" t="s">
-        <v>110</v>
-      </c>
-      <c r="F13" s="73" t="s">
-        <v>111</v>
-      </c>
-      <c r="G13" s="75" t="s">
-        <v>44</v>
-      </c>
-      <c r="H13" s="73" t="s">
-        <v>112</v>
-      </c>
-      <c r="I13" s="73" t="s">
-        <v>53</v>
-      </c>
-      <c r="J13" s="72" t="s">
-        <v>21</v>
-      </c>
-      <c r="K13" s="72"/>
-      <c r="L13" s="72"/>
-      <c r="M13" s="72"/>
-      <c r="N13" s="72" t="s">
-        <v>54</v>
-      </c>
-      <c r="O13" s="76"/>
-    </row>
-    <row r="14" spans="1:15" ht="62.25">
-      <c r="A14" s="71" t="s">
-        <v>113</v>
-      </c>
-      <c r="B14" s="72" t="s">
-        <v>114</v>
-      </c>
-      <c r="C14" s="73" t="s">
-        <v>49</v>
-      </c>
-      <c r="D14" s="73" t="s">
-        <v>115</v>
-      </c>
-      <c r="E14" s="73" t="s">
-        <v>116</v>
-      </c>
-      <c r="F14" s="73" t="s">
-        <v>117</v>
-      </c>
-      <c r="G14" s="75" t="s">
-        <v>44</v>
-      </c>
-      <c r="H14" s="73" t="s">
-        <v>118</v>
-      </c>
-      <c r="I14" s="73" t="s">
-        <v>53</v>
-      </c>
-      <c r="J14" s="72" t="s">
-        <v>21</v>
-      </c>
-      <c r="K14" s="72"/>
-      <c r="L14" s="72"/>
-      <c r="M14" s="72" t="str">
-        <f>A13</f>
-        <v>102_Dev1022</v>
-      </c>
-      <c r="N14" s="72"/>
-      <c r="O14" s="76"/>
-    </row>
-    <row r="15" spans="1:15" ht="101.25" customHeight="1">
-      <c r="A15" s="71" t="s">
-        <v>119</v>
-      </c>
-      <c r="B15" s="72" t="s">
-        <v>120</v>
-      </c>
-      <c r="C15" s="73" t="s">
-        <v>49</v>
-      </c>
-      <c r="D15" s="73" t="s">
-        <v>121</v>
-      </c>
-      <c r="E15" s="73" t="s">
-        <v>122</v>
-      </c>
-      <c r="F15" s="73" t="s">
-        <v>123</v>
-      </c>
-      <c r="G15" s="75" t="s">
-        <v>44</v>
-      </c>
-      <c r="H15" s="80" t="s">
-        <v>124</v>
-      </c>
-      <c r="I15" s="73" t="s">
-        <v>84</v>
-      </c>
-      <c r="J15" s="72" t="s">
-        <v>21</v>
-      </c>
-      <c r="K15" s="72"/>
-      <c r="L15" s="72"/>
-      <c r="M15" s="72"/>
-      <c r="N15" s="72" t="s">
-        <v>54</v>
-      </c>
-      <c r="O15" s="76"/>
-    </row>
-    <row r="16" spans="1:15" ht="24.75">
-      <c r="A16" s="71" t="s">
-        <v>125</v>
-      </c>
-      <c r="B16" s="72" t="s">
-        <v>126</v>
-      </c>
-      <c r="C16" s="73" t="s">
-        <v>40</v>
-      </c>
-      <c r="D16" s="73" t="s">
-        <v>127</v>
-      </c>
-      <c r="E16" s="73" t="s">
-        <v>128</v>
-      </c>
-      <c r="F16" s="73" t="s">
-        <v>129</v>
-      </c>
-      <c r="G16" s="75" t="s">
-        <v>44</v>
-      </c>
-      <c r="H16" s="73" t="s">
-        <v>130</v>
-      </c>
-      <c r="I16" s="73" t="s">
-        <v>131</v>
-      </c>
-      <c r="J16" s="72" t="s">
-        <v>21</v>
-      </c>
-      <c r="K16" s="72"/>
-      <c r="L16" s="72"/>
-      <c r="M16" s="72"/>
-      <c r="N16" s="72"/>
-      <c r="O16" s="76"/>
-    </row>
-    <row r="17" spans="1:15" ht="27">
-      <c r="A17" s="71" t="s">
-        <v>132</v>
-      </c>
-      <c r="B17" s="72" t="s">
-        <v>133</v>
-      </c>
-      <c r="C17" s="84" t="s">
-        <v>49</v>
-      </c>
-      <c r="D17" s="73" t="s">
-        <v>134</v>
-      </c>
-      <c r="E17" s="73" t="s">
-        <v>135</v>
-      </c>
-      <c r="F17" s="73" t="s">
-        <v>136</v>
-      </c>
-      <c r="G17" s="75" t="s">
-        <v>137</v>
-      </c>
-      <c r="H17" s="73" t="s">
-        <v>137</v>
-      </c>
-      <c r="I17" s="73"/>
-      <c r="J17" s="72"/>
-      <c r="K17" s="72"/>
-      <c r="L17" s="72"/>
-      <c r="M17" s="72"/>
-      <c r="N17" s="72"/>
-      <c r="O17" s="76" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" ht="81">
-      <c r="A18" s="71" t="s">
-        <v>139</v>
-      </c>
-      <c r="B18" s="103" t="s">
-        <v>140</v>
-      </c>
-      <c r="C18" s="78" t="s">
-        <v>49</v>
-      </c>
-      <c r="D18" s="75" t="s">
-        <v>141</v>
-      </c>
-      <c r="E18" s="75" t="s">
-        <v>142</v>
-      </c>
-      <c r="F18" s="75" t="s">
-        <v>143</v>
-      </c>
-      <c r="G18" s="75" t="s">
-        <v>44</v>
-      </c>
-      <c r="H18" s="85" t="s">
-        <v>144</v>
-      </c>
-      <c r="I18" s="73" t="s">
-        <v>145</v>
-      </c>
-      <c r="J18" s="72" t="s">
-        <v>21</v>
-      </c>
-      <c r="K18" s="72"/>
-      <c r="L18" s="72"/>
-      <c r="M18" s="72"/>
-      <c r="N18" s="72" t="s">
-        <v>54</v>
-      </c>
-      <c r="O18" s="86"/>
-    </row>
-    <row r="19" spans="1:15" ht="100.5" customHeight="1">
-      <c r="A19" s="71" t="s">
-        <v>146</v>
-      </c>
-      <c r="B19" s="103" t="s">
-        <v>147</v>
-      </c>
-      <c r="C19" s="78" t="s">
-        <v>74</v>
-      </c>
-      <c r="D19" s="75" t="s">
-        <v>148</v>
-      </c>
-      <c r="E19" s="75" t="s">
-        <v>149</v>
-      </c>
-      <c r="F19" s="75" t="s">
-        <v>150</v>
-      </c>
-      <c r="G19" s="75" t="s">
-        <v>44</v>
-      </c>
-      <c r="H19" s="85" t="s">
-        <v>144</v>
-      </c>
-      <c r="I19" s="73" t="s">
-        <v>84</v>
-      </c>
-      <c r="J19" s="72" t="s">
-        <v>21</v>
-      </c>
-      <c r="K19" s="72"/>
-      <c r="L19" s="72"/>
-      <c r="M19" s="72"/>
-      <c r="N19" s="72" t="s">
-        <v>54</v>
-      </c>
-      <c r="O19" s="76"/>
-    </row>
-    <row r="20" spans="1:15" s="44" customFormat="1" ht="81">
-      <c r="A20" s="71" t="s">
-        <v>151</v>
-      </c>
-      <c r="B20" s="103" t="s">
-        <v>152</v>
-      </c>
-      <c r="C20" s="78" t="s">
-        <v>74</v>
-      </c>
-      <c r="D20" s="75" t="s">
-        <v>153</v>
-      </c>
-      <c r="E20" s="75" t="s">
-        <v>154</v>
-      </c>
-      <c r="F20" s="75" t="s">
-        <v>155</v>
-      </c>
-      <c r="G20" s="75" t="s">
-        <v>44</v>
-      </c>
-      <c r="H20" s="85" t="s">
-        <v>156</v>
-      </c>
-      <c r="I20" s="73" t="s">
-        <v>53</v>
-      </c>
-      <c r="J20" s="72" t="s">
-        <v>21</v>
-      </c>
-      <c r="K20" s="87"/>
-      <c r="L20" s="87"/>
-      <c r="M20" s="72"/>
-      <c r="N20" s="87"/>
-      <c r="O20" s="76"/>
-    </row>
-    <row r="21" spans="1:15" ht="27">
-      <c r="A21" s="71" t="s">
-        <v>157</v>
-      </c>
-      <c r="B21" s="103" t="s">
-        <v>158</v>
-      </c>
-      <c r="C21" s="78" t="s">
-        <v>74</v>
-      </c>
-      <c r="D21" s="75" t="s">
-        <v>159</v>
-      </c>
-      <c r="E21" s="75" t="s">
-        <v>160</v>
-      </c>
-      <c r="F21" s="75" t="s">
-        <v>161</v>
-      </c>
-      <c r="G21" s="75" t="s">
-        <v>44</v>
-      </c>
-      <c r="H21" s="85" t="s">
-        <v>162</v>
-      </c>
-      <c r="I21" s="73" t="s">
-        <v>84</v>
-      </c>
-      <c r="J21" s="72" t="s">
-        <v>21</v>
-      </c>
-      <c r="K21" s="87"/>
-      <c r="L21" s="87"/>
-      <c r="M21" s="72"/>
-      <c r="N21" s="87"/>
-      <c r="O21" s="76"/>
-    </row>
-    <row r="22" spans="1:15" ht="94.5">
-      <c r="A22" s="71" t="s">
-        <v>163</v>
-      </c>
-      <c r="B22" s="103" t="s">
-        <v>164</v>
-      </c>
-      <c r="C22" s="78" t="s">
-        <v>74</v>
-      </c>
-      <c r="D22" s="75" t="s">
-        <v>165</v>
-      </c>
-      <c r="E22" s="75" t="s">
-        <v>166</v>
-      </c>
-      <c r="F22" s="75" t="s">
-        <v>167</v>
-      </c>
-      <c r="G22" s="75" t="s">
-        <v>44</v>
-      </c>
-      <c r="H22" s="85" t="s">
-        <v>168</v>
-      </c>
-      <c r="I22" s="73" t="s">
-        <v>53</v>
-      </c>
-      <c r="J22" s="72" t="s">
-        <v>21</v>
-      </c>
-      <c r="K22" s="87"/>
-      <c r="L22" s="87"/>
-      <c r="M22" s="72"/>
-      <c r="N22" s="87"/>
-      <c r="O22" s="76"/>
-    </row>
-    <row r="23" spans="1:15" ht="67.5">
-      <c r="A23" s="71" t="s">
-        <v>169</v>
-      </c>
-      <c r="B23" s="103" t="s">
-        <v>170</v>
-      </c>
-      <c r="C23" s="78" t="s">
-        <v>74</v>
-      </c>
-      <c r="D23" s="75" t="s">
-        <v>171</v>
-      </c>
-      <c r="E23" s="75" t="s">
-        <v>172</v>
-      </c>
-      <c r="F23" s="45" t="s">
-        <v>173</v>
-      </c>
-      <c r="G23" s="75" t="s">
-        <v>44</v>
-      </c>
-      <c r="H23" s="85" t="s">
-        <v>174</v>
-      </c>
-      <c r="I23" s="73" t="s">
-        <v>84</v>
-      </c>
-      <c r="J23" s="72" t="s">
-        <v>21</v>
-      </c>
-      <c r="K23" s="87"/>
-      <c r="L23" s="87"/>
-      <c r="M23" s="72" t="str">
-        <f>A22</f>
-        <v>102_Dev2005</v>
-      </c>
-      <c r="N23" s="87"/>
-      <c r="O23" s="76"/>
-    </row>
-    <row r="24" spans="1:15" ht="81">
-      <c r="A24" s="71" t="s">
-        <v>175</v>
-      </c>
-      <c r="B24" s="103" t="s">
-        <v>176</v>
-      </c>
-      <c r="C24" s="78" t="s">
-        <v>40</v>
-      </c>
-      <c r="D24" s="75" t="s">
-        <v>177</v>
-      </c>
-      <c r="E24" s="75" t="s">
-        <v>178</v>
-      </c>
-      <c r="F24" s="45" t="s">
-        <v>179</v>
-      </c>
-      <c r="G24" s="75" t="s">
-        <v>44</v>
-      </c>
-      <c r="H24" s="85" t="s">
-        <v>156</v>
-      </c>
-      <c r="I24" s="73" t="s">
-        <v>53</v>
-      </c>
-      <c r="J24" s="72" t="s">
-        <v>21</v>
-      </c>
-      <c r="K24" s="87"/>
-      <c r="L24" s="87"/>
-      <c r="M24" s="72"/>
-      <c r="N24" s="87"/>
-      <c r="O24" s="76"/>
-    </row>
-    <row r="25" spans="1:15" s="44" customFormat="1" ht="40.5">
-      <c r="A25" s="71" t="s">
-        <v>180</v>
-      </c>
-      <c r="B25" s="103" t="s">
-        <v>181</v>
-      </c>
-      <c r="C25" s="78" t="s">
-        <v>40</v>
-      </c>
-      <c r="D25" s="75" t="s">
-        <v>182</v>
-      </c>
-      <c r="E25" s="75" t="s">
-        <v>183</v>
-      </c>
-      <c r="F25" s="45" t="s">
-        <v>184</v>
-      </c>
-      <c r="G25" s="75" t="s">
-        <v>44</v>
-      </c>
-      <c r="H25" s="85" t="s">
-        <v>137</v>
-      </c>
-      <c r="I25" s="73" t="s">
-        <v>53</v>
-      </c>
-      <c r="J25" s="72" t="s">
-        <v>21</v>
-      </c>
-      <c r="K25" s="87"/>
-      <c r="L25" s="87"/>
-      <c r="M25" s="72" t="str">
-        <f>A24</f>
-        <v>102_Dev2009</v>
-      </c>
-      <c r="N25" s="87"/>
-      <c r="O25" s="76"/>
-    </row>
-    <row r="26" spans="1:15" ht="72.75" customHeight="1">
-      <c r="A26" s="71" t="s">
-        <v>185</v>
-      </c>
-      <c r="B26" s="103" t="s">
-        <v>186</v>
-      </c>
-      <c r="C26" s="78" t="s">
-        <v>40</v>
-      </c>
-      <c r="D26" s="75" t="s">
-        <v>187</v>
-      </c>
-      <c r="E26" s="75" t="s">
-        <v>188</v>
-      </c>
-      <c r="F26" s="45" t="s">
-        <v>189</v>
-      </c>
-      <c r="G26" s="75" t="s">
-        <v>44</v>
-      </c>
-      <c r="H26" s="85" t="s">
-        <v>190</v>
-      </c>
-      <c r="I26" s="73" t="s">
-        <v>84</v>
-      </c>
-      <c r="J26" s="72" t="s">
-        <v>21</v>
-      </c>
-      <c r="K26" s="87"/>
-      <c r="L26" s="87"/>
-      <c r="M26" s="72" t="str">
-        <f>A18</f>
-        <v>102_Dev2001</v>
-      </c>
-      <c r="N26" s="87"/>
-      <c r="O26" s="76"/>
-    </row>
-    <row r="27" spans="1:15" ht="62.25">
-      <c r="A27" s="71" t="s">
-        <v>191</v>
-      </c>
-      <c r="B27" s="103" t="s">
-        <v>192</v>
-      </c>
-      <c r="C27" s="78" t="s">
-        <v>40</v>
-      </c>
-      <c r="D27" s="75" t="s">
-        <v>193</v>
-      </c>
-      <c r="E27" s="75" t="s">
-        <v>128</v>
-      </c>
-      <c r="F27" s="45" t="s">
-        <v>129</v>
-      </c>
-      <c r="G27" s="75" t="s">
-        <v>44</v>
-      </c>
-      <c r="H27" s="85" t="s">
-        <v>194</v>
-      </c>
-      <c r="I27" s="73" t="s">
-        <v>195</v>
-      </c>
-      <c r="J27" s="72" t="s">
-        <v>21</v>
-      </c>
-      <c r="K27" s="87"/>
-      <c r="L27" s="87"/>
-      <c r="M27" s="72"/>
-      <c r="N27" s="87"/>
-      <c r="O27" s="76"/>
-    </row>
-    <row r="28" spans="1:15" ht="27">
-      <c r="A28" s="71" t="s">
-        <v>196</v>
-      </c>
-      <c r="B28" s="103" t="s">
-        <v>197</v>
-      </c>
-      <c r="C28" s="78" t="s">
-        <v>49</v>
-      </c>
-      <c r="D28" s="75" t="s">
-        <v>198</v>
-      </c>
-      <c r="E28" s="75" t="s">
-        <v>199</v>
-      </c>
-      <c r="F28" s="75" t="s">
-        <v>200</v>
-      </c>
-      <c r="G28" s="75" t="s">
-        <v>44</v>
-      </c>
-      <c r="H28" s="85" t="s">
-        <v>201</v>
-      </c>
-      <c r="I28" s="73" t="s">
-        <v>53</v>
-      </c>
-      <c r="J28" s="72" t="s">
-        <v>21</v>
-      </c>
-      <c r="K28" s="72"/>
-      <c r="L28" s="72"/>
-      <c r="M28" s="88" t="s">
-        <v>202</v>
-      </c>
-      <c r="N28" s="72"/>
-      <c r="O28" s="76"/>
-    </row>
-    <row r="29" spans="1:15" ht="24.75">
-      <c r="A29" s="71" t="s">
-        <v>203</v>
-      </c>
-      <c r="B29" s="103" t="s">
-        <v>204</v>
-      </c>
-      <c r="C29" s="78" t="s">
-        <v>49</v>
-      </c>
-      <c r="D29" s="89" t="s">
-        <v>205</v>
-      </c>
-      <c r="E29" s="90" t="s">
-        <v>206</v>
-      </c>
-      <c r="F29" s="75" t="s">
-        <v>207</v>
-      </c>
-      <c r="G29" s="75" t="s">
-        <v>44</v>
-      </c>
-      <c r="H29" s="85" t="s">
-        <v>208</v>
-      </c>
-      <c r="I29" s="73" t="s">
-        <v>53</v>
-      </c>
-      <c r="J29" s="72" t="s">
-        <v>21</v>
-      </c>
-      <c r="K29" s="72"/>
-      <c r="L29" s="72"/>
-      <c r="M29" s="89" t="s">
-        <v>202</v>
-      </c>
-      <c r="N29" s="72" t="s">
-        <v>54</v>
-      </c>
-      <c r="O29" s="76"/>
-    </row>
-    <row r="30" spans="1:15" ht="40.5">
-      <c r="A30" s="71" t="s">
-        <v>209</v>
-      </c>
-      <c r="B30" s="103" t="s">
-        <v>210</v>
-      </c>
-      <c r="C30" s="78" t="s">
-        <v>49</v>
-      </c>
-      <c r="D30" s="75" t="s">
-        <v>211</v>
-      </c>
-      <c r="E30" s="75" t="s">
-        <v>212</v>
-      </c>
-      <c r="F30" s="45" t="s">
-        <v>213</v>
-      </c>
-      <c r="G30" s="75" t="s">
-        <v>137</v>
-      </c>
-      <c r="H30" s="85" t="s">
-        <v>137</v>
-      </c>
-      <c r="I30" s="73"/>
-      <c r="J30" s="72"/>
-      <c r="K30" s="87"/>
-      <c r="L30" s="87"/>
-      <c r="M30" s="72"/>
-      <c r="N30" s="87"/>
-      <c r="O30" s="76" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15" ht="67.5">
-      <c r="A31" s="91" t="s">
-        <v>214</v>
-      </c>
-      <c r="B31" s="103" t="s">
-        <v>215</v>
-      </c>
-      <c r="C31" s="78" t="s">
-        <v>49</v>
-      </c>
-      <c r="D31" s="75" t="s">
-        <v>216</v>
-      </c>
-      <c r="E31" s="75" t="s">
-        <v>217</v>
-      </c>
-      <c r="F31" s="75" t="s">
-        <v>218</v>
-      </c>
-      <c r="G31" s="75" t="s">
-        <v>44</v>
-      </c>
-      <c r="H31" s="85" t="s">
-        <v>219</v>
-      </c>
-      <c r="I31" s="73" t="s">
-        <v>53</v>
-      </c>
-      <c r="J31" s="72" t="s">
-        <v>21</v>
-      </c>
-      <c r="K31" s="87"/>
-      <c r="L31" s="87"/>
-      <c r="M31" s="72"/>
-      <c r="N31" s="87"/>
-      <c r="O31" s="86"/>
-    </row>
-    <row r="32" spans="1:15" ht="67.5">
-      <c r="A32" s="91" t="s">
-        <v>220</v>
-      </c>
-      <c r="B32" s="103" t="s">
-        <v>221</v>
-      </c>
-      <c r="C32" s="78" t="s">
-        <v>74</v>
-      </c>
-      <c r="D32" s="75" t="s">
-        <v>222</v>
-      </c>
-      <c r="E32" s="72" t="s">
-        <v>223</v>
-      </c>
-      <c r="F32" s="75" t="s">
-        <v>224</v>
-      </c>
-      <c r="G32" s="75" t="s">
-        <v>44</v>
-      </c>
-      <c r="H32" s="81" t="s">
-        <v>60</v>
-      </c>
-      <c r="I32" s="73" t="s">
-        <v>84</v>
-      </c>
-      <c r="J32" s="72" t="s">
-        <v>21</v>
-      </c>
-      <c r="K32" s="87"/>
-      <c r="L32" s="87"/>
-      <c r="M32" s="72"/>
-      <c r="N32" s="87"/>
-      <c r="O32" s="76"/>
-    </row>
-    <row r="33" spans="1:15" ht="40.5">
-      <c r="A33" s="91" t="s">
-        <v>225</v>
-      </c>
-      <c r="B33" s="103" t="s">
-        <v>226</v>
-      </c>
-      <c r="C33" s="78" t="s">
-        <v>74</v>
-      </c>
-      <c r="D33" s="75" t="s">
-        <v>227</v>
-      </c>
-      <c r="E33" s="75" t="s">
-        <v>228</v>
-      </c>
-      <c r="F33" s="75" t="s">
-        <v>224</v>
-      </c>
-      <c r="G33" s="75" t="s">
-        <v>44</v>
-      </c>
-      <c r="H33" s="85" t="s">
-        <v>229</v>
-      </c>
-      <c r="I33" s="73" t="s">
-        <v>84</v>
-      </c>
-      <c r="J33" s="72" t="s">
-        <v>21</v>
-      </c>
-      <c r="K33" s="87"/>
-      <c r="L33" s="87"/>
-      <c r="M33" s="72"/>
-      <c r="N33" s="87"/>
-      <c r="O33" s="76"/>
-    </row>
-    <row r="34" spans="1:15" ht="40.5">
-      <c r="A34" s="91" t="s">
-        <v>230</v>
-      </c>
-      <c r="B34" s="103" t="s">
-        <v>231</v>
-      </c>
-      <c r="C34" s="78" t="s">
-        <v>74</v>
-      </c>
-      <c r="D34" s="75" t="s">
-        <v>232</v>
-      </c>
-      <c r="E34" s="75" t="s">
-        <v>233</v>
-      </c>
-      <c r="F34" s="75" t="s">
-        <v>224</v>
-      </c>
-      <c r="G34" s="75" t="s">
-        <v>44</v>
-      </c>
-      <c r="H34" s="85" t="s">
-        <v>71</v>
-      </c>
-      <c r="I34" s="73" t="s">
-        <v>84</v>
-      </c>
-      <c r="J34" s="72" t="s">
-        <v>21</v>
-      </c>
-      <c r="K34" s="87"/>
-      <c r="L34" s="87"/>
-      <c r="M34" s="72"/>
-      <c r="N34" s="87"/>
-      <c r="O34" s="76"/>
-    </row>
-    <row r="35" spans="1:15" ht="93" customHeight="1">
-      <c r="A35" s="91" t="s">
-        <v>234</v>
-      </c>
-      <c r="B35" s="103" t="s">
-        <v>235</v>
-      </c>
-      <c r="C35" s="78" t="s">
-        <v>74</v>
-      </c>
-      <c r="D35" s="45" t="s">
-        <v>236</v>
-      </c>
-      <c r="E35" s="45" t="s">
-        <v>237</v>
-      </c>
-      <c r="F35" s="45" t="s">
-        <v>238</v>
-      </c>
-      <c r="G35" s="75" t="s">
-        <v>44</v>
-      </c>
-      <c r="H35" s="85" t="s">
-        <v>239</v>
-      </c>
-      <c r="I35" s="73" t="s">
-        <v>84</v>
-      </c>
-      <c r="J35" s="72" t="s">
-        <v>21</v>
-      </c>
-      <c r="K35" s="87"/>
-      <c r="L35" s="87"/>
-      <c r="M35" s="72"/>
-      <c r="N35" s="87"/>
-      <c r="O35" s="76"/>
-    </row>
-    <row r="36" spans="1:15" ht="72" customHeight="1">
-      <c r="A36" s="92" t="s">
-        <v>240</v>
-      </c>
-      <c r="B36" s="103" t="s">
-        <v>241</v>
-      </c>
-      <c r="C36" s="78" t="s">
-        <v>49</v>
-      </c>
-      <c r="D36" s="45" t="s">
-        <v>242</v>
-      </c>
-      <c r="E36" s="45" t="s">
-        <v>243</v>
-      </c>
-      <c r="F36" s="75" t="s">
-        <v>244</v>
-      </c>
-      <c r="G36" s="75" t="s">
-        <v>44</v>
-      </c>
-      <c r="H36" s="85" t="s">
-        <v>245</v>
-      </c>
-      <c r="I36" s="73" t="s">
-        <v>53</v>
-      </c>
-      <c r="J36" s="72" t="s">
-        <v>21</v>
-      </c>
-      <c r="K36" s="87"/>
-      <c r="L36" s="87"/>
-      <c r="M36" s="72"/>
-      <c r="N36" s="87"/>
-      <c r="O36" s="76"/>
-    </row>
-    <row r="37" spans="1:15" ht="81">
-      <c r="A37" s="92" t="s">
-        <v>246</v>
-      </c>
-      <c r="B37" s="103" t="s">
-        <v>247</v>
-      </c>
-      <c r="C37" s="78" t="s">
-        <v>40</v>
-      </c>
-      <c r="D37" s="45" t="s">
-        <v>248</v>
-      </c>
-      <c r="E37" s="45" t="s">
-        <v>249</v>
-      </c>
-      <c r="F37" s="75" t="s">
-        <v>250</v>
-      </c>
-      <c r="G37" s="75" t="s">
-        <v>44</v>
-      </c>
-      <c r="H37" s="85" t="s">
-        <v>229</v>
-      </c>
-      <c r="I37" s="73" t="s">
-        <v>84</v>
-      </c>
-      <c r="J37" s="72" t="s">
-        <v>21</v>
-      </c>
-      <c r="K37" s="87"/>
-      <c r="L37" s="87"/>
-      <c r="M37" s="72" t="str">
-        <f>A36</f>
-        <v>102_Dev3006</v>
-      </c>
-      <c r="N37" s="87"/>
-      <c r="O37" s="76"/>
-    </row>
-    <row r="38" spans="1:15" ht="50.25">
-      <c r="A38" s="92" t="s">
-        <v>251</v>
-      </c>
-      <c r="B38" s="103" t="s">
-        <v>252</v>
-      </c>
-      <c r="C38" s="78" t="s">
-        <v>40</v>
-      </c>
-      <c r="D38" s="75" t="s">
-        <v>253</v>
-      </c>
-      <c r="E38" s="75" t="s">
-        <v>128</v>
-      </c>
-      <c r="F38" s="75" t="s">
-        <v>254</v>
-      </c>
-      <c r="G38" s="75" t="s">
-        <v>44</v>
-      </c>
-      <c r="H38" s="85" t="s">
-        <v>255</v>
-      </c>
-      <c r="I38" s="73" t="s">
-        <v>256</v>
-      </c>
-      <c r="J38" s="72" t="s">
-        <v>21</v>
-      </c>
-      <c r="K38" s="87"/>
-      <c r="L38" s="87"/>
-      <c r="M38" s="72"/>
-      <c r="N38" s="87"/>
-      <c r="O38" s="76"/>
-    </row>
-    <row r="39" spans="1:15" ht="53.25">
-      <c r="A39" s="91" t="s">
-        <v>257</v>
-      </c>
-      <c r="B39" s="103" t="s">
-        <v>258</v>
-      </c>
-      <c r="C39" s="78" t="s">
-        <v>74</v>
-      </c>
-      <c r="D39" s="75" t="s">
-        <v>259</v>
-      </c>
-      <c r="E39" s="75" t="s">
-        <v>260</v>
-      </c>
-      <c r="F39" s="75" t="s">
-        <v>261</v>
-      </c>
-      <c r="G39" s="75" t="s">
-        <v>44</v>
-      </c>
-      <c r="H39" s="85" t="s">
-        <v>255</v>
-      </c>
-      <c r="I39" s="73" t="s">
-        <v>53</v>
-      </c>
-      <c r="J39" s="72" t="s">
-        <v>21</v>
-      </c>
-      <c r="K39" s="87"/>
-      <c r="L39" s="87"/>
-      <c r="M39" s="72"/>
-      <c r="N39" s="87"/>
-      <c r="O39" s="76"/>
-    </row>
-    <row r="40" spans="1:15" ht="126.75" customHeight="1">
-      <c r="A40" s="91" t="s">
-        <v>262</v>
-      </c>
-      <c r="B40" s="103" t="s">
-        <v>263</v>
-      </c>
-      <c r="C40" s="78" t="s">
-        <v>49</v>
-      </c>
-      <c r="D40" s="75" t="s">
-        <v>264</v>
-      </c>
-      <c r="E40" s="93" t="s">
-        <v>265</v>
-      </c>
-      <c r="F40" s="75" t="s">
-        <v>266</v>
-      </c>
-      <c r="G40" s="75" t="s">
-        <v>44</v>
-      </c>
-      <c r="H40" s="85" t="s">
-        <v>229</v>
-      </c>
-      <c r="I40" s="73" t="s">
-        <v>84</v>
-      </c>
-      <c r="J40" s="72" t="s">
-        <v>21</v>
-      </c>
-      <c r="K40" s="87"/>
-      <c r="L40" s="87"/>
-      <c r="M40" s="72"/>
-      <c r="N40" s="87"/>
-      <c r="O40" s="94" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="41" spans="1:15" ht="40.5">
-      <c r="A41" s="91" t="s">
-        <v>268</v>
-      </c>
-      <c r="B41" s="103" t="s">
-        <v>269</v>
-      </c>
-      <c r="C41" s="78" t="s">
-        <v>49</v>
-      </c>
-      <c r="D41" s="75" t="s">
-        <v>270</v>
-      </c>
-      <c r="E41" s="75" t="s">
-        <v>271</v>
-      </c>
-      <c r="F41" s="75" t="s">
-        <v>272</v>
-      </c>
-      <c r="G41" s="75" t="s">
-        <v>137</v>
-      </c>
-      <c r="H41" s="85" t="s">
-        <v>137</v>
-      </c>
-      <c r="I41" s="45"/>
-      <c r="J41" s="85"/>
-      <c r="K41" s="87"/>
-      <c r="L41" s="87"/>
-      <c r="M41" s="72"/>
-      <c r="N41" s="87"/>
-      <c r="O41" s="76" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="42" spans="1:15" ht="40.5">
-      <c r="A42" s="91" t="s">
-        <v>273</v>
-      </c>
-      <c r="B42" s="103" t="s">
-        <v>274</v>
-      </c>
-      <c r="C42" s="78" t="s">
-        <v>49</v>
-      </c>
-      <c r="D42" s="75" t="s">
-        <v>275</v>
-      </c>
-      <c r="E42" s="75" t="s">
-        <v>276</v>
-      </c>
-      <c r="F42" s="75" t="s">
-        <v>277</v>
-      </c>
-      <c r="G42" s="75" t="s">
-        <v>44</v>
-      </c>
-      <c r="H42" s="85" t="s">
-        <v>278</v>
-      </c>
-      <c r="I42" s="75" t="s">
-        <v>53</v>
-      </c>
-      <c r="J42" s="72" t="s">
-        <v>21</v>
-      </c>
-      <c r="K42" s="87"/>
-      <c r="L42" s="87"/>
-      <c r="M42" s="72"/>
-      <c r="N42" s="87"/>
-      <c r="O42" s="76"/>
-    </row>
-    <row r="43" spans="1:15" ht="27">
-      <c r="A43" s="91" t="s">
-        <v>279</v>
-      </c>
-      <c r="B43" s="103" t="s">
-        <v>280</v>
-      </c>
-      <c r="C43" s="78" t="s">
-        <v>40</v>
-      </c>
-      <c r="D43" s="75" t="s">
-        <v>281</v>
-      </c>
-      <c r="E43" s="75" t="s">
-        <v>282</v>
-      </c>
-      <c r="F43" s="75" t="s">
-        <v>283</v>
-      </c>
-      <c r="G43" s="75" t="s">
-        <v>44</v>
-      </c>
-      <c r="H43" s="95" t="s">
-        <v>284</v>
-      </c>
-      <c r="I43" s="95" t="s">
-        <v>285</v>
-      </c>
-      <c r="J43" s="95" t="s">
-        <v>21</v>
-      </c>
-      <c r="K43" s="87"/>
-      <c r="L43" s="87"/>
-      <c r="M43" s="72"/>
-      <c r="N43" s="87"/>
-      <c r="O43" s="76"/>
-    </row>
-    <row r="44" spans="1:15" ht="40.5">
-      <c r="A44" s="91" t="s">
-        <v>286</v>
-      </c>
-      <c r="B44" s="103" t="s">
-        <v>287</v>
-      </c>
-      <c r="C44" s="78" t="s">
-        <v>40</v>
-      </c>
-      <c r="D44" s="75" t="s">
-        <v>288</v>
-      </c>
-      <c r="E44" s="75" t="s">
-        <v>128</v>
-      </c>
-      <c r="F44" s="75" t="s">
-        <v>254</v>
-      </c>
-      <c r="G44" s="75" t="s">
-        <v>44</v>
-      </c>
-      <c r="H44" s="85" t="s">
-        <v>289</v>
-      </c>
-      <c r="I44" s="75" t="s">
-        <v>53</v>
-      </c>
-      <c r="J44" s="72" t="s">
-        <v>21</v>
-      </c>
-      <c r="K44" s="87"/>
-      <c r="L44" s="87"/>
-      <c r="M44" s="72"/>
-      <c r="N44" s="87"/>
-      <c r="O44" s="76"/>
-    </row>
-    <row r="45" spans="1:15" ht="152.25">
-      <c r="A45" s="91" t="s">
-        <v>290</v>
-      </c>
-      <c r="B45" s="103" t="s">
-        <v>291</v>
-      </c>
-      <c r="C45" s="78" t="s">
-        <v>74</v>
-      </c>
-      <c r="D45" s="104" t="s">
-        <v>292</v>
-      </c>
-      <c r="E45" s="104" t="s">
-        <v>293</v>
-      </c>
-      <c r="F45" s="87" t="s">
-        <v>294</v>
-      </c>
-      <c r="G45" s="75" t="s">
-        <v>137</v>
-      </c>
-      <c r="H45" s="85" t="s">
-        <v>137</v>
-      </c>
-      <c r="I45" s="95" t="s">
-        <v>46</v>
-      </c>
-      <c r="J45" s="95" t="s">
-        <v>21</v>
-      </c>
-      <c r="K45" s="87"/>
-      <c r="L45" s="87"/>
-      <c r="M45" s="72"/>
-      <c r="N45" s="87" t="s">
-        <v>54</v>
-      </c>
-      <c r="O45" s="76" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="46" spans="1:15" ht="137.25">
-      <c r="A46" s="91" t="s">
-        <v>296</v>
-      </c>
-      <c r="B46" s="103" t="s">
-        <v>297</v>
-      </c>
-      <c r="C46" s="78" t="s">
-        <v>74</v>
-      </c>
-      <c r="D46" s="45" t="s">
-        <v>298</v>
-      </c>
-      <c r="E46" s="104" t="s">
-        <v>299</v>
-      </c>
-      <c r="F46" s="87" t="s">
-        <v>294</v>
-      </c>
-      <c r="G46" s="75" t="s">
-        <v>137</v>
-      </c>
-      <c r="H46" s="85" t="s">
-        <v>137</v>
-      </c>
-      <c r="I46" s="95" t="s">
-        <v>46</v>
-      </c>
-      <c r="J46" s="72" t="s">
-        <v>21</v>
-      </c>
-      <c r="K46" s="87"/>
-      <c r="L46" s="87"/>
-      <c r="M46" s="72"/>
-      <c r="N46" s="87" t="s">
-        <v>54</v>
-      </c>
-      <c r="O46" s="104" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="47" spans="1:15" ht="53.25">
-      <c r="A47" s="77" t="s">
-        <v>301</v>
-      </c>
-      <c r="B47" s="103" t="s">
-        <v>302</v>
-      </c>
-      <c r="C47" s="78" t="s">
-        <v>49</v>
-      </c>
-      <c r="D47" s="75" t="s">
-        <v>303</v>
-      </c>
-      <c r="E47" s="75" t="s">
-        <v>304</v>
-      </c>
-      <c r="F47" s="75" t="s">
-        <v>305</v>
-      </c>
-      <c r="G47" s="75" t="s">
-        <v>44</v>
-      </c>
-      <c r="H47" s="75" t="s">
-        <v>306</v>
-      </c>
-      <c r="I47" s="75" t="s">
-        <v>307</v>
-      </c>
-      <c r="J47" s="75" t="s">
-        <v>21</v>
-      </c>
-      <c r="K47" s="87"/>
-      <c r="L47" s="87"/>
-      <c r="M47" s="72"/>
-      <c r="N47" s="87"/>
-      <c r="O47" s="76"/>
-    </row>
-    <row r="48" spans="1:15" ht="40.5">
-      <c r="A48" s="77" t="s">
-        <v>308</v>
-      </c>
-      <c r="B48" s="103" t="s">
-        <v>309</v>
-      </c>
-      <c r="C48" s="78" t="s">
-        <v>74</v>
-      </c>
-      <c r="D48" s="75" t="s">
-        <v>310</v>
-      </c>
-      <c r="E48" s="96" t="s">
-        <v>311</v>
-      </c>
-      <c r="F48" s="96" t="s">
-        <v>312</v>
-      </c>
-      <c r="G48" s="75" t="s">
-        <v>44</v>
-      </c>
-      <c r="H48" s="79" t="s">
-        <v>313</v>
-      </c>
-      <c r="I48" s="75" t="s">
-        <v>307</v>
-      </c>
-      <c r="J48" s="72" t="s">
-        <v>21</v>
-      </c>
-      <c r="K48" s="87"/>
-      <c r="L48" s="87"/>
-      <c r="M48" s="72"/>
-      <c r="N48" s="87"/>
-      <c r="O48" s="76"/>
-    </row>
-    <row r="49" spans="1:15" ht="27">
-      <c r="A49" s="77" t="s">
-        <v>314</v>
-      </c>
-      <c r="B49" s="103" t="s">
-        <v>315</v>
-      </c>
-      <c r="C49" s="78" t="s">
-        <v>74</v>
-      </c>
-      <c r="D49" s="75" t="s">
-        <v>316</v>
-      </c>
-      <c r="E49" s="75" t="s">
-        <v>317</v>
-      </c>
-      <c r="F49" s="75" t="s">
-        <v>318</v>
-      </c>
-      <c r="G49" s="75" t="s">
-        <v>44</v>
-      </c>
-      <c r="H49" s="75" t="s">
-        <v>319</v>
-      </c>
-      <c r="I49" s="75" t="s">
-        <v>307</v>
-      </c>
-      <c r="J49" s="75" t="s">
-        <v>21</v>
-      </c>
-      <c r="K49" s="87"/>
-      <c r="L49" s="87"/>
-      <c r="M49" s="72"/>
-      <c r="N49" s="87"/>
-      <c r="O49" s="76"/>
-    </row>
-    <row r="50" spans="1:15" ht="27">
-      <c r="A50" s="97" t="s">
-        <v>320</v>
-      </c>
-      <c r="B50" s="103" t="s">
-        <v>321</v>
-      </c>
-      <c r="C50" s="98" t="s">
-        <v>40</v>
-      </c>
-      <c r="D50" s="99" t="s">
-        <v>322</v>
-      </c>
-      <c r="E50" s="99" t="s">
-        <v>323</v>
-      </c>
-      <c r="F50" s="99" t="s">
-        <v>294</v>
-      </c>
-      <c r="G50" s="99" t="s">
-        <v>44</v>
-      </c>
-      <c r="H50" s="100" t="s">
-        <v>324</v>
-      </c>
-      <c r="I50" s="99" t="s">
-        <v>53</v>
-      </c>
-      <c r="J50" s="101" t="s">
-        <v>21</v>
-      </c>
-      <c r="K50" s="102"/>
-      <c r="L50" s="102"/>
-      <c r="M50" s="101"/>
-      <c r="N50" s="102"/>
-      <c r="O50" s="76"/>
-    </row>
-    <row r="51" spans="1:15" ht="15">
+      <c r="K30" s="94"/>
+      <c r="L30" s="94"/>
+      <c r="M30" s="93"/>
+      <c r="N30" s="94"/>
+      <c r="O30" s="72"/>
+    </row>
+    <row r="31" spans="1:15" ht="15" x14ac:dyDescent="0.2">
+      <c r="A31" s="51"/>
+      <c r="C31" s="51"/>
+      <c r="D31" s="52"/>
+      <c r="E31" s="53"/>
+      <c r="F31" s="53"/>
+      <c r="G31" s="52"/>
+      <c r="H31" s="54"/>
+      <c r="I31" s="52"/>
+      <c r="J31" s="2"/>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A32" s="51"/>
+      <c r="C32" s="51"/>
+      <c r="D32" s="52"/>
+      <c r="E32" s="55"/>
+      <c r="F32" s="52"/>
+      <c r="G32" s="52"/>
+      <c r="H32" s="54"/>
+      <c r="I32" s="52"/>
+      <c r="J32" s="2"/>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A33" s="51"/>
+      <c r="C33" s="51"/>
+      <c r="D33" s="52"/>
+      <c r="E33" s="55"/>
+      <c r="F33" s="56"/>
+      <c r="G33" s="52"/>
+      <c r="H33" s="54"/>
+      <c r="I33" s="52"/>
+      <c r="J33" s="2"/>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A34" s="51"/>
+      <c r="C34" s="51"/>
+      <c r="D34" s="52"/>
+      <c r="E34" s="55"/>
+      <c r="F34" s="56"/>
+      <c r="G34" s="52"/>
+      <c r="H34" s="54"/>
+      <c r="I34" s="52"/>
+      <c r="J34" s="2"/>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A35" s="51"/>
+      <c r="C35" s="51"/>
+      <c r="D35" s="52"/>
+      <c r="E35" s="55"/>
+      <c r="F35" s="56"/>
+      <c r="G35" s="52"/>
+      <c r="H35" s="54"/>
+      <c r="I35" s="52"/>
+      <c r="J35" s="2"/>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A36" s="51"/>
+      <c r="C36" s="51"/>
+      <c r="D36" s="52"/>
+      <c r="E36" s="55"/>
+      <c r="F36" s="52"/>
+      <c r="G36" s="52"/>
+      <c r="H36" s="54"/>
+      <c r="I36" s="52"/>
+      <c r="J36" s="2"/>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A37" s="51"/>
+      <c r="C37" s="51"/>
+      <c r="D37" s="52"/>
+      <c r="E37" s="55"/>
+      <c r="F37" s="52"/>
+      <c r="G37" s="52"/>
+      <c r="H37" s="54"/>
+      <c r="I37" s="52"/>
+      <c r="J37" s="2"/>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A38" s="51"/>
+      <c r="C38" s="51"/>
+      <c r="D38" s="52"/>
+      <c r="E38" s="55"/>
+      <c r="F38" s="56"/>
+      <c r="G38" s="52"/>
+      <c r="H38" s="54"/>
+      <c r="I38" s="52"/>
+      <c r="J38" s="2"/>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A39" s="51"/>
+      <c r="C39" s="51"/>
+      <c r="D39" s="52"/>
+      <c r="E39" s="55"/>
+      <c r="F39" s="56"/>
+      <c r="G39" s="52"/>
+      <c r="H39" s="54"/>
+      <c r="I39" s="52"/>
+      <c r="J39" s="2"/>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A40" s="51"/>
+      <c r="C40" s="51"/>
+      <c r="D40" s="52"/>
+      <c r="E40" s="55"/>
+      <c r="F40" s="56"/>
+      <c r="G40" s="52"/>
+      <c r="H40" s="54"/>
+      <c r="I40" s="52"/>
+      <c r="J40" s="2"/>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A41" s="51"/>
+      <c r="C41" s="51"/>
+      <c r="D41" s="52"/>
+      <c r="E41" s="55"/>
+      <c r="F41" s="56"/>
+      <c r="G41" s="52"/>
+      <c r="H41" s="54"/>
+      <c r="I41" s="52"/>
+      <c r="J41" s="2"/>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A42" s="51"/>
+      <c r="C42" s="51"/>
+      <c r="D42" s="52"/>
+      <c r="E42" s="55"/>
+      <c r="F42" s="56"/>
+      <c r="G42" s="52"/>
+      <c r="H42" s="54"/>
+      <c r="I42" s="52"/>
+      <c r="J42" s="2"/>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A43" s="51"/>
+      <c r="C43" s="51"/>
+      <c r="D43" s="52"/>
+      <c r="E43" s="55"/>
+      <c r="F43" s="56"/>
+      <c r="G43" s="52"/>
+      <c r="H43" s="54"/>
+      <c r="I43" s="52"/>
+      <c r="J43" s="2"/>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A44" s="51"/>
+      <c r="C44" s="51"/>
+      <c r="D44" s="52"/>
+      <c r="E44" s="55"/>
+      <c r="F44" s="52"/>
+      <c r="G44" s="52"/>
+      <c r="H44" s="54"/>
+      <c r="I44" s="52"/>
+      <c r="J44" s="2"/>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A45" s="51"/>
+      <c r="C45" s="51"/>
+      <c r="D45" s="52"/>
+      <c r="E45" s="55"/>
+      <c r="F45" s="52"/>
+      <c r="G45" s="52"/>
+      <c r="H45" s="54"/>
+      <c r="I45" s="52"/>
+      <c r="J45" s="2"/>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A46" s="51"/>
+      <c r="C46" s="51"/>
+      <c r="D46" s="52"/>
+      <c r="E46" s="55"/>
+      <c r="F46" s="52"/>
+      <c r="G46" s="52"/>
+      <c r="H46" s="54"/>
+      <c r="I46" s="52"/>
+      <c r="J46" s="2"/>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A47" s="51"/>
+      <c r="C47" s="51"/>
+      <c r="D47" s="52"/>
+      <c r="E47" s="55"/>
+      <c r="F47" s="56"/>
+      <c r="G47" s="52"/>
+      <c r="H47" s="54"/>
+      <c r="I47" s="52"/>
+      <c r="J47" s="2"/>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A48" s="51"/>
+      <c r="C48" s="51"/>
+      <c r="D48" s="52"/>
+      <c r="E48" s="55"/>
+      <c r="F48" s="52"/>
+      <c r="G48" s="52"/>
+      <c r="H48" s="54"/>
+      <c r="I48" s="52"/>
+      <c r="J48" s="2"/>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A49" s="51"/>
+      <c r="C49" s="51"/>
+      <c r="D49" s="52"/>
+      <c r="E49" s="55"/>
+      <c r="F49" s="52"/>
+      <c r="G49" s="52"/>
+      <c r="H49" s="54"/>
+      <c r="I49" s="52"/>
+      <c r="J49" s="2"/>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A50" s="51"/>
+      <c r="C50" s="51"/>
+      <c r="D50" s="52"/>
+      <c r="E50" s="55"/>
+      <c r="F50" s="56"/>
+      <c r="G50" s="52"/>
+      <c r="H50" s="54"/>
+      <c r="I50" s="52"/>
+      <c r="J50" s="2"/>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A51" s="51"/>
       <c r="C51" s="51"/>
       <c r="D51" s="52"/>
-      <c r="E51" s="53"/>
-      <c r="F51" s="53"/>
+      <c r="E51" s="55"/>
+      <c r="F51" s="56"/>
       <c r="G51" s="52"/>
       <c r="H51" s="54"/>
       <c r="I51" s="52"/>
       <c r="J51" s="2"/>
     </row>
-    <row r="52" spans="1:15">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A52" s="51"/>
       <c r="C52" s="51"/>
       <c r="D52" s="52"/>
       <c r="E52" s="55"/>
-      <c r="F52" s="52"/>
+      <c r="F52" s="56"/>
       <c r="G52" s="52"/>
       <c r="H52" s="54"/>
       <c r="I52" s="52"/>
       <c r="J52" s="2"/>
     </row>
-    <row r="53" spans="1:15">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A53" s="51"/>
       <c r="C53" s="51"/>
       <c r="D53" s="52"/>
@@ -5223,29 +4213,29 @@
       <c r="I53" s="52"/>
       <c r="J53" s="2"/>
     </row>
-    <row r="54" spans="1:15">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A54" s="51"/>
       <c r="C54" s="51"/>
       <c r="D54" s="52"/>
       <c r="E54" s="55"/>
-      <c r="F54" s="56"/>
+      <c r="F54" s="52"/>
       <c r="G54" s="52"/>
       <c r="H54" s="54"/>
       <c r="I54" s="52"/>
       <c r="J54" s="2"/>
     </row>
-    <row r="55" spans="1:15">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A55" s="51"/>
       <c r="C55" s="51"/>
       <c r="D55" s="52"/>
       <c r="E55" s="55"/>
-      <c r="F55" s="56"/>
+      <c r="F55" s="52"/>
       <c r="G55" s="52"/>
       <c r="H55" s="54"/>
       <c r="I55" s="52"/>
       <c r="J55" s="2"/>
     </row>
-    <row r="56" spans="1:15">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A56" s="51"/>
       <c r="C56" s="51"/>
       <c r="D56" s="52"/>
@@ -5256,7 +4246,7 @@
       <c r="I56" s="52"/>
       <c r="J56" s="2"/>
     </row>
-    <row r="57" spans="1:15">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A57" s="51"/>
       <c r="C57" s="51"/>
       <c r="D57" s="52"/>
@@ -5267,73 +4257,73 @@
       <c r="I57" s="52"/>
       <c r="J57" s="2"/>
     </row>
-    <row r="58" spans="1:15">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A58" s="51"/>
       <c r="C58" s="51"/>
       <c r="D58" s="52"/>
       <c r="E58" s="55"/>
-      <c r="F58" s="56"/>
+      <c r="F58" s="52"/>
       <c r="G58" s="52"/>
       <c r="H58" s="54"/>
       <c r="I58" s="52"/>
       <c r="J58" s="2"/>
     </row>
-    <row r="59" spans="1:15">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A59" s="51"/>
       <c r="C59" s="51"/>
       <c r="D59" s="52"/>
       <c r="E59" s="55"/>
-      <c r="F59" s="56"/>
+      <c r="F59" s="52"/>
       <c r="G59" s="52"/>
       <c r="H59" s="54"/>
       <c r="I59" s="52"/>
       <c r="J59" s="2"/>
     </row>
-    <row r="60" spans="1:15">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A60" s="51"/>
       <c r="C60" s="51"/>
       <c r="D60" s="52"/>
       <c r="E60" s="55"/>
-      <c r="F60" s="56"/>
+      <c r="F60" s="52"/>
       <c r="G60" s="52"/>
       <c r="H60" s="54"/>
       <c r="I60" s="52"/>
       <c r="J60" s="2"/>
     </row>
-    <row r="61" spans="1:15">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A61" s="51"/>
       <c r="C61" s="51"/>
       <c r="D61" s="52"/>
       <c r="E61" s="55"/>
-      <c r="F61" s="56"/>
+      <c r="F61" s="57"/>
       <c r="G61" s="52"/>
       <c r="H61" s="54"/>
       <c r="I61" s="52"/>
       <c r="J61" s="2"/>
     </row>
-    <row r="62" spans="1:15">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A62" s="51"/>
       <c r="C62" s="51"/>
       <c r="D62" s="52"/>
       <c r="E62" s="55"/>
-      <c r="F62" s="56"/>
+      <c r="F62" s="52"/>
       <c r="G62" s="52"/>
       <c r="H62" s="54"/>
       <c r="I62" s="52"/>
       <c r="J62" s="2"/>
     </row>
-    <row r="63" spans="1:15">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A63" s="51"/>
       <c r="C63" s="51"/>
       <c r="D63" s="52"/>
       <c r="E63" s="55"/>
-      <c r="F63" s="56"/>
+      <c r="F63" s="52"/>
       <c r="G63" s="52"/>
       <c r="H63" s="54"/>
       <c r="I63" s="52"/>
       <c r="J63" s="2"/>
     </row>
-    <row r="64" spans="1:15">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A64" s="51"/>
       <c r="C64" s="51"/>
       <c r="D64" s="52"/>
@@ -5344,7 +4334,7 @@
       <c r="I64" s="52"/>
       <c r="J64" s="2"/>
     </row>
-    <row r="65" spans="1:10">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A65" s="51"/>
       <c r="C65" s="51"/>
       <c r="D65" s="52"/>
@@ -5355,7 +4345,7 @@
       <c r="I65" s="52"/>
       <c r="J65" s="2"/>
     </row>
-    <row r="66" spans="1:10">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A66" s="51"/>
       <c r="C66" s="51"/>
       <c r="D66" s="52"/>
@@ -5366,18 +4356,18 @@
       <c r="I66" s="52"/>
       <c r="J66" s="2"/>
     </row>
-    <row r="67" spans="1:10">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A67" s="51"/>
       <c r="C67" s="51"/>
       <c r="D67" s="52"/>
       <c r="E67" s="55"/>
-      <c r="F67" s="56"/>
+      <c r="F67" s="52"/>
       <c r="G67" s="52"/>
       <c r="H67" s="54"/>
       <c r="I67" s="52"/>
       <c r="J67" s="2"/>
     </row>
-    <row r="68" spans="1:10">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A68" s="51"/>
       <c r="C68" s="51"/>
       <c r="D68" s="52"/>
@@ -5388,7 +4378,7 @@
       <c r="I68" s="52"/>
       <c r="J68" s="2"/>
     </row>
-    <row r="69" spans="1:10">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A69" s="51"/>
       <c r="C69" s="51"/>
       <c r="D69" s="52"/>
@@ -5399,29 +4389,29 @@
       <c r="I69" s="52"/>
       <c r="J69" s="2"/>
     </row>
-    <row r="70" spans="1:10">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A70" s="51"/>
       <c r="C70" s="51"/>
-      <c r="D70" s="52"/>
-      <c r="E70" s="55"/>
+      <c r="D70" s="56"/>
+      <c r="E70" s="58"/>
       <c r="F70" s="56"/>
       <c r="G70" s="52"/>
       <c r="H70" s="54"/>
       <c r="I70" s="52"/>
       <c r="J70" s="2"/>
     </row>
-    <row r="71" spans="1:10">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A71" s="51"/>
       <c r="C71" s="51"/>
-      <c r="D71" s="52"/>
-      <c r="E71" s="55"/>
+      <c r="D71" s="56"/>
+      <c r="E71" s="58"/>
       <c r="F71" s="56"/>
       <c r="G71" s="52"/>
       <c r="H71" s="54"/>
       <c r="I71" s="52"/>
       <c r="J71" s="2"/>
     </row>
-    <row r="72" spans="1:10">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A72" s="51"/>
       <c r="C72" s="51"/>
       <c r="D72" s="52"/>
@@ -5432,18 +4422,18 @@
       <c r="I72" s="52"/>
       <c r="J72" s="2"/>
     </row>
-    <row r="73" spans="1:10">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A73" s="51"/>
       <c r="C73" s="51"/>
       <c r="D73" s="52"/>
       <c r="E73" s="55"/>
-      <c r="F73" s="56"/>
+      <c r="F73" s="52"/>
       <c r="G73" s="52"/>
       <c r="H73" s="54"/>
       <c r="I73" s="52"/>
       <c r="J73" s="2"/>
     </row>
-    <row r="74" spans="1:10">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A74" s="51"/>
       <c r="C74" s="51"/>
       <c r="D74" s="52"/>
@@ -5454,7 +4444,7 @@
       <c r="I74" s="52"/>
       <c r="J74" s="2"/>
     </row>
-    <row r="75" spans="1:10">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A75" s="51"/>
       <c r="C75" s="51"/>
       <c r="D75" s="52"/>
@@ -5465,7 +4455,7 @@
       <c r="I75" s="52"/>
       <c r="J75" s="2"/>
     </row>
-    <row r="76" spans="1:10">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A76" s="51"/>
       <c r="C76" s="51"/>
       <c r="D76" s="52"/>
@@ -5476,40 +4466,40 @@
       <c r="I76" s="52"/>
       <c r="J76" s="2"/>
     </row>
-    <row r="77" spans="1:10">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A77" s="51"/>
       <c r="C77" s="51"/>
-      <c r="D77" s="52"/>
-      <c r="E77" s="55"/>
+      <c r="D77" s="56"/>
+      <c r="E77" s="58"/>
       <c r="F77" s="52"/>
       <c r="G77" s="52"/>
       <c r="H77" s="54"/>
-      <c r="I77" s="52"/>
+      <c r="I77" s="56"/>
       <c r="J77" s="2"/>
     </row>
-    <row r="78" spans="1:10">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A78" s="51"/>
       <c r="C78" s="51"/>
-      <c r="D78" s="52"/>
-      <c r="E78" s="55"/>
+      <c r="D78" s="56"/>
+      <c r="E78" s="58"/>
       <c r="F78" s="52"/>
       <c r="G78" s="52"/>
       <c r="H78" s="54"/>
-      <c r="I78" s="52"/>
+      <c r="I78" s="56"/>
       <c r="J78" s="2"/>
     </row>
-    <row r="79" spans="1:10">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A79" s="51"/>
       <c r="C79" s="51"/>
-      <c r="D79" s="52"/>
-      <c r="E79" s="55"/>
+      <c r="D79" s="56"/>
+      <c r="E79" s="58"/>
       <c r="F79" s="52"/>
       <c r="G79" s="52"/>
       <c r="H79" s="54"/>
-      <c r="I79" s="52"/>
+      <c r="I79" s="56"/>
       <c r="J79" s="2"/>
     </row>
-    <row r="80" spans="1:10">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A80" s="51"/>
       <c r="C80" s="51"/>
       <c r="D80" s="52"/>
@@ -5520,18 +4510,18 @@
       <c r="I80" s="52"/>
       <c r="J80" s="2"/>
     </row>
-    <row r="81" spans="1:10">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A81" s="51"/>
       <c r="C81" s="51"/>
       <c r="D81" s="52"/>
       <c r="E81" s="55"/>
-      <c r="F81" s="57"/>
+      <c r="F81" s="52"/>
       <c r="G81" s="52"/>
       <c r="H81" s="54"/>
       <c r="I81" s="52"/>
       <c r="J81" s="2"/>
     </row>
-    <row r="82" spans="1:10">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A82" s="51"/>
       <c r="C82" s="51"/>
       <c r="D82" s="52"/>
@@ -5539,10 +4529,10 @@
       <c r="F82" s="52"/>
       <c r="G82" s="52"/>
       <c r="H82" s="54"/>
-      <c r="I82" s="52"/>
+      <c r="I82" s="56"/>
       <c r="J82" s="2"/>
     </row>
-    <row r="83" spans="1:10">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A83" s="51"/>
       <c r="C83" s="51"/>
       <c r="D83" s="52"/>
@@ -5553,7 +4543,7 @@
       <c r="I83" s="52"/>
       <c r="J83" s="2"/>
     </row>
-    <row r="84" spans="1:10">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A84" s="51"/>
       <c r="C84" s="51"/>
       <c r="D84" s="52"/>
@@ -5564,7 +4554,7 @@
       <c r="I84" s="52"/>
       <c r="J84" s="2"/>
     </row>
-    <row r="85" spans="1:10">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A85" s="51"/>
       <c r="C85" s="51"/>
       <c r="D85" s="52"/>
@@ -5575,62 +4565,60 @@
       <c r="I85" s="52"/>
       <c r="J85" s="2"/>
     </row>
-    <row r="86" spans="1:10">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A86" s="51"/>
       <c r="C86" s="51"/>
-      <c r="D86" s="52"/>
-      <c r="E86" s="55"/>
-      <c r="F86" s="52"/>
+      <c r="D86" s="56"/>
+      <c r="E86" s="58"/>
+      <c r="F86" s="56"/>
       <c r="G86" s="52"/>
       <c r="H86" s="54"/>
-      <c r="I86" s="52"/>
+      <c r="I86" s="56"/>
       <c r="J86" s="2"/>
     </row>
-    <row r="87" spans="1:10">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A87" s="51"/>
       <c r="C87" s="51"/>
-      <c r="D87" s="52"/>
-      <c r="E87" s="55"/>
+      <c r="D87" s="56"/>
+      <c r="E87" s="58"/>
       <c r="F87" s="52"/>
       <c r="G87" s="52"/>
       <c r="H87" s="54"/>
-      <c r="I87" s="52"/>
+      <c r="I87" s="56"/>
       <c r="J87" s="2"/>
     </row>
-    <row r="88" spans="1:10">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A88" s="51"/>
       <c r="C88" s="51"/>
-      <c r="D88" s="52"/>
-      <c r="E88" s="55"/>
+      <c r="D88" s="56"/>
+      <c r="E88" s="58"/>
       <c r="F88" s="52"/>
       <c r="G88" s="52"/>
       <c r="H88" s="54"/>
-      <c r="I88" s="52"/>
+      <c r="I88" s="56"/>
       <c r="J88" s="2"/>
     </row>
-    <row r="89" spans="1:10">
-      <c r="A89" s="51"/>
-      <c r="C89" s="51"/>
-      <c r="D89" s="52"/>
-      <c r="E89" s="55"/>
+    <row r="89" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A89" s="52"/>
+      <c r="C89" s="52"/>
+      <c r="D89" s="56"/>
+      <c r="E89" s="58"/>
       <c r="F89" s="52"/>
       <c r="G89" s="52"/>
       <c r="H89" s="54"/>
-      <c r="I89" s="52"/>
-      <c r="J89" s="2"/>
-    </row>
-    <row r="90" spans="1:10">
-      <c r="A90" s="51"/>
-      <c r="C90" s="51"/>
+      <c r="I89" s="56"/>
+    </row>
+    <row r="90" spans="1:10" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="A90" s="52"/>
+      <c r="C90" s="52"/>
       <c r="D90" s="56"/>
       <c r="E90" s="58"/>
-      <c r="F90" s="56"/>
+      <c r="F90" s="52"/>
       <c r="G90" s="52"/>
-      <c r="H90" s="54"/>
-      <c r="I90" s="52"/>
-      <c r="J90" s="2"/>
-    </row>
-    <row r="91" spans="1:10">
+      <c r="H90"/>
+      <c r="I90" s="56"/>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A91" s="51"/>
       <c r="C91" s="51"/>
       <c r="D91" s="56"/>
@@ -5638,98 +4626,98 @@
       <c r="F91" s="56"/>
       <c r="G91" s="52"/>
       <c r="H91" s="54"/>
-      <c r="I91" s="52"/>
+      <c r="I91" s="56"/>
       <c r="J91" s="2"/>
     </row>
-    <row r="92" spans="1:10">
-      <c r="A92" s="51"/>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A92" s="52"/>
       <c r="C92" s="51"/>
-      <c r="D92" s="52"/>
-      <c r="E92" s="55"/>
+      <c r="D92" s="56"/>
+      <c r="E92" s="58"/>
       <c r="F92" s="56"/>
       <c r="G92" s="52"/>
       <c r="H92" s="54"/>
-      <c r="I92" s="52"/>
+      <c r="I92" s="56"/>
       <c r="J92" s="2"/>
     </row>
-    <row r="93" spans="1:10">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A93" s="51"/>
       <c r="C93" s="51"/>
-      <c r="D93" s="52"/>
-      <c r="E93" s="55"/>
-      <c r="F93" s="52"/>
+      <c r="D93" s="56"/>
+      <c r="E93" s="58"/>
+      <c r="F93" s="56"/>
       <c r="G93" s="52"/>
       <c r="H93" s="54"/>
-      <c r="I93" s="52"/>
+      <c r="I93" s="56"/>
       <c r="J93" s="2"/>
     </row>
-    <row r="94" spans="1:10">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A94" s="51"/>
       <c r="C94" s="51"/>
-      <c r="D94" s="52"/>
-      <c r="E94" s="55"/>
-      <c r="F94" s="52"/>
+      <c r="D94" s="56"/>
+      <c r="E94" s="58"/>
+      <c r="F94" s="56"/>
       <c r="G94" s="52"/>
       <c r="H94" s="54"/>
-      <c r="I94" s="52"/>
+      <c r="I94" s="56"/>
       <c r="J94" s="2"/>
     </row>
-    <row r="95" spans="1:10">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A95" s="51"/>
       <c r="C95" s="51"/>
-      <c r="D95" s="52"/>
-      <c r="E95" s="55"/>
-      <c r="F95" s="52"/>
+      <c r="D95" s="56"/>
+      <c r="E95" s="58"/>
+      <c r="F95" s="56"/>
       <c r="G95" s="52"/>
       <c r="H95" s="54"/>
-      <c r="I95" s="52"/>
+      <c r="I95" s="56"/>
       <c r="J95" s="2"/>
     </row>
-    <row r="96" spans="1:10">
+    <row r="96" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A96" s="51"/>
       <c r="C96" s="51"/>
-      <c r="D96" s="52"/>
-      <c r="E96" s="55"/>
-      <c r="F96" s="52"/>
+      <c r="D96" s="56"/>
+      <c r="E96" s="58"/>
+      <c r="F96" s="56"/>
       <c r="G96" s="52"/>
       <c r="H96" s="54"/>
-      <c r="I96" s="52"/>
+      <c r="I96" s="56"/>
       <c r="J96" s="2"/>
     </row>
-    <row r="97" spans="1:10">
+    <row r="97" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A97" s="51"/>
       <c r="C97" s="51"/>
       <c r="D97" s="56"/>
       <c r="E97" s="58"/>
-      <c r="F97" s="52"/>
+      <c r="F97" s="56"/>
       <c r="G97" s="52"/>
       <c r="H97" s="54"/>
       <c r="I97" s="56"/>
       <c r="J97" s="2"/>
     </row>
-    <row r="98" spans="1:10">
+    <row r="98" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A98" s="51"/>
       <c r="C98" s="51"/>
       <c r="D98" s="56"/>
       <c r="E98" s="58"/>
-      <c r="F98" s="52"/>
+      <c r="F98" s="56"/>
       <c r="G98" s="52"/>
       <c r="H98" s="54"/>
       <c r="I98" s="56"/>
       <c r="J98" s="2"/>
     </row>
-    <row r="99" spans="1:10">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A99" s="51"/>
       <c r="C99" s="51"/>
-      <c r="D99" s="56"/>
-      <c r="E99" s="58"/>
+      <c r="D99" s="52"/>
+      <c r="E99" s="55"/>
       <c r="F99" s="52"/>
       <c r="G99" s="52"/>
       <c r="H99" s="54"/>
-      <c r="I99" s="56"/>
+      <c r="I99" s="52"/>
       <c r="J99" s="2"/>
     </row>
-    <row r="100" spans="1:10">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A100" s="51"/>
       <c r="C100" s="51"/>
       <c r="D100" s="52"/>
@@ -5740,7 +4728,7 @@
       <c r="I100" s="52"/>
       <c r="J100" s="2"/>
     </row>
-    <row r="101" spans="1:10">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A101" s="51"/>
       <c r="C101" s="51"/>
       <c r="D101" s="52"/>
@@ -5751,236 +4739,238 @@
       <c r="I101" s="52"/>
       <c r="J101" s="2"/>
     </row>
-    <row r="102" spans="1:10">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A102" s="51"/>
       <c r="C102" s="51"/>
-      <c r="D102" s="52"/>
-      <c r="E102" s="55"/>
+      <c r="D102" s="56"/>
+      <c r="E102" s="58"/>
       <c r="F102" s="52"/>
-      <c r="G102" s="52"/>
+      <c r="G102" s="56"/>
       <c r="H102" s="54"/>
       <c r="I102" s="56"/>
       <c r="J102" s="2"/>
     </row>
-    <row r="103" spans="1:10">
+    <row r="103" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A103" s="51"/>
       <c r="C103" s="51"/>
       <c r="D103" s="52"/>
       <c r="E103" s="55"/>
       <c r="F103" s="52"/>
-      <c r="G103" s="52"/>
+      <c r="G103" s="56"/>
       <c r="H103" s="54"/>
       <c r="I103" s="52"/>
       <c r="J103" s="2"/>
     </row>
-    <row r="104" spans="1:10">
+    <row r="104" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A104" s="51"/>
       <c r="C104" s="51"/>
-      <c r="D104" s="52"/>
-      <c r="E104" s="55"/>
-      <c r="F104" s="52"/>
-      <c r="G104" s="52"/>
+      <c r="D104" s="56"/>
+      <c r="E104" s="58"/>
+      <c r="F104" s="56"/>
+      <c r="G104" s="56"/>
       <c r="H104" s="54"/>
-      <c r="I104" s="52"/>
+      <c r="I104" s="56"/>
       <c r="J104" s="2"/>
     </row>
-    <row r="105" spans="1:10">
+    <row r="105" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A105" s="51"/>
       <c r="C105" s="51"/>
       <c r="D105" s="52"/>
       <c r="E105" s="55"/>
       <c r="F105" s="52"/>
-      <c r="G105" s="52"/>
+      <c r="G105" s="56"/>
       <c r="H105" s="54"/>
       <c r="I105" s="52"/>
       <c r="J105" s="2"/>
     </row>
-    <row r="106" spans="1:10">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A106" s="51"/>
       <c r="C106" s="51"/>
-      <c r="D106" s="56"/>
-      <c r="E106" s="58"/>
-      <c r="F106" s="56"/>
-      <c r="G106" s="52"/>
+      <c r="D106" s="57"/>
+      <c r="E106" s="55"/>
+      <c r="F106" s="57"/>
+      <c r="G106" s="56"/>
       <c r="H106" s="54"/>
-      <c r="I106" s="56"/>
+      <c r="I106" s="52"/>
       <c r="J106" s="2"/>
     </row>
-    <row r="107" spans="1:10">
+    <row r="107" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A107" s="51"/>
       <c r="C107" s="51"/>
-      <c r="D107" s="56"/>
-      <c r="E107" s="58"/>
+      <c r="D107" s="52"/>
+      <c r="E107" s="55"/>
       <c r="F107" s="52"/>
-      <c r="G107" s="52"/>
+      <c r="G107" s="56"/>
       <c r="H107" s="54"/>
-      <c r="I107" s="56"/>
+      <c r="I107" s="52"/>
       <c r="J107" s="2"/>
     </row>
-    <row r="108" spans="1:10">
+    <row r="108" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A108" s="51"/>
       <c r="C108" s="51"/>
-      <c r="D108" s="56"/>
-      <c r="E108" s="58"/>
+      <c r="D108" s="52"/>
+      <c r="E108" s="55"/>
       <c r="F108" s="52"/>
-      <c r="G108" s="52"/>
+      <c r="G108" s="56"/>
       <c r="H108" s="54"/>
-      <c r="I108" s="56"/>
+      <c r="I108" s="52"/>
       <c r="J108" s="2"/>
     </row>
-    <row r="109" spans="1:10" s="2" customFormat="1">
-      <c r="A109" s="52"/>
-      <c r="C109" s="52"/>
+    <row r="109" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A109" s="51"/>
+      <c r="C109" s="51"/>
       <c r="D109" s="56"/>
       <c r="E109" s="58"/>
       <c r="F109" s="52"/>
-      <c r="G109" s="52"/>
+      <c r="G109" s="56"/>
       <c r="H109" s="54"/>
       <c r="I109" s="56"/>
-    </row>
-    <row r="110" spans="1:10" s="2" customFormat="1" ht="15">
-      <c r="A110" s="52"/>
-      <c r="C110" s="52"/>
-      <c r="D110" s="56"/>
-      <c r="E110" s="58"/>
+      <c r="J109" s="2"/>
+    </row>
+    <row r="110" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A110" s="51"/>
+      <c r="C110" s="51"/>
+      <c r="D110" s="52"/>
+      <c r="E110" s="55"/>
       <c r="F110" s="52"/>
-      <c r="G110" s="52"/>
-      <c r="H110"/>
-      <c r="I110" s="56"/>
-    </row>
-    <row r="111" spans="1:10">
+      <c r="G110" s="56"/>
+      <c r="H110" s="54"/>
+      <c r="I110" s="52"/>
+      <c r="J110" s="2"/>
+    </row>
+    <row r="111" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A111" s="51"/>
       <c r="C111" s="51"/>
       <c r="D111" s="56"/>
       <c r="E111" s="58"/>
       <c r="F111" s="56"/>
-      <c r="G111" s="52"/>
+      <c r="G111" s="56"/>
       <c r="H111" s="54"/>
       <c r="I111" s="56"/>
       <c r="J111" s="2"/>
     </row>
-    <row r="112" spans="1:10">
-      <c r="A112" s="52"/>
+    <row r="112" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A112" s="51"/>
       <c r="C112" s="51"/>
       <c r="D112" s="56"/>
       <c r="E112" s="58"/>
       <c r="F112" s="56"/>
-      <c r="G112" s="52"/>
+      <c r="G112" s="56"/>
       <c r="H112" s="54"/>
       <c r="I112" s="56"/>
       <c r="J112" s="2"/>
     </row>
-    <row r="113" spans="1:10">
+    <row r="113" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A113" s="51"/>
       <c r="C113" s="51"/>
-      <c r="D113" s="56"/>
-      <c r="E113" s="58"/>
-      <c r="F113" s="56"/>
-      <c r="G113" s="52"/>
+      <c r="D113" s="52"/>
+      <c r="E113" s="55"/>
+      <c r="F113" s="52"/>
+      <c r="G113" s="56"/>
       <c r="H113" s="54"/>
-      <c r="I113" s="56"/>
+      <c r="I113" s="52"/>
       <c r="J113" s="2"/>
     </row>
-    <row r="114" spans="1:10">
+    <row r="114" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A114" s="51"/>
       <c r="C114" s="51"/>
-      <c r="D114" s="56"/>
-      <c r="E114" s="58"/>
-      <c r="F114" s="56"/>
-      <c r="G114" s="52"/>
+      <c r="D114" s="52"/>
+      <c r="E114" s="55"/>
+      <c r="F114" s="52"/>
+      <c r="G114" s="56"/>
       <c r="H114" s="54"/>
-      <c r="I114" s="56"/>
+      <c r="I114" s="52"/>
       <c r="J114" s="2"/>
     </row>
-    <row r="115" spans="1:10">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A115" s="51"/>
       <c r="C115" s="51"/>
-      <c r="D115" s="56"/>
-      <c r="E115" s="58"/>
-      <c r="F115" s="56"/>
-      <c r="G115" s="52"/>
+      <c r="D115" s="52"/>
+      <c r="E115" s="55"/>
+      <c r="F115" s="52"/>
+      <c r="G115" s="56"/>
       <c r="H115" s="54"/>
-      <c r="I115" s="56"/>
+      <c r="I115" s="52"/>
       <c r="J115" s="2"/>
     </row>
-    <row r="116" spans="1:10">
-      <c r="A116" s="51"/>
+    <row r="116" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A116" s="52"/>
       <c r="C116" s="51"/>
-      <c r="D116" s="56"/>
-      <c r="E116" s="58"/>
-      <c r="F116" s="56"/>
-      <c r="G116" s="52"/>
+      <c r="D116" s="52"/>
+      <c r="E116" s="55"/>
+      <c r="F116" s="52"/>
+      <c r="G116" s="56"/>
       <c r="H116" s="54"/>
-      <c r="I116" s="56"/>
+      <c r="I116" s="52"/>
       <c r="J116" s="2"/>
     </row>
-    <row r="117" spans="1:10">
+    <row r="117" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A117" s="51"/>
       <c r="C117" s="51"/>
       <c r="D117" s="56"/>
       <c r="E117" s="58"/>
       <c r="F117" s="56"/>
-      <c r="G117" s="52"/>
+      <c r="G117" s="56"/>
       <c r="H117" s="54"/>
-      <c r="I117" s="56"/>
+      <c r="I117" s="52"/>
       <c r="J117" s="2"/>
     </row>
-    <row r="118" spans="1:10">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A118" s="51"/>
       <c r="C118" s="51"/>
-      <c r="D118" s="56"/>
-      <c r="E118" s="58"/>
+      <c r="D118" s="52"/>
+      <c r="E118" s="55"/>
       <c r="F118" s="56"/>
-      <c r="G118" s="52"/>
+      <c r="G118" s="56"/>
       <c r="H118" s="54"/>
-      <c r="I118" s="56"/>
+      <c r="I118" s="52"/>
       <c r="J118" s="2"/>
     </row>
-    <row r="119" spans="1:10">
+    <row r="119" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A119" s="51"/>
       <c r="C119" s="51"/>
       <c r="D119" s="52"/>
       <c r="E119" s="55"/>
-      <c r="F119" s="52"/>
-      <c r="G119" s="52"/>
+      <c r="F119" s="56"/>
+      <c r="G119" s="56"/>
       <c r="H119" s="54"/>
       <c r="I119" s="52"/>
       <c r="J119" s="2"/>
     </row>
-    <row r="120" spans="1:10">
+    <row r="120" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A120" s="51"/>
       <c r="C120" s="51"/>
       <c r="D120" s="52"/>
       <c r="E120" s="55"/>
-      <c r="F120" s="52"/>
-      <c r="G120" s="52"/>
+      <c r="F120" s="56"/>
+      <c r="G120" s="56"/>
       <c r="H120" s="54"/>
       <c r="I120" s="52"/>
       <c r="J120" s="2"/>
     </row>
-    <row r="121" spans="1:10">
+    <row r="121" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A121" s="51"/>
       <c r="C121" s="51"/>
       <c r="D121" s="52"/>
       <c r="E121" s="55"/>
       <c r="F121" s="52"/>
-      <c r="G121" s="52"/>
+      <c r="G121" s="56"/>
       <c r="H121" s="54"/>
       <c r="I121" s="52"/>
       <c r="J121" s="2"/>
     </row>
-    <row r="122" spans="1:10">
+    <row r="122" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A122" s="51"/>
       <c r="C122" s="51"/>
-      <c r="D122" s="56"/>
-      <c r="E122" s="58"/>
+      <c r="D122" s="52"/>
+      <c r="E122" s="55"/>
       <c r="F122" s="52"/>
       <c r="G122" s="56"/>
       <c r="H122" s="54"/>
-      <c r="I122" s="56"/>
+      <c r="I122" s="52"/>
       <c r="J122" s="2"/>
     </row>
-    <row r="123" spans="1:10">
+    <row r="123" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A123" s="51"/>
       <c r="C123" s="51"/>
       <c r="D123" s="52"/>
@@ -5991,18 +4981,18 @@
       <c r="I123" s="52"/>
       <c r="J123" s="2"/>
     </row>
-    <row r="124" spans="1:10">
+    <row r="124" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A124" s="51"/>
       <c r="C124" s="51"/>
-      <c r="D124" s="56"/>
-      <c r="E124" s="58"/>
-      <c r="F124" s="56"/>
+      <c r="D124" s="52"/>
+      <c r="E124" s="55"/>
+      <c r="F124" s="52"/>
       <c r="G124" s="56"/>
       <c r="H124" s="54"/>
-      <c r="I124" s="56"/>
+      <c r="I124" s="52"/>
       <c r="J124" s="2"/>
     </row>
-    <row r="125" spans="1:10">
+    <row r="125" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A125" s="51"/>
       <c r="C125" s="51"/>
       <c r="D125" s="52"/>
@@ -6013,18 +5003,18 @@
       <c r="I125" s="52"/>
       <c r="J125" s="2"/>
     </row>
-    <row r="126" spans="1:10">
+    <row r="126" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A126" s="51"/>
       <c r="C126" s="51"/>
-      <c r="D126" s="57"/>
-      <c r="E126" s="55"/>
-      <c r="F126" s="57"/>
+      <c r="D126" s="56"/>
+      <c r="E126" s="58"/>
+      <c r="F126" s="56"/>
       <c r="G126" s="56"/>
       <c r="H126" s="54"/>
-      <c r="I126" s="52"/>
+      <c r="I126" s="56"/>
       <c r="J126" s="2"/>
     </row>
-    <row r="127" spans="1:10">
+    <row r="127" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A127" s="51"/>
       <c r="C127" s="51"/>
       <c r="D127" s="52"/>
@@ -6035,7 +5025,7 @@
       <c r="I127" s="52"/>
       <c r="J127" s="2"/>
     </row>
-    <row r="128" spans="1:10">
+    <row r="128" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A128" s="51"/>
       <c r="C128" s="51"/>
       <c r="D128" s="52"/>
@@ -6046,18 +5036,18 @@
       <c r="I128" s="52"/>
       <c r="J128" s="2"/>
     </row>
-    <row r="129" spans="1:10">
+    <row r="129" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A129" s="51"/>
       <c r="C129" s="51"/>
       <c r="D129" s="56"/>
       <c r="E129" s="58"/>
-      <c r="F129" s="52"/>
+      <c r="F129" s="56"/>
       <c r="G129" s="56"/>
       <c r="H129" s="54"/>
       <c r="I129" s="56"/>
       <c r="J129" s="2"/>
     </row>
-    <row r="130" spans="1:10">
+    <row r="130" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A130" s="51"/>
       <c r="C130" s="51"/>
       <c r="D130" s="52"/>
@@ -6068,29 +5058,29 @@
       <c r="I130" s="52"/>
       <c r="J130" s="2"/>
     </row>
-    <row r="131" spans="1:10">
+    <row r="131" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A131" s="51"/>
       <c r="C131" s="51"/>
-      <c r="D131" s="56"/>
-      <c r="E131" s="58"/>
-      <c r="F131" s="56"/>
+      <c r="D131" s="52"/>
+      <c r="E131" s="55"/>
+      <c r="F131" s="52"/>
       <c r="G131" s="56"/>
       <c r="H131" s="54"/>
-      <c r="I131" s="56"/>
+      <c r="I131" s="52"/>
       <c r="J131" s="2"/>
     </row>
-    <row r="132" spans="1:10">
+    <row r="132" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A132" s="51"/>
       <c r="C132" s="51"/>
-      <c r="D132" s="56"/>
-      <c r="E132" s="58"/>
-      <c r="F132" s="56"/>
+      <c r="D132" s="52"/>
+      <c r="E132" s="55"/>
+      <c r="F132" s="52"/>
       <c r="G132" s="56"/>
       <c r="H132" s="54"/>
-      <c r="I132" s="56"/>
+      <c r="I132" s="52"/>
       <c r="J132" s="2"/>
     </row>
-    <row r="133" spans="1:10">
+    <row r="133" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A133" s="51"/>
       <c r="C133" s="51"/>
       <c r="D133" s="52"/>
@@ -6101,7 +5091,7 @@
       <c r="I133" s="52"/>
       <c r="J133" s="2"/>
     </row>
-    <row r="134" spans="1:10">
+    <row r="134" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A134" s="51"/>
       <c r="C134" s="51"/>
       <c r="D134" s="52"/>
@@ -6112,7 +5102,7 @@
       <c r="I134" s="52"/>
       <c r="J134" s="2"/>
     </row>
-    <row r="135" spans="1:10">
+    <row r="135" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A135" s="51"/>
       <c r="C135" s="51"/>
       <c r="D135" s="52"/>
@@ -6123,8 +5113,8 @@
       <c r="I135" s="52"/>
       <c r="J135" s="2"/>
     </row>
-    <row r="136" spans="1:10">
-      <c r="A136" s="52"/>
+    <row r="136" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A136" s="51"/>
       <c r="C136" s="51"/>
       <c r="D136" s="52"/>
       <c r="E136" s="55"/>
@@ -6134,51 +5124,51 @@
       <c r="I136" s="52"/>
       <c r="J136" s="2"/>
     </row>
-    <row r="137" spans="1:10">
+    <row r="137" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A137" s="51"/>
       <c r="C137" s="51"/>
-      <c r="D137" s="56"/>
-      <c r="E137" s="58"/>
-      <c r="F137" s="56"/>
+      <c r="D137" s="52"/>
+      <c r="E137" s="55"/>
+      <c r="F137" s="52"/>
       <c r="G137" s="56"/>
       <c r="H137" s="54"/>
       <c r="I137" s="52"/>
       <c r="J137" s="2"/>
     </row>
-    <row r="138" spans="1:10">
+    <row r="138" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A138" s="51"/>
       <c r="C138" s="51"/>
       <c r="D138" s="52"/>
       <c r="E138" s="55"/>
-      <c r="F138" s="56"/>
+      <c r="F138" s="52"/>
       <c r="G138" s="56"/>
       <c r="H138" s="54"/>
       <c r="I138" s="52"/>
       <c r="J138" s="2"/>
     </row>
-    <row r="139" spans="1:10">
+    <row r="139" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A139" s="51"/>
       <c r="C139" s="51"/>
       <c r="D139" s="52"/>
       <c r="E139" s="55"/>
-      <c r="F139" s="56"/>
+      <c r="F139" s="52"/>
       <c r="G139" s="56"/>
       <c r="H139" s="54"/>
       <c r="I139" s="52"/>
       <c r="J139" s="2"/>
     </row>
-    <row r="140" spans="1:10">
+    <row r="140" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A140" s="51"/>
       <c r="C140" s="51"/>
       <c r="D140" s="52"/>
       <c r="E140" s="55"/>
-      <c r="F140" s="56"/>
+      <c r="F140" s="52"/>
       <c r="G140" s="56"/>
       <c r="H140" s="54"/>
       <c r="I140" s="52"/>
       <c r="J140" s="2"/>
     </row>
-    <row r="141" spans="1:10">
+    <row r="141" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A141" s="51"/>
       <c r="C141" s="51"/>
       <c r="D141" s="52"/>
@@ -6189,7 +5179,7 @@
       <c r="I141" s="52"/>
       <c r="J141" s="2"/>
     </row>
-    <row r="142" spans="1:10">
+    <row r="142" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A142" s="51"/>
       <c r="C142" s="51"/>
       <c r="D142" s="52"/>
@@ -6200,7 +5190,7 @@
       <c r="I142" s="52"/>
       <c r="J142" s="2"/>
     </row>
-    <row r="143" spans="1:10">
+    <row r="143" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A143" s="51"/>
       <c r="C143" s="51"/>
       <c r="D143" s="52"/>
@@ -6211,7 +5201,7 @@
       <c r="I143" s="52"/>
       <c r="J143" s="2"/>
     </row>
-    <row r="144" spans="1:10">
+    <row r="144" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A144" s="51"/>
       <c r="C144" s="51"/>
       <c r="D144" s="52"/>
@@ -6222,7 +5212,7 @@
       <c r="I144" s="52"/>
       <c r="J144" s="2"/>
     </row>
-    <row r="145" spans="1:10">
+    <row r="145" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A145" s="51"/>
       <c r="C145" s="51"/>
       <c r="D145" s="52"/>
@@ -6233,18 +5223,18 @@
       <c r="I145" s="52"/>
       <c r="J145" s="2"/>
     </row>
-    <row r="146" spans="1:10">
+    <row r="146" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A146" s="51"/>
       <c r="C146" s="51"/>
-      <c r="D146" s="56"/>
-      <c r="E146" s="58"/>
-      <c r="F146" s="56"/>
+      <c r="D146" s="52"/>
+      <c r="E146" s="55"/>
+      <c r="F146" s="52"/>
       <c r="G146" s="56"/>
       <c r="H146" s="54"/>
-      <c r="I146" s="56"/>
+      <c r="I146" s="52"/>
       <c r="J146" s="2"/>
     </row>
-    <row r="147" spans="1:10">
+    <row r="147" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A147" s="51"/>
       <c r="C147" s="51"/>
       <c r="D147" s="52"/>
@@ -6255,29 +5245,29 @@
       <c r="I147" s="52"/>
       <c r="J147" s="2"/>
     </row>
-    <row r="148" spans="1:10">
+    <row r="148" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A148" s="51"/>
       <c r="C148" s="51"/>
-      <c r="D148" s="52"/>
-      <c r="E148" s="55"/>
-      <c r="F148" s="52"/>
+      <c r="D148" s="56"/>
+      <c r="E148" s="58"/>
+      <c r="F148" s="56"/>
       <c r="G148" s="56"/>
       <c r="H148" s="54"/>
-      <c r="I148" s="52"/>
+      <c r="I148" s="56"/>
       <c r="J148" s="2"/>
     </row>
-    <row r="149" spans="1:10">
+    <row r="149" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A149" s="51"/>
       <c r="C149" s="51"/>
-      <c r="D149" s="56"/>
-      <c r="E149" s="58"/>
-      <c r="F149" s="56"/>
+      <c r="D149" s="52"/>
+      <c r="E149" s="55"/>
+      <c r="F149" s="52"/>
       <c r="G149" s="56"/>
       <c r="H149" s="54"/>
-      <c r="I149" s="56"/>
+      <c r="I149" s="52"/>
       <c r="J149" s="2"/>
     </row>
-    <row r="150" spans="1:10">
+    <row r="150" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A150" s="51"/>
       <c r="C150" s="51"/>
       <c r="D150" s="52"/>
@@ -6288,7 +5278,7 @@
       <c r="I150" s="52"/>
       <c r="J150" s="2"/>
     </row>
-    <row r="151" spans="1:10">
+    <row r="151" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A151" s="51"/>
       <c r="C151" s="51"/>
       <c r="D151" s="52"/>
@@ -6299,7 +5289,7 @@
       <c r="I151" s="52"/>
       <c r="J151" s="2"/>
     </row>
-    <row r="152" spans="1:10">
+    <row r="152" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A152" s="51"/>
       <c r="C152" s="51"/>
       <c r="D152" s="52"/>
@@ -6310,7 +5300,7 @@
       <c r="I152" s="52"/>
       <c r="J152" s="2"/>
     </row>
-    <row r="153" spans="1:10">
+    <row r="153" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A153" s="51"/>
       <c r="C153" s="51"/>
       <c r="D153" s="52"/>
@@ -6321,7 +5311,7 @@
       <c r="I153" s="52"/>
       <c r="J153" s="2"/>
     </row>
-    <row r="154" spans="1:10">
+    <row r="154" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A154" s="51"/>
       <c r="C154" s="51"/>
       <c r="D154" s="52"/>
@@ -6332,7 +5322,7 @@
       <c r="I154" s="52"/>
       <c r="J154" s="2"/>
     </row>
-    <row r="155" spans="1:10">
+    <row r="155" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A155" s="51"/>
       <c r="C155" s="51"/>
       <c r="D155" s="52"/>
@@ -6343,7 +5333,7 @@
       <c r="I155" s="52"/>
       <c r="J155" s="2"/>
     </row>
-    <row r="156" spans="1:10">
+    <row r="156" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A156" s="51"/>
       <c r="C156" s="51"/>
       <c r="D156" s="52"/>
@@ -6354,7 +5344,7 @@
       <c r="I156" s="52"/>
       <c r="J156" s="2"/>
     </row>
-    <row r="157" spans="1:10">
+    <row r="157" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A157" s="51"/>
       <c r="C157" s="51"/>
       <c r="D157" s="52"/>
@@ -6365,7 +5355,7 @@
       <c r="I157" s="52"/>
       <c r="J157" s="2"/>
     </row>
-    <row r="158" spans="1:10">
+    <row r="158" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A158" s="51"/>
       <c r="C158" s="51"/>
       <c r="D158" s="52"/>
@@ -6376,18 +5366,18 @@
       <c r="I158" s="52"/>
       <c r="J158" s="2"/>
     </row>
-    <row r="159" spans="1:10">
+    <row r="159" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A159" s="51"/>
       <c r="C159" s="51"/>
-      <c r="D159" s="52"/>
-      <c r="E159" s="55"/>
-      <c r="F159" s="52"/>
+      <c r="D159" s="56"/>
+      <c r="E159" s="58"/>
+      <c r="F159" s="56"/>
       <c r="G159" s="56"/>
       <c r="H159" s="54"/>
-      <c r="I159" s="52"/>
+      <c r="I159" s="56"/>
       <c r="J159" s="2"/>
     </row>
-    <row r="160" spans="1:10">
+    <row r="160" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A160" s="51"/>
       <c r="C160" s="51"/>
       <c r="D160" s="52"/>
@@ -6398,18 +5388,18 @@
       <c r="I160" s="52"/>
       <c r="J160" s="2"/>
     </row>
-    <row r="161" spans="1:10">
+    <row r="161" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A161" s="51"/>
       <c r="C161" s="51"/>
-      <c r="D161" s="52"/>
-      <c r="E161" s="55"/>
-      <c r="F161" s="52"/>
+      <c r="D161" s="56"/>
+      <c r="E161" s="58"/>
+      <c r="F161" s="56"/>
       <c r="G161" s="56"/>
       <c r="H161" s="54"/>
-      <c r="I161" s="52"/>
+      <c r="I161" s="56"/>
       <c r="J161" s="2"/>
     </row>
-    <row r="162" spans="1:10">
+    <row r="162" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A162" s="51"/>
       <c r="C162" s="51"/>
       <c r="D162" s="52"/>
@@ -6420,7 +5410,7 @@
       <c r="I162" s="52"/>
       <c r="J162" s="2"/>
     </row>
-    <row r="163" spans="1:10">
+    <row r="163" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A163" s="51"/>
       <c r="C163" s="51"/>
       <c r="D163" s="52"/>
@@ -6431,7 +5421,7 @@
       <c r="I163" s="52"/>
       <c r="J163" s="2"/>
     </row>
-    <row r="164" spans="1:10">
+    <row r="164" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A164" s="51"/>
       <c r="C164" s="51"/>
       <c r="D164" s="52"/>
@@ -6442,7 +5432,7 @@
       <c r="I164" s="52"/>
       <c r="J164" s="2"/>
     </row>
-    <row r="165" spans="1:10">
+    <row r="165" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A165" s="51"/>
       <c r="C165" s="51"/>
       <c r="D165" s="52"/>
@@ -6453,7 +5443,7 @@
       <c r="I165" s="52"/>
       <c r="J165" s="2"/>
     </row>
-    <row r="166" spans="1:10">
+    <row r="166" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A166" s="51"/>
       <c r="C166" s="51"/>
       <c r="D166" s="52"/>
@@ -6464,7 +5454,7 @@
       <c r="I166" s="52"/>
       <c r="J166" s="2"/>
     </row>
-    <row r="167" spans="1:10">
+    <row r="167" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A167" s="51"/>
       <c r="C167" s="51"/>
       <c r="D167" s="52"/>
@@ -6475,18 +5465,18 @@
       <c r="I167" s="52"/>
       <c r="J167" s="2"/>
     </row>
-    <row r="168" spans="1:10">
+    <row r="168" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A168" s="51"/>
       <c r="C168" s="51"/>
-      <c r="D168" s="56"/>
-      <c r="E168" s="58"/>
-      <c r="F168" s="56"/>
+      <c r="D168" s="52"/>
+      <c r="E168" s="55"/>
+      <c r="F168" s="52"/>
       <c r="G168" s="56"/>
       <c r="H168" s="54"/>
-      <c r="I168" s="56"/>
+      <c r="I168" s="52"/>
       <c r="J168" s="2"/>
     </row>
-    <row r="169" spans="1:10">
+    <row r="169" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A169" s="51"/>
       <c r="C169" s="51"/>
       <c r="D169" s="52"/>
@@ -6497,18 +5487,18 @@
       <c r="I169" s="52"/>
       <c r="J169" s="2"/>
     </row>
-    <row r="170" spans="1:10">
+    <row r="170" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A170" s="51"/>
       <c r="C170" s="51"/>
-      <c r="D170" s="52"/>
-      <c r="E170" s="55"/>
-      <c r="F170" s="52"/>
+      <c r="D170" s="56"/>
+      <c r="E170" s="58"/>
+      <c r="F170" s="56"/>
       <c r="G170" s="56"/>
       <c r="H170" s="54"/>
-      <c r="I170" s="52"/>
+      <c r="I170" s="56"/>
       <c r="J170" s="2"/>
     </row>
-    <row r="171" spans="1:10">
+    <row r="171" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A171" s="51"/>
       <c r="C171" s="51"/>
       <c r="D171" s="52"/>
@@ -6519,7 +5509,7 @@
       <c r="I171" s="52"/>
       <c r="J171" s="2"/>
     </row>
-    <row r="172" spans="1:10">
+    <row r="172" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A172" s="51"/>
       <c r="C172" s="51"/>
       <c r="D172" s="52"/>
@@ -6530,7 +5520,7 @@
       <c r="I172" s="52"/>
       <c r="J172" s="2"/>
     </row>
-    <row r="173" spans="1:10">
+    <row r="173" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A173" s="51"/>
       <c r="C173" s="51"/>
       <c r="D173" s="52"/>
@@ -6541,7 +5531,7 @@
       <c r="I173" s="52"/>
       <c r="J173" s="2"/>
     </row>
-    <row r="174" spans="1:10">
+    <row r="174" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A174" s="51"/>
       <c r="C174" s="51"/>
       <c r="D174" s="52"/>
@@ -6552,7 +5542,7 @@
       <c r="I174" s="52"/>
       <c r="J174" s="2"/>
     </row>
-    <row r="175" spans="1:10">
+    <row r="175" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A175" s="51"/>
       <c r="C175" s="51"/>
       <c r="D175" s="52"/>
@@ -6563,18 +5553,18 @@
       <c r="I175" s="52"/>
       <c r="J175" s="2"/>
     </row>
-    <row r="176" spans="1:10">
+    <row r="176" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A176" s="51"/>
       <c r="C176" s="51"/>
-      <c r="D176" s="52"/>
-      <c r="E176" s="55"/>
+      <c r="D176" s="56"/>
+      <c r="E176" s="58"/>
       <c r="F176" s="52"/>
       <c r="G176" s="56"/>
       <c r="H176" s="54"/>
-      <c r="I176" s="52"/>
+      <c r="I176" s="56"/>
       <c r="J176" s="2"/>
     </row>
-    <row r="177" spans="1:10">
+    <row r="177" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A177" s="51"/>
       <c r="C177" s="51"/>
       <c r="D177" s="52"/>
@@ -6585,7 +5575,7 @@
       <c r="I177" s="52"/>
       <c r="J177" s="2"/>
     </row>
-    <row r="178" spans="1:10">
+    <row r="178" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A178" s="51"/>
       <c r="C178" s="51"/>
       <c r="D178" s="52"/>
@@ -6596,62 +5586,62 @@
       <c r="I178" s="52"/>
       <c r="J178" s="2"/>
     </row>
-    <row r="179" spans="1:10">
+    <row r="179" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A179" s="51"/>
       <c r="C179" s="51"/>
-      <c r="D179" s="56"/>
-      <c r="E179" s="58"/>
-      <c r="F179" s="56"/>
+      <c r="D179" s="52"/>
+      <c r="E179" s="55"/>
+      <c r="F179" s="52"/>
       <c r="G179" s="56"/>
       <c r="H179" s="54"/>
-      <c r="I179" s="56"/>
+      <c r="I179" s="52"/>
       <c r="J179" s="2"/>
     </row>
-    <row r="180" spans="1:10">
+    <row r="180" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A180" s="51"/>
       <c r="C180" s="51"/>
-      <c r="D180" s="52"/>
-      <c r="E180" s="55"/>
+      <c r="D180" s="56"/>
+      <c r="E180" s="58"/>
       <c r="F180" s="52"/>
       <c r="G180" s="56"/>
       <c r="H180" s="54"/>
-      <c r="I180" s="52"/>
+      <c r="I180" s="56"/>
       <c r="J180" s="2"/>
     </row>
-    <row r="181" spans="1:10">
+    <row r="181" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A181" s="51"/>
       <c r="C181" s="51"/>
-      <c r="D181" s="56"/>
-      <c r="E181" s="58"/>
-      <c r="F181" s="56"/>
+      <c r="D181" s="52"/>
+      <c r="E181" s="55"/>
+      <c r="F181" s="52"/>
       <c r="G181" s="56"/>
       <c r="H181" s="54"/>
-      <c r="I181" s="56"/>
+      <c r="I181" s="52"/>
       <c r="J181" s="2"/>
     </row>
-    <row r="182" spans="1:10">
+    <row r="182" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A182" s="51"/>
       <c r="C182" s="51"/>
-      <c r="D182" s="52"/>
-      <c r="E182" s="55"/>
-      <c r="F182" s="52"/>
+      <c r="D182" s="56"/>
+      <c r="E182" s="58"/>
+      <c r="F182" s="56"/>
       <c r="G182" s="56"/>
       <c r="H182" s="54"/>
-      <c r="I182" s="52"/>
+      <c r="I182" s="56"/>
       <c r="J182" s="2"/>
     </row>
-    <row r="183" spans="1:10">
+    <row r="183" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A183" s="51"/>
       <c r="C183" s="51"/>
-      <c r="D183" s="52"/>
-      <c r="E183" s="55"/>
-      <c r="F183" s="52"/>
+      <c r="D183" s="56"/>
+      <c r="E183" s="58"/>
+      <c r="F183" s="56"/>
       <c r="G183" s="56"/>
       <c r="H183" s="54"/>
-      <c r="I183" s="52"/>
+      <c r="I183" s="56"/>
       <c r="J183" s="2"/>
     </row>
-    <row r="184" spans="1:10">
+    <row r="184" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A184" s="51"/>
       <c r="C184" s="51"/>
       <c r="D184" s="52"/>
@@ -6659,10 +5649,10 @@
       <c r="F184" s="52"/>
       <c r="G184" s="56"/>
       <c r="H184" s="54"/>
-      <c r="I184" s="52"/>
+      <c r="I184" s="56"/>
       <c r="J184" s="2"/>
     </row>
-    <row r="185" spans="1:10">
+    <row r="185" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A185" s="51"/>
       <c r="C185" s="51"/>
       <c r="D185" s="52"/>
@@ -6670,10 +5660,10 @@
       <c r="F185" s="52"/>
       <c r="G185" s="56"/>
       <c r="H185" s="54"/>
-      <c r="I185" s="52"/>
+      <c r="I185" s="56"/>
       <c r="J185" s="2"/>
     </row>
-    <row r="186" spans="1:10">
+    <row r="186" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A186" s="51"/>
       <c r="C186" s="51"/>
       <c r="D186" s="52"/>
@@ -6681,10 +5671,10 @@
       <c r="F186" s="52"/>
       <c r="G186" s="56"/>
       <c r="H186" s="54"/>
-      <c r="I186" s="52"/>
+      <c r="I186" s="56"/>
       <c r="J186" s="2"/>
     </row>
-    <row r="187" spans="1:10">
+    <row r="187" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A187" s="51"/>
       <c r="C187" s="51"/>
       <c r="D187" s="52"/>
@@ -6695,7 +5685,7 @@
       <c r="I187" s="52"/>
       <c r="J187" s="2"/>
     </row>
-    <row r="188" spans="1:10">
+    <row r="188" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A188" s="51"/>
       <c r="C188" s="51"/>
       <c r="D188" s="52"/>
@@ -6706,7 +5696,7 @@
       <c r="I188" s="52"/>
       <c r="J188" s="2"/>
     </row>
-    <row r="189" spans="1:10">
+    <row r="189" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A189" s="51"/>
       <c r="C189" s="51"/>
       <c r="D189" s="52"/>
@@ -6717,84 +5707,84 @@
       <c r="I189" s="52"/>
       <c r="J189" s="2"/>
     </row>
-    <row r="190" spans="1:10">
+    <row r="190" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A190" s="51"/>
       <c r="C190" s="51"/>
-      <c r="D190" s="56"/>
-      <c r="E190" s="58"/>
-      <c r="F190" s="56"/>
+      <c r="D190" s="52"/>
+      <c r="E190" s="55"/>
+      <c r="F190" s="52"/>
       <c r="G190" s="56"/>
       <c r="H190" s="54"/>
-      <c r="I190" s="56"/>
+      <c r="I190" s="52"/>
       <c r="J190" s="2"/>
     </row>
-    <row r="191" spans="1:10">
+    <row r="191" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A191" s="51"/>
       <c r="C191" s="51"/>
-      <c r="D191" s="52"/>
-      <c r="E191" s="55"/>
-      <c r="F191" s="52"/>
+      <c r="D191" s="56"/>
+      <c r="E191" s="58"/>
+      <c r="F191" s="56"/>
       <c r="G191" s="56"/>
       <c r="H191" s="54"/>
-      <c r="I191" s="52"/>
+      <c r="I191" s="56"/>
       <c r="J191" s="2"/>
     </row>
-    <row r="192" spans="1:10">
+    <row r="192" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A192" s="51"/>
       <c r="C192" s="51"/>
-      <c r="D192" s="52"/>
-      <c r="E192" s="55"/>
-      <c r="F192" s="52"/>
+      <c r="D192" s="56"/>
+      <c r="E192" s="58"/>
+      <c r="F192" s="56"/>
       <c r="G192" s="56"/>
       <c r="H192" s="54"/>
-      <c r="I192" s="52"/>
+      <c r="I192" s="56"/>
       <c r="J192" s="2"/>
     </row>
-    <row r="193" spans="1:10">
+    <row r="193" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A193" s="51"/>
       <c r="C193" s="51"/>
-      <c r="D193" s="52"/>
-      <c r="E193" s="55"/>
-      <c r="F193" s="52"/>
+      <c r="D193" s="56"/>
+      <c r="E193" s="58"/>
+      <c r="F193" s="56"/>
       <c r="G193" s="56"/>
       <c r="H193" s="54"/>
-      <c r="I193" s="52"/>
+      <c r="I193" s="56"/>
       <c r="J193" s="2"/>
     </row>
-    <row r="194" spans="1:10">
+    <row r="194" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A194" s="51"/>
       <c r="C194" s="51"/>
-      <c r="D194" s="52"/>
-      <c r="E194" s="55"/>
-      <c r="F194" s="52"/>
+      <c r="D194" s="56"/>
+      <c r="E194" s="58"/>
+      <c r="F194" s="56"/>
       <c r="G194" s="56"/>
       <c r="H194" s="54"/>
-      <c r="I194" s="52"/>
+      <c r="I194" s="56"/>
       <c r="J194" s="2"/>
     </row>
-    <row r="195" spans="1:10">
+    <row r="195" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A195" s="51"/>
       <c r="C195" s="51"/>
       <c r="D195" s="52"/>
-      <c r="E195" s="55"/>
+      <c r="E195" s="58"/>
       <c r="F195" s="52"/>
       <c r="G195" s="56"/>
       <c r="H195" s="54"/>
       <c r="I195" s="52"/>
       <c r="J195" s="2"/>
     </row>
-    <row r="196" spans="1:10">
+    <row r="196" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A196" s="51"/>
       <c r="C196" s="51"/>
-      <c r="D196" s="56"/>
+      <c r="D196" s="52"/>
       <c r="E196" s="58"/>
       <c r="F196" s="52"/>
       <c r="G196" s="56"/>
       <c r="H196" s="54"/>
-      <c r="I196" s="56"/>
+      <c r="I196" s="52"/>
       <c r="J196" s="2"/>
     </row>
-    <row r="197" spans="1:10">
+    <row r="197" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A197" s="51"/>
       <c r="C197" s="51"/>
       <c r="D197" s="52"/>
@@ -6805,7 +5795,7 @@
       <c r="I197" s="52"/>
       <c r="J197" s="2"/>
     </row>
-    <row r="198" spans="1:10">
+    <row r="198" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A198" s="51"/>
       <c r="C198" s="51"/>
       <c r="D198" s="52"/>
@@ -6816,7 +5806,7 @@
       <c r="I198" s="52"/>
       <c r="J198" s="2"/>
     </row>
-    <row r="199" spans="1:10">
+    <row r="199" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A199" s="51"/>
       <c r="C199" s="51"/>
       <c r="D199" s="52"/>
@@ -6827,18 +5817,18 @@
       <c r="I199" s="52"/>
       <c r="J199" s="2"/>
     </row>
-    <row r="200" spans="1:10">
+    <row r="200" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A200" s="51"/>
       <c r="C200" s="51"/>
-      <c r="D200" s="56"/>
-      <c r="E200" s="58"/>
+      <c r="D200" s="52"/>
+      <c r="E200" s="55"/>
       <c r="F200" s="52"/>
       <c r="G200" s="56"/>
       <c r="H200" s="54"/>
-      <c r="I200" s="56"/>
+      <c r="I200" s="52"/>
       <c r="J200" s="2"/>
     </row>
-    <row r="201" spans="1:10">
+    <row r="201" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A201" s="51"/>
       <c r="C201" s="51"/>
       <c r="D201" s="52"/>
@@ -6849,51 +5839,51 @@
       <c r="I201" s="52"/>
       <c r="J201" s="2"/>
     </row>
-    <row r="202" spans="1:10">
+    <row r="202" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A202" s="51"/>
       <c r="C202" s="51"/>
-      <c r="D202" s="56"/>
-      <c r="E202" s="58"/>
-      <c r="F202" s="56"/>
+      <c r="D202" s="52"/>
+      <c r="E202" s="55"/>
+      <c r="F202" s="52"/>
       <c r="G202" s="56"/>
       <c r="H202" s="54"/>
-      <c r="I202" s="56"/>
+      <c r="I202" s="52"/>
       <c r="J202" s="2"/>
     </row>
-    <row r="203" spans="1:10">
+    <row r="203" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A203" s="51"/>
       <c r="C203" s="51"/>
       <c r="D203" s="56"/>
       <c r="E203" s="58"/>
-      <c r="F203" s="56"/>
+      <c r="F203" s="52"/>
       <c r="G203" s="56"/>
       <c r="H203" s="54"/>
       <c r="I203" s="56"/>
       <c r="J203" s="2"/>
     </row>
-    <row r="204" spans="1:10">
+    <row r="204" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A204" s="51"/>
       <c r="C204" s="51"/>
       <c r="D204" s="52"/>
-      <c r="E204" s="55"/>
+      <c r="E204" s="58"/>
       <c r="F204" s="52"/>
       <c r="G204" s="56"/>
       <c r="H204" s="54"/>
       <c r="I204" s="56"/>
       <c r="J204" s="2"/>
     </row>
-    <row r="205" spans="1:10">
+    <row r="205" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A205" s="51"/>
       <c r="C205" s="51"/>
       <c r="D205" s="52"/>
-      <c r="E205" s="55"/>
+      <c r="E205" s="58"/>
       <c r="F205" s="52"/>
       <c r="G205" s="56"/>
       <c r="H205" s="54"/>
-      <c r="I205" s="56"/>
+      <c r="I205" s="52"/>
       <c r="J205" s="2"/>
     </row>
-    <row r="206" spans="1:10">
+    <row r="206" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A206" s="51"/>
       <c r="C206" s="51"/>
       <c r="D206" s="52"/>
@@ -6901,10 +5891,10 @@
       <c r="F206" s="52"/>
       <c r="G206" s="56"/>
       <c r="H206" s="54"/>
-      <c r="I206" s="56"/>
+      <c r="I206" s="52"/>
       <c r="J206" s="2"/>
     </row>
-    <row r="207" spans="1:10">
+    <row r="207" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A207" s="51"/>
       <c r="C207" s="51"/>
       <c r="D207" s="52"/>
@@ -6915,18 +5905,18 @@
       <c r="I207" s="52"/>
       <c r="J207" s="2"/>
     </row>
-    <row r="208" spans="1:10">
+    <row r="208" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A208" s="51"/>
       <c r="C208" s="51"/>
       <c r="D208" s="52"/>
       <c r="E208" s="55"/>
       <c r="F208" s="52"/>
-      <c r="G208" s="56"/>
+      <c r="G208" s="52"/>
       <c r="H208" s="54"/>
       <c r="I208" s="52"/>
       <c r="J208" s="2"/>
     </row>
-    <row r="209" spans="1:10">
+    <row r="209" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A209" s="51"/>
       <c r="C209" s="51"/>
       <c r="D209" s="52"/>
@@ -6937,7 +5927,7 @@
       <c r="I209" s="52"/>
       <c r="J209" s="2"/>
     </row>
-    <row r="210" spans="1:10">
+    <row r="210" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A210" s="51"/>
       <c r="C210" s="51"/>
       <c r="D210" s="52"/>
@@ -6948,54 +5938,54 @@
       <c r="I210" s="52"/>
       <c r="J210" s="2"/>
     </row>
-    <row r="211" spans="1:10">
+    <row r="211" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A211" s="51"/>
       <c r="C211" s="51"/>
-      <c r="D211" s="56"/>
-      <c r="E211" s="58"/>
-      <c r="F211" s="56"/>
+      <c r="D211" s="52"/>
+      <c r="E211" s="55"/>
+      <c r="F211" s="52"/>
       <c r="G211" s="56"/>
       <c r="H211" s="54"/>
-      <c r="I211" s="56"/>
+      <c r="I211" s="52"/>
       <c r="J211" s="2"/>
     </row>
-    <row r="212" spans="1:10">
+    <row r="212" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A212" s="51"/>
       <c r="C212" s="51"/>
-      <c r="D212" s="56"/>
-      <c r="E212" s="58"/>
-      <c r="F212" s="56"/>
+      <c r="D212" s="52"/>
+      <c r="E212" s="55"/>
+      <c r="F212" s="52"/>
       <c r="G212" s="56"/>
       <c r="H212" s="54"/>
-      <c r="I212" s="56"/>
+      <c r="I212" s="52"/>
       <c r="J212" s="2"/>
     </row>
-    <row r="213" spans="1:10">
+    <row r="213" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A213" s="51"/>
       <c r="C213" s="51"/>
-      <c r="D213" s="56"/>
-      <c r="E213" s="58"/>
-      <c r="F213" s="56"/>
+      <c r="D213" s="52"/>
+      <c r="E213" s="55"/>
+      <c r="F213" s="52"/>
       <c r="G213" s="56"/>
       <c r="H213" s="54"/>
-      <c r="I213" s="56"/>
+      <c r="I213" s="52"/>
       <c r="J213" s="2"/>
     </row>
-    <row r="214" spans="1:10">
+    <row r="214" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A214" s="51"/>
       <c r="C214" s="51"/>
-      <c r="D214" s="56"/>
-      <c r="E214" s="58"/>
-      <c r="F214" s="56"/>
+      <c r="D214" s="52"/>
+      <c r="E214" s="55"/>
+      <c r="F214" s="52"/>
       <c r="G214" s="56"/>
       <c r="H214" s="54"/>
-      <c r="I214" s="56"/>
+      <c r="I214" s="52"/>
       <c r="J214" s="2"/>
     </row>
-    <row r="215" spans="1:10">
+    <row r="215" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A215" s="51"/>
       <c r="C215" s="51"/>
-      <c r="D215" s="52"/>
+      <c r="D215" s="56"/>
       <c r="E215" s="58"/>
       <c r="F215" s="52"/>
       <c r="G215" s="56"/>
@@ -7003,40 +5993,40 @@
       <c r="I215" s="52"/>
       <c r="J215" s="2"/>
     </row>
-    <row r="216" spans="1:10">
+    <row r="216" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A216" s="51"/>
       <c r="C216" s="51"/>
-      <c r="D216" s="52"/>
+      <c r="D216" s="56"/>
       <c r="E216" s="58"/>
-      <c r="F216" s="52"/>
+      <c r="F216" s="56"/>
       <c r="G216" s="56"/>
       <c r="H216" s="54"/>
       <c r="I216" s="52"/>
       <c r="J216" s="2"/>
     </row>
-    <row r="217" spans="1:10">
+    <row r="217" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A217" s="51"/>
       <c r="C217" s="51"/>
       <c r="D217" s="52"/>
-      <c r="E217" s="55"/>
+      <c r="E217" s="58"/>
       <c r="F217" s="52"/>
       <c r="G217" s="56"/>
       <c r="H217" s="54"/>
       <c r="I217" s="52"/>
       <c r="J217" s="2"/>
     </row>
-    <row r="218" spans="1:10">
+    <row r="218" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A218" s="51"/>
       <c r="C218" s="51"/>
       <c r="D218" s="52"/>
-      <c r="E218" s="55"/>
+      <c r="E218" s="58"/>
       <c r="F218" s="52"/>
       <c r="G218" s="56"/>
       <c r="H218" s="54"/>
       <c r="I218" s="52"/>
       <c r="J218" s="2"/>
     </row>
-    <row r="219" spans="1:10">
+    <row r="219" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A219" s="51"/>
       <c r="C219" s="51"/>
       <c r="D219" s="52"/>
@@ -7047,7 +6037,7 @@
       <c r="I219" s="52"/>
       <c r="J219" s="2"/>
     </row>
-    <row r="220" spans="1:10">
+    <row r="220" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A220" s="51"/>
       <c r="C220" s="51"/>
       <c r="D220" s="52"/>
@@ -7058,7 +6048,7 @@
       <c r="I220" s="52"/>
       <c r="J220" s="2"/>
     </row>
-    <row r="221" spans="1:10">
+    <row r="221" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A221" s="51"/>
       <c r="C221" s="51"/>
       <c r="D221" s="52"/>
@@ -7069,51 +6059,51 @@
       <c r="I221" s="52"/>
       <c r="J221" s="2"/>
     </row>
-    <row r="222" spans="1:10">
+    <row r="222" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A222" s="51"/>
       <c r="C222" s="51"/>
-      <c r="D222" s="52"/>
-      <c r="E222" s="55"/>
+      <c r="D222" s="56"/>
+      <c r="E222" s="58"/>
       <c r="F222" s="52"/>
       <c r="G222" s="56"/>
       <c r="H222" s="54"/>
       <c r="I222" s="52"/>
       <c r="J222" s="2"/>
     </row>
-    <row r="223" spans="1:10">
+    <row r="223" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A223" s="51"/>
       <c r="C223" s="51"/>
-      <c r="D223" s="56"/>
-      <c r="E223" s="58"/>
+      <c r="D223" s="52"/>
+      <c r="E223" s="55"/>
       <c r="F223" s="52"/>
       <c r="G223" s="56"/>
       <c r="H223" s="54"/>
-      <c r="I223" s="56"/>
+      <c r="I223" s="52"/>
       <c r="J223" s="2"/>
     </row>
-    <row r="224" spans="1:10">
+    <row r="224" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A224" s="51"/>
       <c r="C224" s="51"/>
       <c r="D224" s="52"/>
-      <c r="E224" s="58"/>
+      <c r="E224" s="55"/>
       <c r="F224" s="52"/>
       <c r="G224" s="56"/>
       <c r="H224" s="54"/>
-      <c r="I224" s="56"/>
+      <c r="I224" s="52"/>
       <c r="J224" s="2"/>
     </row>
-    <row r="225" spans="1:10">
+    <row r="225" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A225" s="51"/>
       <c r="C225" s="51"/>
       <c r="D225" s="52"/>
-      <c r="E225" s="58"/>
+      <c r="E225" s="55"/>
       <c r="F225" s="52"/>
       <c r="G225" s="56"/>
       <c r="H225" s="54"/>
       <c r="I225" s="52"/>
       <c r="J225" s="2"/>
     </row>
-    <row r="226" spans="1:10">
+    <row r="226" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A226" s="51"/>
       <c r="C226" s="51"/>
       <c r="D226" s="52"/>
@@ -7124,7 +6114,7 @@
       <c r="I226" s="52"/>
       <c r="J226" s="2"/>
     </row>
-    <row r="227" spans="1:10">
+    <row r="227" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A227" s="51"/>
       <c r="C227" s="51"/>
       <c r="D227" s="52"/>
@@ -7135,18 +6125,18 @@
       <c r="I227" s="52"/>
       <c r="J227" s="2"/>
     </row>
-    <row r="228" spans="1:10">
+    <row r="228" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A228" s="51"/>
       <c r="C228" s="51"/>
       <c r="D228" s="52"/>
       <c r="E228" s="55"/>
       <c r="F228" s="52"/>
-      <c r="G228" s="52"/>
+      <c r="G228" s="56"/>
       <c r="H228" s="54"/>
       <c r="I228" s="52"/>
       <c r="J228" s="2"/>
     </row>
-    <row r="229" spans="1:10">
+    <row r="229" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A229" s="51"/>
       <c r="C229" s="51"/>
       <c r="D229" s="52"/>
@@ -7157,7 +6147,7 @@
       <c r="I229" s="52"/>
       <c r="J229" s="2"/>
     </row>
-    <row r="230" spans="1:10">
+    <row r="230" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A230" s="51"/>
       <c r="C230" s="51"/>
       <c r="D230" s="52"/>
@@ -7168,95 +6158,95 @@
       <c r="I230" s="52"/>
       <c r="J230" s="2"/>
     </row>
-    <row r="231" spans="1:10">
+    <row r="231" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A231" s="51"/>
       <c r="C231" s="51"/>
-      <c r="D231" s="52"/>
-      <c r="E231" s="55"/>
+      <c r="D231" s="56"/>
+      <c r="E231" s="58"/>
       <c r="F231" s="52"/>
       <c r="G231" s="56"/>
       <c r="H231" s="54"/>
       <c r="I231" s="52"/>
       <c r="J231" s="2"/>
     </row>
-    <row r="232" spans="1:10">
+    <row r="232" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A232" s="51"/>
       <c r="C232" s="51"/>
       <c r="D232" s="52"/>
-      <c r="E232" s="55"/>
+      <c r="E232" s="58"/>
       <c r="F232" s="52"/>
       <c r="G232" s="56"/>
       <c r="H232" s="54"/>
       <c r="I232" s="52"/>
       <c r="J232" s="2"/>
     </row>
-    <row r="233" spans="1:10">
+    <row r="233" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A233" s="51"/>
       <c r="C233" s="51"/>
       <c r="D233" s="52"/>
-      <c r="E233" s="55"/>
+      <c r="E233" s="58"/>
       <c r="F233" s="52"/>
       <c r="G233" s="56"/>
       <c r="H233" s="54"/>
       <c r="I233" s="52"/>
       <c r="J233" s="2"/>
     </row>
-    <row r="234" spans="1:10">
+    <row r="234" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A234" s="51"/>
       <c r="C234" s="51"/>
       <c r="D234" s="52"/>
-      <c r="E234" s="55"/>
+      <c r="E234" s="58"/>
       <c r="F234" s="52"/>
       <c r="G234" s="56"/>
       <c r="H234" s="54"/>
       <c r="I234" s="52"/>
       <c r="J234" s="2"/>
     </row>
-    <row r="235" spans="1:10">
+    <row r="235" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A235" s="51"/>
       <c r="C235" s="51"/>
-      <c r="D235" s="56"/>
-      <c r="E235" s="58"/>
+      <c r="D235" s="52"/>
+      <c r="E235" s="55"/>
       <c r="F235" s="52"/>
       <c r="G235" s="56"/>
       <c r="H235" s="54"/>
       <c r="I235" s="52"/>
       <c r="J235" s="2"/>
     </row>
-    <row r="236" spans="1:10">
-      <c r="A236" s="51"/>
+    <row r="236" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A236" s="52"/>
       <c r="C236" s="51"/>
-      <c r="D236" s="56"/>
+      <c r="D236" s="52"/>
       <c r="E236" s="58"/>
-      <c r="F236" s="56"/>
+      <c r="F236" s="52"/>
       <c r="G236" s="56"/>
       <c r="H236" s="54"/>
       <c r="I236" s="52"/>
       <c r="J236" s="2"/>
     </row>
-    <row r="237" spans="1:10">
+    <row r="237" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A237" s="51"/>
       <c r="C237" s="51"/>
       <c r="D237" s="52"/>
-      <c r="E237" s="58"/>
+      <c r="E237" s="55"/>
       <c r="F237" s="52"/>
       <c r="G237" s="56"/>
       <c r="H237" s="54"/>
       <c r="I237" s="52"/>
       <c r="J237" s="2"/>
     </row>
-    <row r="238" spans="1:10">
+    <row r="238" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A238" s="51"/>
       <c r="C238" s="51"/>
       <c r="D238" s="52"/>
-      <c r="E238" s="58"/>
+      <c r="E238" s="55"/>
       <c r="F238" s="52"/>
       <c r="G238" s="56"/>
       <c r="H238" s="54"/>
       <c r="I238" s="52"/>
       <c r="J238" s="2"/>
     </row>
-    <row r="239" spans="1:10">
+    <row r="239" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A239" s="51"/>
       <c r="C239" s="51"/>
       <c r="D239" s="52"/>
@@ -7267,29 +6257,29 @@
       <c r="I239" s="52"/>
       <c r="J239" s="2"/>
     </row>
-    <row r="240" spans="1:10">
-      <c r="A240" s="51"/>
+    <row r="240" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A240" s="52"/>
       <c r="C240" s="51"/>
       <c r="D240" s="52"/>
-      <c r="E240" s="55"/>
+      <c r="E240" s="58"/>
       <c r="F240" s="52"/>
       <c r="G240" s="56"/>
       <c r="H240" s="54"/>
       <c r="I240" s="52"/>
       <c r="J240" s="2"/>
     </row>
-    <row r="241" spans="1:10">
+    <row r="241" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A241" s="51"/>
       <c r="C241" s="51"/>
       <c r="D241" s="52"/>
-      <c r="E241" s="55"/>
+      <c r="E241" s="58"/>
       <c r="F241" s="52"/>
       <c r="G241" s="56"/>
       <c r="H241" s="54"/>
       <c r="I241" s="52"/>
       <c r="J241" s="2"/>
     </row>
-    <row r="242" spans="1:10">
+    <row r="242" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A242" s="51"/>
       <c r="C242" s="51"/>
       <c r="D242" s="56"/>
@@ -7300,7 +6290,7 @@
       <c r="I242" s="52"/>
       <c r="J242" s="2"/>
     </row>
-    <row r="243" spans="1:10">
+    <row r="243" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A243" s="51"/>
       <c r="C243" s="51"/>
       <c r="D243" s="52"/>
@@ -7311,18 +6301,18 @@
       <c r="I243" s="52"/>
       <c r="J243" s="2"/>
     </row>
-    <row r="244" spans="1:10">
+    <row r="244" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A244" s="51"/>
       <c r="C244" s="51"/>
       <c r="D244" s="52"/>
-      <c r="E244" s="55"/>
+      <c r="E244" s="58"/>
       <c r="F244" s="52"/>
       <c r="G244" s="56"/>
       <c r="H244" s="54"/>
       <c r="I244" s="52"/>
       <c r="J244" s="2"/>
     </row>
-    <row r="245" spans="1:10">
+    <row r="245" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A245" s="51"/>
       <c r="C245" s="51"/>
       <c r="D245" s="52"/>
@@ -7333,51 +6323,51 @@
       <c r="I245" s="52"/>
       <c r="J245" s="2"/>
     </row>
-    <row r="246" spans="1:10">
+    <row r="246" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A246" s="51"/>
       <c r="C246" s="51"/>
-      <c r="D246" s="52"/>
-      <c r="E246" s="55"/>
-      <c r="F246" s="52"/>
+      <c r="D246" s="56"/>
+      <c r="E246" s="58"/>
+      <c r="F246" s="56"/>
       <c r="G246" s="56"/>
       <c r="H246" s="54"/>
       <c r="I246" s="52"/>
       <c r="J246" s="2"/>
     </row>
-    <row r="247" spans="1:10">
+    <row r="247" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A247" s="51"/>
       <c r="C247" s="51"/>
-      <c r="D247" s="52"/>
-      <c r="E247" s="55"/>
-      <c r="F247" s="52"/>
+      <c r="D247" s="56"/>
+      <c r="E247" s="58"/>
+      <c r="F247" s="56"/>
       <c r="G247" s="56"/>
       <c r="H247" s="54"/>
       <c r="I247" s="52"/>
       <c r="J247" s="2"/>
     </row>
-    <row r="248" spans="1:10">
+    <row r="248" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A248" s="51"/>
       <c r="C248" s="51"/>
-      <c r="D248" s="52"/>
-      <c r="E248" s="55"/>
-      <c r="F248" s="52"/>
+      <c r="D248" s="56"/>
+      <c r="E248" s="58"/>
+      <c r="F248" s="56"/>
       <c r="G248" s="56"/>
       <c r="H248" s="54"/>
       <c r="I248" s="52"/>
       <c r="J248" s="2"/>
     </row>
-    <row r="249" spans="1:10">
+    <row r="249" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A249" s="51"/>
       <c r="C249" s="51"/>
       <c r="D249" s="52"/>
-      <c r="E249" s="55"/>
+      <c r="E249" s="58"/>
       <c r="F249" s="52"/>
       <c r="G249" s="56"/>
       <c r="H249" s="54"/>
       <c r="I249" s="52"/>
       <c r="J249" s="2"/>
     </row>
-    <row r="250" spans="1:10">
+    <row r="250" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A250" s="51"/>
       <c r="C250" s="51"/>
       <c r="D250" s="52"/>
@@ -7388,73 +6378,73 @@
       <c r="I250" s="52"/>
       <c r="J250" s="2"/>
     </row>
-    <row r="251" spans="1:10">
+    <row r="251" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A251" s="51"/>
       <c r="C251" s="51"/>
-      <c r="D251" s="56"/>
-      <c r="E251" s="58"/>
+      <c r="D251" s="52"/>
+      <c r="E251" s="55"/>
       <c r="F251" s="52"/>
       <c r="G251" s="56"/>
       <c r="H251" s="54"/>
       <c r="I251" s="52"/>
       <c r="J251" s="2"/>
     </row>
-    <row r="252" spans="1:10">
+    <row r="252" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A252" s="51"/>
       <c r="C252" s="51"/>
       <c r="D252" s="52"/>
-      <c r="E252" s="58"/>
+      <c r="E252" s="55"/>
       <c r="F252" s="52"/>
       <c r="G252" s="56"/>
       <c r="H252" s="54"/>
       <c r="I252" s="52"/>
       <c r="J252" s="2"/>
     </row>
-    <row r="253" spans="1:10">
+    <row r="253" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A253" s="51"/>
       <c r="C253" s="51"/>
       <c r="D253" s="52"/>
-      <c r="E253" s="58"/>
+      <c r="E253" s="55"/>
       <c r="F253" s="52"/>
       <c r="G253" s="56"/>
       <c r="H253" s="54"/>
       <c r="I253" s="52"/>
       <c r="J253" s="2"/>
     </row>
-    <row r="254" spans="1:10">
+    <row r="254" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A254" s="51"/>
       <c r="C254" s="51"/>
-      <c r="D254" s="52"/>
+      <c r="D254" s="56"/>
       <c r="E254" s="58"/>
-      <c r="F254" s="52"/>
+      <c r="F254" s="56"/>
       <c r="G254" s="56"/>
       <c r="H254" s="54"/>
       <c r="I254" s="52"/>
       <c r="J254" s="2"/>
     </row>
-    <row r="255" spans="1:10">
+    <row r="255" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A255" s="51"/>
       <c r="C255" s="51"/>
-      <c r="D255" s="52"/>
-      <c r="E255" s="55"/>
-      <c r="F255" s="52"/>
+      <c r="D255" s="56"/>
+      <c r="E255" s="58"/>
+      <c r="F255" s="56"/>
       <c r="G255" s="56"/>
       <c r="H255" s="54"/>
       <c r="I255" s="52"/>
       <c r="J255" s="2"/>
     </row>
-    <row r="256" spans="1:10">
-      <c r="A256" s="52"/>
+    <row r="256" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A256" s="51"/>
       <c r="C256" s="51"/>
       <c r="D256" s="52"/>
-      <c r="E256" s="58"/>
+      <c r="E256" s="55"/>
       <c r="F256" s="52"/>
       <c r="G256" s="56"/>
       <c r="H256" s="54"/>
       <c r="I256" s="52"/>
       <c r="J256" s="2"/>
     </row>
-    <row r="257" spans="1:10">
+    <row r="257" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A257" s="51"/>
       <c r="C257" s="51"/>
       <c r="D257" s="52"/>
@@ -7465,7 +6455,7 @@
       <c r="I257" s="52"/>
       <c r="J257" s="2"/>
     </row>
-    <row r="258" spans="1:10">
+    <row r="258" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A258" s="51"/>
       <c r="C258" s="51"/>
       <c r="D258" s="52"/>
@@ -7476,7 +6466,7 @@
       <c r="I258" s="52"/>
       <c r="J258" s="2"/>
     </row>
-    <row r="259" spans="1:10">
+    <row r="259" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A259" s="51"/>
       <c r="C259" s="51"/>
       <c r="D259" s="52"/>
@@ -7487,32 +6477,32 @@
       <c r="I259" s="52"/>
       <c r="J259" s="2"/>
     </row>
-    <row r="260" spans="1:10">
-      <c r="A260" s="52"/>
+    <row r="260" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A260" s="51"/>
       <c r="C260" s="51"/>
       <c r="D260" s="52"/>
-      <c r="E260" s="58"/>
+      <c r="E260" s="55"/>
       <c r="F260" s="52"/>
       <c r="G260" s="56"/>
       <c r="H260" s="54"/>
       <c r="I260" s="52"/>
       <c r="J260" s="2"/>
     </row>
-    <row r="261" spans="1:10">
+    <row r="261" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A261" s="51"/>
       <c r="C261" s="51"/>
       <c r="D261" s="52"/>
-      <c r="E261" s="58"/>
+      <c r="E261" s="55"/>
       <c r="F261" s="52"/>
       <c r="G261" s="56"/>
       <c r="H261" s="54"/>
       <c r="I261" s="52"/>
       <c r="J261" s="2"/>
     </row>
-    <row r="262" spans="1:10">
+    <row r="262" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A262" s="51"/>
       <c r="C262" s="51"/>
-      <c r="D262" s="56"/>
+      <c r="D262" s="52"/>
       <c r="E262" s="58"/>
       <c r="F262" s="52"/>
       <c r="G262" s="56"/>
@@ -7520,7 +6510,7 @@
       <c r="I262" s="52"/>
       <c r="J262" s="2"/>
     </row>
-    <row r="263" spans="1:10">
+    <row r="263" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A263" s="51"/>
       <c r="C263" s="51"/>
       <c r="D263" s="52"/>
@@ -7531,18 +6521,22 @@
       <c r="I263" s="52"/>
       <c r="J263" s="2"/>
     </row>
-    <row r="264" spans="1:10">
+    <row r="264" spans="1:14" ht="15" x14ac:dyDescent="0.2">
       <c r="A264" s="51"/>
+      <c r="B264" s="2"/>
       <c r="C264" s="51"/>
-      <c r="D264" s="52"/>
-      <c r="E264" s="58"/>
-      <c r="F264" s="52"/>
-      <c r="G264" s="56"/>
+      <c r="D264" s="59"/>
+      <c r="E264" s="60"/>
+      <c r="F264" s="59"/>
+      <c r="G264" s="52"/>
       <c r="H264" s="54"/>
-      <c r="I264" s="52"/>
+      <c r="I264" s="61"/>
       <c r="J264" s="2"/>
-    </row>
-    <row r="265" spans="1:10">
+      <c r="K264" s="2"/>
+      <c r="L264" s="2"/>
+      <c r="N264" s="2"/>
+    </row>
+    <row r="265" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A265" s="51"/>
       <c r="C265" s="51"/>
       <c r="D265" s="52"/>
@@ -7553,51 +6547,51 @@
       <c r="I265" s="52"/>
       <c r="J265" s="2"/>
     </row>
-    <row r="266" spans="1:10">
+    <row r="266" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A266" s="51"/>
       <c r="C266" s="51"/>
-      <c r="D266" s="56"/>
-      <c r="E266" s="58"/>
-      <c r="F266" s="56"/>
+      <c r="D266" s="52"/>
+      <c r="E266" s="55"/>
+      <c r="F266" s="52"/>
       <c r="G266" s="56"/>
       <c r="H266" s="54"/>
       <c r="I266" s="52"/>
       <c r="J266" s="2"/>
     </row>
-    <row r="267" spans="1:10">
+    <row r="267" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A267" s="51"/>
       <c r="C267" s="51"/>
-      <c r="D267" s="56"/>
-      <c r="E267" s="58"/>
-      <c r="F267" s="56"/>
+      <c r="D267" s="52"/>
+      <c r="E267" s="55"/>
+      <c r="F267" s="52"/>
       <c r="G267" s="56"/>
       <c r="H267" s="54"/>
       <c r="I267" s="52"/>
       <c r="J267" s="2"/>
     </row>
-    <row r="268" spans="1:10">
+    <row r="268" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A268" s="51"/>
       <c r="C268" s="51"/>
-      <c r="D268" s="56"/>
-      <c r="E268" s="58"/>
-      <c r="F268" s="56"/>
+      <c r="D268" s="52"/>
+      <c r="E268" s="55"/>
+      <c r="F268" s="52"/>
       <c r="G268" s="56"/>
       <c r="H268" s="54"/>
       <c r="I268" s="52"/>
       <c r="J268" s="2"/>
     </row>
-    <row r="269" spans="1:10">
+    <row r="269" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A269" s="51"/>
       <c r="C269" s="51"/>
-      <c r="D269" s="52"/>
+      <c r="D269" s="56"/>
       <c r="E269" s="58"/>
       <c r="F269" s="52"/>
       <c r="G269" s="56"/>
       <c r="H269" s="54"/>
-      <c r="I269" s="52"/>
+      <c r="I269" s="56"/>
       <c r="J269" s="2"/>
     </row>
-    <row r="270" spans="1:10">
+    <row r="270" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A270" s="51"/>
       <c r="C270" s="51"/>
       <c r="D270" s="52"/>
@@ -7608,7 +6602,7 @@
       <c r="I270" s="52"/>
       <c r="J270" s="2"/>
     </row>
-    <row r="271" spans="1:10">
+    <row r="271" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A271" s="51"/>
       <c r="C271" s="51"/>
       <c r="D271" s="52"/>
@@ -7619,7 +6613,7 @@
       <c r="I271" s="52"/>
       <c r="J271" s="2"/>
     </row>
-    <row r="272" spans="1:10">
+    <row r="272" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A272" s="51"/>
       <c r="C272" s="51"/>
       <c r="D272" s="52"/>
@@ -7630,7 +6624,7 @@
       <c r="I272" s="52"/>
       <c r="J272" s="2"/>
     </row>
-    <row r="273" spans="1:14">
+    <row r="273" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A273" s="51"/>
       <c r="C273" s="51"/>
       <c r="D273" s="52"/>
@@ -7641,29 +6635,29 @@
       <c r="I273" s="52"/>
       <c r="J273" s="2"/>
     </row>
-    <row r="274" spans="1:14">
+    <row r="274" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A274" s="51"/>
       <c r="C274" s="51"/>
-      <c r="D274" s="56"/>
-      <c r="E274" s="58"/>
-      <c r="F274" s="56"/>
+      <c r="D274" s="52"/>
+      <c r="E274" s="55"/>
+      <c r="F274" s="52"/>
       <c r="G274" s="56"/>
       <c r="H274" s="54"/>
       <c r="I274" s="52"/>
       <c r="J274" s="2"/>
     </row>
-    <row r="275" spans="1:14">
+    <row r="275" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A275" s="51"/>
       <c r="C275" s="51"/>
-      <c r="D275" s="56"/>
-      <c r="E275" s="58"/>
-      <c r="F275" s="56"/>
+      <c r="D275" s="52"/>
+      <c r="E275" s="55"/>
+      <c r="F275" s="52"/>
       <c r="G275" s="56"/>
       <c r="H275" s="54"/>
       <c r="I275" s="52"/>
       <c r="J275" s="2"/>
     </row>
-    <row r="276" spans="1:14">
+    <row r="276" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A276" s="51"/>
       <c r="C276" s="51"/>
       <c r="D276" s="52"/>
@@ -7674,7 +6668,7 @@
       <c r="I276" s="52"/>
       <c r="J276" s="2"/>
     </row>
-    <row r="277" spans="1:14">
+    <row r="277" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A277" s="51"/>
       <c r="C277" s="51"/>
       <c r="D277" s="52"/>
@@ -7685,7 +6679,7 @@
       <c r="I277" s="52"/>
       <c r="J277" s="2"/>
     </row>
-    <row r="278" spans="1:14">
+    <row r="278" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A278" s="51"/>
       <c r="C278" s="51"/>
       <c r="D278" s="52"/>
@@ -7696,7 +6690,7 @@
       <c r="I278" s="52"/>
       <c r="J278" s="2"/>
     </row>
-    <row r="279" spans="1:14">
+    <row r="279" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A279" s="51"/>
       <c r="C279" s="51"/>
       <c r="D279" s="52"/>
@@ -7707,7 +6701,7 @@
       <c r="I279" s="52"/>
       <c r="J279" s="2"/>
     </row>
-    <row r="280" spans="1:14">
+    <row r="280" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A280" s="51"/>
       <c r="C280" s="51"/>
       <c r="D280" s="52"/>
@@ -7718,7 +6712,7 @@
       <c r="I280" s="52"/>
       <c r="J280" s="2"/>
     </row>
-    <row r="281" spans="1:14">
+    <row r="281" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A281" s="51"/>
       <c r="C281" s="51"/>
       <c r="D281" s="52"/>
@@ -7729,18 +6723,18 @@
       <c r="I281" s="52"/>
       <c r="J281" s="2"/>
     </row>
-    <row r="282" spans="1:14">
+    <row r="282" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A282" s="51"/>
       <c r="C282" s="51"/>
       <c r="D282" s="52"/>
-      <c r="E282" s="58"/>
+      <c r="E282" s="55"/>
       <c r="F282" s="52"/>
       <c r="G282" s="56"/>
       <c r="H282" s="54"/>
       <c r="I282" s="52"/>
       <c r="J282" s="2"/>
     </row>
-    <row r="283" spans="1:14">
+    <row r="283" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A283" s="51"/>
       <c r="C283" s="51"/>
       <c r="D283" s="52"/>
@@ -7751,22 +6745,18 @@
       <c r="I283" s="52"/>
       <c r="J283" s="2"/>
     </row>
-    <row r="284" spans="1:14" ht="15">
+    <row r="284" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A284" s="51"/>
-      <c r="B284" s="2"/>
       <c r="C284" s="51"/>
-      <c r="D284" s="59"/>
-      <c r="E284" s="60"/>
-      <c r="F284" s="59"/>
-      <c r="G284" s="52"/>
+      <c r="D284" s="52"/>
+      <c r="E284" s="55"/>
+      <c r="F284" s="52"/>
+      <c r="G284" s="56"/>
       <c r="H284" s="54"/>
-      <c r="I284" s="61"/>
+      <c r="I284" s="52"/>
       <c r="J284" s="2"/>
-      <c r="K284" s="2"/>
-      <c r="L284" s="2"/>
-      <c r="N284" s="2"/>
-    </row>
-    <row r="285" spans="1:14">
+    </row>
+    <row r="285" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A285" s="51"/>
       <c r="C285" s="51"/>
       <c r="D285" s="52"/>
@@ -7777,7 +6767,7 @@
       <c r="I285" s="52"/>
       <c r="J285" s="2"/>
     </row>
-    <row r="286" spans="1:14">
+    <row r="286" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A286" s="51"/>
       <c r="C286" s="51"/>
       <c r="D286" s="52"/>
@@ -7788,7 +6778,7 @@
       <c r="I286" s="52"/>
       <c r="J286" s="2"/>
     </row>
-    <row r="287" spans="1:14">
+    <row r="287" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A287" s="51"/>
       <c r="C287" s="51"/>
       <c r="D287" s="52"/>
@@ -7799,7 +6789,7 @@
       <c r="I287" s="52"/>
       <c r="J287" s="2"/>
     </row>
-    <row r="288" spans="1:14">
+    <row r="288" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A288" s="51"/>
       <c r="C288" s="51"/>
       <c r="D288" s="52"/>
@@ -7810,18 +6800,18 @@
       <c r="I288" s="52"/>
       <c r="J288" s="2"/>
     </row>
-    <row r="289" spans="1:10">
+    <row r="289" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A289" s="51"/>
       <c r="C289" s="51"/>
-      <c r="D289" s="56"/>
-      <c r="E289" s="58"/>
+      <c r="D289" s="52"/>
+      <c r="E289" s="55"/>
       <c r="F289" s="52"/>
       <c r="G289" s="56"/>
       <c r="H289" s="54"/>
-      <c r="I289" s="56"/>
+      <c r="I289" s="52"/>
       <c r="J289" s="2"/>
     </row>
-    <row r="290" spans="1:10">
+    <row r="290" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A290" s="51"/>
       <c r="C290" s="51"/>
       <c r="D290" s="52"/>
@@ -7832,7 +6822,7 @@
       <c r="I290" s="52"/>
       <c r="J290" s="2"/>
     </row>
-    <row r="291" spans="1:10">
+    <row r="291" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A291" s="51"/>
       <c r="C291" s="51"/>
       <c r="D291" s="52"/>
@@ -7840,10 +6830,10 @@
       <c r="F291" s="52"/>
       <c r="G291" s="56"/>
       <c r="H291" s="54"/>
-      <c r="I291" s="52"/>
+      <c r="I291" s="56"/>
       <c r="J291" s="2"/>
     </row>
-    <row r="292" spans="1:10">
+    <row r="292" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A292" s="51"/>
       <c r="C292" s="51"/>
       <c r="D292" s="52"/>
@@ -7854,10 +6844,10 @@
       <c r="I292" s="52"/>
       <c r="J292" s="2"/>
     </row>
-    <row r="293" spans="1:10">
+    <row r="293" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A293" s="51"/>
       <c r="C293" s="51"/>
-      <c r="D293" s="52"/>
+      <c r="D293" s="51"/>
       <c r="E293" s="55"/>
       <c r="F293" s="52"/>
       <c r="G293" s="56"/>
@@ -7865,7 +6855,7 @@
       <c r="I293" s="52"/>
       <c r="J293" s="2"/>
     </row>
-    <row r="294" spans="1:10">
+    <row r="294" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A294" s="51"/>
       <c r="C294" s="51"/>
       <c r="D294" s="52"/>
@@ -7876,7 +6866,7 @@
       <c r="I294" s="52"/>
       <c r="J294" s="2"/>
     </row>
-    <row r="295" spans="1:10">
+    <row r="295" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A295" s="51"/>
       <c r="C295" s="51"/>
       <c r="D295" s="52"/>
@@ -7887,7 +6877,7 @@
       <c r="I295" s="52"/>
       <c r="J295" s="2"/>
     </row>
-    <row r="296" spans="1:10">
+    <row r="296" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A296" s="51"/>
       <c r="C296" s="51"/>
       <c r="D296" s="52"/>
@@ -7898,7 +6888,7 @@
       <c r="I296" s="52"/>
       <c r="J296" s="2"/>
     </row>
-    <row r="297" spans="1:10">
+    <row r="297" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A297" s="51"/>
       <c r="C297" s="51"/>
       <c r="D297" s="52"/>
@@ -7909,7 +6899,7 @@
       <c r="I297" s="52"/>
       <c r="J297" s="2"/>
     </row>
-    <row r="298" spans="1:10">
+    <row r="298" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A298" s="51"/>
       <c r="C298" s="51"/>
       <c r="D298" s="52"/>
@@ -7920,7 +6910,7 @@
       <c r="I298" s="52"/>
       <c r="J298" s="2"/>
     </row>
-    <row r="299" spans="1:10">
+    <row r="299" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A299" s="51"/>
       <c r="C299" s="51"/>
       <c r="D299" s="52"/>
@@ -7931,29 +6921,29 @@
       <c r="I299" s="52"/>
       <c r="J299" s="2"/>
     </row>
-    <row r="300" spans="1:10">
+    <row r="300" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A300" s="51"/>
       <c r="C300" s="51"/>
-      <c r="D300" s="52"/>
-      <c r="E300" s="55"/>
+      <c r="D300" s="56"/>
+      <c r="E300" s="58"/>
       <c r="F300" s="52"/>
       <c r="G300" s="56"/>
       <c r="H300" s="54"/>
-      <c r="I300" s="52"/>
+      <c r="I300" s="56"/>
       <c r="J300" s="2"/>
     </row>
-    <row r="301" spans="1:10">
+    <row r="301" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A301" s="51"/>
       <c r="C301" s="51"/>
       <c r="D301" s="52"/>
-      <c r="E301" s="55"/>
-      <c r="F301" s="52"/>
+      <c r="E301" s="58"/>
+      <c r="F301" s="56"/>
       <c r="G301" s="56"/>
       <c r="H301" s="54"/>
-      <c r="I301" s="52"/>
+      <c r="I301" s="56"/>
       <c r="J301" s="2"/>
     </row>
-    <row r="302" spans="1:10">
+    <row r="302" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A302" s="51"/>
       <c r="C302" s="51"/>
       <c r="D302" s="52"/>
@@ -7964,7 +6954,7 @@
       <c r="I302" s="52"/>
       <c r="J302" s="2"/>
     </row>
-    <row r="303" spans="1:10">
+    <row r="303" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A303" s="51"/>
       <c r="C303" s="51"/>
       <c r="D303" s="52"/>
@@ -7975,7 +6965,7 @@
       <c r="I303" s="52"/>
       <c r="J303" s="2"/>
     </row>
-    <row r="304" spans="1:10">
+    <row r="304" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A304" s="51"/>
       <c r="C304" s="51"/>
       <c r="D304" s="52"/>
@@ -7986,7 +6976,7 @@
       <c r="I304" s="52"/>
       <c r="J304" s="2"/>
     </row>
-    <row r="305" spans="1:10">
+    <row r="305" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A305" s="51"/>
       <c r="C305" s="51"/>
       <c r="D305" s="52"/>
@@ -7997,7 +6987,7 @@
       <c r="I305" s="52"/>
       <c r="J305" s="2"/>
     </row>
-    <row r="306" spans="1:10">
+    <row r="306" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A306" s="51"/>
       <c r="C306" s="51"/>
       <c r="D306" s="52"/>
@@ -8008,7 +6998,7 @@
       <c r="I306" s="52"/>
       <c r="J306" s="2"/>
     </row>
-    <row r="307" spans="1:10">
+    <row r="307" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A307" s="51"/>
       <c r="C307" s="51"/>
       <c r="D307" s="52"/>
@@ -8019,7 +7009,7 @@
       <c r="I307" s="52"/>
       <c r="J307" s="2"/>
     </row>
-    <row r="308" spans="1:10">
+    <row r="308" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A308" s="51"/>
       <c r="C308" s="51"/>
       <c r="D308" s="52"/>
@@ -8030,7 +7020,7 @@
       <c r="I308" s="52"/>
       <c r="J308" s="2"/>
     </row>
-    <row r="309" spans="1:10">
+    <row r="309" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A309" s="51"/>
       <c r="C309" s="51"/>
       <c r="D309" s="52"/>
@@ -8041,238 +7031,238 @@
       <c r="I309" s="52"/>
       <c r="J309" s="2"/>
     </row>
-    <row r="310" spans="1:10">
+    <row r="310" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A310" s="51"/>
       <c r="C310" s="51"/>
       <c r="D310" s="52"/>
-      <c r="E310" s="55"/>
+      <c r="E310" s="52"/>
       <c r="F310" s="52"/>
-      <c r="G310" s="56"/>
+      <c r="G310" s="52"/>
       <c r="H310" s="54"/>
       <c r="I310" s="52"/>
       <c r="J310" s="2"/>
     </row>
-    <row r="311" spans="1:10">
+    <row r="311" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A311" s="51"/>
       <c r="C311" s="51"/>
       <c r="D311" s="52"/>
-      <c r="E311" s="55"/>
+      <c r="E311" s="52"/>
       <c r="F311" s="52"/>
-      <c r="G311" s="56"/>
+      <c r="G311" s="52"/>
       <c r="H311" s="54"/>
-      <c r="I311" s="56"/>
+      <c r="I311" s="52"/>
       <c r="J311" s="2"/>
     </row>
-    <row r="312" spans="1:10">
+    <row r="312" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A312" s="51"/>
       <c r="C312" s="51"/>
       <c r="D312" s="52"/>
-      <c r="E312" s="55"/>
+      <c r="E312" s="52"/>
       <c r="F312" s="52"/>
-      <c r="G312" s="56"/>
+      <c r="G312" s="52"/>
       <c r="H312" s="54"/>
       <c r="I312" s="52"/>
       <c r="J312" s="2"/>
     </row>
-    <row r="313" spans="1:10">
+    <row r="313" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A313" s="51"/>
       <c r="C313" s="51"/>
-      <c r="D313" s="51"/>
-      <c r="E313" s="55"/>
+      <c r="D313" s="52"/>
+      <c r="E313" s="52"/>
       <c r="F313" s="52"/>
-      <c r="G313" s="56"/>
+      <c r="G313" s="52"/>
       <c r="H313" s="54"/>
       <c r="I313" s="52"/>
       <c r="J313" s="2"/>
     </row>
-    <row r="314" spans="1:10">
+    <row r="314" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A314" s="51"/>
       <c r="C314" s="51"/>
       <c r="D314" s="52"/>
-      <c r="E314" s="55"/>
+      <c r="E314" s="52"/>
       <c r="F314" s="52"/>
-      <c r="G314" s="56"/>
+      <c r="G314" s="52"/>
       <c r="H314" s="54"/>
       <c r="I314" s="52"/>
       <c r="J314" s="2"/>
     </row>
-    <row r="315" spans="1:10">
+    <row r="315" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A315" s="51"/>
       <c r="C315" s="51"/>
       <c r="D315" s="52"/>
-      <c r="E315" s="55"/>
+      <c r="E315" s="52"/>
       <c r="F315" s="52"/>
-      <c r="G315" s="56"/>
+      <c r="G315" s="52"/>
       <c r="H315" s="54"/>
       <c r="I315" s="52"/>
       <c r="J315" s="2"/>
     </row>
-    <row r="316" spans="1:10">
+    <row r="316" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A316" s="51"/>
       <c r="C316" s="51"/>
       <c r="D316" s="52"/>
-      <c r="E316" s="55"/>
+      <c r="E316" s="52"/>
       <c r="F316" s="52"/>
-      <c r="G316" s="56"/>
+      <c r="G316" s="52"/>
       <c r="H316" s="54"/>
       <c r="I316" s="52"/>
       <c r="J316" s="2"/>
     </row>
-    <row r="317" spans="1:10">
+    <row r="317" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A317" s="51"/>
       <c r="C317" s="51"/>
-      <c r="D317" s="52"/>
-      <c r="E317" s="55"/>
-      <c r="F317" s="52"/>
+      <c r="D317" s="56"/>
+      <c r="E317" s="56"/>
+      <c r="F317" s="56"/>
       <c r="G317" s="56"/>
       <c r="H317" s="54"/>
-      <c r="I317" s="52"/>
+      <c r="I317" s="56"/>
       <c r="J317" s="2"/>
     </row>
-    <row r="318" spans="1:10">
+    <row r="318" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A318" s="51"/>
       <c r="C318" s="51"/>
       <c r="D318" s="52"/>
-      <c r="E318" s="55"/>
+      <c r="E318" s="52"/>
       <c r="F318" s="52"/>
-      <c r="G318" s="56"/>
+      <c r="G318" s="52"/>
       <c r="H318" s="54"/>
       <c r="I318" s="52"/>
       <c r="J318" s="2"/>
     </row>
-    <row r="319" spans="1:10">
+    <row r="319" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A319" s="51"/>
       <c r="C319" s="51"/>
       <c r="D319" s="52"/>
-      <c r="E319" s="55"/>
+      <c r="E319" s="52"/>
       <c r="F319" s="52"/>
-      <c r="G319" s="56"/>
+      <c r="G319" s="52"/>
       <c r="H319" s="54"/>
       <c r="I319" s="52"/>
       <c r="J319" s="2"/>
     </row>
-    <row r="320" spans="1:10">
+    <row r="320" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A320" s="51"/>
       <c r="C320" s="51"/>
-      <c r="D320" s="56"/>
-      <c r="E320" s="58"/>
+      <c r="D320" s="52"/>
+      <c r="E320" s="52"/>
       <c r="F320" s="52"/>
-      <c r="G320" s="56"/>
+      <c r="G320" s="52"/>
       <c r="H320" s="54"/>
-      <c r="I320" s="56"/>
+      <c r="I320" s="52"/>
       <c r="J320" s="2"/>
     </row>
-    <row r="321" spans="1:10">
+    <row r="321" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A321" s="51"/>
       <c r="C321" s="51"/>
       <c r="D321" s="52"/>
-      <c r="E321" s="58"/>
-      <c r="F321" s="56"/>
-      <c r="G321" s="56"/>
+      <c r="E321" s="52"/>
+      <c r="F321" s="52"/>
+      <c r="G321" s="52"/>
       <c r="H321" s="54"/>
-      <c r="I321" s="56"/>
+      <c r="I321" s="52"/>
       <c r="J321" s="2"/>
     </row>
-    <row r="322" spans="1:10">
+    <row r="322" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A322" s="51"/>
       <c r="C322" s="51"/>
       <c r="D322" s="52"/>
-      <c r="E322" s="55"/>
+      <c r="E322" s="52"/>
       <c r="F322" s="52"/>
-      <c r="G322" s="56"/>
+      <c r="G322" s="52"/>
       <c r="H322" s="54"/>
       <c r="I322" s="52"/>
       <c r="J322" s="2"/>
     </row>
-    <row r="323" spans="1:10">
+    <row r="323" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A323" s="51"/>
       <c r="C323" s="51"/>
       <c r="D323" s="52"/>
-      <c r="E323" s="55"/>
+      <c r="E323" s="52"/>
       <c r="F323" s="52"/>
-      <c r="G323" s="56"/>
+      <c r="G323" s="52"/>
       <c r="H323" s="54"/>
       <c r="I323" s="52"/>
       <c r="J323" s="2"/>
     </row>
-    <row r="324" spans="1:10">
+    <row r="324" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A324" s="51"/>
       <c r="C324" s="51"/>
       <c r="D324" s="52"/>
-      <c r="E324" s="55"/>
+      <c r="E324" s="52"/>
       <c r="F324" s="52"/>
-      <c r="G324" s="56"/>
+      <c r="G324" s="52"/>
       <c r="H324" s="54"/>
       <c r="I324" s="52"/>
       <c r="J324" s="2"/>
     </row>
-    <row r="325" spans="1:10">
+    <row r="325" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A325" s="51"/>
       <c r="C325" s="51"/>
       <c r="D325" s="52"/>
-      <c r="E325" s="55"/>
+      <c r="E325" s="52"/>
       <c r="F325" s="52"/>
-      <c r="G325" s="56"/>
+      <c r="G325" s="52"/>
       <c r="H325" s="54"/>
       <c r="I325" s="52"/>
       <c r="J325" s="2"/>
     </row>
-    <row r="326" spans="1:10">
+    <row r="326" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A326" s="51"/>
       <c r="C326" s="51"/>
       <c r="D326" s="52"/>
-      <c r="E326" s="55"/>
+      <c r="E326" s="52"/>
       <c r="F326" s="52"/>
-      <c r="G326" s="56"/>
+      <c r="G326" s="52"/>
       <c r="H326" s="54"/>
       <c r="I326" s="52"/>
       <c r="J326" s="2"/>
     </row>
-    <row r="327" spans="1:10">
+    <row r="327" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A327" s="51"/>
       <c r="C327" s="51"/>
       <c r="D327" s="52"/>
-      <c r="E327" s="55"/>
+      <c r="E327" s="52"/>
       <c r="F327" s="52"/>
-      <c r="G327" s="56"/>
+      <c r="G327" s="52"/>
       <c r="H327" s="54"/>
       <c r="I327" s="52"/>
       <c r="J327" s="2"/>
     </row>
-    <row r="328" spans="1:10">
+    <row r="328" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A328" s="51"/>
       <c r="C328" s="51"/>
       <c r="D328" s="52"/>
-      <c r="E328" s="55"/>
+      <c r="E328" s="52"/>
       <c r="F328" s="52"/>
-      <c r="G328" s="56"/>
+      <c r="G328" s="52"/>
       <c r="H328" s="54"/>
       <c r="I328" s="52"/>
       <c r="J328" s="2"/>
     </row>
-    <row r="329" spans="1:10">
+    <row r="329" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A329" s="51"/>
       <c r="C329" s="51"/>
       <c r="D329" s="52"/>
-      <c r="E329" s="55"/>
+      <c r="E329" s="52"/>
       <c r="F329" s="52"/>
-      <c r="G329" s="56"/>
+      <c r="G329" s="52"/>
       <c r="H329" s="54"/>
       <c r="I329" s="52"/>
       <c r="J329" s="2"/>
     </row>
-    <row r="330" spans="1:10">
+    <row r="330" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A330" s="51"/>
       <c r="C330" s="51"/>
-      <c r="D330" s="52"/>
-      <c r="E330" s="52"/>
-      <c r="F330" s="52"/>
-      <c r="G330" s="52"/>
+      <c r="D330" s="56"/>
+      <c r="E330" s="56"/>
+      <c r="F330" s="56"/>
+      <c r="G330" s="56"/>
       <c r="H330" s="54"/>
-      <c r="I330" s="52"/>
+      <c r="I330" s="56"/>
       <c r="J330" s="2"/>
     </row>
-    <row r="331" spans="1:10">
+    <row r="331" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A331" s="51"/>
       <c r="C331" s="51"/>
       <c r="D331" s="52"/>
@@ -8283,7 +7273,7 @@
       <c r="I331" s="52"/>
       <c r="J331" s="2"/>
     </row>
-    <row r="332" spans="1:10">
+    <row r="332" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A332" s="51"/>
       <c r="C332" s="51"/>
       <c r="D332" s="52"/>
@@ -8294,29 +7284,29 @@
       <c r="I332" s="52"/>
       <c r="J332" s="2"/>
     </row>
-    <row r="333" spans="1:10">
+    <row r="333" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A333" s="51"/>
       <c r="C333" s="51"/>
       <c r="D333" s="52"/>
       <c r="E333" s="52"/>
-      <c r="F333" s="52"/>
-      <c r="G333" s="52"/>
+      <c r="F333" s="62"/>
+      <c r="G333" s="62"/>
       <c r="H333" s="54"/>
       <c r="I333" s="52"/>
       <c r="J333" s="2"/>
     </row>
-    <row r="334" spans="1:10">
+    <row r="334" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A334" s="51"/>
       <c r="C334" s="51"/>
-      <c r="D334" s="52"/>
-      <c r="E334" s="52"/>
-      <c r="F334" s="52"/>
-      <c r="G334" s="52"/>
+      <c r="D334" s="56"/>
+      <c r="E334" s="56"/>
+      <c r="F334" s="56"/>
+      <c r="G334" s="56"/>
       <c r="H334" s="54"/>
-      <c r="I334" s="52"/>
+      <c r="I334" s="56"/>
       <c r="J334" s="2"/>
     </row>
-    <row r="335" spans="1:10">
+    <row r="335" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A335" s="51"/>
       <c r="C335" s="51"/>
       <c r="D335" s="52"/>
@@ -8327,29 +7317,29 @@
       <c r="I335" s="52"/>
       <c r="J335" s="2"/>
     </row>
-    <row r="336" spans="1:10">
+    <row r="336" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A336" s="51"/>
       <c r="C336" s="51"/>
       <c r="D336" s="52"/>
-      <c r="E336" s="52"/>
+      <c r="E336" s="63"/>
       <c r="F336" s="52"/>
       <c r="G336" s="52"/>
       <c r="H336" s="54"/>
       <c r="I336" s="52"/>
       <c r="J336" s="2"/>
     </row>
-    <row r="337" spans="1:10">
+    <row r="337" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A337" s="51"/>
       <c r="C337" s="51"/>
-      <c r="D337" s="56"/>
-      <c r="E337" s="56"/>
-      <c r="F337" s="56"/>
-      <c r="G337" s="56"/>
+      <c r="D337" s="62"/>
+      <c r="E337" s="52"/>
+      <c r="F337" s="62"/>
+      <c r="G337" s="62"/>
       <c r="H337" s="54"/>
-      <c r="I337" s="56"/>
+      <c r="I337" s="52"/>
       <c r="J337" s="2"/>
     </row>
-    <row r="338" spans="1:10">
+    <row r="338" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A338" s="51"/>
       <c r="C338" s="51"/>
       <c r="D338" s="52"/>
@@ -8360,7 +7350,7 @@
       <c r="I338" s="52"/>
       <c r="J338" s="2"/>
     </row>
-    <row r="339" spans="1:10">
+    <row r="339" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A339" s="51"/>
       <c r="C339" s="51"/>
       <c r="D339" s="52"/>
@@ -8371,7 +7361,7 @@
       <c r="I339" s="52"/>
       <c r="J339" s="2"/>
     </row>
-    <row r="340" spans="1:10">
+    <row r="340" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A340" s="51"/>
       <c r="C340" s="51"/>
       <c r="D340" s="52"/>
@@ -8382,7 +7372,7 @@
       <c r="I340" s="52"/>
       <c r="J340" s="2"/>
     </row>
-    <row r="341" spans="1:10">
+    <row r="341" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A341" s="51"/>
       <c r="C341" s="51"/>
       <c r="D341" s="52"/>
@@ -8393,8 +7383,8 @@
       <c r="I341" s="52"/>
       <c r="J341" s="2"/>
     </row>
-    <row r="342" spans="1:10">
-      <c r="A342" s="51"/>
+    <row r="342" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A342" s="52"/>
       <c r="C342" s="51"/>
       <c r="D342" s="52"/>
       <c r="E342" s="52"/>
@@ -8404,8 +7394,8 @@
       <c r="I342" s="52"/>
       <c r="J342" s="2"/>
     </row>
-    <row r="343" spans="1:10">
-      <c r="A343" s="51"/>
+    <row r="343" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A343" s="52"/>
       <c r="C343" s="51"/>
       <c r="D343" s="52"/>
       <c r="E343" s="52"/>
@@ -8415,8 +7405,8 @@
       <c r="I343" s="52"/>
       <c r="J343" s="2"/>
     </row>
-    <row r="344" spans="1:10">
-      <c r="A344" s="51"/>
+    <row r="344" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A344" s="52"/>
       <c r="C344" s="51"/>
       <c r="D344" s="52"/>
       <c r="E344" s="52"/>
@@ -8426,7 +7416,7 @@
       <c r="I344" s="52"/>
       <c r="J344" s="2"/>
     </row>
-    <row r="345" spans="1:10">
+    <row r="345" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A345" s="51"/>
       <c r="C345" s="51"/>
       <c r="D345" s="52"/>
@@ -8437,18 +7427,18 @@
       <c r="I345" s="52"/>
       <c r="J345" s="2"/>
     </row>
-    <row r="346" spans="1:10">
+    <row r="346" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A346" s="51"/>
       <c r="C346" s="51"/>
-      <c r="D346" s="52"/>
+      <c r="D346" s="62"/>
       <c r="E346" s="52"/>
       <c r="F346" s="52"/>
       <c r="G346" s="52"/>
       <c r="H346" s="54"/>
-      <c r="I346" s="52"/>
+      <c r="I346" s="64"/>
       <c r="J346" s="2"/>
     </row>
-    <row r="347" spans="1:10">
+    <row r="347" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A347" s="51"/>
       <c r="C347" s="51"/>
       <c r="D347" s="52"/>
@@ -8459,7 +7449,7 @@
       <c r="I347" s="52"/>
       <c r="J347" s="2"/>
     </row>
-    <row r="348" spans="1:10">
+    <row r="348" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A348" s="51"/>
       <c r="C348" s="51"/>
       <c r="D348" s="52"/>
@@ -8470,7 +7460,7 @@
       <c r="I348" s="52"/>
       <c r="J348" s="2"/>
     </row>
-    <row r="349" spans="1:10">
+    <row r="349" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A349" s="51"/>
       <c r="C349" s="51"/>
       <c r="D349" s="52"/>
@@ -8481,18 +7471,18 @@
       <c r="I349" s="52"/>
       <c r="J349" s="2"/>
     </row>
-    <row r="350" spans="1:10">
+    <row r="350" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A350" s="51"/>
       <c r="C350" s="51"/>
-      <c r="D350" s="56"/>
-      <c r="E350" s="56"/>
-      <c r="F350" s="56"/>
-      <c r="G350" s="56"/>
+      <c r="D350" s="52"/>
+      <c r="E350" s="52"/>
+      <c r="F350" s="52"/>
+      <c r="G350" s="52"/>
       <c r="H350" s="54"/>
-      <c r="I350" s="56"/>
+      <c r="I350" s="52"/>
       <c r="J350" s="2"/>
     </row>
-    <row r="351" spans="1:10">
+    <row r="351" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A351" s="51"/>
       <c r="C351" s="51"/>
       <c r="D351" s="52"/>
@@ -8503,40 +7493,40 @@
       <c r="I351" s="52"/>
       <c r="J351" s="2"/>
     </row>
-    <row r="352" spans="1:10">
+    <row r="352" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A352" s="51"/>
       <c r="C352" s="51"/>
-      <c r="D352" s="52"/>
-      <c r="E352" s="52"/>
-      <c r="F352" s="52"/>
-      <c r="G352" s="52"/>
+      <c r="D352" s="56"/>
+      <c r="E352" s="56"/>
+      <c r="F352" s="56"/>
+      <c r="G352" s="56"/>
       <c r="H352" s="54"/>
-      <c r="I352" s="52"/>
+      <c r="I352" s="56"/>
       <c r="J352" s="2"/>
     </row>
-    <row r="353" spans="1:10">
+    <row r="353" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A353" s="51"/>
       <c r="C353" s="51"/>
-      <c r="D353" s="52"/>
-      <c r="E353" s="52"/>
-      <c r="F353" s="62"/>
-      <c r="G353" s="62"/>
+      <c r="D353" s="56"/>
+      <c r="E353" s="56"/>
+      <c r="F353" s="56"/>
+      <c r="G353" s="56"/>
       <c r="H353" s="54"/>
-      <c r="I353" s="52"/>
+      <c r="I353" s="56"/>
       <c r="J353" s="2"/>
     </row>
-    <row r="354" spans="1:10">
+    <row r="354" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A354" s="51"/>
       <c r="C354" s="51"/>
-      <c r="D354" s="56"/>
-      <c r="E354" s="56"/>
-      <c r="F354" s="56"/>
-      <c r="G354" s="56"/>
+      <c r="D354" s="52"/>
+      <c r="E354" s="52"/>
+      <c r="F354" s="52"/>
+      <c r="G354" s="52"/>
       <c r="H354" s="54"/>
-      <c r="I354" s="56"/>
+      <c r="I354" s="52"/>
       <c r="J354" s="2"/>
     </row>
-    <row r="355" spans="1:10">
+    <row r="355" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A355" s="51"/>
       <c r="C355" s="51"/>
       <c r="D355" s="52"/>
@@ -8544,32 +7534,32 @@
       <c r="F355" s="52"/>
       <c r="G355" s="52"/>
       <c r="H355" s="54"/>
-      <c r="I355" s="52"/>
+      <c r="I355" s="56"/>
       <c r="J355" s="2"/>
     </row>
-    <row r="356" spans="1:10">
+    <row r="356" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A356" s="51"/>
       <c r="C356" s="51"/>
-      <c r="D356" s="52"/>
-      <c r="E356" s="63"/>
-      <c r="F356" s="52"/>
-      <c r="G356" s="52"/>
+      <c r="D356" s="56"/>
+      <c r="E356" s="56"/>
+      <c r="F356" s="56"/>
+      <c r="G356" s="56"/>
       <c r="H356" s="54"/>
-      <c r="I356" s="52"/>
+      <c r="I356" s="56"/>
       <c r="J356" s="2"/>
     </row>
-    <row r="357" spans="1:10">
+    <row r="357" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A357" s="51"/>
       <c r="C357" s="51"/>
-      <c r="D357" s="62"/>
+      <c r="D357" s="52"/>
       <c r="E357" s="52"/>
-      <c r="F357" s="62"/>
-      <c r="G357" s="62"/>
+      <c r="F357" s="52"/>
+      <c r="G357" s="52"/>
       <c r="H357" s="54"/>
       <c r="I357" s="52"/>
       <c r="J357" s="2"/>
     </row>
-    <row r="358" spans="1:10">
+    <row r="358" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A358" s="51"/>
       <c r="C358" s="51"/>
       <c r="D358" s="52"/>
@@ -8580,7 +7570,7 @@
       <c r="I358" s="52"/>
       <c r="J358" s="2"/>
     </row>
-    <row r="359" spans="1:10">
+    <row r="359" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A359" s="51"/>
       <c r="C359" s="51"/>
       <c r="D359" s="52"/>
@@ -8591,7 +7581,7 @@
       <c r="I359" s="52"/>
       <c r="J359" s="2"/>
     </row>
-    <row r="360" spans="1:10">
+    <row r="360" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A360" s="51"/>
       <c r="C360" s="51"/>
       <c r="D360" s="52"/>
@@ -8602,7 +7592,7 @@
       <c r="I360" s="52"/>
       <c r="J360" s="2"/>
     </row>
-    <row r="361" spans="1:10">
+    <row r="361" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A361" s="51"/>
       <c r="C361" s="51"/>
       <c r="D361" s="52"/>
@@ -8613,8 +7603,8 @@
       <c r="I361" s="52"/>
       <c r="J361" s="2"/>
     </row>
-    <row r="362" spans="1:10">
-      <c r="A362" s="52"/>
+    <row r="362" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A362" s="51"/>
       <c r="C362" s="51"/>
       <c r="D362" s="52"/>
       <c r="E362" s="52"/>
@@ -8624,8 +7614,8 @@
       <c r="I362" s="52"/>
       <c r="J362" s="2"/>
     </row>
-    <row r="363" spans="1:10">
-      <c r="A363" s="52"/>
+    <row r="363" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A363" s="51"/>
       <c r="C363" s="51"/>
       <c r="D363" s="52"/>
       <c r="E363" s="52"/>
@@ -8635,8 +7625,8 @@
       <c r="I363" s="52"/>
       <c r="J363" s="2"/>
     </row>
-    <row r="364" spans="1:10">
-      <c r="A364" s="52"/>
+    <row r="364" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A364" s="51"/>
       <c r="C364" s="51"/>
       <c r="D364" s="52"/>
       <c r="E364" s="52"/>
@@ -8646,7 +7636,7 @@
       <c r="I364" s="52"/>
       <c r="J364" s="2"/>
     </row>
-    <row r="365" spans="1:10">
+    <row r="365" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A365" s="51"/>
       <c r="C365" s="51"/>
       <c r="D365" s="52"/>
@@ -8657,18 +7647,18 @@
       <c r="I365" s="52"/>
       <c r="J365" s="2"/>
     </row>
-    <row r="366" spans="1:10">
+    <row r="366" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A366" s="51"/>
       <c r="C366" s="51"/>
-      <c r="D366" s="62"/>
+      <c r="D366" s="52"/>
       <c r="E366" s="52"/>
       <c r="F366" s="52"/>
       <c r="G366" s="52"/>
       <c r="H366" s="54"/>
-      <c r="I366" s="64"/>
+      <c r="I366" s="52"/>
       <c r="J366" s="2"/>
     </row>
-    <row r="367" spans="1:10">
+    <row r="367" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A367" s="51"/>
       <c r="C367" s="51"/>
       <c r="D367" s="52"/>
@@ -8679,7 +7669,7 @@
       <c r="I367" s="52"/>
       <c r="J367" s="2"/>
     </row>
-    <row r="368" spans="1:10">
+    <row r="368" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A368" s="51"/>
       <c r="C368" s="51"/>
       <c r="D368" s="52"/>
@@ -8690,7 +7680,7 @@
       <c r="I368" s="52"/>
       <c r="J368" s="2"/>
     </row>
-    <row r="369" spans="1:10">
+    <row r="369" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A369" s="51"/>
       <c r="C369" s="51"/>
       <c r="D369" s="52"/>
@@ -8701,7 +7691,7 @@
       <c r="I369" s="52"/>
       <c r="J369" s="2"/>
     </row>
-    <row r="370" spans="1:10">
+    <row r="370" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A370" s="51"/>
       <c r="C370" s="51"/>
       <c r="D370" s="52"/>
@@ -8712,7 +7702,7 @@
       <c r="I370" s="52"/>
       <c r="J370" s="2"/>
     </row>
-    <row r="371" spans="1:10">
+    <row r="371" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A371" s="51"/>
       <c r="C371" s="51"/>
       <c r="D371" s="52"/>
@@ -8723,29 +7713,29 @@
       <c r="I371" s="52"/>
       <c r="J371" s="2"/>
     </row>
-    <row r="372" spans="1:10">
+    <row r="372" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A372" s="51"/>
       <c r="C372" s="51"/>
-      <c r="D372" s="56"/>
-      <c r="E372" s="56"/>
-      <c r="F372" s="56"/>
-      <c r="G372" s="56"/>
+      <c r="D372" s="52"/>
+      <c r="E372" s="52"/>
+      <c r="F372" s="52"/>
+      <c r="G372" s="52"/>
       <c r="H372" s="54"/>
-      <c r="I372" s="56"/>
+      <c r="I372" s="52"/>
       <c r="J372" s="2"/>
     </row>
-    <row r="373" spans="1:10">
+    <row r="373" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A373" s="51"/>
       <c r="C373" s="51"/>
-      <c r="D373" s="56"/>
-      <c r="E373" s="56"/>
-      <c r="F373" s="56"/>
-      <c r="G373" s="56"/>
+      <c r="D373" s="52"/>
+      <c r="E373" s="52"/>
+      <c r="F373" s="52"/>
+      <c r="G373" s="52"/>
       <c r="H373" s="54"/>
-      <c r="I373" s="56"/>
+      <c r="I373" s="52"/>
       <c r="J373" s="2"/>
     </row>
-    <row r="374" spans="1:10">
+    <row r="374" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A374" s="51"/>
       <c r="C374" s="51"/>
       <c r="D374" s="52"/>
@@ -8756,7 +7746,7 @@
       <c r="I374" s="52"/>
       <c r="J374" s="2"/>
     </row>
-    <row r="375" spans="1:10">
+    <row r="375" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A375" s="51"/>
       <c r="C375" s="51"/>
       <c r="D375" s="52"/>
@@ -8764,21 +7754,21 @@
       <c r="F375" s="52"/>
       <c r="G375" s="52"/>
       <c r="H375" s="54"/>
-      <c r="I375" s="56"/>
+      <c r="I375" s="52"/>
       <c r="J375" s="2"/>
     </row>
-    <row r="376" spans="1:10">
+    <row r="376" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A376" s="51"/>
       <c r="C376" s="51"/>
-      <c r="D376" s="56"/>
-      <c r="E376" s="56"/>
-      <c r="F376" s="56"/>
-      <c r="G376" s="56"/>
+      <c r="D376" s="52"/>
+      <c r="E376" s="52"/>
+      <c r="F376" s="52"/>
+      <c r="G376" s="52"/>
       <c r="H376" s="54"/>
-      <c r="I376" s="56"/>
+      <c r="I376" s="52"/>
       <c r="J376" s="2"/>
     </row>
-    <row r="377" spans="1:10">
+    <row r="377" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A377" s="51"/>
       <c r="C377" s="51"/>
       <c r="D377" s="52"/>
@@ -8789,18 +7779,18 @@
       <c r="I377" s="52"/>
       <c r="J377" s="2"/>
     </row>
-    <row r="378" spans="1:10">
+    <row r="378" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A378" s="51"/>
       <c r="C378" s="51"/>
       <c r="D378" s="52"/>
       <c r="E378" s="52"/>
-      <c r="F378" s="52"/>
-      <c r="G378" s="52"/>
+      <c r="F378" s="56"/>
+      <c r="G378" s="56"/>
       <c r="H378" s="54"/>
       <c r="I378" s="52"/>
       <c r="J378" s="2"/>
     </row>
-    <row r="379" spans="1:10">
+    <row r="379" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A379" s="51"/>
       <c r="C379" s="51"/>
       <c r="D379" s="52"/>
@@ -8811,7 +7801,7 @@
       <c r="I379" s="52"/>
       <c r="J379" s="2"/>
     </row>
-    <row r="380" spans="1:10">
+    <row r="380" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A380" s="51"/>
       <c r="C380" s="51"/>
       <c r="D380" s="52"/>
@@ -8822,7 +7812,7 @@
       <c r="I380" s="52"/>
       <c r="J380" s="2"/>
     </row>
-    <row r="381" spans="1:10">
+    <row r="381" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A381" s="51"/>
       <c r="C381" s="51"/>
       <c r="D381" s="52"/>
@@ -8833,10 +7823,10 @@
       <c r="I381" s="52"/>
       <c r="J381" s="2"/>
     </row>
-    <row r="382" spans="1:10">
+    <row r="382" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A382" s="51"/>
       <c r="C382" s="51"/>
-      <c r="D382" s="52"/>
+      <c r="D382" s="62"/>
       <c r="E382" s="52"/>
       <c r="F382" s="52"/>
       <c r="G382" s="52"/>
@@ -8844,227 +7834,207 @@
       <c r="I382" s="52"/>
       <c r="J382" s="2"/>
     </row>
-    <row r="383" spans="1:10">
+    <row r="383" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A383" s="51"/>
       <c r="C383" s="51"/>
       <c r="D383" s="52"/>
       <c r="E383" s="52"/>
       <c r="F383" s="52"/>
       <c r="G383" s="52"/>
-      <c r="H383" s="54"/>
       <c r="I383" s="52"/>
       <c r="J383" s="2"/>
     </row>
-    <row r="384" spans="1:10">
+    <row r="384" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A384" s="51"/>
       <c r="C384" s="51"/>
       <c r="D384" s="52"/>
       <c r="E384" s="52"/>
       <c r="F384" s="52"/>
       <c r="G384" s="52"/>
-      <c r="H384" s="54"/>
       <c r="I384" s="52"/>
       <c r="J384" s="2"/>
     </row>
-    <row r="385" spans="1:10">
+    <row r="385" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A385" s="51"/>
       <c r="C385" s="51"/>
       <c r="D385" s="52"/>
       <c r="E385" s="52"/>
       <c r="F385" s="52"/>
       <c r="G385" s="52"/>
-      <c r="H385" s="54"/>
       <c r="I385" s="52"/>
       <c r="J385" s="2"/>
     </row>
-    <row r="386" spans="1:10">
+    <row r="386" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A386" s="51"/>
       <c r="C386" s="51"/>
       <c r="D386" s="52"/>
       <c r="E386" s="52"/>
       <c r="F386" s="52"/>
       <c r="G386" s="52"/>
-      <c r="H386" s="54"/>
       <c r="I386" s="52"/>
       <c r="J386" s="2"/>
     </row>
-    <row r="387" spans="1:10">
+    <row r="387" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A387" s="51"/>
       <c r="C387" s="51"/>
       <c r="D387" s="52"/>
       <c r="E387" s="52"/>
       <c r="F387" s="52"/>
       <c r="G387" s="52"/>
-      <c r="H387" s="54"/>
       <c r="I387" s="52"/>
       <c r="J387" s="2"/>
     </row>
-    <row r="388" spans="1:10">
+    <row r="388" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A388" s="51"/>
       <c r="C388" s="51"/>
       <c r="D388" s="52"/>
       <c r="E388" s="52"/>
       <c r="F388" s="52"/>
       <c r="G388" s="52"/>
-      <c r="H388" s="54"/>
       <c r="I388" s="52"/>
       <c r="J388" s="2"/>
     </row>
-    <row r="389" spans="1:10">
+    <row r="389" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A389" s="51"/>
       <c r="C389" s="51"/>
       <c r="D389" s="52"/>
       <c r="E389" s="52"/>
       <c r="F389" s="52"/>
       <c r="G389" s="52"/>
-      <c r="H389" s="54"/>
       <c r="I389" s="52"/>
       <c r="J389" s="2"/>
     </row>
-    <row r="390" spans="1:10">
+    <row r="390" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A390" s="51"/>
       <c r="C390" s="51"/>
       <c r="D390" s="52"/>
       <c r="E390" s="52"/>
       <c r="F390" s="52"/>
       <c r="G390" s="52"/>
-      <c r="H390" s="54"/>
       <c r="I390" s="52"/>
       <c r="J390" s="2"/>
     </row>
-    <row r="391" spans="1:10">
+    <row r="391" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A391" s="51"/>
       <c r="C391" s="51"/>
       <c r="D391" s="52"/>
       <c r="E391" s="52"/>
       <c r="F391" s="52"/>
       <c r="G391" s="52"/>
-      <c r="H391" s="54"/>
       <c r="I391" s="52"/>
       <c r="J391" s="2"/>
     </row>
-    <row r="392" spans="1:10">
+    <row r="392" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A392" s="51"/>
       <c r="C392" s="51"/>
       <c r="D392" s="52"/>
       <c r="E392" s="52"/>
       <c r="F392" s="52"/>
       <c r="G392" s="52"/>
-      <c r="H392" s="54"/>
       <c r="I392" s="52"/>
       <c r="J392" s="2"/>
     </row>
-    <row r="393" spans="1:10">
+    <row r="393" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A393" s="51"/>
       <c r="C393" s="51"/>
       <c r="D393" s="52"/>
       <c r="E393" s="52"/>
       <c r="F393" s="52"/>
       <c r="G393" s="52"/>
-      <c r="H393" s="54"/>
       <c r="I393" s="52"/>
       <c r="J393" s="2"/>
     </row>
-    <row r="394" spans="1:10">
+    <row r="394" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A394" s="51"/>
       <c r="C394" s="51"/>
       <c r="D394" s="52"/>
       <c r="E394" s="52"/>
       <c r="F394" s="52"/>
       <c r="G394" s="52"/>
-      <c r="H394" s="54"/>
       <c r="I394" s="52"/>
       <c r="J394" s="2"/>
     </row>
-    <row r="395" spans="1:10">
+    <row r="395" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A395" s="51"/>
       <c r="C395" s="51"/>
       <c r="D395" s="52"/>
       <c r="E395" s="52"/>
       <c r="F395" s="52"/>
       <c r="G395" s="52"/>
-      <c r="H395" s="54"/>
       <c r="I395" s="52"/>
       <c r="J395" s="2"/>
     </row>
-    <row r="396" spans="1:10">
+    <row r="396" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A396" s="51"/>
       <c r="C396" s="51"/>
       <c r="D396" s="52"/>
       <c r="E396" s="52"/>
       <c r="F396" s="52"/>
       <c r="G396" s="52"/>
-      <c r="H396" s="54"/>
       <c r="I396" s="52"/>
       <c r="J396" s="2"/>
     </row>
-    <row r="397" spans="1:10">
+    <row r="397" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A397" s="51"/>
       <c r="C397" s="51"/>
       <c r="D397" s="52"/>
       <c r="E397" s="52"/>
       <c r="F397" s="52"/>
       <c r="G397" s="52"/>
-      <c r="H397" s="54"/>
       <c r="I397" s="52"/>
       <c r="J397" s="2"/>
     </row>
-    <row r="398" spans="1:10">
+    <row r="398" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A398" s="51"/>
       <c r="C398" s="51"/>
       <c r="D398" s="52"/>
       <c r="E398" s="52"/>
-      <c r="F398" s="56"/>
-      <c r="G398" s="56"/>
-      <c r="H398" s="54"/>
+      <c r="F398" s="52"/>
+      <c r="G398" s="52"/>
       <c r="I398" s="52"/>
       <c r="J398" s="2"/>
     </row>
-    <row r="399" spans="1:10">
+    <row r="399" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A399" s="51"/>
       <c r="C399" s="51"/>
       <c r="D399" s="52"/>
       <c r="E399" s="52"/>
-      <c r="F399" s="52"/>
-      <c r="G399" s="52"/>
-      <c r="H399" s="54"/>
+      <c r="F399" s="51"/>
+      <c r="G399" s="51"/>
       <c r="I399" s="52"/>
       <c r="J399" s="2"/>
     </row>
-    <row r="400" spans="1:10">
+    <row r="400" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A400" s="51"/>
       <c r="C400" s="51"/>
       <c r="D400" s="52"/>
       <c r="E400" s="52"/>
       <c r="F400" s="52"/>
       <c r="G400" s="52"/>
-      <c r="H400" s="54"/>
       <c r="I400" s="52"/>
       <c r="J400" s="2"/>
     </row>
-    <row r="401" spans="1:10">
+    <row r="401" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A401" s="51"/>
       <c r="C401" s="51"/>
       <c r="D401" s="52"/>
       <c r="E401" s="52"/>
       <c r="F401" s="52"/>
       <c r="G401" s="52"/>
-      <c r="H401" s="54"/>
       <c r="I401" s="52"/>
       <c r="J401" s="2"/>
     </row>
-    <row r="402" spans="1:10">
+    <row r="402" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A402" s="51"/>
       <c r="C402" s="51"/>
-      <c r="D402" s="62"/>
+      <c r="D402" s="52"/>
       <c r="E402" s="52"/>
       <c r="F402" s="52"/>
       <c r="G402" s="52"/>
-      <c r="H402" s="54"/>
       <c r="I402" s="52"/>
       <c r="J402" s="2"/>
     </row>
-    <row r="403" spans="1:10">
+    <row r="403" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A403" s="51"/>
       <c r="C403" s="51"/>
       <c r="D403" s="52"/>
@@ -9074,7 +8044,7 @@
       <c r="I403" s="52"/>
       <c r="J403" s="2"/>
     </row>
-    <row r="404" spans="1:10">
+    <row r="404" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A404" s="51"/>
       <c r="C404" s="51"/>
       <c r="D404" s="52"/>
@@ -9084,7 +8054,7 @@
       <c r="I404" s="52"/>
       <c r="J404" s="2"/>
     </row>
-    <row r="405" spans="1:10">
+    <row r="405" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A405" s="51"/>
       <c r="C405" s="51"/>
       <c r="D405" s="52"/>
@@ -9094,242 +8064,42 @@
       <c r="I405" s="52"/>
       <c r="J405" s="2"/>
     </row>
-    <row r="406" spans="1:10">
-      <c r="A406" s="51"/>
-      <c r="C406" s="51"/>
-      <c r="D406" s="52"/>
-      <c r="E406" s="52"/>
-      <c r="F406" s="52"/>
-      <c r="G406" s="52"/>
-      <c r="I406" s="52"/>
-      <c r="J406" s="2"/>
-    </row>
-    <row r="407" spans="1:10">
-      <c r="A407" s="51"/>
-      <c r="C407" s="51"/>
-      <c r="D407" s="52"/>
-      <c r="E407" s="52"/>
-      <c r="F407" s="52"/>
-      <c r="G407" s="52"/>
-      <c r="I407" s="52"/>
-      <c r="J407" s="2"/>
-    </row>
-    <row r="408" spans="1:10">
-      <c r="A408" s="51"/>
-      <c r="C408" s="51"/>
-      <c r="D408" s="52"/>
-      <c r="E408" s="52"/>
-      <c r="F408" s="52"/>
-      <c r="G408" s="52"/>
-      <c r="I408" s="52"/>
-      <c r="J408" s="2"/>
-    </row>
-    <row r="409" spans="1:10">
-      <c r="A409" s="51"/>
-      <c r="C409" s="51"/>
-      <c r="D409" s="52"/>
-      <c r="E409" s="52"/>
-      <c r="F409" s="52"/>
-      <c r="G409" s="52"/>
-      <c r="I409" s="52"/>
-      <c r="J409" s="2"/>
-    </row>
-    <row r="410" spans="1:10">
-      <c r="A410" s="51"/>
-      <c r="C410" s="51"/>
-      <c r="D410" s="52"/>
-      <c r="E410" s="52"/>
-      <c r="F410" s="52"/>
-      <c r="G410" s="52"/>
-      <c r="I410" s="52"/>
-      <c r="J410" s="2"/>
-    </row>
-    <row r="411" spans="1:10">
-      <c r="A411" s="51"/>
-      <c r="C411" s="51"/>
-      <c r="D411" s="52"/>
-      <c r="E411" s="52"/>
-      <c r="F411" s="52"/>
-      <c r="G411" s="52"/>
-      <c r="I411" s="52"/>
-      <c r="J411" s="2"/>
-    </row>
-    <row r="412" spans="1:10">
-      <c r="A412" s="51"/>
-      <c r="C412" s="51"/>
-      <c r="D412" s="52"/>
-      <c r="E412" s="52"/>
-      <c r="F412" s="52"/>
-      <c r="G412" s="52"/>
-      <c r="I412" s="52"/>
-      <c r="J412" s="2"/>
-    </row>
-    <row r="413" spans="1:10">
-      <c r="A413" s="51"/>
-      <c r="C413" s="51"/>
-      <c r="D413" s="52"/>
-      <c r="E413" s="52"/>
-      <c r="F413" s="52"/>
-      <c r="G413" s="52"/>
-      <c r="I413" s="52"/>
-      <c r="J413" s="2"/>
-    </row>
-    <row r="414" spans="1:10">
-      <c r="A414" s="51"/>
-      <c r="C414" s="51"/>
-      <c r="D414" s="52"/>
-      <c r="E414" s="52"/>
-      <c r="F414" s="52"/>
-      <c r="G414" s="52"/>
-      <c r="I414" s="52"/>
-      <c r="J414" s="2"/>
-    </row>
-    <row r="415" spans="1:10">
-      <c r="A415" s="51"/>
-      <c r="C415" s="51"/>
-      <c r="D415" s="52"/>
-      <c r="E415" s="52"/>
-      <c r="F415" s="52"/>
-      <c r="G415" s="52"/>
-      <c r="I415" s="52"/>
-      <c r="J415" s="2"/>
-    </row>
-    <row r="416" spans="1:10">
-      <c r="A416" s="51"/>
-      <c r="C416" s="51"/>
-      <c r="D416" s="52"/>
-      <c r="E416" s="52"/>
-      <c r="F416" s="52"/>
-      <c r="G416" s="52"/>
-      <c r="I416" s="52"/>
-      <c r="J416" s="2"/>
-    </row>
-    <row r="417" spans="1:10">
-      <c r="A417" s="51"/>
-      <c r="C417" s="51"/>
-      <c r="D417" s="52"/>
-      <c r="E417" s="52"/>
-      <c r="F417" s="52"/>
-      <c r="G417" s="52"/>
-      <c r="I417" s="52"/>
-      <c r="J417" s="2"/>
-    </row>
-    <row r="418" spans="1:10">
-      <c r="A418" s="51"/>
-      <c r="C418" s="51"/>
-      <c r="D418" s="52"/>
-      <c r="E418" s="52"/>
-      <c r="F418" s="52"/>
-      <c r="G418" s="52"/>
-      <c r="I418" s="52"/>
-      <c r="J418" s="2"/>
-    </row>
-    <row r="419" spans="1:10">
-      <c r="A419" s="51"/>
-      <c r="C419" s="51"/>
-      <c r="D419" s="52"/>
-      <c r="E419" s="52"/>
-      <c r="F419" s="51"/>
-      <c r="G419" s="51"/>
-      <c r="I419" s="52"/>
-      <c r="J419" s="2"/>
-    </row>
-    <row r="420" spans="1:10">
-      <c r="A420" s="51"/>
-      <c r="C420" s="51"/>
-      <c r="D420" s="52"/>
-      <c r="E420" s="52"/>
-      <c r="F420" s="52"/>
-      <c r="G420" s="52"/>
-      <c r="I420" s="52"/>
-      <c r="J420" s="2"/>
-    </row>
-    <row r="421" spans="1:10">
-      <c r="A421" s="51"/>
-      <c r="C421" s="51"/>
-      <c r="D421" s="52"/>
-      <c r="E421" s="52"/>
-      <c r="F421" s="52"/>
-      <c r="G421" s="52"/>
-      <c r="I421" s="52"/>
-      <c r="J421" s="2"/>
-    </row>
-    <row r="422" spans="1:10">
-      <c r="A422" s="51"/>
-      <c r="C422" s="51"/>
-      <c r="D422" s="52"/>
-      <c r="E422" s="52"/>
-      <c r="F422" s="52"/>
-      <c r="G422" s="52"/>
-      <c r="I422" s="52"/>
-      <c r="J422" s="2"/>
-    </row>
-    <row r="423" spans="1:10">
-      <c r="A423" s="51"/>
-      <c r="C423" s="51"/>
-      <c r="D423" s="52"/>
-      <c r="E423" s="52"/>
-      <c r="F423" s="52"/>
-      <c r="G423" s="52"/>
-      <c r="I423" s="52"/>
-      <c r="J423" s="2"/>
-    </row>
-    <row r="424" spans="1:10">
-      <c r="A424" s="51"/>
-      <c r="C424" s="51"/>
-      <c r="D424" s="52"/>
-      <c r="E424" s="52"/>
-      <c r="F424" s="52"/>
-      <c r="G424" s="52"/>
-      <c r="I424" s="52"/>
-      <c r="J424" s="2"/>
-    </row>
-    <row r="425" spans="1:10">
-      <c r="A425" s="51"/>
-      <c r="C425" s="51"/>
-      <c r="D425" s="52"/>
-      <c r="E425" s="52"/>
-      <c r="F425" s="52"/>
-      <c r="G425" s="52"/>
-      <c r="I425" s="52"/>
-      <c r="J425" s="2"/>
-    </row>
-    <row r="426" spans="1:10"/>
-    <row r="427" spans="1:10"/>
-    <row r="428" spans="1:10"/>
-    <row r="429" spans="1:10"/>
-    <row r="430" spans="1:10"/>
-    <row r="431" spans="1:10"/>
-    <row r="432" spans="1:10"/>
-    <row r="433"/>
-    <row r="434"/>
-    <row r="435"/>
-    <row r="438"/>
-    <row r="439"/>
-    <row r="440"/>
-    <row r="441"/>
-    <row r="442"/>
-    <row r="443"/>
-    <row r="444"/>
-    <row r="445"/>
-    <row r="446"/>
-    <row r="447"/>
-    <row r="448"/>
-    <row r="449"/>
-    <row r="450"/>
-    <row r="454"/>
-    <row r="455"/>
-    <row r="456"/>
-    <row r="457"/>
-    <row r="458"/>
-    <row r="459"/>
-    <row r="460"/>
+    <row r="406" spans="1:10" x14ac:dyDescent="0.2"/>
+    <row r="407" spans="1:10" x14ac:dyDescent="0.2"/>
+    <row r="408" spans="1:10" x14ac:dyDescent="0.2"/>
+    <row r="409" spans="1:10" x14ac:dyDescent="0.2"/>
+    <row r="410" spans="1:10" x14ac:dyDescent="0.2"/>
+    <row r="411" spans="1:10" x14ac:dyDescent="0.2"/>
+    <row r="412" spans="1:10" x14ac:dyDescent="0.2"/>
+    <row r="413" spans="1:10" x14ac:dyDescent="0.2"/>
+    <row r="414" spans="1:10" x14ac:dyDescent="0.2"/>
+    <row r="415" spans="1:10" x14ac:dyDescent="0.2"/>
+    <row r="418" x14ac:dyDescent="0.2"/>
+    <row r="419" x14ac:dyDescent="0.2"/>
+    <row r="420" x14ac:dyDescent="0.2"/>
+    <row r="421" x14ac:dyDescent="0.2"/>
+    <row r="422" x14ac:dyDescent="0.2"/>
+    <row r="423" x14ac:dyDescent="0.2"/>
+    <row r="424" x14ac:dyDescent="0.2"/>
+    <row r="425" x14ac:dyDescent="0.2"/>
+    <row r="426" x14ac:dyDescent="0.2"/>
+    <row r="427" x14ac:dyDescent="0.2"/>
+    <row r="428" x14ac:dyDescent="0.2"/>
+    <row r="429" x14ac:dyDescent="0.2"/>
+    <row r="430" x14ac:dyDescent="0.2"/>
+    <row r="434" x14ac:dyDescent="0.2"/>
+    <row r="435" x14ac:dyDescent="0.2"/>
+    <row r="436" x14ac:dyDescent="0.2"/>
+    <row r="437" x14ac:dyDescent="0.2"/>
+    <row r="438" x14ac:dyDescent="0.2"/>
+    <row r="439" x14ac:dyDescent="0.2"/>
+    <row r="440" x14ac:dyDescent="0.2"/>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="C24:C30 C229:C280 C282:C315 C51:C118 C320:C425 C43:C46 C12:C13 C37:C41" xr:uid="{F4198816-401D-4203-B3CE-5E76A7EEB9A7}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="C209:C260 C262:C295 C31:C98 C300:C405 C23:C26 C12:C15 C20:C21" xr:uid="{F4198816-401D-4203-B3CE-5E76A7EEB9A7}">
       <formula1>"Critical Error,Error,Warning"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C281 C119:C228 C284 C316:C319 C31:C36 C28:C29 C14:C23 C42 C45:C50 C2:C11" xr:uid="{4C235110-81B0-4ABB-9DC7-6EC79F361847}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C261 C99:C208 C264 C296:C299 C22 C25:C30 C2:C11 C14 C16:C19" xr:uid="{4C235110-81B0-4ABB-9DC7-6EC79F361847}">
       <formula1>"Critical Error, Error, Warning"</formula1>
     </dataValidation>
   </dataValidations>
@@ -9345,7 +8115,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7268D69-AC57-4E25-815A-64C0B549121C}">
   <dimension ref="A1:H8"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="3" width="13.5703125" customWidth="1"/>
     <col min="4" max="4" width="25" style="40" customWidth="1"/>
@@ -9355,39 +8125,39 @@
     <col min="8" max="8" width="72.140625" style="42" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="36" t="s">
-        <v>325</v>
+        <v>214</v>
       </c>
       <c r="B1" s="36" t="s">
-        <v>326</v>
+        <v>215</v>
       </c>
       <c r="C1" s="36" t="s">
-        <v>327</v>
+        <v>216</v>
       </c>
       <c r="D1" s="39" t="s">
-        <v>328</v>
+        <v>217</v>
       </c>
       <c r="E1" s="36" t="s">
-        <v>329</v>
+        <v>218</v>
       </c>
       <c r="F1" s="36"/>
       <c r="G1" s="36" t="s">
-        <v>330</v>
+        <v>219</v>
       </c>
       <c r="H1" s="41" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>332</v>
+        <v>221</v>
       </c>
       <c r="B2" s="37">
         <v>45580</v>
       </c>
       <c r="C2" s="37" t="s">
-        <v>333</v>
+        <v>222</v>
       </c>
       <c r="D2" s="40">
         <v>1001</v>
@@ -9396,21 +8166,21 @@
         <v>1029</v>
       </c>
       <c r="G2" s="38" t="s">
-        <v>334</v>
+        <v>223</v>
       </c>
       <c r="H2" s="42" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="28.9">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>332</v>
+        <v>221</v>
       </c>
       <c r="B3" s="37">
         <v>45580</v>
       </c>
       <c r="C3" t="s">
-        <v>336</v>
+        <v>225</v>
       </c>
       <c r="D3" s="40">
         <v>2001</v>
@@ -9419,18 +8189,18 @@
         <v>2013</v>
       </c>
       <c r="H3" s="42" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="43.15">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>332</v>
+        <v>221</v>
       </c>
       <c r="B4" s="37">
         <v>45580</v>
       </c>
       <c r="C4" t="s">
-        <v>338</v>
+        <v>227</v>
       </c>
       <c r="D4" s="40">
         <v>3001</v>
@@ -9439,38 +8209,38 @@
         <v>3019</v>
       </c>
       <c r="H4" s="42" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="28.9">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>332</v>
+        <v>221</v>
       </c>
       <c r="B5" s="37">
         <v>45580</v>
       </c>
       <c r="C5" t="s">
-        <v>340</v>
+        <v>229</v>
       </c>
       <c r="D5" s="40" t="s">
-        <v>137</v>
+        <v>92</v>
       </c>
       <c r="E5" t="s">
-        <v>137</v>
+        <v>92</v>
       </c>
       <c r="H5" s="43" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>332</v>
+        <v>221</v>
       </c>
       <c r="B6" s="37">
         <v>45580</v>
       </c>
       <c r="C6" t="s">
-        <v>342</v>
+        <v>231</v>
       </c>
       <c r="D6" s="40">
         <v>5001</v>
@@ -9479,15 +8249,15 @@
         <v>5010</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>332</v>
+        <v>221</v>
       </c>
       <c r="B7" s="37">
         <v>45580</v>
       </c>
       <c r="C7" t="s">
-        <v>343</v>
+        <v>232</v>
       </c>
       <c r="D7" s="40">
         <v>9001</v>
@@ -9496,21 +8266,21 @@
         <v>9005</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>344</v>
+        <v>233</v>
       </c>
       <c r="B8" s="37">
         <v>45614</v>
       </c>
       <c r="C8" t="s">
-        <v>345</v>
+        <v>234</v>
       </c>
       <c r="D8" s="40" t="s">
-        <v>346</v>
+        <v>235</v>
       </c>
       <c r="E8" t="s">
-        <v>346</v>
+        <v>235</v>
       </c>
     </row>
   </sheetData>

--- a/sources_S158/2.0.0/S-158_102_Validation_Checks_2_0_0.xlsx
+++ b/sources_S158/2.0.0/S-158_102_Validation_Checks_2_0_0.xlsx
@@ -27,7 +27,7 @@
     <author>Raphael Malyankar</author>
   </authors>
   <commentList>
-    <comment ref="E92" authorId="0">
+    <comment ref="E89" authorId="0">
       <text>
         <r>
           <rPr>
@@ -56,13 +56,13 @@
               <xdr:from>
                 <xdr:col>5</xdr:col>
                 <xdr:colOff>15</xdr:colOff>
-                <xdr:row>192</xdr:row>
+                <xdr:row>189</xdr:row>
                 <xdr:rowOff>14</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>6</xdr:col>
                 <xdr:colOff>-81</xdr:colOff>
-                <xdr:row>197</xdr:row>
+                <xdr:row>194</xdr:row>
                 <xdr:rowOff>8</xdr:rowOff>
               </xdr:to>
             </anchor>
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="215">
   <si>
     <t xml:space="preserve">Metadata of S-100 Validation Check Specification</t>
   </si>
@@ -423,81 +423,63 @@
     <t xml:space="preserve">Table 5-1 (S-102 Coordinate Reference Systems), Table 10-2 (Root group attributes)</t>
   </si>
   <si>
-    <t xml:space="preserve">102_Dev1029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102_1015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Root group structural error, must be corrected before further checks can be processed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IF any of the Phase 1 checks designated as terminator checks were failed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Correct root group structure before proceeding to next phase</t>
+    <t xml:space="preserve">102_Dev2002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102_2002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Error</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HDF attributes of quality coverage must have the same values as bathymetry coverage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IF the HDF attributes of QualityOfBathymetryCoverage have values different from the corresponding attributes of BathymetryCoverage except datacoding format</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Correct attributes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Table 10-4 (Attributes of BathymetryCoverage feature container group), 10.2.8 (para. 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102_Dev2004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102_2004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Axis names must conform to CRS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">If the contents of dataset axisNames do not conform to the CRS specified by horizontalCRS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Correct the axisNames dataset</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2.1.1.1.9, 4.2.1.1.3.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102_Dev2010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102_2008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The number of quality instance groups in &lt;QTYPE&gt; does not match the value of attribute numInstances</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IF the number of groups named &lt;QTYPE&gt;.N is not equal to the value of attribute numInstances</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Correct attribute numInstances or the the number of quality instance groups in &lt;QTYPE&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">N/A</t>
   </si>
   <si>
-    <t xml:space="preserve">Gateway to next phase</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102_Dev2002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102_2002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Error</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HDF attributes of quality coverage must have the same values as bathymetry coverage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IF the HDF attributes of QualityOfBathymetryCoverage have values different from the corresponding attributes of BathymetryCoverage except datacoding format</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Correct attributes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Table 10-4 (Attributes of BathymetryCoverage feature container group), 10.2.8 (para. 1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102_Dev2004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102_2004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Axis names must conform to CRS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">If the contents of dataset axisNames do not conform to the CRS specified by horizontalCRS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Correct the axisNames dataset</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2.1.1.1.9, 4.2.1.1.3.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102_Dev2010</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102_2008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The number of quality instance groups in &lt;QTYPE&gt; does not match the value of attribute numInstances</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IF the number of groups named &lt;QTYPE&gt;.N is not equal to the value of attribute numInstances</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Correct attribute numInstances or the the number of quality instance groups in &lt;QTYPE&gt;</t>
-  </si>
-  <si>
     <t xml:space="preserve">102_Dev2011</t>
   </si>
   <si>
@@ -535,21 +517,6 @@
   </si>
   <si>
     <t xml:space="preserve">100_0214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102_Dev2013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102_2013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Feature container group error, must be corrected before feature instance checks can be processed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IF any of the Phase 2 checks designated as terminator checks were failed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Correct error before  proceeding to next phase</t>
   </si>
   <si>
     <t xml:space="preserve">102_Dev3001</t>
@@ -634,21 +601,6 @@
   </si>
   <si>
     <t xml:space="preserve">10.2.5, 10.2.9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102_Dev3019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102_3011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Instance group structural error, must be corrected before further checks can be processed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IF any of the Phase 3 checks designated as terminator checks were failed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Correct &lt;FINST&gt; group structure before proceeding to next phase</t>
   </si>
   <si>
     <t xml:space="preserve">102_Dev5004</t>
@@ -1345,239 +1297,243 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="5" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="5" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="5" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="5" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="5" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="5" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="5" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="5" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="5" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="5" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="5" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="5" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="5" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="5" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="5" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="5" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="9" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="9" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="9" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="9" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="9" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="13" fillId="9" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="9" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="9" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="21" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="21" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1585,75 +1541,71 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="20" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="20" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1665,59 +1617,59 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1735,7 +1687,7 @@
     <cellStyle name="Neutral 3" xfId="23"/>
     <cellStyle name="Excel Built-in Good" xfId="24"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="5">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1771,14 +1723,6 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FF548235"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -1848,8 +1792,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabelle1" displayName="Tabelle1" ref="A1:O29" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:O29"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabelle1" displayName="Tabelle1" ref="A1:O26" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:O26"/>
   <tableColumns count="15">
     <tableColumn id="1" name="Dev ID "/>
     <tableColumn id="2" name="Check ID"/>
@@ -2050,223 +1994,227 @@
   <dimension ref="A2:H20"/>
   <sheetFormatPr defaultColWidth="9.14453125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="36.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="14.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="6.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="20.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="3" width="36.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="12.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="1" width="14.7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="6.43"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="33" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="4"/>
-    </row>
-    <row r="3" s="5" customFormat="true" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="6" t="s">
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="5"/>
+    </row>
+    <row r="3" s="6" customFormat="true" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B3" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="9"/>
-    </row>
-    <row r="4" s="5" customFormat="true" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="6" t="s">
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="10"/>
+    </row>
+    <row r="4" s="6" customFormat="true" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B4" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="9"/>
-    </row>
-    <row r="5" s="5" customFormat="true" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="6" t="s">
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="10"/>
+    </row>
+    <row r="5" s="6" customFormat="true" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B5" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="9"/>
-    </row>
-    <row r="6" s="5" customFormat="true" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="6" t="s">
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="10"/>
+    </row>
+    <row r="6" s="6" customFormat="true" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="9"/>
-    </row>
-    <row r="7" s="5" customFormat="true" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="6" t="s">
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="10"/>
+    </row>
+    <row r="7" s="6" customFormat="true" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="9"/>
-    </row>
-    <row r="8" s="5" customFormat="true" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="6" t="s">
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="10"/>
+    </row>
+    <row r="8" s="6" customFormat="true" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B8" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="12" t="n">
+      <c r="C8" s="13" t="n">
         <v>46022</v>
       </c>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="9"/>
-    </row>
-    <row r="9" s="5" customFormat="true" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="6" t="s">
+      <c r="D8" s="9"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="10"/>
+    </row>
+    <row r="9" s="6" customFormat="true" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B9" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="13" t="n">
+      <c r="C9" s="14" t="n">
         <f aca="false">C8</f>
         <v>46022</v>
       </c>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="9"/>
-    </row>
-    <row r="10" s="5" customFormat="true" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="6" t="s">
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="10"/>
+    </row>
+    <row r="10" s="6" customFormat="true" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B10" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="14" t="s">
+      <c r="C10" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="9"/>
-    </row>
-    <row r="11" s="5" customFormat="true" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="6" t="s">
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="10"/>
+    </row>
+    <row r="11" s="6" customFormat="true" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B11" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="9"/>
-    </row>
-    <row r="12" s="5" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="15"/>
-      <c r="C12" s="16" t="s">
+      <c r="D11" s="9"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="10"/>
+    </row>
+    <row r="12" s="6" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B12" s="16"/>
+      <c r="C12" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="D12" s="17" t="s">
+      <c r="D12" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="E12" s="18" t="s">
+      <c r="E12" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="F12" s="18"/>
-      <c r="G12" s="9"/>
-    </row>
-    <row r="13" s="5" customFormat="true" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="15" t="s">
+      <c r="F12" s="19"/>
+      <c r="G12" s="10"/>
+    </row>
+    <row r="13" s="6" customFormat="true" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B13" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D13" s="19" t="s">
+      <c r="D13" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="E13" s="19"/>
-      <c r="F13" s="20"/>
-      <c r="G13" s="9"/>
-    </row>
-    <row r="14" s="5" customFormat="true" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="15"/>
-      <c r="C14" s="21" t="s">
+      <c r="E13" s="20"/>
+      <c r="F13" s="21"/>
+      <c r="G13" s="10"/>
+    </row>
+    <row r="14" s="6" customFormat="true" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B14" s="16"/>
+      <c r="C14" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="D14" s="19" t="s">
+      <c r="D14" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="E14" s="22"/>
-      <c r="F14" s="23"/>
-      <c r="G14" s="9"/>
-    </row>
-    <row r="15" s="5" customFormat="true" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="15"/>
-      <c r="C15" s="24"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="20"/>
-      <c r="F15" s="22"/>
-      <c r="G15" s="9"/>
-    </row>
-    <row r="16" s="5" customFormat="true" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="15"/>
-      <c r="C16" s="25"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="26"/>
-      <c r="F16" s="26"/>
-      <c r="G16" s="9"/>
-    </row>
-    <row r="17" s="5" customFormat="true" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="15"/>
-      <c r="C17" s="27"/>
-      <c r="D17" s="26"/>
-      <c r="E17" s="26"/>
-      <c r="F17" s="26"/>
-      <c r="G17" s="9"/>
-    </row>
-    <row r="18" s="5" customFormat="true" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="15"/>
-      <c r="C18" s="28"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
-      <c r="G18" s="9"/>
-    </row>
-    <row r="19" s="5" customFormat="true" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="29"/>
-      <c r="C19" s="30"/>
-      <c r="D19" s="31"/>
-      <c r="E19" s="31"/>
-      <c r="F19" s="31"/>
-      <c r="G19" s="32"/>
+      <c r="E14" s="23"/>
+      <c r="F14" s="24"/>
+      <c r="G14" s="10"/>
+    </row>
+    <row r="15" s="6" customFormat="true" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B15" s="16"/>
+      <c r="C15" s="25"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="21"/>
+      <c r="F15" s="23"/>
+      <c r="G15" s="10"/>
+    </row>
+    <row r="16" s="6" customFormat="true" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B16" s="16"/>
+      <c r="C16" s="26"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="27"/>
+      <c r="F16" s="27"/>
+      <c r="G16" s="10"/>
+    </row>
+    <row r="17" s="6" customFormat="true" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B17" s="16"/>
+      <c r="C17" s="28"/>
+      <c r="D17" s="27"/>
+      <c r="E17" s="27"/>
+      <c r="F17" s="27"/>
+      <c r="G17" s="10"/>
+    </row>
+    <row r="18" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="6"/>
+      <c r="B18" s="16"/>
+      <c r="C18" s="29"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="9"/>
+      <c r="G18" s="10"/>
+      <c r="H18" s="6"/>
+    </row>
+    <row r="19" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="6"/>
+      <c r="B19" s="30"/>
+      <c r="C19" s="31"/>
+      <c r="D19" s="32"/>
+      <c r="E19" s="32"/>
+      <c r="F19" s="32"/>
+      <c r="G19" s="33"/>
+      <c r="H19" s="6"/>
     </row>
     <row r="20" customFormat="false" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="5"/>
-      <c r="B20" s="33"/>
-      <c r="C20" s="34"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
-      <c r="G20" s="5"/>
-      <c r="H20" s="5"/>
+      <c r="A20" s="6"/>
+      <c r="B20" s="34"/>
+      <c r="C20" s="35"/>
+      <c r="D20" s="6"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="6"/>
+      <c r="H20" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2295,1170 +2243,1098 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:O1048576"/>
-  <sheetFormatPr defaultColWidth="8.71484375" defaultRowHeight="12.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.72265625" defaultRowHeight="12.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="35" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="35" width="12.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="35" width="13.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="35" width="33.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="36" width="42.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="35" width="28.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="35" width="20.72"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="37" width="16.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="36" width="22.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="35" width="11.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="35" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="35" width="10.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="36" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="35" width="12.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="36" width="15.72"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="16" style="35" width="8.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="36" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="36" width="12.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="36" width="13.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="36" width="33.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="37" width="42.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="36" width="28.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="36" width="20.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="38" width="16.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="37" width="22.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="36" width="11.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="36" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="36" width="10.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="37" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="36" width="12.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="37" width="15.72"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="16" style="36" width="8.72"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="39" t="s">
+      <c r="B1" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="C1" s="39" t="s">
+      <c r="C1" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="D1" s="39" t="s">
+      <c r="D1" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="E1" s="39" t="s">
+      <c r="E1" s="40" t="s">
         <v>27</v>
       </c>
-      <c r="F1" s="39" t="s">
+      <c r="F1" s="40" t="s">
         <v>28</v>
       </c>
-      <c r="G1" s="39" t="s">
+      <c r="G1" s="40" t="s">
         <v>29</v>
       </c>
-      <c r="H1" s="40" t="s">
+      <c r="H1" s="41" t="s">
         <v>30</v>
       </c>
-      <c r="I1" s="41" t="s">
+      <c r="I1" s="42" t="s">
         <v>31</v>
       </c>
-      <c r="J1" s="41" t="s">
+      <c r="J1" s="42" t="s">
         <v>32</v>
       </c>
-      <c r="K1" s="41" t="s">
+      <c r="K1" s="42" t="s">
         <v>33</v>
       </c>
-      <c r="L1" s="41" t="s">
+      <c r="L1" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="M1" s="41" t="s">
+      <c r="M1" s="42" t="s">
         <v>35</v>
       </c>
-      <c r="N1" s="41" t="s">
+      <c r="N1" s="42" t="s">
         <v>36</v>
       </c>
-      <c r="O1" s="42" t="s">
+      <c r="O1" s="43" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="43" t="s">
+      <c r="A2" s="44" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="44" t="s">
+      <c r="B2" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="C2" s="45" t="s">
+      <c r="C2" s="46" t="s">
         <v>40</v>
       </c>
-      <c r="D2" s="46" t="s">
+      <c r="D2" s="47" t="s">
         <v>41</v>
       </c>
-      <c r="E2" s="46" t="s">
+      <c r="E2" s="47" t="s">
         <v>42</v>
       </c>
-      <c r="F2" s="46" t="s">
+      <c r="F2" s="47" t="s">
         <v>43</v>
       </c>
-      <c r="G2" s="46" t="s">
+      <c r="G2" s="47" t="s">
         <v>44</v>
       </c>
-      <c r="H2" s="47" t="s">
+      <c r="H2" s="48" t="s">
         <v>45</v>
       </c>
-      <c r="I2" s="48" t="s">
+      <c r="I2" s="49" t="s">
         <v>46</v>
       </c>
-      <c r="J2" s="44" t="s">
+      <c r="J2" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="K2" s="44"/>
-      <c r="L2" s="44"/>
-      <c r="M2" s="44"/>
-      <c r="N2" s="44"/>
-      <c r="O2" s="49"/>
+      <c r="K2" s="45"/>
+      <c r="L2" s="45"/>
+      <c r="M2" s="45"/>
+      <c r="N2" s="45"/>
+      <c r="O2" s="50"/>
     </row>
     <row r="3" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="50" t="s">
+      <c r="A3" s="51" t="s">
         <v>47</v>
       </c>
-      <c r="B3" s="44" t="s">
+      <c r="B3" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="C3" s="51" t="s">
+      <c r="C3" s="52" t="s">
         <v>49</v>
       </c>
-      <c r="D3" s="51" t="s">
+      <c r="D3" s="52" t="s">
         <v>50</v>
       </c>
-      <c r="E3" s="52" t="s">
+      <c r="E3" s="53" t="s">
         <v>51</v>
       </c>
-      <c r="F3" s="51" t="s">
+      <c r="F3" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="G3" s="46" t="s">
+      <c r="G3" s="47" t="s">
         <v>44</v>
       </c>
-      <c r="H3" s="51" t="n">
+      <c r="H3" s="52" t="n">
         <v>10.2</v>
       </c>
-      <c r="I3" s="51" t="s">
+      <c r="I3" s="52" t="s">
         <v>53</v>
       </c>
-      <c r="J3" s="44" t="s">
+      <c r="J3" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="K3" s="44"/>
-      <c r="L3" s="44"/>
-      <c r="M3" s="44"/>
-      <c r="N3" s="44" t="s">
+      <c r="K3" s="45"/>
+      <c r="L3" s="45"/>
+      <c r="M3" s="45"/>
+      <c r="N3" s="45" t="s">
         <v>54</v>
       </c>
-      <c r="O3" s="49"/>
+      <c r="O3" s="50"/>
     </row>
     <row r="4" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="50" t="s">
+      <c r="A4" s="51" t="s">
         <v>55</v>
       </c>
-      <c r="B4" s="44" t="s">
+      <c r="B4" s="45" t="s">
         <v>56</v>
       </c>
-      <c r="C4" s="51" t="s">
+      <c r="C4" s="52" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="51" t="s">
+      <c r="D4" s="52" t="s">
         <v>57</v>
       </c>
-      <c r="E4" s="53" t="s">
+      <c r="E4" s="54" t="s">
         <v>58</v>
       </c>
-      <c r="F4" s="51" t="s">
+      <c r="F4" s="52" t="s">
         <v>59</v>
       </c>
-      <c r="G4" s="46" t="s">
+      <c r="G4" s="47" t="s">
         <v>44</v>
       </c>
-      <c r="H4" s="54" t="s">
+      <c r="H4" s="55" t="s">
         <v>60</v>
       </c>
-      <c r="I4" s="51" t="s">
+      <c r="I4" s="52" t="s">
         <v>53</v>
       </c>
-      <c r="J4" s="44" t="s">
+      <c r="J4" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="K4" s="55"/>
-      <c r="L4" s="55"/>
-      <c r="M4" s="55"/>
-      <c r="N4" s="44" t="s">
+      <c r="K4" s="56"/>
+      <c r="L4" s="56"/>
+      <c r="M4" s="56"/>
+      <c r="N4" s="45" t="s">
         <v>54</v>
       </c>
-      <c r="O4" s="49"/>
+      <c r="O4" s="50"/>
     </row>
     <row r="5" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="50" t="s">
+      <c r="A5" s="51" t="s">
         <v>61</v>
       </c>
-      <c r="B5" s="44" t="s">
+      <c r="B5" s="45" t="s">
         <v>62</v>
       </c>
-      <c r="C5" s="51" t="s">
+      <c r="C5" s="52" t="s">
         <v>40</v>
       </c>
-      <c r="D5" s="51" t="s">
+      <c r="D5" s="52" t="s">
         <v>63</v>
       </c>
-      <c r="E5" s="51" t="s">
+      <c r="E5" s="52" t="s">
         <v>64</v>
       </c>
-      <c r="F5" s="51" t="s">
+      <c r="F5" s="52" t="s">
         <v>65</v>
       </c>
-      <c r="G5" s="46" t="s">
+      <c r="G5" s="47" t="s">
         <v>44</v>
       </c>
-      <c r="H5" s="53" t="s">
+      <c r="H5" s="54" t="s">
         <v>66</v>
       </c>
-      <c r="I5" s="51" t="s">
+      <c r="I5" s="52" t="s">
         <v>67</v>
       </c>
-      <c r="J5" s="44" t="s">
+      <c r="J5" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="K5" s="55"/>
-      <c r="L5" s="55"/>
-      <c r="M5" s="55"/>
-      <c r="N5" s="55"/>
-      <c r="O5" s="49"/>
+      <c r="K5" s="56"/>
+      <c r="L5" s="56"/>
+      <c r="M5" s="56"/>
+      <c r="N5" s="56"/>
+      <c r="O5" s="50"/>
     </row>
     <row r="6" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="50" t="s">
+      <c r="A6" s="51" t="s">
         <v>68</v>
       </c>
-      <c r="B6" s="44" t="s">
+      <c r="B6" s="45" t="s">
         <v>69</v>
       </c>
-      <c r="C6" s="51" t="s">
+      <c r="C6" s="52" t="s">
         <v>40</v>
       </c>
-      <c r="D6" s="51" t="s">
+      <c r="D6" s="52" t="s">
         <v>70</v>
       </c>
-      <c r="E6" s="51" t="s">
+      <c r="E6" s="52" t="s">
         <v>71</v>
       </c>
-      <c r="F6" s="51" t="s">
+      <c r="F6" s="52" t="s">
         <v>72</v>
       </c>
-      <c r="G6" s="46" t="s">
+      <c r="G6" s="47" t="s">
         <v>44</v>
       </c>
-      <c r="H6" s="51" t="s">
+      <c r="H6" s="52" t="s">
         <v>73</v>
       </c>
-      <c r="I6" s="51" t="s">
+      <c r="I6" s="52" t="s">
         <v>67</v>
       </c>
-      <c r="J6" s="44" t="s">
+      <c r="J6" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="K6" s="56"/>
-      <c r="L6" s="55"/>
-      <c r="M6" s="55"/>
-      <c r="N6" s="55"/>
-      <c r="O6" s="49"/>
+      <c r="K6" s="57"/>
+      <c r="L6" s="56"/>
+      <c r="M6" s="56"/>
+      <c r="N6" s="56"/>
+      <c r="O6" s="50"/>
     </row>
     <row r="7" customFormat="false" ht="74.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="50" t="s">
+      <c r="A7" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="B7" s="44" t="s">
+      <c r="B7" s="45" t="s">
         <v>75</v>
       </c>
-      <c r="C7" s="51" t="s">
+      <c r="C7" s="52" t="s">
         <v>49</v>
       </c>
-      <c r="D7" s="53" t="s">
+      <c r="D7" s="54" t="s">
         <v>76</v>
       </c>
-      <c r="E7" s="52" t="s">
+      <c r="E7" s="53" t="s">
         <v>77</v>
       </c>
-      <c r="F7" s="51" t="s">
+      <c r="F7" s="52" t="s">
         <v>78</v>
       </c>
-      <c r="G7" s="46" t="s">
+      <c r="G7" s="47" t="s">
         <v>44</v>
       </c>
-      <c r="H7" s="53" t="s">
+      <c r="H7" s="54" t="s">
         <v>79</v>
       </c>
-      <c r="I7" s="51" t="s">
+      <c r="I7" s="52" t="s">
         <v>67</v>
       </c>
-      <c r="J7" s="44" t="s">
+      <c r="J7" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="K7" s="44"/>
-      <c r="L7" s="44"/>
-      <c r="M7" s="44"/>
-      <c r="N7" s="44"/>
-      <c r="O7" s="49"/>
-    </row>
-    <row r="8" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="50" t="s">
+      <c r="K7" s="45"/>
+      <c r="L7" s="45"/>
+      <c r="M7" s="45"/>
+      <c r="N7" s="45"/>
+      <c r="O7" s="50"/>
+    </row>
+    <row r="8" customFormat="false" ht="100.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="51" t="s">
         <v>80</v>
       </c>
-      <c r="B8" s="44" t="s">
+      <c r="B8" s="58" t="s">
         <v>81</v>
       </c>
-      <c r="C8" s="51" t="s">
-        <v>49</v>
-      </c>
-      <c r="D8" s="51" t="s">
+      <c r="C8" s="46" t="s">
         <v>82</v>
       </c>
-      <c r="E8" s="51" t="s">
+      <c r="D8" s="47" t="s">
         <v>83</v>
       </c>
-      <c r="F8" s="51" t="s">
+      <c r="E8" s="47" t="s">
         <v>84</v>
       </c>
-      <c r="G8" s="46" t="s">
+      <c r="F8" s="47" t="s">
         <v>85</v>
       </c>
-      <c r="H8" s="51" t="s">
-        <v>85</v>
-      </c>
-      <c r="I8" s="51"/>
-      <c r="J8" s="44"/>
-      <c r="K8" s="44"/>
-      <c r="L8" s="44"/>
-      <c r="M8" s="44"/>
-      <c r="N8" s="44"/>
-      <c r="O8" s="49" t="s">
+      <c r="G8" s="47" t="s">
+        <v>44</v>
+      </c>
+      <c r="H8" s="59" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="100.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="50" t="s">
+      <c r="I8" s="52" t="s">
+        <v>67</v>
+      </c>
+      <c r="J8" s="45" t="s">
+        <v>21</v>
+      </c>
+      <c r="K8" s="45"/>
+      <c r="L8" s="45"/>
+      <c r="M8" s="45"/>
+      <c r="N8" s="45" t="s">
+        <v>54</v>
+      </c>
+      <c r="O8" s="50"/>
+    </row>
+    <row r="9" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="51" t="s">
         <v>87</v>
       </c>
-      <c r="B9" s="57" t="s">
+      <c r="B9" s="58" t="s">
         <v>88</v>
       </c>
-      <c r="C9" s="45" t="s">
+      <c r="C9" s="46" t="s">
+        <v>82</v>
+      </c>
+      <c r="D9" s="47" t="s">
         <v>89</v>
       </c>
-      <c r="D9" s="46" t="s">
+      <c r="E9" s="47" t="s">
         <v>90</v>
       </c>
-      <c r="E9" s="46" t="s">
+      <c r="F9" s="47" t="s">
         <v>91</v>
       </c>
-      <c r="F9" s="46" t="s">
+      <c r="G9" s="47" t="s">
+        <v>44</v>
+      </c>
+      <c r="H9" s="59" t="s">
         <v>92</v>
       </c>
-      <c r="G9" s="46" t="s">
+      <c r="I9" s="52" t="s">
+        <v>67</v>
+      </c>
+      <c r="J9" s="45" t="s">
+        <v>21</v>
+      </c>
+      <c r="K9" s="60"/>
+      <c r="L9" s="60"/>
+      <c r="M9" s="45"/>
+      <c r="N9" s="60"/>
+      <c r="O9" s="50"/>
+    </row>
+    <row r="10" s="62" customFormat="true" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="51" t="s">
+        <v>93</v>
+      </c>
+      <c r="B10" s="58" t="s">
+        <v>94</v>
+      </c>
+      <c r="C10" s="46" t="s">
+        <v>40</v>
+      </c>
+      <c r="D10" s="47" t="s">
+        <v>95</v>
+      </c>
+      <c r="E10" s="47" t="s">
+        <v>96</v>
+      </c>
+      <c r="F10" s="61" t="s">
+        <v>97</v>
+      </c>
+      <c r="G10" s="47" t="s">
         <v>44</v>
       </c>
-      <c r="H9" s="58" t="s">
-        <v>93</v>
-      </c>
-      <c r="I9" s="51" t="s">
-        <v>67</v>
-      </c>
-      <c r="J9" s="44" t="s">
+      <c r="H10" s="59" t="s">
+        <v>98</v>
+      </c>
+      <c r="I10" s="52" t="s">
+        <v>53</v>
+      </c>
+      <c r="J10" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="K9" s="44"/>
-      <c r="L9" s="44"/>
-      <c r="M9" s="44"/>
-      <c r="N9" s="44" t="s">
-        <v>54</v>
-      </c>
-      <c r="O9" s="49"/>
-    </row>
-    <row r="10" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="50" t="s">
-        <v>94</v>
-      </c>
-      <c r="B10" s="57" t="s">
-        <v>95</v>
-      </c>
-      <c r="C10" s="45" t="s">
-        <v>89</v>
-      </c>
-      <c r="D10" s="46" t="s">
-        <v>96</v>
-      </c>
-      <c r="E10" s="46" t="s">
-        <v>97</v>
-      </c>
-      <c r="F10" s="46" t="s">
-        <v>98</v>
-      </c>
-      <c r="G10" s="46" t="s">
-        <v>44</v>
-      </c>
-      <c r="H10" s="58" t="s">
-        <v>99</v>
-      </c>
-      <c r="I10" s="51" t="s">
-        <v>67</v>
-      </c>
-      <c r="J10" s="44" t="s">
-        <v>21</v>
-      </c>
-      <c r="K10" s="59"/>
-      <c r="L10" s="59"/>
-      <c r="M10" s="44"/>
-      <c r="N10" s="59"/>
-      <c r="O10" s="49"/>
-    </row>
-    <row r="11" s="61" customFormat="true" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="50" t="s">
-        <v>100</v>
-      </c>
-      <c r="B11" s="57" t="s">
-        <v>101</v>
-      </c>
-      <c r="C11" s="45" t="s">
-        <v>40</v>
-      </c>
-      <c r="D11" s="46" t="s">
-        <v>102</v>
-      </c>
-      <c r="E11" s="46" t="s">
-        <v>103</v>
-      </c>
-      <c r="F11" s="60" t="s">
-        <v>104</v>
-      </c>
-      <c r="G11" s="46" t="s">
-        <v>44</v>
-      </c>
-      <c r="H11" s="58" t="s">
-        <v>85</v>
-      </c>
-      <c r="I11" s="51" t="s">
-        <v>53</v>
-      </c>
-      <c r="J11" s="44" t="s">
-        <v>21</v>
-      </c>
-      <c r="K11" s="59"/>
-      <c r="L11" s="59"/>
-      <c r="M11" s="44" t="e">
+      <c r="K10" s="60"/>
+      <c r="L10" s="60"/>
+      <c r="M10" s="45" t="e">
         <f aca="false">#ref!</f>
         <v>#NAME?</v>
       </c>
-      <c r="N11" s="59"/>
-      <c r="O11" s="49"/>
-    </row>
-    <row r="12" customFormat="false" ht="72.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="50" t="s">
-        <v>105</v>
-      </c>
-      <c r="B12" s="57" t="s">
-        <v>106</v>
-      </c>
-      <c r="C12" s="45" t="s">
+      <c r="N10" s="60"/>
+      <c r="O10" s="50"/>
+    </row>
+    <row r="11" customFormat="false" ht="72.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="51" t="s">
+        <v>99</v>
+      </c>
+      <c r="B11" s="58" t="s">
+        <v>100</v>
+      </c>
+      <c r="C11" s="46" t="s">
         <v>40</v>
       </c>
-      <c r="D12" s="46" t="s">
-        <v>107</v>
-      </c>
-      <c r="E12" s="46" t="s">
-        <v>108</v>
-      </c>
-      <c r="F12" s="60" t="s">
-        <v>109</v>
-      </c>
-      <c r="G12" s="46" t="s">
+      <c r="D11" s="47" t="s">
+        <v>101</v>
+      </c>
+      <c r="E11" s="47" t="s">
+        <v>102</v>
+      </c>
+      <c r="F11" s="61" t="s">
+        <v>103</v>
+      </c>
+      <c r="G11" s="47" t="s">
         <v>44</v>
       </c>
-      <c r="H12" s="58" t="s">
-        <v>110</v>
-      </c>
-      <c r="I12" s="51" t="s">
+      <c r="H11" s="59" t="s">
+        <v>104</v>
+      </c>
+      <c r="I11" s="52" t="s">
         <v>67</v>
       </c>
-      <c r="J12" s="44" t="s">
+      <c r="J11" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="K12" s="59"/>
-      <c r="L12" s="59"/>
-      <c r="M12" s="44" t="e">
+      <c r="K11" s="60"/>
+      <c r="L11" s="60"/>
+      <c r="M11" s="45" t="e">
         <f aca="false">#ref!</f>
         <v>#NAME?</v>
       </c>
-      <c r="N12" s="59"/>
-      <c r="O12" s="49"/>
-    </row>
-    <row r="13" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="50" t="s">
+      <c r="N11" s="60"/>
+      <c r="O11" s="50"/>
+    </row>
+    <row r="12" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="51" t="s">
+        <v>105</v>
+      </c>
+      <c r="B12" s="58" t="s">
+        <v>106</v>
+      </c>
+      <c r="C12" s="46" t="s">
+        <v>49</v>
+      </c>
+      <c r="D12" s="49" t="s">
+        <v>107</v>
+      </c>
+      <c r="E12" s="63" t="s">
+        <v>108</v>
+      </c>
+      <c r="F12" s="47" t="s">
+        <v>109</v>
+      </c>
+      <c r="G12" s="47" t="s">
+        <v>44</v>
+      </c>
+      <c r="H12" s="59" t="s">
+        <v>110</v>
+      </c>
+      <c r="I12" s="52" t="s">
+        <v>53</v>
+      </c>
+      <c r="J12" s="45" t="s">
+        <v>21</v>
+      </c>
+      <c r="K12" s="45"/>
+      <c r="L12" s="45"/>
+      <c r="M12" s="49" t="s">
         <v>111</v>
       </c>
-      <c r="B13" s="57" t="s">
+      <c r="N12" s="45" t="s">
+        <v>54</v>
+      </c>
+      <c r="O12" s="50"/>
+    </row>
+    <row r="13" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="64" t="s">
         <v>112</v>
       </c>
-      <c r="C13" s="45" t="s">
+      <c r="B13" s="58" t="s">
+        <v>113</v>
+      </c>
+      <c r="C13" s="46" t="s">
         <v>49</v>
       </c>
-      <c r="D13" s="62" t="s">
-        <v>113</v>
-      </c>
-      <c r="E13" s="63" t="s">
+      <c r="D13" s="47" t="s">
         <v>114</v>
       </c>
-      <c r="F13" s="46" t="s">
+      <c r="E13" s="47" t="s">
         <v>115</v>
       </c>
-      <c r="G13" s="46" t="s">
+      <c r="F13" s="47" t="s">
+        <v>116</v>
+      </c>
+      <c r="G13" s="47" t="s">
         <v>44</v>
       </c>
-      <c r="H13" s="58" t="s">
-        <v>116</v>
-      </c>
-      <c r="I13" s="51" t="s">
+      <c r="H13" s="59" t="s">
+        <v>117</v>
+      </c>
+      <c r="I13" s="52" t="s">
         <v>53</v>
       </c>
-      <c r="J13" s="44" t="s">
+      <c r="J13" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="K13" s="44"/>
-      <c r="L13" s="44"/>
-      <c r="M13" s="62" t="s">
-        <v>117</v>
-      </c>
-      <c r="N13" s="44" t="s">
-        <v>54</v>
-      </c>
-      <c r="O13" s="49"/>
-    </row>
-    <row r="14" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="50" t="s">
+      <c r="K13" s="60"/>
+      <c r="L13" s="60"/>
+      <c r="M13" s="45"/>
+      <c r="N13" s="60"/>
+      <c r="O13" s="65"/>
+    </row>
+    <row r="14" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="64" t="s">
         <v>118</v>
       </c>
-      <c r="B14" s="57" t="s">
+      <c r="B14" s="58" t="s">
         <v>119</v>
       </c>
-      <c r="C14" s="45" t="s">
-        <v>49</v>
-      </c>
-      <c r="D14" s="46" t="s">
+      <c r="C14" s="46" t="s">
+        <v>82</v>
+      </c>
+      <c r="D14" s="47" t="s">
         <v>120</v>
       </c>
-      <c r="E14" s="46" t="s">
+      <c r="E14" s="45" t="s">
         <v>121</v>
       </c>
-      <c r="F14" s="60" t="s">
+      <c r="F14" s="47" t="s">
         <v>122</v>
       </c>
-      <c r="G14" s="46" t="s">
-        <v>85</v>
-      </c>
-      <c r="H14" s="58" t="s">
-        <v>85</v>
-      </c>
-      <c r="I14" s="51"/>
-      <c r="J14" s="44"/>
-      <c r="K14" s="59"/>
-      <c r="L14" s="59"/>
-      <c r="M14" s="44"/>
-      <c r="N14" s="59"/>
-      <c r="O14" s="49" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G14" s="47" t="s">
+        <v>44</v>
+      </c>
+      <c r="H14" s="55" t="s">
+        <v>60</v>
+      </c>
+      <c r="I14" s="52" t="s">
+        <v>67</v>
+      </c>
+      <c r="J14" s="45" t="s">
+        <v>21</v>
+      </c>
+      <c r="K14" s="60"/>
+      <c r="L14" s="60"/>
+      <c r="M14" s="45"/>
+      <c r="N14" s="60"/>
+      <c r="O14" s="50"/>
+    </row>
+    <row r="15" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="64" t="s">
         <v>123</v>
       </c>
-      <c r="B15" s="57" t="s">
+      <c r="B15" s="58" t="s">
         <v>124</v>
       </c>
-      <c r="C15" s="45" t="s">
+      <c r="C15" s="46" t="s">
+        <v>82</v>
+      </c>
+      <c r="D15" s="47" t="s">
+        <v>125</v>
+      </c>
+      <c r="E15" s="47" t="s">
+        <v>126</v>
+      </c>
+      <c r="F15" s="47" t="s">
+        <v>122</v>
+      </c>
+      <c r="G15" s="47" t="s">
+        <v>44</v>
+      </c>
+      <c r="H15" s="59" t="s">
+        <v>66</v>
+      </c>
+      <c r="I15" s="52" t="s">
+        <v>67</v>
+      </c>
+      <c r="J15" s="45" t="s">
+        <v>21</v>
+      </c>
+      <c r="K15" s="60"/>
+      <c r="L15" s="60"/>
+      <c r="M15" s="45"/>
+      <c r="N15" s="60"/>
+      <c r="O15" s="50"/>
+    </row>
+    <row r="16" customFormat="false" ht="93" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="64" t="s">
+        <v>127</v>
+      </c>
+      <c r="B16" s="58" t="s">
+        <v>128</v>
+      </c>
+      <c r="C16" s="46" t="s">
+        <v>82</v>
+      </c>
+      <c r="D16" s="61" t="s">
+        <v>129</v>
+      </c>
+      <c r="E16" s="61" t="s">
+        <v>130</v>
+      </c>
+      <c r="F16" s="61" t="s">
+        <v>131</v>
+      </c>
+      <c r="G16" s="47" t="s">
+        <v>44</v>
+      </c>
+      <c r="H16" s="59" t="s">
+        <v>132</v>
+      </c>
+      <c r="I16" s="52" t="s">
+        <v>67</v>
+      </c>
+      <c r="J16" s="45" t="s">
+        <v>21</v>
+      </c>
+      <c r="K16" s="60"/>
+      <c r="L16" s="60"/>
+      <c r="M16" s="45"/>
+      <c r="N16" s="60"/>
+      <c r="O16" s="50"/>
+    </row>
+    <row r="17" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="64" t="s">
+        <v>133</v>
+      </c>
+      <c r="B17" s="58" t="s">
+        <v>134</v>
+      </c>
+      <c r="C17" s="46" t="s">
+        <v>82</v>
+      </c>
+      <c r="D17" s="47" t="s">
+        <v>135</v>
+      </c>
+      <c r="E17" s="47" t="s">
+        <v>136</v>
+      </c>
+      <c r="F17" s="47" t="s">
+        <v>137</v>
+      </c>
+      <c r="G17" s="47" t="s">
+        <v>44</v>
+      </c>
+      <c r="H17" s="59" t="s">
+        <v>138</v>
+      </c>
+      <c r="I17" s="52" t="s">
+        <v>53</v>
+      </c>
+      <c r="J17" s="45" t="s">
+        <v>21</v>
+      </c>
+      <c r="K17" s="60"/>
+      <c r="L17" s="60"/>
+      <c r="M17" s="45"/>
+      <c r="N17" s="60"/>
+      <c r="O17" s="50"/>
+    </row>
+    <row r="18" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="64" t="s">
+        <v>139</v>
+      </c>
+      <c r="B18" s="58" t="s">
+        <v>140</v>
+      </c>
+      <c r="C18" s="46" t="s">
         <v>49</v>
       </c>
-      <c r="D15" s="46" t="s">
-        <v>125</v>
-      </c>
-      <c r="E15" s="46" t="s">
-        <v>126</v>
-      </c>
-      <c r="F15" s="46" t="s">
-        <v>127</v>
-      </c>
-      <c r="G15" s="46" t="s">
+      <c r="D18" s="47" t="s">
+        <v>141</v>
+      </c>
+      <c r="E18" s="47" t="s">
+        <v>142</v>
+      </c>
+      <c r="F18" s="47" t="s">
+        <v>143</v>
+      </c>
+      <c r="G18" s="47" t="s">
         <v>44</v>
       </c>
-      <c r="H15" s="58" t="s">
-        <v>128</v>
-      </c>
-      <c r="I15" s="51" t="s">
+      <c r="H18" s="59" t="s">
+        <v>144</v>
+      </c>
+      <c r="I18" s="47" t="s">
         <v>53</v>
       </c>
-      <c r="J15" s="44" t="s">
+      <c r="J18" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="K15" s="59"/>
-      <c r="L15" s="59"/>
-      <c r="M15" s="44"/>
-      <c r="N15" s="59"/>
-      <c r="O15" s="65"/>
-    </row>
-    <row r="16" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="64" t="s">
-        <v>129</v>
-      </c>
-      <c r="B16" s="57" t="s">
-        <v>130</v>
-      </c>
-      <c r="C16" s="45" t="s">
-        <v>89</v>
-      </c>
-      <c r="D16" s="46" t="s">
-        <v>131</v>
-      </c>
-      <c r="E16" s="44" t="s">
-        <v>132</v>
-      </c>
-      <c r="F16" s="46" t="s">
-        <v>133</v>
-      </c>
-      <c r="G16" s="46" t="s">
+      <c r="K18" s="60"/>
+      <c r="L18" s="60"/>
+      <c r="M18" s="45"/>
+      <c r="N18" s="60"/>
+      <c r="O18" s="50"/>
+    </row>
+    <row r="19" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="64" t="s">
+        <v>145</v>
+      </c>
+      <c r="B19" s="58" t="s">
+        <v>146</v>
+      </c>
+      <c r="C19" s="46" t="s">
+        <v>40</v>
+      </c>
+      <c r="D19" s="47" t="s">
+        <v>147</v>
+      </c>
+      <c r="E19" s="47" t="s">
+        <v>148</v>
+      </c>
+      <c r="F19" s="47" t="s">
+        <v>149</v>
+      </c>
+      <c r="G19" s="47" t="s">
         <v>44</v>
       </c>
-      <c r="H16" s="54" t="s">
-        <v>60</v>
-      </c>
-      <c r="I16" s="51" t="s">
-        <v>67</v>
-      </c>
-      <c r="J16" s="44" t="s">
+      <c r="H19" s="66" t="s">
+        <v>150</v>
+      </c>
+      <c r="I19" s="66" t="s">
+        <v>151</v>
+      </c>
+      <c r="J19" s="66" t="s">
         <v>21</v>
       </c>
-      <c r="K16" s="59"/>
-      <c r="L16" s="59"/>
-      <c r="M16" s="44"/>
-      <c r="N16" s="59"/>
-      <c r="O16" s="49"/>
-    </row>
-    <row r="17" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="64" t="s">
-        <v>134</v>
-      </c>
-      <c r="B17" s="57" t="s">
-        <v>135</v>
-      </c>
-      <c r="C17" s="45" t="s">
-        <v>89</v>
-      </c>
-      <c r="D17" s="46" t="s">
-        <v>136</v>
-      </c>
-      <c r="E17" s="46" t="s">
-        <v>137</v>
-      </c>
-      <c r="F17" s="46" t="s">
-        <v>133</v>
-      </c>
-      <c r="G17" s="46" t="s">
-        <v>44</v>
-      </c>
-      <c r="H17" s="58" t="s">
-        <v>66</v>
-      </c>
-      <c r="I17" s="51" t="s">
-        <v>67</v>
-      </c>
-      <c r="J17" s="44" t="s">
-        <v>21</v>
-      </c>
-      <c r="K17" s="59"/>
-      <c r="L17" s="59"/>
-      <c r="M17" s="44"/>
-      <c r="N17" s="59"/>
-      <c r="O17" s="49"/>
-    </row>
-    <row r="18" customFormat="false" ht="93" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="64" t="s">
-        <v>138</v>
-      </c>
-      <c r="B18" s="57" t="s">
-        <v>139</v>
-      </c>
-      <c r="C18" s="45" t="s">
-        <v>89</v>
-      </c>
-      <c r="D18" s="60" t="s">
-        <v>140</v>
-      </c>
-      <c r="E18" s="60" t="s">
-        <v>141</v>
-      </c>
-      <c r="F18" s="60" t="s">
-        <v>142</v>
-      </c>
-      <c r="G18" s="46" t="s">
-        <v>44</v>
-      </c>
-      <c r="H18" s="58" t="s">
-        <v>143</v>
-      </c>
-      <c r="I18" s="51" t="s">
-        <v>67</v>
-      </c>
-      <c r="J18" s="44" t="s">
-        <v>21</v>
-      </c>
-      <c r="K18" s="59"/>
-      <c r="L18" s="59"/>
-      <c r="M18" s="44"/>
-      <c r="N18" s="59"/>
-      <c r="O18" s="49"/>
-    </row>
-    <row r="19" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="64" t="s">
-        <v>144</v>
-      </c>
-      <c r="B19" s="57" t="s">
-        <v>145</v>
-      </c>
-      <c r="C19" s="45" t="s">
-        <v>89</v>
-      </c>
-      <c r="D19" s="46" t="s">
-        <v>146</v>
-      </c>
-      <c r="E19" s="46" t="s">
-        <v>147</v>
-      </c>
-      <c r="F19" s="46" t="s">
-        <v>148</v>
-      </c>
-      <c r="G19" s="46" t="s">
-        <v>44</v>
-      </c>
-      <c r="H19" s="58" t="s">
-        <v>149</v>
-      </c>
-      <c r="I19" s="51" t="s">
-        <v>53</v>
-      </c>
-      <c r="J19" s="44" t="s">
-        <v>21</v>
-      </c>
-      <c r="K19" s="59"/>
-      <c r="L19" s="59"/>
-      <c r="M19" s="44"/>
-      <c r="N19" s="59"/>
-      <c r="O19" s="49"/>
+      <c r="K19" s="60"/>
+      <c r="L19" s="60"/>
+      <c r="M19" s="45"/>
+      <c r="N19" s="60"/>
+      <c r="O19" s="50"/>
     </row>
     <row r="20" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="64" t="s">
-        <v>150</v>
-      </c>
-      <c r="B20" s="57" t="s">
-        <v>151</v>
-      </c>
-      <c r="C20" s="45" t="s">
+        <v>152</v>
+      </c>
+      <c r="B20" s="58" t="s">
+        <v>153</v>
+      </c>
+      <c r="C20" s="46" t="s">
+        <v>40</v>
+      </c>
+      <c r="D20" s="47" t="s">
+        <v>154</v>
+      </c>
+      <c r="E20" s="47" t="s">
+        <v>155</v>
+      </c>
+      <c r="F20" s="47" t="s">
+        <v>156</v>
+      </c>
+      <c r="G20" s="47" t="s">
+        <v>44</v>
+      </c>
+      <c r="H20" s="59" t="s">
+        <v>157</v>
+      </c>
+      <c r="I20" s="47" t="s">
+        <v>53</v>
+      </c>
+      <c r="J20" s="45" t="s">
+        <v>21</v>
+      </c>
+      <c r="K20" s="60"/>
+      <c r="L20" s="60"/>
+      <c r="M20" s="45"/>
+      <c r="N20" s="60"/>
+      <c r="O20" s="50"/>
+    </row>
+    <row r="21" customFormat="false" ht="150" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="64" t="s">
+        <v>158</v>
+      </c>
+      <c r="B21" s="58" t="s">
+        <v>159</v>
+      </c>
+      <c r="C21" s="46" t="s">
+        <v>82</v>
+      </c>
+      <c r="D21" s="67" t="s">
+        <v>160</v>
+      </c>
+      <c r="E21" s="67" t="s">
+        <v>161</v>
+      </c>
+      <c r="F21" s="60" t="s">
+        <v>162</v>
+      </c>
+      <c r="G21" s="47" t="s">
+        <v>98</v>
+      </c>
+      <c r="H21" s="59" t="s">
+        <v>98</v>
+      </c>
+      <c r="I21" s="66" t="s">
+        <v>46</v>
+      </c>
+      <c r="J21" s="66" t="s">
+        <v>21</v>
+      </c>
+      <c r="K21" s="60"/>
+      <c r="L21" s="60"/>
+      <c r="M21" s="45"/>
+      <c r="N21" s="60" t="s">
+        <v>54</v>
+      </c>
+      <c r="O21" s="50" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="64" t="s">
+        <v>164</v>
+      </c>
+      <c r="B22" s="58" t="s">
+        <v>165</v>
+      </c>
+      <c r="C22" s="46" t="s">
+        <v>82</v>
+      </c>
+      <c r="D22" s="61" t="s">
+        <v>166</v>
+      </c>
+      <c r="E22" s="67" t="s">
+        <v>167</v>
+      </c>
+      <c r="F22" s="60" t="s">
+        <v>162</v>
+      </c>
+      <c r="G22" s="47" t="s">
+        <v>98</v>
+      </c>
+      <c r="H22" s="59" t="s">
+        <v>98</v>
+      </c>
+      <c r="I22" s="66" t="s">
+        <v>46</v>
+      </c>
+      <c r="J22" s="45" t="s">
+        <v>21</v>
+      </c>
+      <c r="K22" s="60"/>
+      <c r="L22" s="60"/>
+      <c r="M22" s="45"/>
+      <c r="N22" s="60" t="s">
+        <v>54</v>
+      </c>
+      <c r="O22" s="67" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="44" t="s">
+        <v>169</v>
+      </c>
+      <c r="B23" s="58" t="s">
+        <v>170</v>
+      </c>
+      <c r="C23" s="46" t="s">
         <v>49</v>
       </c>
-      <c r="D20" s="46" t="s">
-        <v>152</v>
-      </c>
-      <c r="E20" s="46" t="s">
-        <v>153</v>
-      </c>
-      <c r="F20" s="46" t="s">
-        <v>154</v>
-      </c>
-      <c r="G20" s="46" t="s">
-        <v>85</v>
-      </c>
-      <c r="H20" s="58" t="s">
-        <v>85</v>
-      </c>
-      <c r="I20" s="60"/>
-      <c r="J20" s="58"/>
-      <c r="K20" s="59"/>
-      <c r="L20" s="59"/>
-      <c r="M20" s="44"/>
-      <c r="N20" s="59"/>
-      <c r="O20" s="49" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="64" t="s">
-        <v>155</v>
-      </c>
-      <c r="B21" s="57" t="s">
-        <v>156</v>
-      </c>
-      <c r="C21" s="45" t="s">
-        <v>49</v>
-      </c>
-      <c r="D21" s="46" t="s">
-        <v>157</v>
-      </c>
-      <c r="E21" s="46" t="s">
-        <v>158</v>
-      </c>
-      <c r="F21" s="46" t="s">
-        <v>159</v>
-      </c>
-      <c r="G21" s="46" t="s">
+      <c r="D23" s="47" t="s">
+        <v>171</v>
+      </c>
+      <c r="E23" s="47" t="s">
+        <v>172</v>
+      </c>
+      <c r="F23" s="47" t="s">
+        <v>173</v>
+      </c>
+      <c r="G23" s="47" t="s">
         <v>44</v>
       </c>
-      <c r="H21" s="58" t="s">
-        <v>160</v>
-      </c>
-      <c r="I21" s="46" t="s">
+      <c r="H23" s="47" t="s">
+        <v>174</v>
+      </c>
+      <c r="I23" s="47" t="s">
+        <v>175</v>
+      </c>
+      <c r="J23" s="47" t="s">
+        <v>21</v>
+      </c>
+      <c r="K23" s="60"/>
+      <c r="L23" s="60"/>
+      <c r="M23" s="45"/>
+      <c r="N23" s="60"/>
+      <c r="O23" s="50"/>
+    </row>
+    <row r="24" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="44" t="s">
+        <v>176</v>
+      </c>
+      <c r="B24" s="58" t="s">
+        <v>177</v>
+      </c>
+      <c r="C24" s="46" t="s">
+        <v>82</v>
+      </c>
+      <c r="D24" s="47" t="s">
+        <v>178</v>
+      </c>
+      <c r="E24" s="47" t="s">
+        <v>179</v>
+      </c>
+      <c r="F24" s="47" t="s">
+        <v>180</v>
+      </c>
+      <c r="G24" s="47" t="s">
+        <v>44</v>
+      </c>
+      <c r="H24" s="48" t="s">
+        <v>181</v>
+      </c>
+      <c r="I24" s="47" t="s">
+        <v>175</v>
+      </c>
+      <c r="J24" s="45" t="s">
+        <v>21</v>
+      </c>
+      <c r="K24" s="60"/>
+      <c r="L24" s="60"/>
+      <c r="M24" s="45"/>
+      <c r="N24" s="60"/>
+      <c r="O24" s="50"/>
+    </row>
+    <row r="25" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="44" t="s">
+        <v>182</v>
+      </c>
+      <c r="B25" s="58" t="s">
+        <v>183</v>
+      </c>
+      <c r="C25" s="46" t="s">
+        <v>82</v>
+      </c>
+      <c r="D25" s="47" t="s">
+        <v>184</v>
+      </c>
+      <c r="E25" s="47" t="s">
+        <v>185</v>
+      </c>
+      <c r="F25" s="47" t="s">
+        <v>186</v>
+      </c>
+      <c r="G25" s="47" t="s">
+        <v>44</v>
+      </c>
+      <c r="H25" s="47" t="s">
+        <v>187</v>
+      </c>
+      <c r="I25" s="47" t="s">
+        <v>175</v>
+      </c>
+      <c r="J25" s="47" t="s">
+        <v>21</v>
+      </c>
+      <c r="K25" s="60"/>
+      <c r="L25" s="60"/>
+      <c r="M25" s="45"/>
+      <c r="N25" s="60"/>
+      <c r="O25" s="50"/>
+    </row>
+    <row r="26" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="68" t="s">
+        <v>188</v>
+      </c>
+      <c r="B26" s="58" t="s">
+        <v>189</v>
+      </c>
+      <c r="C26" s="69" t="s">
+        <v>40</v>
+      </c>
+      <c r="D26" s="70" t="s">
+        <v>190</v>
+      </c>
+      <c r="E26" s="70" t="s">
+        <v>191</v>
+      </c>
+      <c r="F26" s="70" t="s">
+        <v>162</v>
+      </c>
+      <c r="G26" s="70" t="s">
+        <v>44</v>
+      </c>
+      <c r="H26" s="71" t="s">
+        <v>192</v>
+      </c>
+      <c r="I26" s="70" t="s">
         <v>53</v>
       </c>
-      <c r="J21" s="44" t="s">
+      <c r="J26" s="72" t="s">
         <v>21</v>
       </c>
-      <c r="K21" s="59"/>
-      <c r="L21" s="59"/>
-      <c r="M21" s="44"/>
-      <c r="N21" s="59"/>
-      <c r="O21" s="49"/>
-    </row>
-    <row r="22" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="64" t="s">
-        <v>161</v>
-      </c>
-      <c r="B22" s="57" t="s">
-        <v>162</v>
-      </c>
-      <c r="C22" s="45" t="s">
-        <v>40</v>
-      </c>
-      <c r="D22" s="46" t="s">
-        <v>163</v>
-      </c>
-      <c r="E22" s="46" t="s">
-        <v>164</v>
-      </c>
-      <c r="F22" s="46" t="s">
-        <v>165</v>
-      </c>
-      <c r="G22" s="46" t="s">
-        <v>44</v>
-      </c>
-      <c r="H22" s="66" t="s">
-        <v>166</v>
-      </c>
-      <c r="I22" s="66" t="s">
-        <v>167</v>
-      </c>
-      <c r="J22" s="66" t="s">
-        <v>21</v>
-      </c>
-      <c r="K22" s="59"/>
-      <c r="L22" s="59"/>
-      <c r="M22" s="44"/>
-      <c r="N22" s="59"/>
-      <c r="O22" s="49"/>
-    </row>
-    <row r="23" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="64" t="s">
-        <v>168</v>
-      </c>
-      <c r="B23" s="57" t="s">
-        <v>169</v>
-      </c>
-      <c r="C23" s="45" t="s">
-        <v>40</v>
-      </c>
-      <c r="D23" s="46" t="s">
-        <v>170</v>
-      </c>
-      <c r="E23" s="46" t="s">
-        <v>171</v>
-      </c>
-      <c r="F23" s="46" t="s">
-        <v>172</v>
-      </c>
-      <c r="G23" s="46" t="s">
-        <v>44</v>
-      </c>
-      <c r="H23" s="58" t="s">
-        <v>173</v>
-      </c>
-      <c r="I23" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="J23" s="44" t="s">
-        <v>21</v>
-      </c>
-      <c r="K23" s="59"/>
-      <c r="L23" s="59"/>
-      <c r="M23" s="44"/>
-      <c r="N23" s="59"/>
-      <c r="O23" s="49"/>
-    </row>
-    <row r="24" customFormat="false" ht="150" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="64" t="s">
-        <v>174</v>
-      </c>
-      <c r="B24" s="57" t="s">
-        <v>175</v>
-      </c>
-      <c r="C24" s="45" t="s">
-        <v>89</v>
-      </c>
-      <c r="D24" s="67" t="s">
-        <v>176</v>
-      </c>
-      <c r="E24" s="67" t="s">
-        <v>177</v>
-      </c>
-      <c r="F24" s="59" t="s">
-        <v>178</v>
-      </c>
-      <c r="G24" s="46" t="s">
-        <v>85</v>
-      </c>
-      <c r="H24" s="58" t="s">
-        <v>85</v>
-      </c>
-      <c r="I24" s="66" t="s">
-        <v>46</v>
-      </c>
-      <c r="J24" s="66" t="s">
-        <v>21</v>
-      </c>
-      <c r="K24" s="59"/>
-      <c r="L24" s="59"/>
-      <c r="M24" s="44"/>
-      <c r="N24" s="59" t="s">
-        <v>54</v>
-      </c>
-      <c r="O24" s="49" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="64" t="s">
-        <v>180</v>
-      </c>
-      <c r="B25" s="57" t="s">
-        <v>181</v>
-      </c>
-      <c r="C25" s="45" t="s">
-        <v>89</v>
-      </c>
-      <c r="D25" s="60" t="s">
-        <v>182</v>
-      </c>
-      <c r="E25" s="67" t="s">
-        <v>183</v>
-      </c>
-      <c r="F25" s="59" t="s">
-        <v>178</v>
-      </c>
-      <c r="G25" s="46" t="s">
-        <v>85</v>
-      </c>
-      <c r="H25" s="58" t="s">
-        <v>85</v>
-      </c>
-      <c r="I25" s="66" t="s">
-        <v>46</v>
-      </c>
-      <c r="J25" s="44" t="s">
-        <v>21</v>
-      </c>
-      <c r="K25" s="59"/>
-      <c r="L25" s="59"/>
-      <c r="M25" s="44"/>
-      <c r="N25" s="59" t="s">
-        <v>54</v>
-      </c>
-      <c r="O25" s="67" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="43" t="s">
-        <v>185</v>
-      </c>
-      <c r="B26" s="57" t="s">
-        <v>186</v>
-      </c>
-      <c r="C26" s="45" t="s">
-        <v>49</v>
-      </c>
-      <c r="D26" s="46" t="s">
-        <v>187</v>
-      </c>
-      <c r="E26" s="46" t="s">
-        <v>188</v>
-      </c>
-      <c r="F26" s="46" t="s">
-        <v>189</v>
-      </c>
-      <c r="G26" s="46" t="s">
-        <v>44</v>
-      </c>
-      <c r="H26" s="46" t="s">
-        <v>190</v>
-      </c>
-      <c r="I26" s="46" t="s">
-        <v>191</v>
-      </c>
-      <c r="J26" s="46" t="s">
-        <v>21</v>
-      </c>
-      <c r="K26" s="59"/>
-      <c r="L26" s="59"/>
-      <c r="M26" s="44"/>
-      <c r="N26" s="59"/>
-      <c r="O26" s="49"/>
-    </row>
-    <row r="27" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="43" t="s">
-        <v>192</v>
-      </c>
-      <c r="B27" s="57" t="s">
-        <v>193</v>
-      </c>
-      <c r="C27" s="45" t="s">
-        <v>89</v>
-      </c>
-      <c r="D27" s="46" t="s">
-        <v>194</v>
-      </c>
-      <c r="E27" s="46" t="s">
-        <v>195</v>
-      </c>
-      <c r="F27" s="46" t="s">
-        <v>196</v>
-      </c>
-      <c r="G27" s="46" t="s">
-        <v>44</v>
-      </c>
-      <c r="H27" s="47" t="s">
-        <v>197</v>
-      </c>
-      <c r="I27" s="46" t="s">
-        <v>191</v>
-      </c>
-      <c r="J27" s="44" t="s">
-        <v>21</v>
-      </c>
-      <c r="K27" s="59"/>
-      <c r="L27" s="59"/>
-      <c r="M27" s="44"/>
-      <c r="N27" s="59"/>
-      <c r="O27" s="49"/>
-    </row>
-    <row r="28" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="43" t="s">
-        <v>198</v>
-      </c>
-      <c r="B28" s="57" t="s">
-        <v>199</v>
-      </c>
-      <c r="C28" s="45" t="s">
-        <v>89</v>
-      </c>
-      <c r="D28" s="46" t="s">
-        <v>200</v>
-      </c>
-      <c r="E28" s="46" t="s">
-        <v>201</v>
-      </c>
-      <c r="F28" s="46" t="s">
-        <v>202</v>
-      </c>
-      <c r="G28" s="46" t="s">
-        <v>44</v>
-      </c>
-      <c r="H28" s="46" t="s">
-        <v>203</v>
-      </c>
-      <c r="I28" s="46" t="s">
-        <v>191</v>
-      </c>
-      <c r="J28" s="46" t="s">
-        <v>21</v>
-      </c>
-      <c r="K28" s="59"/>
-      <c r="L28" s="59"/>
-      <c r="M28" s="44"/>
-      <c r="N28" s="59"/>
-      <c r="O28" s="49"/>
-    </row>
-    <row r="29" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="68" t="s">
-        <v>204</v>
-      </c>
-      <c r="B29" s="57" t="s">
-        <v>205</v>
-      </c>
-      <c r="C29" s="69" t="s">
-        <v>40</v>
-      </c>
-      <c r="D29" s="70" t="s">
-        <v>206</v>
-      </c>
-      <c r="E29" s="70" t="s">
-        <v>207</v>
-      </c>
-      <c r="F29" s="70" t="s">
-        <v>178</v>
-      </c>
-      <c r="G29" s="70" t="s">
-        <v>44</v>
-      </c>
-      <c r="H29" s="71" t="s">
-        <v>208</v>
-      </c>
-      <c r="I29" s="70" t="s">
-        <v>53</v>
-      </c>
-      <c r="J29" s="72" t="s">
-        <v>21</v>
-      </c>
-      <c r="K29" s="73"/>
-      <c r="L29" s="73"/>
-      <c r="M29" s="72"/>
-      <c r="N29" s="73"/>
-      <c r="O29" s="49"/>
-    </row>
-    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K26" s="73"/>
+      <c r="L26" s="73"/>
+      <c r="M26" s="72"/>
+      <c r="N26" s="73"/>
+      <c r="O26" s="50"/>
+    </row>
+    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="74"/>
+      <c r="C27" s="74"/>
+      <c r="D27" s="75"/>
+      <c r="E27" s="76"/>
+      <c r="F27" s="76"/>
+      <c r="G27" s="75"/>
+      <c r="H27" s="77"/>
+      <c r="I27" s="75"/>
+      <c r="J27" s="37"/>
+    </row>
+    <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="74"/>
+      <c r="C28" s="74"/>
+      <c r="D28" s="75"/>
+      <c r="E28" s="78"/>
+      <c r="F28" s="75"/>
+      <c r="G28" s="75"/>
+      <c r="H28" s="77"/>
+      <c r="I28" s="75"/>
+      <c r="J28" s="37"/>
+    </row>
+    <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="74"/>
+      <c r="C29" s="74"/>
+      <c r="D29" s="75"/>
+      <c r="E29" s="78"/>
+      <c r="F29" s="79"/>
+      <c r="G29" s="75"/>
+      <c r="H29" s="77"/>
+      <c r="I29" s="75"/>
+      <c r="J29" s="37"/>
+    </row>
+    <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="74"/>
       <c r="C30" s="74"/>
       <c r="D30" s="75"/>
-      <c r="E30" s="76"/>
-      <c r="F30" s="76"/>
+      <c r="E30" s="78"/>
+      <c r="F30" s="79"/>
       <c r="G30" s="75"/>
       <c r="H30" s="77"/>
       <c r="I30" s="75"/>
-      <c r="J30" s="36"/>
+      <c r="J30" s="37"/>
     </row>
     <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="74"/>
       <c r="C31" s="74"/>
       <c r="D31" s="75"/>
       <c r="E31" s="78"/>
-      <c r="F31" s="75"/>
+      <c r="F31" s="79"/>
       <c r="G31" s="75"/>
       <c r="H31" s="77"/>
       <c r="I31" s="75"/>
-      <c r="J31" s="36"/>
+      <c r="J31" s="37"/>
     </row>
     <row r="32" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="74"/>
       <c r="C32" s="74"/>
       <c r="D32" s="75"/>
       <c r="E32" s="78"/>
-      <c r="F32" s="79"/>
+      <c r="F32" s="75"/>
       <c r="G32" s="75"/>
       <c r="H32" s="77"/>
       <c r="I32" s="75"/>
-      <c r="J32" s="36"/>
+      <c r="J32" s="37"/>
     </row>
     <row r="33" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="74"/>
       <c r="C33" s="74"/>
       <c r="D33" s="75"/>
       <c r="E33" s="78"/>
-      <c r="F33" s="79"/>
+      <c r="F33" s="75"/>
       <c r="G33" s="75"/>
       <c r="H33" s="77"/>
       <c r="I33" s="75"/>
-      <c r="J33" s="36"/>
+      <c r="J33" s="37"/>
     </row>
     <row r="34" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="74"/>
@@ -3469,29 +3345,29 @@
       <c r="G34" s="75"/>
       <c r="H34" s="77"/>
       <c r="I34" s="75"/>
-      <c r="J34" s="36"/>
+      <c r="J34" s="37"/>
     </row>
     <row r="35" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="74"/>
       <c r="C35" s="74"/>
       <c r="D35" s="75"/>
       <c r="E35" s="78"/>
-      <c r="F35" s="75"/>
+      <c r="F35" s="79"/>
       <c r="G35" s="75"/>
       <c r="H35" s="77"/>
       <c r="I35" s="75"/>
-      <c r="J35" s="36"/>
+      <c r="J35" s="37"/>
     </row>
     <row r="36" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="74"/>
       <c r="C36" s="74"/>
       <c r="D36" s="75"/>
       <c r="E36" s="78"/>
-      <c r="F36" s="75"/>
+      <c r="F36" s="79"/>
       <c r="G36" s="75"/>
       <c r="H36" s="77"/>
       <c r="I36" s="75"/>
-      <c r="J36" s="36"/>
+      <c r="J36" s="37"/>
     </row>
     <row r="37" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="74"/>
@@ -3502,7 +3378,7 @@
       <c r="G37" s="75"/>
       <c r="H37" s="77"/>
       <c r="I37" s="75"/>
-      <c r="J37" s="36"/>
+      <c r="J37" s="37"/>
     </row>
     <row r="38" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="74"/>
@@ -3513,7 +3389,7 @@
       <c r="G38" s="75"/>
       <c r="H38" s="77"/>
       <c r="I38" s="75"/>
-      <c r="J38" s="36"/>
+      <c r="J38" s="37"/>
     </row>
     <row r="39" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="74"/>
@@ -3524,51 +3400,51 @@
       <c r="G39" s="75"/>
       <c r="H39" s="77"/>
       <c r="I39" s="75"/>
-      <c r="J39" s="36"/>
+      <c r="J39" s="37"/>
     </row>
     <row r="40" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="74"/>
       <c r="C40" s="74"/>
       <c r="D40" s="75"/>
       <c r="E40" s="78"/>
-      <c r="F40" s="79"/>
+      <c r="F40" s="75"/>
       <c r="G40" s="75"/>
       <c r="H40" s="77"/>
       <c r="I40" s="75"/>
-      <c r="J40" s="36"/>
+      <c r="J40" s="37"/>
     </row>
     <row r="41" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="74"/>
       <c r="C41" s="74"/>
       <c r="D41" s="75"/>
       <c r="E41" s="78"/>
-      <c r="F41" s="79"/>
+      <c r="F41" s="75"/>
       <c r="G41" s="75"/>
       <c r="H41" s="77"/>
       <c r="I41" s="75"/>
-      <c r="J41" s="36"/>
+      <c r="J41" s="37"/>
     </row>
     <row r="42" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="74"/>
       <c r="C42" s="74"/>
       <c r="D42" s="75"/>
       <c r="E42" s="78"/>
-      <c r="F42" s="79"/>
+      <c r="F42" s="75"/>
       <c r="G42" s="75"/>
       <c r="H42" s="77"/>
       <c r="I42" s="75"/>
-      <c r="J42" s="36"/>
+      <c r="J42" s="37"/>
     </row>
     <row r="43" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="74"/>
       <c r="C43" s="74"/>
       <c r="D43" s="75"/>
       <c r="E43" s="78"/>
-      <c r="F43" s="75"/>
+      <c r="F43" s="79"/>
       <c r="G43" s="75"/>
       <c r="H43" s="77"/>
       <c r="I43" s="75"/>
-      <c r="J43" s="36"/>
+      <c r="J43" s="37"/>
     </row>
     <row r="44" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="74"/>
@@ -3579,7 +3455,7 @@
       <c r="G44" s="75"/>
       <c r="H44" s="77"/>
       <c r="I44" s="75"/>
-      <c r="J44" s="36"/>
+      <c r="J44" s="37"/>
     </row>
     <row r="45" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="74"/>
@@ -3590,7 +3466,7 @@
       <c r="G45" s="75"/>
       <c r="H45" s="77"/>
       <c r="I45" s="75"/>
-      <c r="J45" s="36"/>
+      <c r="J45" s="37"/>
     </row>
     <row r="46" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="74"/>
@@ -3601,29 +3477,29 @@
       <c r="G46" s="75"/>
       <c r="H46" s="77"/>
       <c r="I46" s="75"/>
-      <c r="J46" s="36"/>
+      <c r="J46" s="37"/>
     </row>
     <row r="47" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="74"/>
       <c r="C47" s="74"/>
       <c r="D47" s="75"/>
       <c r="E47" s="78"/>
-      <c r="F47" s="75"/>
+      <c r="F47" s="79"/>
       <c r="G47" s="75"/>
       <c r="H47" s="77"/>
       <c r="I47" s="75"/>
-      <c r="J47" s="36"/>
+      <c r="J47" s="37"/>
     </row>
     <row r="48" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="74"/>
       <c r="C48" s="74"/>
       <c r="D48" s="75"/>
       <c r="E48" s="78"/>
-      <c r="F48" s="75"/>
+      <c r="F48" s="79"/>
       <c r="G48" s="75"/>
       <c r="H48" s="77"/>
       <c r="I48" s="75"/>
-      <c r="J48" s="36"/>
+      <c r="J48" s="37"/>
     </row>
     <row r="49" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="74"/>
@@ -3634,40 +3510,40 @@
       <c r="G49" s="75"/>
       <c r="H49" s="77"/>
       <c r="I49" s="75"/>
-      <c r="J49" s="36"/>
+      <c r="J49" s="37"/>
     </row>
     <row r="50" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="74"/>
       <c r="C50" s="74"/>
       <c r="D50" s="75"/>
       <c r="E50" s="78"/>
-      <c r="F50" s="79"/>
+      <c r="F50" s="75"/>
       <c r="G50" s="75"/>
       <c r="H50" s="77"/>
       <c r="I50" s="75"/>
-      <c r="J50" s="36"/>
+      <c r="J50" s="37"/>
     </row>
     <row r="51" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="74"/>
       <c r="C51" s="74"/>
       <c r="D51" s="75"/>
       <c r="E51" s="78"/>
-      <c r="F51" s="79"/>
+      <c r="F51" s="75"/>
       <c r="G51" s="75"/>
       <c r="H51" s="77"/>
       <c r="I51" s="75"/>
-      <c r="J51" s="36"/>
+      <c r="J51" s="37"/>
     </row>
     <row r="52" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="74"/>
       <c r="C52" s="74"/>
       <c r="D52" s="75"/>
       <c r="E52" s="78"/>
-      <c r="F52" s="79"/>
+      <c r="F52" s="75"/>
       <c r="G52" s="75"/>
       <c r="H52" s="77"/>
       <c r="I52" s="75"/>
-      <c r="J52" s="36"/>
+      <c r="J52" s="37"/>
     </row>
     <row r="53" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="74"/>
@@ -3678,7 +3554,7 @@
       <c r="G53" s="75"/>
       <c r="H53" s="77"/>
       <c r="I53" s="75"/>
-      <c r="J53" s="36"/>
+      <c r="J53" s="37"/>
     </row>
     <row r="54" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="74"/>
@@ -3689,7 +3565,7 @@
       <c r="G54" s="75"/>
       <c r="H54" s="77"/>
       <c r="I54" s="75"/>
-      <c r="J54" s="36"/>
+      <c r="J54" s="37"/>
     </row>
     <row r="55" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="74"/>
@@ -3700,7 +3576,7 @@
       <c r="G55" s="75"/>
       <c r="H55" s="77"/>
       <c r="I55" s="75"/>
-      <c r="J55" s="36"/>
+      <c r="J55" s="37"/>
     </row>
     <row r="56" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="74"/>
@@ -3711,7 +3587,7 @@
       <c r="G56" s="75"/>
       <c r="H56" s="77"/>
       <c r="I56" s="75"/>
-      <c r="J56" s="36"/>
+      <c r="J56" s="37"/>
     </row>
     <row r="57" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="74"/>
@@ -3722,7 +3598,7 @@
       <c r="G57" s="75"/>
       <c r="H57" s="77"/>
       <c r="I57" s="75"/>
-      <c r="J57" s="36"/>
+      <c r="J57" s="37"/>
     </row>
     <row r="58" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="74"/>
@@ -3733,7 +3609,7 @@
       <c r="G58" s="75"/>
       <c r="H58" s="77"/>
       <c r="I58" s="75"/>
-      <c r="J58" s="36"/>
+      <c r="J58" s="37"/>
     </row>
     <row r="59" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="74"/>
@@ -3744,7 +3620,7 @@
       <c r="G59" s="75"/>
       <c r="H59" s="77"/>
       <c r="I59" s="75"/>
-      <c r="J59" s="36"/>
+      <c r="J59" s="37"/>
     </row>
     <row r="60" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="74"/>
@@ -3755,7 +3631,7 @@
       <c r="G60" s="75"/>
       <c r="H60" s="77"/>
       <c r="I60" s="75"/>
-      <c r="J60" s="36"/>
+      <c r="J60" s="37"/>
     </row>
     <row r="61" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="74"/>
@@ -3766,7 +3642,7 @@
       <c r="G61" s="75"/>
       <c r="H61" s="77"/>
       <c r="I61" s="75"/>
-      <c r="J61" s="36"/>
+      <c r="J61" s="37"/>
     </row>
     <row r="62" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="74"/>
@@ -3777,7 +3653,7 @@
       <c r="G62" s="75"/>
       <c r="H62" s="77"/>
       <c r="I62" s="75"/>
-      <c r="J62" s="36"/>
+      <c r="J62" s="37"/>
     </row>
     <row r="63" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="74"/>
@@ -3788,7 +3664,7 @@
       <c r="G63" s="75"/>
       <c r="H63" s="77"/>
       <c r="I63" s="75"/>
-      <c r="J63" s="36"/>
+      <c r="J63" s="37"/>
     </row>
     <row r="64" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="74"/>
@@ -3799,7 +3675,7 @@
       <c r="G64" s="75"/>
       <c r="H64" s="77"/>
       <c r="I64" s="75"/>
-      <c r="J64" s="36"/>
+      <c r="J64" s="37"/>
     </row>
     <row r="65" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="74"/>
@@ -3810,73 +3686,73 @@
       <c r="G65" s="75"/>
       <c r="H65" s="77"/>
       <c r="I65" s="75"/>
-      <c r="J65" s="36"/>
+      <c r="J65" s="37"/>
     </row>
     <row r="66" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="74"/>
       <c r="C66" s="74"/>
-      <c r="D66" s="75"/>
-      <c r="E66" s="78"/>
-      <c r="F66" s="75"/>
+      <c r="D66" s="79"/>
+      <c r="E66" s="80"/>
+      <c r="F66" s="79"/>
       <c r="G66" s="75"/>
       <c r="H66" s="77"/>
       <c r="I66" s="75"/>
-      <c r="J66" s="36"/>
+      <c r="J66" s="37"/>
     </row>
     <row r="67" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="74"/>
       <c r="C67" s="74"/>
-      <c r="D67" s="75"/>
-      <c r="E67" s="78"/>
-      <c r="F67" s="75"/>
+      <c r="D67" s="79"/>
+      <c r="E67" s="80"/>
+      <c r="F67" s="79"/>
       <c r="G67" s="75"/>
       <c r="H67" s="77"/>
       <c r="I67" s="75"/>
-      <c r="J67" s="36"/>
+      <c r="J67" s="37"/>
     </row>
     <row r="68" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="74"/>
       <c r="C68" s="74"/>
       <c r="D68" s="75"/>
       <c r="E68" s="78"/>
-      <c r="F68" s="75"/>
+      <c r="F68" s="79"/>
       <c r="G68" s="75"/>
       <c r="H68" s="77"/>
       <c r="I68" s="75"/>
-      <c r="J68" s="36"/>
+      <c r="J68" s="37"/>
     </row>
     <row r="69" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="74"/>
       <c r="C69" s="74"/>
-      <c r="D69" s="79"/>
-      <c r="E69" s="80"/>
-      <c r="F69" s="79"/>
+      <c r="D69" s="75"/>
+      <c r="E69" s="78"/>
+      <c r="F69" s="75"/>
       <c r="G69" s="75"/>
       <c r="H69" s="77"/>
       <c r="I69" s="75"/>
-      <c r="J69" s="36"/>
+      <c r="J69" s="37"/>
     </row>
     <row r="70" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="74"/>
       <c r="C70" s="74"/>
-      <c r="D70" s="79"/>
-      <c r="E70" s="80"/>
-      <c r="F70" s="79"/>
+      <c r="D70" s="75"/>
+      <c r="E70" s="78"/>
+      <c r="F70" s="75"/>
       <c r="G70" s="75"/>
       <c r="H70" s="77"/>
       <c r="I70" s="75"/>
-      <c r="J70" s="36"/>
+      <c r="J70" s="37"/>
     </row>
     <row r="71" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="74"/>
       <c r="C71" s="74"/>
       <c r="D71" s="75"/>
       <c r="E71" s="78"/>
-      <c r="F71" s="79"/>
+      <c r="F71" s="75"/>
       <c r="G71" s="75"/>
       <c r="H71" s="77"/>
       <c r="I71" s="75"/>
-      <c r="J71" s="36"/>
+      <c r="J71" s="37"/>
     </row>
     <row r="72" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="74"/>
@@ -3887,73 +3763,73 @@
       <c r="G72" s="75"/>
       <c r="H72" s="77"/>
       <c r="I72" s="75"/>
-      <c r="J72" s="36"/>
+      <c r="J72" s="37"/>
     </row>
     <row r="73" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="74"/>
       <c r="C73" s="74"/>
-      <c r="D73" s="75"/>
-      <c r="E73" s="78"/>
+      <c r="D73" s="79"/>
+      <c r="E73" s="80"/>
       <c r="F73" s="75"/>
       <c r="G73" s="75"/>
       <c r="H73" s="77"/>
-      <c r="I73" s="75"/>
-      <c r="J73" s="36"/>
+      <c r="I73" s="79"/>
+      <c r="J73" s="37"/>
     </row>
     <row r="74" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="74"/>
       <c r="C74" s="74"/>
-      <c r="D74" s="75"/>
-      <c r="E74" s="78"/>
+      <c r="D74" s="79"/>
+      <c r="E74" s="80"/>
       <c r="F74" s="75"/>
       <c r="G74" s="75"/>
       <c r="H74" s="77"/>
-      <c r="I74" s="75"/>
-      <c r="J74" s="36"/>
+      <c r="I74" s="79"/>
+      <c r="J74" s="37"/>
     </row>
     <row r="75" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="74"/>
       <c r="C75" s="74"/>
-      <c r="D75" s="75"/>
-      <c r="E75" s="78"/>
+      <c r="D75" s="79"/>
+      <c r="E75" s="80"/>
       <c r="F75" s="75"/>
       <c r="G75" s="75"/>
       <c r="H75" s="77"/>
-      <c r="I75" s="75"/>
-      <c r="J75" s="36"/>
+      <c r="I75" s="79"/>
+      <c r="J75" s="37"/>
     </row>
     <row r="76" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="74"/>
       <c r="C76" s="74"/>
-      <c r="D76" s="79"/>
-      <c r="E76" s="80"/>
+      <c r="D76" s="75"/>
+      <c r="E76" s="78"/>
       <c r="F76" s="75"/>
       <c r="G76" s="75"/>
       <c r="H76" s="77"/>
-      <c r="I76" s="79"/>
-      <c r="J76" s="36"/>
+      <c r="I76" s="75"/>
+      <c r="J76" s="37"/>
     </row>
     <row r="77" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="74"/>
       <c r="C77" s="74"/>
-      <c r="D77" s="79"/>
-      <c r="E77" s="80"/>
+      <c r="D77" s="75"/>
+      <c r="E77" s="78"/>
       <c r="F77" s="75"/>
       <c r="G77" s="75"/>
       <c r="H77" s="77"/>
-      <c r="I77" s="79"/>
-      <c r="J77" s="36"/>
+      <c r="I77" s="75"/>
+      <c r="J77" s="37"/>
     </row>
     <row r="78" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="74"/>
       <c r="C78" s="74"/>
-      <c r="D78" s="79"/>
-      <c r="E78" s="80"/>
+      <c r="D78" s="75"/>
+      <c r="E78" s="78"/>
       <c r="F78" s="75"/>
       <c r="G78" s="75"/>
       <c r="H78" s="77"/>
       <c r="I78" s="79"/>
-      <c r="J78" s="36"/>
+      <c r="J78" s="37"/>
     </row>
     <row r="79" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="74"/>
@@ -3964,7 +3840,7 @@
       <c r="G79" s="75"/>
       <c r="H79" s="77"/>
       <c r="I79" s="75"/>
-      <c r="J79" s="36"/>
+      <c r="J79" s="37"/>
     </row>
     <row r="80" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="74"/>
@@ -3975,7 +3851,7 @@
       <c r="G80" s="75"/>
       <c r="H80" s="77"/>
       <c r="I80" s="75"/>
-      <c r="J80" s="36"/>
+      <c r="J80" s="37"/>
     </row>
     <row r="81" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="74"/>
@@ -3985,93 +3861,93 @@
       <c r="F81" s="75"/>
       <c r="G81" s="75"/>
       <c r="H81" s="77"/>
-      <c r="I81" s="79"/>
-      <c r="J81" s="36"/>
+      <c r="I81" s="75"/>
+      <c r="J81" s="37"/>
     </row>
     <row r="82" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="74"/>
       <c r="C82" s="74"/>
-      <c r="D82" s="75"/>
-      <c r="E82" s="78"/>
-      <c r="F82" s="75"/>
+      <c r="D82" s="79"/>
+      <c r="E82" s="80"/>
+      <c r="F82" s="79"/>
       <c r="G82" s="75"/>
       <c r="H82" s="77"/>
-      <c r="I82" s="75"/>
-      <c r="J82" s="36"/>
+      <c r="I82" s="79"/>
+      <c r="J82" s="37"/>
     </row>
     <row r="83" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="74"/>
       <c r="C83" s="74"/>
-      <c r="D83" s="75"/>
-      <c r="E83" s="78"/>
+      <c r="D83" s="79"/>
+      <c r="E83" s="80"/>
       <c r="F83" s="75"/>
       <c r="G83" s="75"/>
       <c r="H83" s="77"/>
-      <c r="I83" s="75"/>
-      <c r="J83" s="36"/>
+      <c r="I83" s="79"/>
+      <c r="J83" s="37"/>
     </row>
     <row r="84" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="74"/>
       <c r="C84" s="74"/>
-      <c r="D84" s="75"/>
-      <c r="E84" s="78"/>
+      <c r="D84" s="79"/>
+      <c r="E84" s="80"/>
       <c r="F84" s="75"/>
       <c r="G84" s="75"/>
       <c r="H84" s="77"/>
-      <c r="I84" s="75"/>
-      <c r="J84" s="36"/>
-    </row>
-    <row r="85" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="74"/>
-      <c r="C85" s="74"/>
+      <c r="I84" s="79"/>
+      <c r="J84" s="37"/>
+    </row>
+    <row r="85" s="37" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="75"/>
+      <c r="C85" s="75"/>
       <c r="D85" s="79"/>
       <c r="E85" s="80"/>
-      <c r="F85" s="79"/>
+      <c r="F85" s="75"/>
       <c r="G85" s="75"/>
       <c r="H85" s="77"/>
       <c r="I85" s="79"/>
-      <c r="J85" s="36"/>
-    </row>
-    <row r="86" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="74"/>
-      <c r="C86" s="74"/>
+    </row>
+    <row r="86" s="37" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="75"/>
+      <c r="C86" s="75"/>
       <c r="D86" s="79"/>
       <c r="E86" s="80"/>
       <c r="F86" s="75"/>
       <c r="G86" s="75"/>
-      <c r="H86" s="77"/>
       <c r="I86" s="79"/>
-      <c r="J86" s="36"/>
     </row>
     <row r="87" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="74"/>
       <c r="C87" s="74"/>
       <c r="D87" s="79"/>
       <c r="E87" s="80"/>
-      <c r="F87" s="75"/>
+      <c r="F87" s="79"/>
       <c r="G87" s="75"/>
       <c r="H87" s="77"/>
       <c r="I87" s="79"/>
-      <c r="J87" s="36"/>
-    </row>
-    <row r="88" s="36" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J87" s="37"/>
+    </row>
+    <row r="88" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="75"/>
-      <c r="C88" s="75"/>
+      <c r="C88" s="74"/>
       <c r="D88" s="79"/>
       <c r="E88" s="80"/>
-      <c r="F88" s="75"/>
+      <c r="F88" s="79"/>
       <c r="G88" s="75"/>
       <c r="H88" s="77"/>
       <c r="I88" s="79"/>
-    </row>
-    <row r="89" s="36" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="75"/>
-      <c r="C89" s="75"/>
+      <c r="J88" s="37"/>
+    </row>
+    <row r="89" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="74"/>
+      <c r="C89" s="74"/>
       <c r="D89" s="79"/>
       <c r="E89" s="80"/>
-      <c r="F89" s="75"/>
+      <c r="F89" s="79"/>
       <c r="G89" s="75"/>
+      <c r="H89" s="77"/>
       <c r="I89" s="79"/>
+      <c r="J89" s="37"/>
     </row>
     <row r="90" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="74"/>
@@ -4082,10 +3958,10 @@
       <c r="G90" s="75"/>
       <c r="H90" s="77"/>
       <c r="I90" s="79"/>
-      <c r="J90" s="36"/>
+      <c r="J90" s="37"/>
     </row>
     <row r="91" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="75"/>
+      <c r="A91" s="74"/>
       <c r="C91" s="74"/>
       <c r="D91" s="79"/>
       <c r="E91" s="80"/>
@@ -4093,7 +3969,7 @@
       <c r="G91" s="75"/>
       <c r="H91" s="77"/>
       <c r="I91" s="79"/>
-      <c r="J91" s="36"/>
+      <c r="J91" s="37"/>
     </row>
     <row r="92" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="74"/>
@@ -4104,7 +3980,7 @@
       <c r="G92" s="75"/>
       <c r="H92" s="77"/>
       <c r="I92" s="79"/>
-      <c r="J92" s="36"/>
+      <c r="J92" s="37"/>
     </row>
     <row r="93" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="74"/>
@@ -4115,7 +3991,7 @@
       <c r="G93" s="75"/>
       <c r="H93" s="77"/>
       <c r="I93" s="79"/>
-      <c r="J93" s="36"/>
+      <c r="J93" s="37"/>
     </row>
     <row r="94" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="74"/>
@@ -4126,51 +4002,51 @@
       <c r="G94" s="75"/>
       <c r="H94" s="77"/>
       <c r="I94" s="79"/>
-      <c r="J94" s="36"/>
+      <c r="J94" s="37"/>
     </row>
     <row r="95" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="74"/>
       <c r="C95" s="74"/>
-      <c r="D95" s="79"/>
-      <c r="E95" s="80"/>
-      <c r="F95" s="79"/>
+      <c r="D95" s="75"/>
+      <c r="E95" s="78"/>
+      <c r="F95" s="75"/>
       <c r="G95" s="75"/>
       <c r="H95" s="77"/>
-      <c r="I95" s="79"/>
-      <c r="J95" s="36"/>
+      <c r="I95" s="75"/>
+      <c r="J95" s="37"/>
     </row>
     <row r="96" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="74"/>
       <c r="C96" s="74"/>
-      <c r="D96" s="79"/>
-      <c r="E96" s="80"/>
-      <c r="F96" s="79"/>
+      <c r="D96" s="75"/>
+      <c r="E96" s="78"/>
+      <c r="F96" s="75"/>
       <c r="G96" s="75"/>
       <c r="H96" s="77"/>
-      <c r="I96" s="79"/>
-      <c r="J96" s="36"/>
+      <c r="I96" s="75"/>
+      <c r="J96" s="37"/>
     </row>
     <row r="97" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="74"/>
       <c r="C97" s="74"/>
-      <c r="D97" s="79"/>
-      <c r="E97" s="80"/>
-      <c r="F97" s="79"/>
+      <c r="D97" s="75"/>
+      <c r="E97" s="78"/>
+      <c r="F97" s="75"/>
       <c r="G97" s="75"/>
       <c r="H97" s="77"/>
-      <c r="I97" s="79"/>
-      <c r="J97" s="36"/>
+      <c r="I97" s="75"/>
+      <c r="J97" s="37"/>
     </row>
     <row r="98" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="74"/>
       <c r="C98" s="74"/>
-      <c r="D98" s="75"/>
-      <c r="E98" s="78"/>
+      <c r="D98" s="79"/>
+      <c r="E98" s="80"/>
       <c r="F98" s="75"/>
-      <c r="G98" s="75"/>
+      <c r="G98" s="79"/>
       <c r="H98" s="77"/>
-      <c r="I98" s="75"/>
-      <c r="J98" s="36"/>
+      <c r="I98" s="79"/>
+      <c r="J98" s="37"/>
     </row>
     <row r="99" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="74"/>
@@ -4178,32 +4054,32 @@
       <c r="D99" s="75"/>
       <c r="E99" s="78"/>
       <c r="F99" s="75"/>
-      <c r="G99" s="75"/>
+      <c r="G99" s="79"/>
       <c r="H99" s="77"/>
       <c r="I99" s="75"/>
-      <c r="J99" s="36"/>
+      <c r="J99" s="37"/>
     </row>
     <row r="100" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="74"/>
       <c r="C100" s="74"/>
-      <c r="D100" s="75"/>
-      <c r="E100" s="78"/>
-      <c r="F100" s="75"/>
-      <c r="G100" s="75"/>
+      <c r="D100" s="79"/>
+      <c r="E100" s="80"/>
+      <c r="F100" s="79"/>
+      <c r="G100" s="79"/>
       <c r="H100" s="77"/>
-      <c r="I100" s="75"/>
-      <c r="J100" s="36"/>
+      <c r="I100" s="79"/>
+      <c r="J100" s="37"/>
     </row>
     <row r="101" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="74"/>
       <c r="C101" s="74"/>
-      <c r="D101" s="79"/>
-      <c r="E101" s="80"/>
+      <c r="D101" s="75"/>
+      <c r="E101" s="78"/>
       <c r="F101" s="75"/>
       <c r="G101" s="79"/>
       <c r="H101" s="77"/>
-      <c r="I101" s="79"/>
-      <c r="J101" s="36"/>
+      <c r="I101" s="75"/>
+      <c r="J101" s="37"/>
     </row>
     <row r="102" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="74"/>
@@ -4214,18 +4090,18 @@
       <c r="G102" s="79"/>
       <c r="H102" s="77"/>
       <c r="I102" s="75"/>
-      <c r="J102" s="36"/>
+      <c r="J102" s="37"/>
     </row>
     <row r="103" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="74"/>
       <c r="C103" s="74"/>
-      <c r="D103" s="79"/>
-      <c r="E103" s="80"/>
-      <c r="F103" s="79"/>
+      <c r="D103" s="75"/>
+      <c r="E103" s="78"/>
+      <c r="F103" s="75"/>
       <c r="G103" s="79"/>
       <c r="H103" s="77"/>
-      <c r="I103" s="79"/>
-      <c r="J103" s="36"/>
+      <c r="I103" s="75"/>
+      <c r="J103" s="37"/>
     </row>
     <row r="104" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="74"/>
@@ -4236,18 +4112,18 @@
       <c r="G104" s="79"/>
       <c r="H104" s="77"/>
       <c r="I104" s="75"/>
-      <c r="J104" s="36"/>
+      <c r="J104" s="37"/>
     </row>
     <row r="105" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="74"/>
       <c r="C105" s="74"/>
-      <c r="D105" s="75"/>
-      <c r="E105" s="78"/>
+      <c r="D105" s="79"/>
+      <c r="E105" s="80"/>
       <c r="F105" s="75"/>
       <c r="G105" s="79"/>
       <c r="H105" s="77"/>
-      <c r="I105" s="75"/>
-      <c r="J105" s="36"/>
+      <c r="I105" s="79"/>
+      <c r="J105" s="37"/>
     </row>
     <row r="106" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="74"/>
@@ -4258,29 +4134,29 @@
       <c r="G106" s="79"/>
       <c r="H106" s="77"/>
       <c r="I106" s="75"/>
-      <c r="J106" s="36"/>
+      <c r="J106" s="37"/>
     </row>
     <row r="107" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="74"/>
       <c r="C107" s="74"/>
-      <c r="D107" s="75"/>
-      <c r="E107" s="78"/>
-      <c r="F107" s="75"/>
+      <c r="D107" s="79"/>
+      <c r="E107" s="80"/>
+      <c r="F107" s="79"/>
       <c r="G107" s="79"/>
       <c r="H107" s="77"/>
-      <c r="I107" s="75"/>
-      <c r="J107" s="36"/>
+      <c r="I107" s="79"/>
+      <c r="J107" s="37"/>
     </row>
     <row r="108" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="74"/>
       <c r="C108" s="74"/>
       <c r="D108" s="79"/>
       <c r="E108" s="80"/>
-      <c r="F108" s="75"/>
+      <c r="F108" s="79"/>
       <c r="G108" s="79"/>
       <c r="H108" s="77"/>
       <c r="I108" s="79"/>
-      <c r="J108" s="36"/>
+      <c r="J108" s="37"/>
     </row>
     <row r="109" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="74"/>
@@ -4291,32 +4167,32 @@
       <c r="G109" s="79"/>
       <c r="H109" s="77"/>
       <c r="I109" s="75"/>
-      <c r="J109" s="36"/>
+      <c r="J109" s="37"/>
     </row>
     <row r="110" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="74"/>
       <c r="C110" s="74"/>
-      <c r="D110" s="79"/>
-      <c r="E110" s="80"/>
-      <c r="F110" s="79"/>
+      <c r="D110" s="75"/>
+      <c r="E110" s="78"/>
+      <c r="F110" s="75"/>
       <c r="G110" s="79"/>
       <c r="H110" s="77"/>
-      <c r="I110" s="79"/>
-      <c r="J110" s="36"/>
+      <c r="I110" s="75"/>
+      <c r="J110" s="37"/>
     </row>
     <row r="111" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="74"/>
       <c r="C111" s="74"/>
-      <c r="D111" s="79"/>
-      <c r="E111" s="80"/>
-      <c r="F111" s="79"/>
+      <c r="D111" s="75"/>
+      <c r="E111" s="78"/>
+      <c r="F111" s="75"/>
       <c r="G111" s="79"/>
       <c r="H111" s="77"/>
-      <c r="I111" s="79"/>
-      <c r="J111" s="36"/>
+      <c r="I111" s="75"/>
+      <c r="J111" s="37"/>
     </row>
     <row r="112" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="74"/>
+      <c r="A112" s="75"/>
       <c r="C112" s="74"/>
       <c r="D112" s="75"/>
       <c r="E112" s="78"/>
@@ -4324,84 +4200,84 @@
       <c r="G112" s="79"/>
       <c r="H112" s="77"/>
       <c r="I112" s="75"/>
-      <c r="J112" s="36"/>
+      <c r="J112" s="37"/>
     </row>
     <row r="113" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="74"/>
       <c r="C113" s="74"/>
-      <c r="D113" s="75"/>
-      <c r="E113" s="78"/>
-      <c r="F113" s="75"/>
+      <c r="D113" s="79"/>
+      <c r="E113" s="80"/>
+      <c r="F113" s="79"/>
       <c r="G113" s="79"/>
       <c r="H113" s="77"/>
       <c r="I113" s="75"/>
-      <c r="J113" s="36"/>
+      <c r="J113" s="37"/>
     </row>
     <row r="114" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="74"/>
       <c r="C114" s="74"/>
       <c r="D114" s="75"/>
       <c r="E114" s="78"/>
-      <c r="F114" s="75"/>
+      <c r="F114" s="79"/>
       <c r="G114" s="79"/>
       <c r="H114" s="77"/>
       <c r="I114" s="75"/>
-      <c r="J114" s="36"/>
+      <c r="J114" s="37"/>
     </row>
     <row r="115" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="75"/>
+      <c r="A115" s="74"/>
       <c r="C115" s="74"/>
       <c r="D115" s="75"/>
       <c r="E115" s="78"/>
-      <c r="F115" s="75"/>
+      <c r="F115" s="79"/>
       <c r="G115" s="79"/>
       <c r="H115" s="77"/>
       <c r="I115" s="75"/>
-      <c r="J115" s="36"/>
+      <c r="J115" s="37"/>
     </row>
     <row r="116" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="74"/>
       <c r="C116" s="74"/>
-      <c r="D116" s="79"/>
-      <c r="E116" s="80"/>
+      <c r="D116" s="75"/>
+      <c r="E116" s="78"/>
       <c r="F116" s="79"/>
       <c r="G116" s="79"/>
       <c r="H116" s="77"/>
       <c r="I116" s="75"/>
-      <c r="J116" s="36"/>
+      <c r="J116" s="37"/>
     </row>
     <row r="117" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="74"/>
       <c r="C117" s="74"/>
       <c r="D117" s="75"/>
       <c r="E117" s="78"/>
-      <c r="F117" s="79"/>
+      <c r="F117" s="75"/>
       <c r="G117" s="79"/>
       <c r="H117" s="77"/>
       <c r="I117" s="75"/>
-      <c r="J117" s="36"/>
+      <c r="J117" s="37"/>
     </row>
     <row r="118" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="74"/>
       <c r="C118" s="74"/>
       <c r="D118" s="75"/>
       <c r="E118" s="78"/>
-      <c r="F118" s="79"/>
+      <c r="F118" s="75"/>
       <c r="G118" s="79"/>
       <c r="H118" s="77"/>
       <c r="I118" s="75"/>
-      <c r="J118" s="36"/>
+      <c r="J118" s="37"/>
     </row>
     <row r="119" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="74"/>
       <c r="C119" s="74"/>
       <c r="D119" s="75"/>
       <c r="E119" s="78"/>
-      <c r="F119" s="79"/>
+      <c r="F119" s="75"/>
       <c r="G119" s="79"/>
       <c r="H119" s="77"/>
       <c r="I119" s="75"/>
-      <c r="J119" s="36"/>
+      <c r="J119" s="37"/>
     </row>
     <row r="120" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="74"/>
@@ -4412,7 +4288,7 @@
       <c r="G120" s="79"/>
       <c r="H120" s="77"/>
       <c r="I120" s="75"/>
-      <c r="J120" s="36"/>
+      <c r="J120" s="37"/>
     </row>
     <row r="121" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="74"/>
@@ -4423,18 +4299,18 @@
       <c r="G121" s="79"/>
       <c r="H121" s="77"/>
       <c r="I121" s="75"/>
-      <c r="J121" s="36"/>
+      <c r="J121" s="37"/>
     </row>
     <row r="122" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="74"/>
       <c r="C122" s="74"/>
-      <c r="D122" s="75"/>
-      <c r="E122" s="78"/>
-      <c r="F122" s="75"/>
+      <c r="D122" s="79"/>
+      <c r="E122" s="80"/>
+      <c r="F122" s="79"/>
       <c r="G122" s="79"/>
       <c r="H122" s="77"/>
-      <c r="I122" s="75"/>
-      <c r="J122" s="36"/>
+      <c r="I122" s="79"/>
+      <c r="J122" s="37"/>
     </row>
     <row r="123" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="74"/>
@@ -4445,7 +4321,7 @@
       <c r="G123" s="79"/>
       <c r="H123" s="77"/>
       <c r="I123" s="75"/>
-      <c r="J123" s="36"/>
+      <c r="J123" s="37"/>
     </row>
     <row r="124" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="74"/>
@@ -4456,7 +4332,7 @@
       <c r="G124" s="79"/>
       <c r="H124" s="77"/>
       <c r="I124" s="75"/>
-      <c r="J124" s="36"/>
+      <c r="J124" s="37"/>
     </row>
     <row r="125" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="74"/>
@@ -4467,7 +4343,7 @@
       <c r="G125" s="79"/>
       <c r="H125" s="77"/>
       <c r="I125" s="79"/>
-      <c r="J125" s="36"/>
+      <c r="J125" s="37"/>
     </row>
     <row r="126" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="74"/>
@@ -4478,7 +4354,7 @@
       <c r="G126" s="79"/>
       <c r="H126" s="77"/>
       <c r="I126" s="75"/>
-      <c r="J126" s="36"/>
+      <c r="J126" s="37"/>
     </row>
     <row r="127" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="74"/>
@@ -4489,18 +4365,18 @@
       <c r="G127" s="79"/>
       <c r="H127" s="77"/>
       <c r="I127" s="75"/>
-      <c r="J127" s="36"/>
+      <c r="J127" s="37"/>
     </row>
     <row r="128" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="74"/>
       <c r="C128" s="74"/>
-      <c r="D128" s="79"/>
-      <c r="E128" s="80"/>
-      <c r="F128" s="79"/>
+      <c r="D128" s="75"/>
+      <c r="E128" s="78"/>
+      <c r="F128" s="75"/>
       <c r="G128" s="79"/>
       <c r="H128" s="77"/>
-      <c r="I128" s="79"/>
-      <c r="J128" s="36"/>
+      <c r="I128" s="75"/>
+      <c r="J128" s="37"/>
     </row>
     <row r="129" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="74"/>
@@ -4511,7 +4387,7 @@
       <c r="G129" s="79"/>
       <c r="H129" s="77"/>
       <c r="I129" s="75"/>
-      <c r="J129" s="36"/>
+      <c r="J129" s="37"/>
     </row>
     <row r="130" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="74"/>
@@ -4522,7 +4398,7 @@
       <c r="G130" s="79"/>
       <c r="H130" s="77"/>
       <c r="I130" s="75"/>
-      <c r="J130" s="36"/>
+      <c r="J130" s="37"/>
     </row>
     <row r="131" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="74"/>
@@ -4533,7 +4409,7 @@
       <c r="G131" s="79"/>
       <c r="H131" s="77"/>
       <c r="I131" s="75"/>
-      <c r="J131" s="36"/>
+      <c r="J131" s="37"/>
     </row>
     <row r="132" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="74"/>
@@ -4544,7 +4420,7 @@
       <c r="G132" s="79"/>
       <c r="H132" s="77"/>
       <c r="I132" s="75"/>
-      <c r="J132" s="36"/>
+      <c r="J132" s="37"/>
     </row>
     <row r="133" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="74"/>
@@ -4555,7 +4431,7 @@
       <c r="G133" s="79"/>
       <c r="H133" s="77"/>
       <c r="I133" s="75"/>
-      <c r="J133" s="36"/>
+      <c r="J133" s="37"/>
     </row>
     <row r="134" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="74"/>
@@ -4566,7 +4442,7 @@
       <c r="G134" s="79"/>
       <c r="H134" s="77"/>
       <c r="I134" s="75"/>
-      <c r="J134" s="36"/>
+      <c r="J134" s="37"/>
     </row>
     <row r="135" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="74"/>
@@ -4577,7 +4453,7 @@
       <c r="G135" s="79"/>
       <c r="H135" s="77"/>
       <c r="I135" s="75"/>
-      <c r="J135" s="36"/>
+      <c r="J135" s="37"/>
     </row>
     <row r="136" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="74"/>
@@ -4588,7 +4464,7 @@
       <c r="G136" s="79"/>
       <c r="H136" s="77"/>
       <c r="I136" s="75"/>
-      <c r="J136" s="36"/>
+      <c r="J136" s="37"/>
     </row>
     <row r="137" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="74"/>
@@ -4599,7 +4475,7 @@
       <c r="G137" s="79"/>
       <c r="H137" s="77"/>
       <c r="I137" s="75"/>
-      <c r="J137" s="36"/>
+      <c r="J137" s="37"/>
     </row>
     <row r="138" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="74"/>
@@ -4610,7 +4486,7 @@
       <c r="G138" s="79"/>
       <c r="H138" s="77"/>
       <c r="I138" s="75"/>
-      <c r="J138" s="36"/>
+      <c r="J138" s="37"/>
     </row>
     <row r="139" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="74"/>
@@ -4621,7 +4497,7 @@
       <c r="G139" s="79"/>
       <c r="H139" s="77"/>
       <c r="I139" s="75"/>
-      <c r="J139" s="36"/>
+      <c r="J139" s="37"/>
     </row>
     <row r="140" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="74"/>
@@ -4632,7 +4508,7 @@
       <c r="G140" s="79"/>
       <c r="H140" s="77"/>
       <c r="I140" s="75"/>
-      <c r="J140" s="36"/>
+      <c r="J140" s="37"/>
     </row>
     <row r="141" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="74"/>
@@ -4643,7 +4519,7 @@
       <c r="G141" s="79"/>
       <c r="H141" s="77"/>
       <c r="I141" s="75"/>
-      <c r="J141" s="36"/>
+      <c r="J141" s="37"/>
     </row>
     <row r="142" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="74"/>
@@ -4654,7 +4530,7 @@
       <c r="G142" s="79"/>
       <c r="H142" s="77"/>
       <c r="I142" s="75"/>
-      <c r="J142" s="36"/>
+      <c r="J142" s="37"/>
     </row>
     <row r="143" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="74"/>
@@ -4665,18 +4541,18 @@
       <c r="G143" s="79"/>
       <c r="H143" s="77"/>
       <c r="I143" s="75"/>
-      <c r="J143" s="36"/>
+      <c r="J143" s="37"/>
     </row>
     <row r="144" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="74"/>
       <c r="C144" s="74"/>
-      <c r="D144" s="75"/>
-      <c r="E144" s="78"/>
-      <c r="F144" s="75"/>
+      <c r="D144" s="79"/>
+      <c r="E144" s="80"/>
+      <c r="F144" s="79"/>
       <c r="G144" s="79"/>
       <c r="H144" s="77"/>
-      <c r="I144" s="75"/>
-      <c r="J144" s="36"/>
+      <c r="I144" s="79"/>
+      <c r="J144" s="37"/>
     </row>
     <row r="145" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="74"/>
@@ -4687,7 +4563,7 @@
       <c r="G145" s="79"/>
       <c r="H145" s="77"/>
       <c r="I145" s="75"/>
-      <c r="J145" s="36"/>
+      <c r="J145" s="37"/>
     </row>
     <row r="146" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="74"/>
@@ -4698,18 +4574,18 @@
       <c r="G146" s="79"/>
       <c r="H146" s="77"/>
       <c r="I146" s="75"/>
-      <c r="J146" s="36"/>
+      <c r="J146" s="37"/>
     </row>
     <row r="147" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="74"/>
       <c r="C147" s="74"/>
-      <c r="D147" s="79"/>
-      <c r="E147" s="80"/>
-      <c r="F147" s="79"/>
+      <c r="D147" s="75"/>
+      <c r="E147" s="78"/>
+      <c r="F147" s="75"/>
       <c r="G147" s="79"/>
       <c r="H147" s="77"/>
-      <c r="I147" s="79"/>
-      <c r="J147" s="36"/>
+      <c r="I147" s="75"/>
+      <c r="J147" s="37"/>
     </row>
     <row r="148" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="74"/>
@@ -4720,7 +4596,7 @@
       <c r="G148" s="79"/>
       <c r="H148" s="77"/>
       <c r="I148" s="75"/>
-      <c r="J148" s="36"/>
+      <c r="J148" s="37"/>
     </row>
     <row r="149" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="74"/>
@@ -4731,7 +4607,7 @@
       <c r="G149" s="79"/>
       <c r="H149" s="77"/>
       <c r="I149" s="75"/>
-      <c r="J149" s="36"/>
+      <c r="J149" s="37"/>
     </row>
     <row r="150" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="74"/>
@@ -4742,7 +4618,7 @@
       <c r="G150" s="79"/>
       <c r="H150" s="77"/>
       <c r="I150" s="75"/>
-      <c r="J150" s="36"/>
+      <c r="J150" s="37"/>
     </row>
     <row r="151" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="74"/>
@@ -4753,7 +4629,7 @@
       <c r="G151" s="79"/>
       <c r="H151" s="77"/>
       <c r="I151" s="75"/>
-      <c r="J151" s="36"/>
+      <c r="J151" s="37"/>
     </row>
     <row r="152" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="74"/>
@@ -4764,7 +4640,7 @@
       <c r="G152" s="79"/>
       <c r="H152" s="77"/>
       <c r="I152" s="75"/>
-      <c r="J152" s="36"/>
+      <c r="J152" s="37"/>
     </row>
     <row r="153" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="74"/>
@@ -4775,7 +4651,7 @@
       <c r="G153" s="79"/>
       <c r="H153" s="77"/>
       <c r="I153" s="75"/>
-      <c r="J153" s="36"/>
+      <c r="J153" s="37"/>
     </row>
     <row r="154" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="74"/>
@@ -4786,18 +4662,18 @@
       <c r="G154" s="79"/>
       <c r="H154" s="77"/>
       <c r="I154" s="75"/>
-      <c r="J154" s="36"/>
+      <c r="J154" s="37"/>
     </row>
     <row r="155" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="74"/>
       <c r="C155" s="74"/>
-      <c r="D155" s="75"/>
-      <c r="E155" s="78"/>
-      <c r="F155" s="75"/>
+      <c r="D155" s="79"/>
+      <c r="E155" s="80"/>
+      <c r="F155" s="79"/>
       <c r="G155" s="79"/>
       <c r="H155" s="77"/>
-      <c r="I155" s="75"/>
-      <c r="J155" s="36"/>
+      <c r="I155" s="79"/>
+      <c r="J155" s="37"/>
     </row>
     <row r="156" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="74"/>
@@ -4808,29 +4684,29 @@
       <c r="G156" s="79"/>
       <c r="H156" s="77"/>
       <c r="I156" s="75"/>
-      <c r="J156" s="36"/>
+      <c r="J156" s="37"/>
     </row>
     <row r="157" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="74"/>
       <c r="C157" s="74"/>
-      <c r="D157" s="75"/>
-      <c r="E157" s="78"/>
-      <c r="F157" s="75"/>
+      <c r="D157" s="79"/>
+      <c r="E157" s="80"/>
+      <c r="F157" s="79"/>
       <c r="G157" s="79"/>
       <c r="H157" s="77"/>
-      <c r="I157" s="75"/>
-      <c r="J157" s="36"/>
+      <c r="I157" s="79"/>
+      <c r="J157" s="37"/>
     </row>
     <row r="158" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="74"/>
       <c r="C158" s="74"/>
-      <c r="D158" s="79"/>
-      <c r="E158" s="80"/>
-      <c r="F158" s="79"/>
+      <c r="D158" s="75"/>
+      <c r="E158" s="78"/>
+      <c r="F158" s="75"/>
       <c r="G158" s="79"/>
       <c r="H158" s="77"/>
-      <c r="I158" s="79"/>
-      <c r="J158" s="36"/>
+      <c r="I158" s="75"/>
+      <c r="J158" s="37"/>
     </row>
     <row r="159" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="74"/>
@@ -4841,18 +4717,18 @@
       <c r="G159" s="79"/>
       <c r="H159" s="77"/>
       <c r="I159" s="75"/>
-      <c r="J159" s="36"/>
+      <c r="J159" s="37"/>
     </row>
     <row r="160" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="74"/>
       <c r="C160" s="74"/>
-      <c r="D160" s="79"/>
-      <c r="E160" s="80"/>
-      <c r="F160" s="79"/>
+      <c r="D160" s="75"/>
+      <c r="E160" s="78"/>
+      <c r="F160" s="75"/>
       <c r="G160" s="79"/>
       <c r="H160" s="77"/>
-      <c r="I160" s="79"/>
-      <c r="J160" s="36"/>
+      <c r="I160" s="75"/>
+      <c r="J160" s="37"/>
     </row>
     <row r="161" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="74"/>
@@ -4863,7 +4739,7 @@
       <c r="G161" s="79"/>
       <c r="H161" s="77"/>
       <c r="I161" s="75"/>
-      <c r="J161" s="36"/>
+      <c r="J161" s="37"/>
     </row>
     <row r="162" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="74"/>
@@ -4874,7 +4750,7 @@
       <c r="G162" s="79"/>
       <c r="H162" s="77"/>
       <c r="I162" s="75"/>
-      <c r="J162" s="36"/>
+      <c r="J162" s="37"/>
     </row>
     <row r="163" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="74"/>
@@ -4885,7 +4761,7 @@
       <c r="G163" s="79"/>
       <c r="H163" s="77"/>
       <c r="I163" s="75"/>
-      <c r="J163" s="36"/>
+      <c r="J163" s="37"/>
     </row>
     <row r="164" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="74"/>
@@ -4896,7 +4772,7 @@
       <c r="G164" s="79"/>
       <c r="H164" s="77"/>
       <c r="I164" s="75"/>
-      <c r="J164" s="36"/>
+      <c r="J164" s="37"/>
     </row>
     <row r="165" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="74"/>
@@ -4907,18 +4783,18 @@
       <c r="G165" s="79"/>
       <c r="H165" s="77"/>
       <c r="I165" s="75"/>
-      <c r="J165" s="36"/>
+      <c r="J165" s="37"/>
     </row>
     <row r="166" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="74"/>
       <c r="C166" s="74"/>
-      <c r="D166" s="75"/>
-      <c r="E166" s="78"/>
-      <c r="F166" s="75"/>
+      <c r="D166" s="79"/>
+      <c r="E166" s="80"/>
+      <c r="F166" s="79"/>
       <c r="G166" s="79"/>
       <c r="H166" s="77"/>
-      <c r="I166" s="75"/>
-      <c r="J166" s="36"/>
+      <c r="I166" s="79"/>
+      <c r="J166" s="37"/>
     </row>
     <row r="167" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="74"/>
@@ -4929,7 +4805,7 @@
       <c r="G167" s="79"/>
       <c r="H167" s="77"/>
       <c r="I167" s="75"/>
-      <c r="J167" s="36"/>
+      <c r="J167" s="37"/>
     </row>
     <row r="168" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="74"/>
@@ -4940,18 +4816,18 @@
       <c r="G168" s="79"/>
       <c r="H168" s="77"/>
       <c r="I168" s="75"/>
-      <c r="J168" s="36"/>
+      <c r="J168" s="37"/>
     </row>
     <row r="169" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="74"/>
       <c r="C169" s="74"/>
-      <c r="D169" s="79"/>
-      <c r="E169" s="80"/>
-      <c r="F169" s="79"/>
+      <c r="D169" s="75"/>
+      <c r="E169" s="78"/>
+      <c r="F169" s="75"/>
       <c r="G169" s="79"/>
       <c r="H169" s="77"/>
-      <c r="I169" s="79"/>
-      <c r="J169" s="36"/>
+      <c r="I169" s="75"/>
+      <c r="J169" s="37"/>
     </row>
     <row r="170" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="74"/>
@@ -4962,7 +4838,7 @@
       <c r="G170" s="79"/>
       <c r="H170" s="77"/>
       <c r="I170" s="75"/>
-      <c r="J170" s="36"/>
+      <c r="J170" s="37"/>
     </row>
     <row r="171" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="74"/>
@@ -4973,18 +4849,18 @@
       <c r="G171" s="79"/>
       <c r="H171" s="77"/>
       <c r="I171" s="75"/>
-      <c r="J171" s="36"/>
+      <c r="J171" s="37"/>
     </row>
     <row r="172" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="74"/>
       <c r="C172" s="74"/>
-      <c r="D172" s="75"/>
-      <c r="E172" s="78"/>
+      <c r="D172" s="79"/>
+      <c r="E172" s="80"/>
       <c r="F172" s="75"/>
       <c r="G172" s="79"/>
       <c r="H172" s="77"/>
-      <c r="I172" s="75"/>
-      <c r="J172" s="36"/>
+      <c r="I172" s="79"/>
+      <c r="J172" s="37"/>
     </row>
     <row r="173" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="74"/>
@@ -4995,7 +4871,7 @@
       <c r="G173" s="79"/>
       <c r="H173" s="77"/>
       <c r="I173" s="75"/>
-      <c r="J173" s="36"/>
+      <c r="J173" s="37"/>
     </row>
     <row r="174" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="74"/>
@@ -5006,29 +4882,29 @@
       <c r="G174" s="79"/>
       <c r="H174" s="77"/>
       <c r="I174" s="75"/>
-      <c r="J174" s="36"/>
+      <c r="J174" s="37"/>
     </row>
     <row r="175" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="74"/>
       <c r="C175" s="74"/>
-      <c r="D175" s="79"/>
-      <c r="E175" s="80"/>
+      <c r="D175" s="75"/>
+      <c r="E175" s="78"/>
       <c r="F175" s="75"/>
       <c r="G175" s="79"/>
       <c r="H175" s="77"/>
-      <c r="I175" s="79"/>
-      <c r="J175" s="36"/>
+      <c r="I175" s="75"/>
+      <c r="J175" s="37"/>
     </row>
     <row r="176" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="74"/>
       <c r="C176" s="74"/>
-      <c r="D176" s="75"/>
-      <c r="E176" s="78"/>
+      <c r="D176" s="79"/>
+      <c r="E176" s="80"/>
       <c r="F176" s="75"/>
       <c r="G176" s="79"/>
       <c r="H176" s="77"/>
-      <c r="I176" s="75"/>
-      <c r="J176" s="36"/>
+      <c r="I176" s="79"/>
+      <c r="J176" s="37"/>
     </row>
     <row r="177" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="74"/>
@@ -5039,29 +4915,29 @@
       <c r="G177" s="79"/>
       <c r="H177" s="77"/>
       <c r="I177" s="75"/>
-      <c r="J177" s="36"/>
+      <c r="J177" s="37"/>
     </row>
     <row r="178" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="74"/>
       <c r="C178" s="74"/>
-      <c r="D178" s="75"/>
-      <c r="E178" s="78"/>
-      <c r="F178" s="75"/>
+      <c r="D178" s="79"/>
+      <c r="E178" s="80"/>
+      <c r="F178" s="79"/>
       <c r="G178" s="79"/>
       <c r="H178" s="77"/>
-      <c r="I178" s="75"/>
-      <c r="J178" s="36"/>
+      <c r="I178" s="79"/>
+      <c r="J178" s="37"/>
     </row>
     <row r="179" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="74"/>
       <c r="C179" s="74"/>
       <c r="D179" s="79"/>
       <c r="E179" s="80"/>
-      <c r="F179" s="75"/>
+      <c r="F179" s="79"/>
       <c r="G179" s="79"/>
       <c r="H179" s="77"/>
       <c r="I179" s="79"/>
-      <c r="J179" s="36"/>
+      <c r="J179" s="37"/>
     </row>
     <row r="180" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="74"/>
@@ -5071,30 +4947,30 @@
       <c r="F180" s="75"/>
       <c r="G180" s="79"/>
       <c r="H180" s="77"/>
-      <c r="I180" s="75"/>
-      <c r="J180" s="36"/>
+      <c r="I180" s="79"/>
+      <c r="J180" s="37"/>
     </row>
     <row r="181" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="74"/>
       <c r="C181" s="74"/>
-      <c r="D181" s="79"/>
-      <c r="E181" s="80"/>
-      <c r="F181" s="79"/>
+      <c r="D181" s="75"/>
+      <c r="E181" s="78"/>
+      <c r="F181" s="75"/>
       <c r="G181" s="79"/>
       <c r="H181" s="77"/>
       <c r="I181" s="79"/>
-      <c r="J181" s="36"/>
+      <c r="J181" s="37"/>
     </row>
     <row r="182" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="74"/>
       <c r="C182" s="74"/>
-      <c r="D182" s="79"/>
-      <c r="E182" s="80"/>
-      <c r="F182" s="79"/>
+      <c r="D182" s="75"/>
+      <c r="E182" s="78"/>
+      <c r="F182" s="75"/>
       <c r="G182" s="79"/>
       <c r="H182" s="77"/>
       <c r="I182" s="79"/>
-      <c r="J182" s="36"/>
+      <c r="J182" s="37"/>
     </row>
     <row r="183" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="74"/>
@@ -5104,8 +4980,8 @@
       <c r="F183" s="75"/>
       <c r="G183" s="79"/>
       <c r="H183" s="77"/>
-      <c r="I183" s="79"/>
-      <c r="J183" s="36"/>
+      <c r="I183" s="75"/>
+      <c r="J183" s="37"/>
     </row>
     <row r="184" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="74"/>
@@ -5115,8 +4991,8 @@
       <c r="F184" s="75"/>
       <c r="G184" s="79"/>
       <c r="H184" s="77"/>
-      <c r="I184" s="79"/>
-      <c r="J184" s="36"/>
+      <c r="I184" s="75"/>
+      <c r="J184" s="37"/>
     </row>
     <row r="185" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="74"/>
@@ -5126,8 +5002,8 @@
       <c r="F185" s="75"/>
       <c r="G185" s="79"/>
       <c r="H185" s="77"/>
-      <c r="I185" s="79"/>
-      <c r="J185" s="36"/>
+      <c r="I185" s="75"/>
+      <c r="J185" s="37"/>
     </row>
     <row r="186" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="74"/>
@@ -5138,40 +5014,40 @@
       <c r="G186" s="79"/>
       <c r="H186" s="77"/>
       <c r="I186" s="75"/>
-      <c r="J186" s="36"/>
+      <c r="J186" s="37"/>
     </row>
     <row r="187" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="74"/>
       <c r="C187" s="74"/>
-      <c r="D187" s="75"/>
-      <c r="E187" s="78"/>
-      <c r="F187" s="75"/>
+      <c r="D187" s="79"/>
+      <c r="E187" s="80"/>
+      <c r="F187" s="79"/>
       <c r="G187" s="79"/>
       <c r="H187" s="77"/>
-      <c r="I187" s="75"/>
-      <c r="J187" s="36"/>
+      <c r="I187" s="79"/>
+      <c r="J187" s="37"/>
     </row>
     <row r="188" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="74"/>
       <c r="C188" s="74"/>
-      <c r="D188" s="75"/>
-      <c r="E188" s="78"/>
-      <c r="F188" s="75"/>
+      <c r="D188" s="79"/>
+      <c r="E188" s="80"/>
+      <c r="F188" s="79"/>
       <c r="G188" s="79"/>
       <c r="H188" s="77"/>
-      <c r="I188" s="75"/>
-      <c r="J188" s="36"/>
+      <c r="I188" s="79"/>
+      <c r="J188" s="37"/>
     </row>
     <row r="189" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="74"/>
       <c r="C189" s="74"/>
-      <c r="D189" s="75"/>
-      <c r="E189" s="78"/>
-      <c r="F189" s="75"/>
+      <c r="D189" s="79"/>
+      <c r="E189" s="80"/>
+      <c r="F189" s="79"/>
       <c r="G189" s="79"/>
       <c r="H189" s="77"/>
-      <c r="I189" s="75"/>
-      <c r="J189" s="36"/>
+      <c r="I189" s="79"/>
+      <c r="J189" s="37"/>
     </row>
     <row r="190" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="74"/>
@@ -5182,62 +5058,62 @@
       <c r="G190" s="79"/>
       <c r="H190" s="77"/>
       <c r="I190" s="79"/>
-      <c r="J190" s="36"/>
+      <c r="J190" s="37"/>
     </row>
     <row r="191" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="74"/>
       <c r="C191" s="74"/>
-      <c r="D191" s="79"/>
+      <c r="D191" s="75"/>
       <c r="E191" s="80"/>
-      <c r="F191" s="79"/>
+      <c r="F191" s="75"/>
       <c r="G191" s="79"/>
       <c r="H191" s="77"/>
-      <c r="I191" s="79"/>
-      <c r="J191" s="36"/>
+      <c r="I191" s="75"/>
+      <c r="J191" s="37"/>
     </row>
     <row r="192" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="74"/>
       <c r="C192" s="74"/>
-      <c r="D192" s="79"/>
+      <c r="D192" s="75"/>
       <c r="E192" s="80"/>
-      <c r="F192" s="79"/>
+      <c r="F192" s="75"/>
       <c r="G192" s="79"/>
       <c r="H192" s="77"/>
-      <c r="I192" s="79"/>
-      <c r="J192" s="36"/>
+      <c r="I192" s="75"/>
+      <c r="J192" s="37"/>
     </row>
     <row r="193" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="74"/>
       <c r="C193" s="74"/>
-      <c r="D193" s="79"/>
-      <c r="E193" s="80"/>
-      <c r="F193" s="79"/>
+      <c r="D193" s="75"/>
+      <c r="E193" s="78"/>
+      <c r="F193" s="75"/>
       <c r="G193" s="79"/>
       <c r="H193" s="77"/>
-      <c r="I193" s="79"/>
-      <c r="J193" s="36"/>
+      <c r="I193" s="75"/>
+      <c r="J193" s="37"/>
     </row>
     <row r="194" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="74"/>
       <c r="C194" s="74"/>
       <c r="D194" s="75"/>
-      <c r="E194" s="80"/>
+      <c r="E194" s="78"/>
       <c r="F194" s="75"/>
       <c r="G194" s="79"/>
       <c r="H194" s="77"/>
       <c r="I194" s="75"/>
-      <c r="J194" s="36"/>
+      <c r="J194" s="37"/>
     </row>
     <row r="195" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="74"/>
       <c r="C195" s="74"/>
       <c r="D195" s="75"/>
-      <c r="E195" s="80"/>
+      <c r="E195" s="78"/>
       <c r="F195" s="75"/>
       <c r="G195" s="79"/>
       <c r="H195" s="77"/>
       <c r="I195" s="75"/>
-      <c r="J195" s="36"/>
+      <c r="J195" s="37"/>
     </row>
     <row r="196" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="74"/>
@@ -5248,7 +5124,7 @@
       <c r="G196" s="79"/>
       <c r="H196" s="77"/>
       <c r="I196" s="75"/>
-      <c r="J196" s="36"/>
+      <c r="J196" s="37"/>
     </row>
     <row r="197" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="74"/>
@@ -5259,7 +5135,7 @@
       <c r="G197" s="79"/>
       <c r="H197" s="77"/>
       <c r="I197" s="75"/>
-      <c r="J197" s="36"/>
+      <c r="J197" s="37"/>
     </row>
     <row r="198" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="74"/>
@@ -5270,73 +5146,73 @@
       <c r="G198" s="79"/>
       <c r="H198" s="77"/>
       <c r="I198" s="75"/>
-      <c r="J198" s="36"/>
+      <c r="J198" s="37"/>
     </row>
     <row r="199" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="74"/>
       <c r="C199" s="74"/>
-      <c r="D199" s="75"/>
-      <c r="E199" s="78"/>
+      <c r="D199" s="79"/>
+      <c r="E199" s="80"/>
       <c r="F199" s="75"/>
       <c r="G199" s="79"/>
       <c r="H199" s="77"/>
-      <c r="I199" s="75"/>
-      <c r="J199" s="36"/>
+      <c r="I199" s="79"/>
+      <c r="J199" s="37"/>
     </row>
     <row r="200" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="74"/>
       <c r="C200" s="74"/>
       <c r="D200" s="75"/>
-      <c r="E200" s="78"/>
+      <c r="E200" s="80"/>
       <c r="F200" s="75"/>
       <c r="G200" s="79"/>
       <c r="H200" s="77"/>
-      <c r="I200" s="75"/>
-      <c r="J200" s="36"/>
+      <c r="I200" s="79"/>
+      <c r="J200" s="37"/>
     </row>
     <row r="201" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="74"/>
       <c r="C201" s="74"/>
       <c r="D201" s="75"/>
-      <c r="E201" s="78"/>
+      <c r="E201" s="80"/>
       <c r="F201" s="75"/>
       <c r="G201" s="79"/>
       <c r="H201" s="77"/>
       <c r="I201" s="75"/>
-      <c r="J201" s="36"/>
+      <c r="J201" s="37"/>
     </row>
     <row r="202" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="74"/>
       <c r="C202" s="74"/>
-      <c r="D202" s="79"/>
-      <c r="E202" s="80"/>
+      <c r="D202" s="75"/>
+      <c r="E202" s="78"/>
       <c r="F202" s="75"/>
       <c r="G202" s="79"/>
       <c r="H202" s="77"/>
-      <c r="I202" s="79"/>
-      <c r="J202" s="36"/>
+      <c r="I202" s="75"/>
+      <c r="J202" s="37"/>
     </row>
     <row r="203" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="74"/>
       <c r="C203" s="74"/>
       <c r="D203" s="75"/>
-      <c r="E203" s="80"/>
+      <c r="E203" s="78"/>
       <c r="F203" s="75"/>
       <c r="G203" s="79"/>
       <c r="H203" s="77"/>
-      <c r="I203" s="79"/>
-      <c r="J203" s="36"/>
+      <c r="I203" s="75"/>
+      <c r="J203" s="37"/>
     </row>
     <row r="204" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="74"/>
       <c r="C204" s="74"/>
       <c r="D204" s="75"/>
-      <c r="E204" s="80"/>
+      <c r="E204" s="78"/>
       <c r="F204" s="75"/>
-      <c r="G204" s="79"/>
+      <c r="G204" s="75"/>
       <c r="H204" s="77"/>
       <c r="I204" s="75"/>
-      <c r="J204" s="36"/>
+      <c r="J204" s="37"/>
     </row>
     <row r="205" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A205" s="74"/>
@@ -5347,7 +5223,7 @@
       <c r="G205" s="79"/>
       <c r="H205" s="77"/>
       <c r="I205" s="75"/>
-      <c r="J205" s="36"/>
+      <c r="J205" s="37"/>
     </row>
     <row r="206" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A206" s="74"/>
@@ -5358,7 +5234,7 @@
       <c r="G206" s="79"/>
       <c r="H206" s="77"/>
       <c r="I206" s="75"/>
-      <c r="J206" s="36"/>
+      <c r="J206" s="37"/>
     </row>
     <row r="207" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A207" s="74"/>
@@ -5366,10 +5242,10 @@
       <c r="D207" s="75"/>
       <c r="E207" s="78"/>
       <c r="F207" s="75"/>
-      <c r="G207" s="75"/>
+      <c r="G207" s="79"/>
       <c r="H207" s="77"/>
       <c r="I207" s="75"/>
-      <c r="J207" s="36"/>
+      <c r="J207" s="37"/>
     </row>
     <row r="208" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="74"/>
@@ -5380,7 +5256,7 @@
       <c r="G208" s="79"/>
       <c r="H208" s="77"/>
       <c r="I208" s="75"/>
-      <c r="J208" s="36"/>
+      <c r="J208" s="37"/>
     </row>
     <row r="209" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A209" s="74"/>
@@ -5391,7 +5267,7 @@
       <c r="G209" s="79"/>
       <c r="H209" s="77"/>
       <c r="I209" s="75"/>
-      <c r="J209" s="36"/>
+      <c r="J209" s="37"/>
     </row>
     <row r="210" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="74"/>
@@ -5402,95 +5278,95 @@
       <c r="G210" s="79"/>
       <c r="H210" s="77"/>
       <c r="I210" s="75"/>
-      <c r="J210" s="36"/>
+      <c r="J210" s="37"/>
     </row>
     <row r="211" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A211" s="74"/>
       <c r="C211" s="74"/>
-      <c r="D211" s="75"/>
-      <c r="E211" s="78"/>
+      <c r="D211" s="79"/>
+      <c r="E211" s="80"/>
       <c r="F211" s="75"/>
       <c r="G211" s="79"/>
       <c r="H211" s="77"/>
       <c r="I211" s="75"/>
-      <c r="J211" s="36"/>
+      <c r="J211" s="37"/>
     </row>
     <row r="212" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A212" s="74"/>
       <c r="C212" s="74"/>
-      <c r="D212" s="75"/>
-      <c r="E212" s="78"/>
-      <c r="F212" s="75"/>
+      <c r="D212" s="79"/>
+      <c r="E212" s="80"/>
+      <c r="F212" s="79"/>
       <c r="G212" s="79"/>
       <c r="H212" s="77"/>
       <c r="I212" s="75"/>
-      <c r="J212" s="36"/>
+      <c r="J212" s="37"/>
     </row>
     <row r="213" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A213" s="74"/>
       <c r="C213" s="74"/>
       <c r="D213" s="75"/>
-      <c r="E213" s="78"/>
+      <c r="E213" s="80"/>
       <c r="F213" s="75"/>
       <c r="G213" s="79"/>
       <c r="H213" s="77"/>
       <c r="I213" s="75"/>
-      <c r="J213" s="36"/>
+      <c r="J213" s="37"/>
     </row>
     <row r="214" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A214" s="74"/>
       <c r="C214" s="74"/>
-      <c r="D214" s="79"/>
+      <c r="D214" s="75"/>
       <c r="E214" s="80"/>
       <c r="F214" s="75"/>
       <c r="G214" s="79"/>
       <c r="H214" s="77"/>
       <c r="I214" s="75"/>
-      <c r="J214" s="36"/>
+      <c r="J214" s="37"/>
     </row>
     <row r="215" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A215" s="74"/>
       <c r="C215" s="74"/>
-      <c r="D215" s="79"/>
-      <c r="E215" s="80"/>
-      <c r="F215" s="79"/>
+      <c r="D215" s="75"/>
+      <c r="E215" s="78"/>
+      <c r="F215" s="75"/>
       <c r="G215" s="79"/>
       <c r="H215" s="77"/>
       <c r="I215" s="75"/>
-      <c r="J215" s="36"/>
+      <c r="J215" s="37"/>
     </row>
     <row r="216" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A216" s="74"/>
       <c r="C216" s="74"/>
       <c r="D216" s="75"/>
-      <c r="E216" s="80"/>
+      <c r="E216" s="78"/>
       <c r="F216" s="75"/>
       <c r="G216" s="79"/>
       <c r="H216" s="77"/>
       <c r="I216" s="75"/>
-      <c r="J216" s="36"/>
+      <c r="J216" s="37"/>
     </row>
     <row r="217" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A217" s="74"/>
       <c r="C217" s="74"/>
       <c r="D217" s="75"/>
-      <c r="E217" s="80"/>
+      <c r="E217" s="78"/>
       <c r="F217" s="75"/>
       <c r="G217" s="79"/>
       <c r="H217" s="77"/>
       <c r="I217" s="75"/>
-      <c r="J217" s="36"/>
+      <c r="J217" s="37"/>
     </row>
     <row r="218" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A218" s="74"/>
       <c r="C218" s="74"/>
-      <c r="D218" s="75"/>
-      <c r="E218" s="78"/>
+      <c r="D218" s="79"/>
+      <c r="E218" s="80"/>
       <c r="F218" s="75"/>
       <c r="G218" s="79"/>
       <c r="H218" s="77"/>
       <c r="I218" s="75"/>
-      <c r="J218" s="36"/>
+      <c r="J218" s="37"/>
     </row>
     <row r="219" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A219" s="74"/>
@@ -5501,7 +5377,7 @@
       <c r="G219" s="79"/>
       <c r="H219" s="77"/>
       <c r="I219" s="75"/>
-      <c r="J219" s="36"/>
+      <c r="J219" s="37"/>
     </row>
     <row r="220" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A220" s="74"/>
@@ -5512,18 +5388,18 @@
       <c r="G220" s="79"/>
       <c r="H220" s="77"/>
       <c r="I220" s="75"/>
-      <c r="J220" s="36"/>
+      <c r="J220" s="37"/>
     </row>
     <row r="221" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A221" s="74"/>
       <c r="C221" s="74"/>
-      <c r="D221" s="79"/>
-      <c r="E221" s="80"/>
+      <c r="D221" s="75"/>
+      <c r="E221" s="78"/>
       <c r="F221" s="75"/>
       <c r="G221" s="79"/>
       <c r="H221" s="77"/>
       <c r="I221" s="75"/>
-      <c r="J221" s="36"/>
+      <c r="J221" s="37"/>
     </row>
     <row r="222" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A222" s="74"/>
@@ -5534,7 +5410,7 @@
       <c r="G222" s="79"/>
       <c r="H222" s="77"/>
       <c r="I222" s="75"/>
-      <c r="J222" s="36"/>
+      <c r="J222" s="37"/>
     </row>
     <row r="223" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A223" s="74"/>
@@ -5545,7 +5421,7 @@
       <c r="G223" s="79"/>
       <c r="H223" s="77"/>
       <c r="I223" s="75"/>
-      <c r="J223" s="36"/>
+      <c r="J223" s="37"/>
     </row>
     <row r="224" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A224" s="74"/>
@@ -5556,7 +5432,7 @@
       <c r="G224" s="79"/>
       <c r="H224" s="77"/>
       <c r="I224" s="75"/>
-      <c r="J224" s="36"/>
+      <c r="J224" s="37"/>
     </row>
     <row r="225" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A225" s="74"/>
@@ -5567,7 +5443,7 @@
       <c r="G225" s="79"/>
       <c r="H225" s="77"/>
       <c r="I225" s="75"/>
-      <c r="J225" s="36"/>
+      <c r="J225" s="37"/>
     </row>
     <row r="226" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A226" s="74"/>
@@ -5578,65 +5454,65 @@
       <c r="G226" s="79"/>
       <c r="H226" s="77"/>
       <c r="I226" s="75"/>
-      <c r="J226" s="36"/>
+      <c r="J226" s="37"/>
     </row>
     <row r="227" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A227" s="74"/>
       <c r="C227" s="74"/>
-      <c r="D227" s="75"/>
-      <c r="E227" s="78"/>
+      <c r="D227" s="79"/>
+      <c r="E227" s="80"/>
       <c r="F227" s="75"/>
       <c r="G227" s="79"/>
       <c r="H227" s="77"/>
       <c r="I227" s="75"/>
-      <c r="J227" s="36"/>
+      <c r="J227" s="37"/>
     </row>
     <row r="228" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A228" s="74"/>
       <c r="C228" s="74"/>
       <c r="D228" s="75"/>
-      <c r="E228" s="78"/>
+      <c r="E228" s="80"/>
       <c r="F228" s="75"/>
       <c r="G228" s="79"/>
       <c r="H228" s="77"/>
       <c r="I228" s="75"/>
-      <c r="J228" s="36"/>
+      <c r="J228" s="37"/>
     </row>
     <row r="229" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A229" s="74"/>
       <c r="C229" s="74"/>
       <c r="D229" s="75"/>
-      <c r="E229" s="78"/>
+      <c r="E229" s="80"/>
       <c r="F229" s="75"/>
       <c r="G229" s="79"/>
       <c r="H229" s="77"/>
       <c r="I229" s="75"/>
-      <c r="J229" s="36"/>
+      <c r="J229" s="37"/>
     </row>
     <row r="230" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A230" s="74"/>
       <c r="C230" s="74"/>
-      <c r="D230" s="79"/>
+      <c r="D230" s="75"/>
       <c r="E230" s="80"/>
       <c r="F230" s="75"/>
       <c r="G230" s="79"/>
       <c r="H230" s="77"/>
       <c r="I230" s="75"/>
-      <c r="J230" s="36"/>
+      <c r="J230" s="37"/>
     </row>
     <row r="231" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A231" s="74"/>
       <c r="C231" s="74"/>
       <c r="D231" s="75"/>
-      <c r="E231" s="80"/>
+      <c r="E231" s="78"/>
       <c r="F231" s="75"/>
       <c r="G231" s="79"/>
       <c r="H231" s="77"/>
       <c r="I231" s="75"/>
-      <c r="J231" s="36"/>
+      <c r="J231" s="37"/>
     </row>
     <row r="232" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A232" s="74"/>
+      <c r="A232" s="75"/>
       <c r="C232" s="74"/>
       <c r="D232" s="75"/>
       <c r="E232" s="80"/>
@@ -5644,18 +5520,18 @@
       <c r="G232" s="79"/>
       <c r="H232" s="77"/>
       <c r="I232" s="75"/>
-      <c r="J232" s="36"/>
+      <c r="J232" s="37"/>
     </row>
     <row r="233" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A233" s="74"/>
       <c r="C233" s="74"/>
       <c r="D233" s="75"/>
-      <c r="E233" s="80"/>
+      <c r="E233" s="78"/>
       <c r="F233" s="75"/>
       <c r="G233" s="79"/>
       <c r="H233" s="77"/>
       <c r="I233" s="75"/>
-      <c r="J233" s="36"/>
+      <c r="J233" s="37"/>
     </row>
     <row r="234" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A234" s="74"/>
@@ -5666,62 +5542,62 @@
       <c r="G234" s="79"/>
       <c r="H234" s="77"/>
       <c r="I234" s="75"/>
-      <c r="J234" s="36"/>
+      <c r="J234" s="37"/>
     </row>
     <row r="235" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A235" s="75"/>
+      <c r="A235" s="74"/>
       <c r="C235" s="74"/>
       <c r="D235" s="75"/>
-      <c r="E235" s="80"/>
+      <c r="E235" s="78"/>
       <c r="F235" s="75"/>
       <c r="G235" s="79"/>
       <c r="H235" s="77"/>
       <c r="I235" s="75"/>
-      <c r="J235" s="36"/>
+      <c r="J235" s="37"/>
     </row>
     <row r="236" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A236" s="74"/>
+      <c r="A236" s="75"/>
       <c r="C236" s="74"/>
       <c r="D236" s="75"/>
-      <c r="E236" s="78"/>
+      <c r="E236" s="80"/>
       <c r="F236" s="75"/>
       <c r="G236" s="79"/>
       <c r="H236" s="77"/>
       <c r="I236" s="75"/>
-      <c r="J236" s="36"/>
+      <c r="J236" s="37"/>
     </row>
     <row r="237" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A237" s="74"/>
       <c r="C237" s="74"/>
       <c r="D237" s="75"/>
-      <c r="E237" s="78"/>
+      <c r="E237" s="80"/>
       <c r="F237" s="75"/>
       <c r="G237" s="79"/>
       <c r="H237" s="77"/>
       <c r="I237" s="75"/>
-      <c r="J237" s="36"/>
+      <c r="J237" s="37"/>
     </row>
     <row r="238" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A238" s="74"/>
       <c r="C238" s="74"/>
-      <c r="D238" s="75"/>
-      <c r="E238" s="78"/>
+      <c r="D238" s="79"/>
+      <c r="E238" s="80"/>
       <c r="F238" s="75"/>
       <c r="G238" s="79"/>
       <c r="H238" s="77"/>
       <c r="I238" s="75"/>
-      <c r="J238" s="36"/>
+      <c r="J238" s="37"/>
     </row>
     <row r="239" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A239" s="75"/>
+      <c r="A239" s="74"/>
       <c r="C239" s="74"/>
       <c r="D239" s="75"/>
-      <c r="E239" s="80"/>
+      <c r="E239" s="78"/>
       <c r="F239" s="75"/>
       <c r="G239" s="79"/>
       <c r="H239" s="77"/>
       <c r="I239" s="75"/>
-      <c r="J239" s="36"/>
+      <c r="J239" s="37"/>
     </row>
     <row r="240" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A240" s="74"/>
@@ -5732,95 +5608,95 @@
       <c r="G240" s="79"/>
       <c r="H240" s="77"/>
       <c r="I240" s="75"/>
-      <c r="J240" s="36"/>
+      <c r="J240" s="37"/>
     </row>
     <row r="241" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A241" s="74"/>
       <c r="C241" s="74"/>
-      <c r="D241" s="79"/>
-      <c r="E241" s="80"/>
+      <c r="D241" s="75"/>
+      <c r="E241" s="78"/>
       <c r="F241" s="75"/>
       <c r="G241" s="79"/>
       <c r="H241" s="77"/>
       <c r="I241" s="75"/>
-      <c r="J241" s="36"/>
+      <c r="J241" s="37"/>
     </row>
     <row r="242" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A242" s="74"/>
       <c r="C242" s="74"/>
-      <c r="D242" s="75"/>
-      <c r="E242" s="78"/>
-      <c r="F242" s="75"/>
+      <c r="D242" s="79"/>
+      <c r="E242" s="80"/>
+      <c r="F242" s="79"/>
       <c r="G242" s="79"/>
       <c r="H242" s="77"/>
       <c r="I242" s="75"/>
-      <c r="J242" s="36"/>
+      <c r="J242" s="37"/>
     </row>
     <row r="243" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A243" s="74"/>
       <c r="C243" s="74"/>
-      <c r="D243" s="75"/>
+      <c r="D243" s="79"/>
       <c r="E243" s="80"/>
-      <c r="F243" s="75"/>
+      <c r="F243" s="79"/>
       <c r="G243" s="79"/>
       <c r="H243" s="77"/>
       <c r="I243" s="75"/>
-      <c r="J243" s="36"/>
+      <c r="J243" s="37"/>
     </row>
     <row r="244" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A244" s="74"/>
       <c r="C244" s="74"/>
-      <c r="D244" s="75"/>
-      <c r="E244" s="78"/>
-      <c r="F244" s="75"/>
+      <c r="D244" s="79"/>
+      <c r="E244" s="80"/>
+      <c r="F244" s="79"/>
       <c r="G244" s="79"/>
       <c r="H244" s="77"/>
       <c r="I244" s="75"/>
-      <c r="J244" s="36"/>
+      <c r="J244" s="37"/>
     </row>
     <row r="245" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A245" s="74"/>
       <c r="C245" s="74"/>
-      <c r="D245" s="79"/>
+      <c r="D245" s="75"/>
       <c r="E245" s="80"/>
-      <c r="F245" s="79"/>
+      <c r="F245" s="75"/>
       <c r="G245" s="79"/>
       <c r="H245" s="77"/>
       <c r="I245" s="75"/>
-      <c r="J245" s="36"/>
+      <c r="J245" s="37"/>
     </row>
     <row r="246" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A246" s="74"/>
       <c r="C246" s="74"/>
-      <c r="D246" s="79"/>
-      <c r="E246" s="80"/>
-      <c r="F246" s="79"/>
+      <c r="D246" s="75"/>
+      <c r="E246" s="78"/>
+      <c r="F246" s="75"/>
       <c r="G246" s="79"/>
       <c r="H246" s="77"/>
       <c r="I246" s="75"/>
-      <c r="J246" s="36"/>
+      <c r="J246" s="37"/>
     </row>
     <row r="247" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A247" s="74"/>
       <c r="C247" s="74"/>
-      <c r="D247" s="79"/>
-      <c r="E247" s="80"/>
-      <c r="F247" s="79"/>
+      <c r="D247" s="75"/>
+      <c r="E247" s="78"/>
+      <c r="F247" s="75"/>
       <c r="G247" s="79"/>
       <c r="H247" s="77"/>
       <c r="I247" s="75"/>
-      <c r="J247" s="36"/>
+      <c r="J247" s="37"/>
     </row>
     <row r="248" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A248" s="74"/>
       <c r="C248" s="74"/>
       <c r="D248" s="75"/>
-      <c r="E248" s="80"/>
+      <c r="E248" s="78"/>
       <c r="F248" s="75"/>
       <c r="G248" s="79"/>
       <c r="H248" s="77"/>
       <c r="I248" s="75"/>
-      <c r="J248" s="36"/>
+      <c r="J248" s="37"/>
     </row>
     <row r="249" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A249" s="74"/>
@@ -5831,29 +5707,29 @@
       <c r="G249" s="79"/>
       <c r="H249" s="77"/>
       <c r="I249" s="75"/>
-      <c r="J249" s="36"/>
+      <c r="J249" s="37"/>
     </row>
     <row r="250" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A250" s="74"/>
       <c r="C250" s="74"/>
-      <c r="D250" s="75"/>
-      <c r="E250" s="78"/>
-      <c r="F250" s="75"/>
+      <c r="D250" s="79"/>
+      <c r="E250" s="80"/>
+      <c r="F250" s="79"/>
       <c r="G250" s="79"/>
       <c r="H250" s="77"/>
       <c r="I250" s="75"/>
-      <c r="J250" s="36"/>
+      <c r="J250" s="37"/>
     </row>
     <row r="251" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A251" s="74"/>
       <c r="C251" s="74"/>
-      <c r="D251" s="75"/>
-      <c r="E251" s="78"/>
-      <c r="F251" s="75"/>
+      <c r="D251" s="79"/>
+      <c r="E251" s="80"/>
+      <c r="F251" s="79"/>
       <c r="G251" s="79"/>
       <c r="H251" s="77"/>
       <c r="I251" s="75"/>
-      <c r="J251" s="36"/>
+      <c r="J251" s="37"/>
     </row>
     <row r="252" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A252" s="74"/>
@@ -5864,29 +5740,29 @@
       <c r="G252" s="79"/>
       <c r="H252" s="77"/>
       <c r="I252" s="75"/>
-      <c r="J252" s="36"/>
+      <c r="J252" s="37"/>
     </row>
     <row r="253" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A253" s="74"/>
       <c r="C253" s="74"/>
-      <c r="D253" s="79"/>
-      <c r="E253" s="80"/>
-      <c r="F253" s="79"/>
+      <c r="D253" s="75"/>
+      <c r="E253" s="78"/>
+      <c r="F253" s="75"/>
       <c r="G253" s="79"/>
       <c r="H253" s="77"/>
       <c r="I253" s="75"/>
-      <c r="J253" s="36"/>
+      <c r="J253" s="37"/>
     </row>
     <row r="254" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A254" s="74"/>
       <c r="C254" s="74"/>
-      <c r="D254" s="79"/>
-      <c r="E254" s="80"/>
-      <c r="F254" s="79"/>
+      <c r="D254" s="75"/>
+      <c r="E254" s="78"/>
+      <c r="F254" s="75"/>
       <c r="G254" s="79"/>
       <c r="H254" s="77"/>
       <c r="I254" s="75"/>
-      <c r="J254" s="36"/>
+      <c r="J254" s="37"/>
     </row>
     <row r="255" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A255" s="74"/>
@@ -5897,7 +5773,7 @@
       <c r="G255" s="79"/>
       <c r="H255" s="77"/>
       <c r="I255" s="75"/>
-      <c r="J255" s="36"/>
+      <c r="J255" s="37"/>
     </row>
     <row r="256" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A256" s="74"/>
@@ -5908,7 +5784,7 @@
       <c r="G256" s="79"/>
       <c r="H256" s="77"/>
       <c r="I256" s="75"/>
-      <c r="J256" s="36"/>
+      <c r="J256" s="37"/>
     </row>
     <row r="257" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A257" s="74"/>
@@ -5919,18 +5795,18 @@
       <c r="G257" s="79"/>
       <c r="H257" s="77"/>
       <c r="I257" s="75"/>
-      <c r="J257" s="36"/>
+      <c r="J257" s="37"/>
     </row>
     <row r="258" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A258" s="74"/>
       <c r="C258" s="74"/>
       <c r="D258" s="75"/>
-      <c r="E258" s="78"/>
+      <c r="E258" s="80"/>
       <c r="F258" s="75"/>
       <c r="G258" s="79"/>
       <c r="H258" s="77"/>
       <c r="I258" s="75"/>
-      <c r="J258" s="36"/>
+      <c r="J258" s="37"/>
     </row>
     <row r="259" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A259" s="74"/>
@@ -5941,29 +5817,33 @@
       <c r="G259" s="79"/>
       <c r="H259" s="77"/>
       <c r="I259" s="75"/>
-      <c r="J259" s="36"/>
-    </row>
-    <row r="260" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J259" s="37"/>
+    </row>
+    <row r="260" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A260" s="74"/>
+      <c r="B260" s="37"/>
       <c r="C260" s="74"/>
-      <c r="D260" s="75"/>
-      <c r="E260" s="78"/>
-      <c r="F260" s="75"/>
-      <c r="G260" s="79"/>
+      <c r="D260" s="81"/>
+      <c r="E260" s="82"/>
+      <c r="F260" s="81"/>
+      <c r="G260" s="75"/>
       <c r="H260" s="77"/>
-      <c r="I260" s="75"/>
-      <c r="J260" s="36"/>
+      <c r="I260" s="83"/>
+      <c r="J260" s="37"/>
+      <c r="K260" s="37"/>
+      <c r="L260" s="37"/>
+      <c r="N260" s="37"/>
     </row>
     <row r="261" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A261" s="74"/>
       <c r="C261" s="74"/>
       <c r="D261" s="75"/>
-      <c r="E261" s="80"/>
+      <c r="E261" s="78"/>
       <c r="F261" s="75"/>
       <c r="G261" s="79"/>
       <c r="H261" s="77"/>
       <c r="I261" s="75"/>
-      <c r="J261" s="36"/>
+      <c r="J261" s="37"/>
     </row>
     <row r="262" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A262" s="74"/>
@@ -5974,22 +5854,18 @@
       <c r="G262" s="79"/>
       <c r="H262" s="77"/>
       <c r="I262" s="75"/>
-      <c r="J262" s="36"/>
-    </row>
-    <row r="263" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J262" s="37"/>
+    </row>
+    <row r="263" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A263" s="74"/>
-      <c r="B263" s="36"/>
       <c r="C263" s="74"/>
-      <c r="D263" s="81"/>
-      <c r="E263" s="82"/>
-      <c r="F263" s="81"/>
-      <c r="G263" s="75"/>
+      <c r="D263" s="75"/>
+      <c r="E263" s="78"/>
+      <c r="F263" s="75"/>
+      <c r="G263" s="79"/>
       <c r="H263" s="77"/>
-      <c r="I263" s="83"/>
-      <c r="J263" s="36"/>
-      <c r="K263" s="36"/>
-      <c r="L263" s="36"/>
-      <c r="N263" s="36"/>
+      <c r="I263" s="75"/>
+      <c r="J263" s="37"/>
     </row>
     <row r="264" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A264" s="74"/>
@@ -6000,18 +5876,18 @@
       <c r="G264" s="79"/>
       <c r="H264" s="77"/>
       <c r="I264" s="75"/>
-      <c r="J264" s="36"/>
+      <c r="J264" s="37"/>
     </row>
     <row r="265" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A265" s="74"/>
       <c r="C265" s="74"/>
-      <c r="D265" s="75"/>
-      <c r="E265" s="78"/>
+      <c r="D265" s="79"/>
+      <c r="E265" s="80"/>
       <c r="F265" s="75"/>
       <c r="G265" s="79"/>
       <c r="H265" s="77"/>
-      <c r="I265" s="75"/>
-      <c r="J265" s="36"/>
+      <c r="I265" s="79"/>
+      <c r="J265" s="37"/>
     </row>
     <row r="266" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A266" s="74"/>
@@ -6022,7 +5898,7 @@
       <c r="G266" s="79"/>
       <c r="H266" s="77"/>
       <c r="I266" s="75"/>
-      <c r="J266" s="36"/>
+      <c r="J266" s="37"/>
     </row>
     <row r="267" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A267" s="74"/>
@@ -6033,18 +5909,18 @@
       <c r="G267" s="79"/>
       <c r="H267" s="77"/>
       <c r="I267" s="75"/>
-      <c r="J267" s="36"/>
+      <c r="J267" s="37"/>
     </row>
     <row r="268" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A268" s="74"/>
       <c r="C268" s="74"/>
-      <c r="D268" s="79"/>
-      <c r="E268" s="80"/>
+      <c r="D268" s="75"/>
+      <c r="E268" s="78"/>
       <c r="F268" s="75"/>
       <c r="G268" s="79"/>
       <c r="H268" s="77"/>
-      <c r="I268" s="79"/>
-      <c r="J268" s="36"/>
+      <c r="I268" s="75"/>
+      <c r="J268" s="37"/>
     </row>
     <row r="269" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A269" s="74"/>
@@ -6055,7 +5931,7 @@
       <c r="G269" s="79"/>
       <c r="H269" s="77"/>
       <c r="I269" s="75"/>
-      <c r="J269" s="36"/>
+      <c r="J269" s="37"/>
     </row>
     <row r="270" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A270" s="74"/>
@@ -6066,7 +5942,7 @@
       <c r="G270" s="79"/>
       <c r="H270" s="77"/>
       <c r="I270" s="75"/>
-      <c r="J270" s="36"/>
+      <c r="J270" s="37"/>
     </row>
     <row r="271" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A271" s="74"/>
@@ -6077,7 +5953,7 @@
       <c r="G271" s="79"/>
       <c r="H271" s="77"/>
       <c r="I271" s="75"/>
-      <c r="J271" s="36"/>
+      <c r="J271" s="37"/>
     </row>
     <row r="272" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A272" s="74"/>
@@ -6088,7 +5964,7 @@
       <c r="G272" s="79"/>
       <c r="H272" s="77"/>
       <c r="I272" s="75"/>
-      <c r="J272" s="36"/>
+      <c r="J272" s="37"/>
     </row>
     <row r="273" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A273" s="74"/>
@@ -6099,7 +5975,7 @@
       <c r="G273" s="79"/>
       <c r="H273" s="77"/>
       <c r="I273" s="75"/>
-      <c r="J273" s="36"/>
+      <c r="J273" s="37"/>
     </row>
     <row r="274" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A274" s="74"/>
@@ -6110,7 +5986,7 @@
       <c r="G274" s="79"/>
       <c r="H274" s="77"/>
       <c r="I274" s="75"/>
-      <c r="J274" s="36"/>
+      <c r="J274" s="37"/>
     </row>
     <row r="275" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A275" s="74"/>
@@ -6121,7 +5997,7 @@
       <c r="G275" s="79"/>
       <c r="H275" s="77"/>
       <c r="I275" s="75"/>
-      <c r="J275" s="36"/>
+      <c r="J275" s="37"/>
     </row>
     <row r="276" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A276" s="74"/>
@@ -6132,7 +6008,7 @@
       <c r="G276" s="79"/>
       <c r="H276" s="77"/>
       <c r="I276" s="75"/>
-      <c r="J276" s="36"/>
+      <c r="J276" s="37"/>
     </row>
     <row r="277" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A277" s="74"/>
@@ -6143,7 +6019,7 @@
       <c r="G277" s="79"/>
       <c r="H277" s="77"/>
       <c r="I277" s="75"/>
-      <c r="J277" s="36"/>
+      <c r="J277" s="37"/>
     </row>
     <row r="278" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A278" s="74"/>
@@ -6154,7 +6030,7 @@
       <c r="G278" s="79"/>
       <c r="H278" s="77"/>
       <c r="I278" s="75"/>
-      <c r="J278" s="36"/>
+      <c r="J278" s="37"/>
     </row>
     <row r="279" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A279" s="74"/>
@@ -6165,7 +6041,7 @@
       <c r="G279" s="79"/>
       <c r="H279" s="77"/>
       <c r="I279" s="75"/>
-      <c r="J279" s="36"/>
+      <c r="J279" s="37"/>
     </row>
     <row r="280" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A280" s="74"/>
@@ -6176,7 +6052,7 @@
       <c r="G280" s="79"/>
       <c r="H280" s="77"/>
       <c r="I280" s="75"/>
-      <c r="J280" s="36"/>
+      <c r="J280" s="37"/>
     </row>
     <row r="281" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A281" s="74"/>
@@ -6187,7 +6063,7 @@
       <c r="G281" s="79"/>
       <c r="H281" s="77"/>
       <c r="I281" s="75"/>
-      <c r="J281" s="36"/>
+      <c r="J281" s="37"/>
     </row>
     <row r="282" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A282" s="74"/>
@@ -6198,7 +6074,7 @@
       <c r="G282" s="79"/>
       <c r="H282" s="77"/>
       <c r="I282" s="75"/>
-      <c r="J282" s="36"/>
+      <c r="J282" s="37"/>
     </row>
     <row r="283" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A283" s="74"/>
@@ -6209,7 +6085,7 @@
       <c r="G283" s="79"/>
       <c r="H283" s="77"/>
       <c r="I283" s="75"/>
-      <c r="J283" s="36"/>
+      <c r="J283" s="37"/>
     </row>
     <row r="284" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A284" s="74"/>
@@ -6220,7 +6096,7 @@
       <c r="G284" s="79"/>
       <c r="H284" s="77"/>
       <c r="I284" s="75"/>
-      <c r="J284" s="36"/>
+      <c r="J284" s="37"/>
     </row>
     <row r="285" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A285" s="74"/>
@@ -6231,7 +6107,7 @@
       <c r="G285" s="79"/>
       <c r="H285" s="77"/>
       <c r="I285" s="75"/>
-      <c r="J285" s="36"/>
+      <c r="J285" s="37"/>
     </row>
     <row r="286" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A286" s="74"/>
@@ -6242,7 +6118,7 @@
       <c r="G286" s="79"/>
       <c r="H286" s="77"/>
       <c r="I286" s="75"/>
-      <c r="J286" s="36"/>
+      <c r="J286" s="37"/>
     </row>
     <row r="287" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A287" s="74"/>
@@ -6252,8 +6128,8 @@
       <c r="F287" s="75"/>
       <c r="G287" s="79"/>
       <c r="H287" s="77"/>
-      <c r="I287" s="75"/>
-      <c r="J287" s="36"/>
+      <c r="I287" s="79"/>
+      <c r="J287" s="37"/>
     </row>
     <row r="288" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A288" s="74"/>
@@ -6264,18 +6140,18 @@
       <c r="G288" s="79"/>
       <c r="H288" s="77"/>
       <c r="I288" s="75"/>
-      <c r="J288" s="36"/>
+      <c r="J288" s="37"/>
     </row>
     <row r="289" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A289" s="74"/>
       <c r="C289" s="74"/>
-      <c r="D289" s="75"/>
+      <c r="D289" s="74"/>
       <c r="E289" s="78"/>
       <c r="F289" s="75"/>
       <c r="G289" s="79"/>
       <c r="H289" s="77"/>
       <c r="I289" s="75"/>
-      <c r="J289" s="36"/>
+      <c r="J289" s="37"/>
     </row>
     <row r="290" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A290" s="74"/>
@@ -6285,8 +6161,8 @@
       <c r="F290" s="75"/>
       <c r="G290" s="79"/>
       <c r="H290" s="77"/>
-      <c r="I290" s="79"/>
-      <c r="J290" s="36"/>
+      <c r="I290" s="75"/>
+      <c r="J290" s="37"/>
     </row>
     <row r="291" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A291" s="74"/>
@@ -6297,18 +6173,18 @@
       <c r="G291" s="79"/>
       <c r="H291" s="77"/>
       <c r="I291" s="75"/>
-      <c r="J291" s="36"/>
+      <c r="J291" s="37"/>
     </row>
     <row r="292" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A292" s="74"/>
       <c r="C292" s="74"/>
-      <c r="D292" s="74"/>
+      <c r="D292" s="75"/>
       <c r="E292" s="78"/>
       <c r="F292" s="75"/>
       <c r="G292" s="79"/>
       <c r="H292" s="77"/>
       <c r="I292" s="75"/>
-      <c r="J292" s="36"/>
+      <c r="J292" s="37"/>
     </row>
     <row r="293" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A293" s="74"/>
@@ -6319,7 +6195,7 @@
       <c r="G293" s="79"/>
       <c r="H293" s="77"/>
       <c r="I293" s="75"/>
-      <c r="J293" s="36"/>
+      <c r="J293" s="37"/>
     </row>
     <row r="294" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A294" s="74"/>
@@ -6330,7 +6206,7 @@
       <c r="G294" s="79"/>
       <c r="H294" s="77"/>
       <c r="I294" s="75"/>
-      <c r="J294" s="36"/>
+      <c r="J294" s="37"/>
     </row>
     <row r="295" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A295" s="74"/>
@@ -6341,29 +6217,29 @@
       <c r="G295" s="79"/>
       <c r="H295" s="77"/>
       <c r="I295" s="75"/>
-      <c r="J295" s="36"/>
+      <c r="J295" s="37"/>
     </row>
     <row r="296" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A296" s="74"/>
       <c r="C296" s="74"/>
-      <c r="D296" s="75"/>
-      <c r="E296" s="78"/>
+      <c r="D296" s="79"/>
+      <c r="E296" s="80"/>
       <c r="F296" s="75"/>
       <c r="G296" s="79"/>
       <c r="H296" s="77"/>
-      <c r="I296" s="75"/>
-      <c r="J296" s="36"/>
+      <c r="I296" s="79"/>
+      <c r="J296" s="37"/>
     </row>
     <row r="297" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A297" s="74"/>
       <c r="C297" s="74"/>
       <c r="D297" s="75"/>
-      <c r="E297" s="78"/>
-      <c r="F297" s="75"/>
+      <c r="E297" s="80"/>
+      <c r="F297" s="79"/>
       <c r="G297" s="79"/>
       <c r="H297" s="77"/>
-      <c r="I297" s="75"/>
-      <c r="J297" s="36"/>
+      <c r="I297" s="79"/>
+      <c r="J297" s="37"/>
     </row>
     <row r="298" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A298" s="74"/>
@@ -6374,29 +6250,29 @@
       <c r="G298" s="79"/>
       <c r="H298" s="77"/>
       <c r="I298" s="75"/>
-      <c r="J298" s="36"/>
+      <c r="J298" s="37"/>
     </row>
     <row r="299" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A299" s="74"/>
       <c r="C299" s="74"/>
-      <c r="D299" s="79"/>
-      <c r="E299" s="80"/>
+      <c r="D299" s="75"/>
+      <c r="E299" s="78"/>
       <c r="F299" s="75"/>
       <c r="G299" s="79"/>
       <c r="H299" s="77"/>
-      <c r="I299" s="79"/>
-      <c r="J299" s="36"/>
+      <c r="I299" s="75"/>
+      <c r="J299" s="37"/>
     </row>
     <row r="300" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A300" s="74"/>
       <c r="C300" s="74"/>
       <c r="D300" s="75"/>
-      <c r="E300" s="80"/>
-      <c r="F300" s="79"/>
+      <c r="E300" s="78"/>
+      <c r="F300" s="75"/>
       <c r="G300" s="79"/>
       <c r="H300" s="77"/>
-      <c r="I300" s="79"/>
-      <c r="J300" s="36"/>
+      <c r="I300" s="75"/>
+      <c r="J300" s="37"/>
     </row>
     <row r="301" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A301" s="74"/>
@@ -6407,7 +6283,7 @@
       <c r="G301" s="79"/>
       <c r="H301" s="77"/>
       <c r="I301" s="75"/>
-      <c r="J301" s="36"/>
+      <c r="J301" s="37"/>
     </row>
     <row r="302" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A302" s="74"/>
@@ -6418,7 +6294,7 @@
       <c r="G302" s="79"/>
       <c r="H302" s="77"/>
       <c r="I302" s="75"/>
-      <c r="J302" s="36"/>
+      <c r="J302" s="37"/>
     </row>
     <row r="303" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A303" s="74"/>
@@ -6429,7 +6305,7 @@
       <c r="G303" s="79"/>
       <c r="H303" s="77"/>
       <c r="I303" s="75"/>
-      <c r="J303" s="36"/>
+      <c r="J303" s="37"/>
     </row>
     <row r="304" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A304" s="74"/>
@@ -6440,7 +6316,7 @@
       <c r="G304" s="79"/>
       <c r="H304" s="77"/>
       <c r="I304" s="75"/>
-      <c r="J304" s="36"/>
+      <c r="J304" s="37"/>
     </row>
     <row r="305" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A305" s="74"/>
@@ -6451,40 +6327,40 @@
       <c r="G305" s="79"/>
       <c r="H305" s="77"/>
       <c r="I305" s="75"/>
-      <c r="J305" s="36"/>
+      <c r="J305" s="37"/>
     </row>
     <row r="306" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A306" s="74"/>
       <c r="C306" s="74"/>
       <c r="D306" s="75"/>
-      <c r="E306" s="78"/>
+      <c r="E306" s="75"/>
       <c r="F306" s="75"/>
-      <c r="G306" s="79"/>
+      <c r="G306" s="75"/>
       <c r="H306" s="77"/>
       <c r="I306" s="75"/>
-      <c r="J306" s="36"/>
+      <c r="J306" s="37"/>
     </row>
     <row r="307" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A307" s="74"/>
       <c r="C307" s="74"/>
       <c r="D307" s="75"/>
-      <c r="E307" s="78"/>
+      <c r="E307" s="75"/>
       <c r="F307" s="75"/>
-      <c r="G307" s="79"/>
+      <c r="G307" s="75"/>
       <c r="H307" s="77"/>
       <c r="I307" s="75"/>
-      <c r="J307" s="36"/>
+      <c r="J307" s="37"/>
     </row>
     <row r="308" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A308" s="74"/>
       <c r="C308" s="74"/>
       <c r="D308" s="75"/>
-      <c r="E308" s="78"/>
+      <c r="E308" s="75"/>
       <c r="F308" s="75"/>
-      <c r="G308" s="79"/>
+      <c r="G308" s="75"/>
       <c r="H308" s="77"/>
       <c r="I308" s="75"/>
-      <c r="J308" s="36"/>
+      <c r="J308" s="37"/>
     </row>
     <row r="309" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A309" s="74"/>
@@ -6495,7 +6371,7 @@
       <c r="G309" s="75"/>
       <c r="H309" s="77"/>
       <c r="I309" s="75"/>
-      <c r="J309" s="36"/>
+      <c r="J309" s="37"/>
     </row>
     <row r="310" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A310" s="74"/>
@@ -6506,7 +6382,7 @@
       <c r="G310" s="75"/>
       <c r="H310" s="77"/>
       <c r="I310" s="75"/>
-      <c r="J310" s="36"/>
+      <c r="J310" s="37"/>
     </row>
     <row r="311" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A311" s="74"/>
@@ -6517,7 +6393,7 @@
       <c r="G311" s="75"/>
       <c r="H311" s="77"/>
       <c r="I311" s="75"/>
-      <c r="J311" s="36"/>
+      <c r="J311" s="37"/>
     </row>
     <row r="312" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A312" s="74"/>
@@ -6528,18 +6404,18 @@
       <c r="G312" s="75"/>
       <c r="H312" s="77"/>
       <c r="I312" s="75"/>
-      <c r="J312" s="36"/>
+      <c r="J312" s="37"/>
     </row>
     <row r="313" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A313" s="74"/>
       <c r="C313" s="74"/>
-      <c r="D313" s="75"/>
-      <c r="E313" s="75"/>
-      <c r="F313" s="75"/>
-      <c r="G313" s="75"/>
+      <c r="D313" s="79"/>
+      <c r="E313" s="79"/>
+      <c r="F313" s="79"/>
+      <c r="G313" s="79"/>
       <c r="H313" s="77"/>
-      <c r="I313" s="75"/>
-      <c r="J313" s="36"/>
+      <c r="I313" s="79"/>
+      <c r="J313" s="37"/>
     </row>
     <row r="314" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A314" s="74"/>
@@ -6550,7 +6426,7 @@
       <c r="G314" s="75"/>
       <c r="H314" s="77"/>
       <c r="I314" s="75"/>
-      <c r="J314" s="36"/>
+      <c r="J314" s="37"/>
     </row>
     <row r="315" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A315" s="74"/>
@@ -6561,18 +6437,18 @@
       <c r="G315" s="75"/>
       <c r="H315" s="77"/>
       <c r="I315" s="75"/>
-      <c r="J315" s="36"/>
+      <c r="J315" s="37"/>
     </row>
     <row r="316" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A316" s="74"/>
       <c r="C316" s="74"/>
-      <c r="D316" s="79"/>
-      <c r="E316" s="79"/>
-      <c r="F316" s="79"/>
-      <c r="G316" s="79"/>
+      <c r="D316" s="75"/>
+      <c r="E316" s="75"/>
+      <c r="F316" s="75"/>
+      <c r="G316" s="75"/>
       <c r="H316" s="77"/>
-      <c r="I316" s="79"/>
-      <c r="J316" s="36"/>
+      <c r="I316" s="75"/>
+      <c r="J316" s="37"/>
     </row>
     <row r="317" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A317" s="74"/>
@@ -6583,7 +6459,7 @@
       <c r="G317" s="75"/>
       <c r="H317" s="77"/>
       <c r="I317" s="75"/>
-      <c r="J317" s="36"/>
+      <c r="J317" s="37"/>
     </row>
     <row r="318" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A318" s="74"/>
@@ -6594,7 +6470,7 @@
       <c r="G318" s="75"/>
       <c r="H318" s="77"/>
       <c r="I318" s="75"/>
-      <c r="J318" s="36"/>
+      <c r="J318" s="37"/>
     </row>
     <row r="319" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A319" s="74"/>
@@ -6605,7 +6481,7 @@
       <c r="G319" s="75"/>
       <c r="H319" s="77"/>
       <c r="I319" s="75"/>
-      <c r="J319" s="36"/>
+      <c r="J319" s="37"/>
     </row>
     <row r="320" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A320" s="74"/>
@@ -6616,7 +6492,7 @@
       <c r="G320" s="75"/>
       <c r="H320" s="77"/>
       <c r="I320" s="75"/>
-      <c r="J320" s="36"/>
+      <c r="J320" s="37"/>
     </row>
     <row r="321" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A321" s="74"/>
@@ -6627,7 +6503,7 @@
       <c r="G321" s="75"/>
       <c r="H321" s="77"/>
       <c r="I321" s="75"/>
-      <c r="J321" s="36"/>
+      <c r="J321" s="37"/>
     </row>
     <row r="322" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A322" s="74"/>
@@ -6638,7 +6514,7 @@
       <c r="G322" s="75"/>
       <c r="H322" s="77"/>
       <c r="I322" s="75"/>
-      <c r="J322" s="36"/>
+      <c r="J322" s="37"/>
     </row>
     <row r="323" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A323" s="74"/>
@@ -6649,7 +6525,7 @@
       <c r="G323" s="75"/>
       <c r="H323" s="77"/>
       <c r="I323" s="75"/>
-      <c r="J323" s="36"/>
+      <c r="J323" s="37"/>
     </row>
     <row r="324" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A324" s="74"/>
@@ -6660,7 +6536,7 @@
       <c r="G324" s="75"/>
       <c r="H324" s="77"/>
       <c r="I324" s="75"/>
-      <c r="J324" s="36"/>
+      <c r="J324" s="37"/>
     </row>
     <row r="325" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A325" s="74"/>
@@ -6671,18 +6547,18 @@
       <c r="G325" s="75"/>
       <c r="H325" s="77"/>
       <c r="I325" s="75"/>
-      <c r="J325" s="36"/>
+      <c r="J325" s="37"/>
     </row>
     <row r="326" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A326" s="74"/>
       <c r="C326" s="74"/>
-      <c r="D326" s="75"/>
-      <c r="E326" s="75"/>
-      <c r="F326" s="75"/>
-      <c r="G326" s="75"/>
+      <c r="D326" s="79"/>
+      <c r="E326" s="79"/>
+      <c r="F326" s="79"/>
+      <c r="G326" s="79"/>
       <c r="H326" s="77"/>
-      <c r="I326" s="75"/>
-      <c r="J326" s="36"/>
+      <c r="I326" s="79"/>
+      <c r="J326" s="37"/>
     </row>
     <row r="327" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A327" s="74"/>
@@ -6693,7 +6569,7 @@
       <c r="G327" s="75"/>
       <c r="H327" s="77"/>
       <c r="I327" s="75"/>
-      <c r="J327" s="36"/>
+      <c r="J327" s="37"/>
     </row>
     <row r="328" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A328" s="74"/>
@@ -6704,29 +6580,29 @@
       <c r="G328" s="75"/>
       <c r="H328" s="77"/>
       <c r="I328" s="75"/>
-      <c r="J328" s="36"/>
+      <c r="J328" s="37"/>
     </row>
     <row r="329" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A329" s="74"/>
       <c r="C329" s="74"/>
-      <c r="D329" s="79"/>
-      <c r="E329" s="79"/>
-      <c r="F329" s="79"/>
-      <c r="G329" s="79"/>
+      <c r="D329" s="75"/>
+      <c r="E329" s="75"/>
+      <c r="F329" s="84"/>
+      <c r="G329" s="84"/>
       <c r="H329" s="77"/>
-      <c r="I329" s="79"/>
-      <c r="J329" s="36"/>
+      <c r="I329" s="75"/>
+      <c r="J329" s="37"/>
     </row>
     <row r="330" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A330" s="74"/>
       <c r="C330" s="74"/>
-      <c r="D330" s="75"/>
-      <c r="E330" s="75"/>
-      <c r="F330" s="75"/>
-      <c r="G330" s="75"/>
+      <c r="D330" s="79"/>
+      <c r="E330" s="79"/>
+      <c r="F330" s="79"/>
+      <c r="G330" s="79"/>
       <c r="H330" s="77"/>
-      <c r="I330" s="75"/>
-      <c r="J330" s="36"/>
+      <c r="I330" s="79"/>
+      <c r="J330" s="37"/>
     </row>
     <row r="331" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A331" s="74"/>
@@ -6737,29 +6613,29 @@
       <c r="G331" s="75"/>
       <c r="H331" s="77"/>
       <c r="I331" s="75"/>
-      <c r="J331" s="36"/>
+      <c r="J331" s="37"/>
     </row>
     <row r="332" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A332" s="74"/>
       <c r="C332" s="74"/>
       <c r="D332" s="75"/>
-      <c r="E332" s="75"/>
-      <c r="F332" s="84"/>
-      <c r="G332" s="84"/>
+      <c r="E332" s="85"/>
+      <c r="F332" s="75"/>
+      <c r="G332" s="75"/>
       <c r="H332" s="77"/>
       <c r="I332" s="75"/>
-      <c r="J332" s="36"/>
+      <c r="J332" s="37"/>
     </row>
     <row r="333" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A333" s="74"/>
       <c r="C333" s="74"/>
-      <c r="D333" s="79"/>
-      <c r="E333" s="79"/>
-      <c r="F333" s="79"/>
-      <c r="G333" s="79"/>
+      <c r="D333" s="84"/>
+      <c r="E333" s="75"/>
+      <c r="F333" s="84"/>
+      <c r="G333" s="84"/>
       <c r="H333" s="77"/>
-      <c r="I333" s="79"/>
-      <c r="J333" s="36"/>
+      <c r="I333" s="75"/>
+      <c r="J333" s="37"/>
     </row>
     <row r="334" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A334" s="74"/>
@@ -6770,29 +6646,29 @@
       <c r="G334" s="75"/>
       <c r="H334" s="77"/>
       <c r="I334" s="75"/>
-      <c r="J334" s="36"/>
+      <c r="J334" s="37"/>
     </row>
     <row r="335" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A335" s="74"/>
       <c r="C335" s="74"/>
       <c r="D335" s="75"/>
-      <c r="E335" s="85"/>
+      <c r="E335" s="75"/>
       <c r="F335" s="75"/>
       <c r="G335" s="75"/>
       <c r="H335" s="77"/>
       <c r="I335" s="75"/>
-      <c r="J335" s="36"/>
+      <c r="J335" s="37"/>
     </row>
     <row r="336" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A336" s="74"/>
       <c r="C336" s="74"/>
-      <c r="D336" s="84"/>
+      <c r="D336" s="75"/>
       <c r="E336" s="75"/>
-      <c r="F336" s="84"/>
-      <c r="G336" s="84"/>
+      <c r="F336" s="75"/>
+      <c r="G336" s="75"/>
       <c r="H336" s="77"/>
       <c r="I336" s="75"/>
-      <c r="J336" s="36"/>
+      <c r="J336" s="37"/>
     </row>
     <row r="337" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A337" s="74"/>
@@ -6803,10 +6679,10 @@
       <c r="G337" s="75"/>
       <c r="H337" s="77"/>
       <c r="I337" s="75"/>
-      <c r="J337" s="36"/>
+      <c r="J337" s="37"/>
     </row>
     <row r="338" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A338" s="74"/>
+      <c r="A338" s="75"/>
       <c r="C338" s="74"/>
       <c r="D338" s="75"/>
       <c r="E338" s="75"/>
@@ -6814,10 +6690,10 @@
       <c r="G338" s="75"/>
       <c r="H338" s="77"/>
       <c r="I338" s="75"/>
-      <c r="J338" s="36"/>
+      <c r="J338" s="37"/>
     </row>
     <row r="339" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A339" s="74"/>
+      <c r="A339" s="75"/>
       <c r="C339" s="74"/>
       <c r="D339" s="75"/>
       <c r="E339" s="75"/>
@@ -6825,10 +6701,10 @@
       <c r="G339" s="75"/>
       <c r="H339" s="77"/>
       <c r="I339" s="75"/>
-      <c r="J339" s="36"/>
+      <c r="J339" s="37"/>
     </row>
     <row r="340" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A340" s="74"/>
+      <c r="A340" s="75"/>
       <c r="C340" s="74"/>
       <c r="D340" s="75"/>
       <c r="E340" s="75"/>
@@ -6836,10 +6712,10 @@
       <c r="G340" s="75"/>
       <c r="H340" s="77"/>
       <c r="I340" s="75"/>
-      <c r="J340" s="36"/>
+      <c r="J340" s="37"/>
     </row>
     <row r="341" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A341" s="75"/>
+      <c r="A341" s="74"/>
       <c r="C341" s="74"/>
       <c r="D341" s="75"/>
       <c r="E341" s="75"/>
@@ -6847,21 +6723,21 @@
       <c r="G341" s="75"/>
       <c r="H341" s="77"/>
       <c r="I341" s="75"/>
-      <c r="J341" s="36"/>
+      <c r="J341" s="37"/>
     </row>
     <row r="342" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A342" s="75"/>
+      <c r="A342" s="74"/>
       <c r="C342" s="74"/>
-      <c r="D342" s="75"/>
+      <c r="D342" s="84"/>
       <c r="E342" s="75"/>
       <c r="F342" s="75"/>
       <c r="G342" s="75"/>
       <c r="H342" s="77"/>
-      <c r="I342" s="75"/>
-      <c r="J342" s="36"/>
+      <c r="I342" s="86"/>
+      <c r="J342" s="37"/>
     </row>
     <row r="343" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A343" s="75"/>
+      <c r="A343" s="74"/>
       <c r="C343" s="74"/>
       <c r="D343" s="75"/>
       <c r="E343" s="75"/>
@@ -6869,7 +6745,7 @@
       <c r="G343" s="75"/>
       <c r="H343" s="77"/>
       <c r="I343" s="75"/>
-      <c r="J343" s="36"/>
+      <c r="J343" s="37"/>
     </row>
     <row r="344" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A344" s="74"/>
@@ -6880,18 +6756,18 @@
       <c r="G344" s="75"/>
       <c r="H344" s="77"/>
       <c r="I344" s="75"/>
-      <c r="J344" s="36"/>
+      <c r="J344" s="37"/>
     </row>
     <row r="345" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A345" s="74"/>
       <c r="C345" s="74"/>
-      <c r="D345" s="84"/>
+      <c r="D345" s="75"/>
       <c r="E345" s="75"/>
       <c r="F345" s="75"/>
       <c r="G345" s="75"/>
       <c r="H345" s="77"/>
-      <c r="I345" s="86"/>
-      <c r="J345" s="36"/>
+      <c r="I345" s="75"/>
+      <c r="J345" s="37"/>
     </row>
     <row r="346" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A346" s="74"/>
@@ -6902,7 +6778,7 @@
       <c r="G346" s="75"/>
       <c r="H346" s="77"/>
       <c r="I346" s="75"/>
-      <c r="J346" s="36"/>
+      <c r="J346" s="37"/>
     </row>
     <row r="347" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A347" s="74"/>
@@ -6913,29 +6789,29 @@
       <c r="G347" s="75"/>
       <c r="H347" s="77"/>
       <c r="I347" s="75"/>
-      <c r="J347" s="36"/>
+      <c r="J347" s="37"/>
     </row>
     <row r="348" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A348" s="74"/>
       <c r="C348" s="74"/>
-      <c r="D348" s="75"/>
-      <c r="E348" s="75"/>
-      <c r="F348" s="75"/>
-      <c r="G348" s="75"/>
+      <c r="D348" s="79"/>
+      <c r="E348" s="79"/>
+      <c r="F348" s="79"/>
+      <c r="G348" s="79"/>
       <c r="H348" s="77"/>
-      <c r="I348" s="75"/>
-      <c r="J348" s="36"/>
+      <c r="I348" s="79"/>
+      <c r="J348" s="37"/>
     </row>
     <row r="349" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A349" s="74"/>
       <c r="C349" s="74"/>
-      <c r="D349" s="75"/>
-      <c r="E349" s="75"/>
-      <c r="F349" s="75"/>
-      <c r="G349" s="75"/>
+      <c r="D349" s="79"/>
+      <c r="E349" s="79"/>
+      <c r="F349" s="79"/>
+      <c r="G349" s="79"/>
       <c r="H349" s="77"/>
-      <c r="I349" s="75"/>
-      <c r="J349" s="36"/>
+      <c r="I349" s="79"/>
+      <c r="J349" s="37"/>
     </row>
     <row r="350" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A350" s="74"/>
@@ -6946,18 +6822,18 @@
       <c r="G350" s="75"/>
       <c r="H350" s="77"/>
       <c r="I350" s="75"/>
-      <c r="J350" s="36"/>
+      <c r="J350" s="37"/>
     </row>
     <row r="351" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A351" s="74"/>
       <c r="C351" s="74"/>
-      <c r="D351" s="79"/>
-      <c r="E351" s="79"/>
-      <c r="F351" s="79"/>
-      <c r="G351" s="79"/>
+      <c r="D351" s="75"/>
+      <c r="E351" s="75"/>
+      <c r="F351" s="75"/>
+      <c r="G351" s="75"/>
       <c r="H351" s="77"/>
       <c r="I351" s="79"/>
-      <c r="J351" s="36"/>
+      <c r="J351" s="37"/>
     </row>
     <row r="352" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A352" s="74"/>
@@ -6968,7 +6844,7 @@
       <c r="G352" s="79"/>
       <c r="H352" s="77"/>
       <c r="I352" s="79"/>
-      <c r="J352" s="36"/>
+      <c r="J352" s="37"/>
     </row>
     <row r="353" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A353" s="74"/>
@@ -6979,7 +6855,7 @@
       <c r="G353" s="75"/>
       <c r="H353" s="77"/>
       <c r="I353" s="75"/>
-      <c r="J353" s="36"/>
+      <c r="J353" s="37"/>
     </row>
     <row r="354" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A354" s="74"/>
@@ -6989,19 +6865,19 @@
       <c r="F354" s="75"/>
       <c r="G354" s="75"/>
       <c r="H354" s="77"/>
-      <c r="I354" s="79"/>
-      <c r="J354" s="36"/>
+      <c r="I354" s="75"/>
+      <c r="J354" s="37"/>
     </row>
     <row r="355" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A355" s="74"/>
       <c r="C355" s="74"/>
-      <c r="D355" s="79"/>
-      <c r="E355" s="79"/>
-      <c r="F355" s="79"/>
-      <c r="G355" s="79"/>
+      <c r="D355" s="75"/>
+      <c r="E355" s="75"/>
+      <c r="F355" s="75"/>
+      <c r="G355" s="75"/>
       <c r="H355" s="77"/>
-      <c r="I355" s="79"/>
-      <c r="J355" s="36"/>
+      <c r="I355" s="75"/>
+      <c r="J355" s="37"/>
     </row>
     <row r="356" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A356" s="74"/>
@@ -7012,7 +6888,7 @@
       <c r="G356" s="75"/>
       <c r="H356" s="77"/>
       <c r="I356" s="75"/>
-      <c r="J356" s="36"/>
+      <c r="J356" s="37"/>
     </row>
     <row r="357" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A357" s="74"/>
@@ -7023,7 +6899,7 @@
       <c r="G357" s="75"/>
       <c r="H357" s="77"/>
       <c r="I357" s="75"/>
-      <c r="J357" s="36"/>
+      <c r="J357" s="37"/>
     </row>
     <row r="358" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A358" s="74"/>
@@ -7034,7 +6910,7 @@
       <c r="G358" s="75"/>
       <c r="H358" s="77"/>
       <c r="I358" s="75"/>
-      <c r="J358" s="36"/>
+      <c r="J358" s="37"/>
     </row>
     <row r="359" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A359" s="74"/>
@@ -7045,7 +6921,7 @@
       <c r="G359" s="75"/>
       <c r="H359" s="77"/>
       <c r="I359" s="75"/>
-      <c r="J359" s="36"/>
+      <c r="J359" s="37"/>
     </row>
     <row r="360" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A360" s="74"/>
@@ -7056,7 +6932,7 @@
       <c r="G360" s="75"/>
       <c r="H360" s="77"/>
       <c r="I360" s="75"/>
-      <c r="J360" s="36"/>
+      <c r="J360" s="37"/>
     </row>
     <row r="361" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A361" s="74"/>
@@ -7067,7 +6943,7 @@
       <c r="G361" s="75"/>
       <c r="H361" s="77"/>
       <c r="I361" s="75"/>
-      <c r="J361" s="36"/>
+      <c r="J361" s="37"/>
     </row>
     <row r="362" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A362" s="74"/>
@@ -7078,7 +6954,7 @@
       <c r="G362" s="75"/>
       <c r="H362" s="77"/>
       <c r="I362" s="75"/>
-      <c r="J362" s="36"/>
+      <c r="J362" s="37"/>
     </row>
     <row r="363" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A363" s="74"/>
@@ -7089,7 +6965,7 @@
       <c r="G363" s="75"/>
       <c r="H363" s="77"/>
       <c r="I363" s="75"/>
-      <c r="J363" s="36"/>
+      <c r="J363" s="37"/>
     </row>
     <row r="364" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A364" s="74"/>
@@ -7100,7 +6976,7 @@
       <c r="G364" s="75"/>
       <c r="H364" s="77"/>
       <c r="I364" s="75"/>
-      <c r="J364" s="36"/>
+      <c r="J364" s="37"/>
     </row>
     <row r="365" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A365" s="74"/>
@@ -7111,7 +6987,7 @@
       <c r="G365" s="75"/>
       <c r="H365" s="77"/>
       <c r="I365" s="75"/>
-      <c r="J365" s="36"/>
+      <c r="J365" s="37"/>
     </row>
     <row r="366" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A366" s="74"/>
@@ -7122,7 +6998,7 @@
       <c r="G366" s="75"/>
       <c r="H366" s="77"/>
       <c r="I366" s="75"/>
-      <c r="J366" s="36"/>
+      <c r="J366" s="37"/>
     </row>
     <row r="367" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A367" s="74"/>
@@ -7133,7 +7009,7 @@
       <c r="G367" s="75"/>
       <c r="H367" s="77"/>
       <c r="I367" s="75"/>
-      <c r="J367" s="36"/>
+      <c r="J367" s="37"/>
     </row>
     <row r="368" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A368" s="74"/>
@@ -7144,7 +7020,7 @@
       <c r="G368" s="75"/>
       <c r="H368" s="77"/>
       <c r="I368" s="75"/>
-      <c r="J368" s="36"/>
+      <c r="J368" s="37"/>
     </row>
     <row r="369" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A369" s="74"/>
@@ -7155,7 +7031,7 @@
       <c r="G369" s="75"/>
       <c r="H369" s="77"/>
       <c r="I369" s="75"/>
-      <c r="J369" s="36"/>
+      <c r="J369" s="37"/>
     </row>
     <row r="370" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A370" s="74"/>
@@ -7166,7 +7042,7 @@
       <c r="G370" s="75"/>
       <c r="H370" s="77"/>
       <c r="I370" s="75"/>
-      <c r="J370" s="36"/>
+      <c r="J370" s="37"/>
     </row>
     <row r="371" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A371" s="74"/>
@@ -7177,7 +7053,7 @@
       <c r="G371" s="75"/>
       <c r="H371" s="77"/>
       <c r="I371" s="75"/>
-      <c r="J371" s="36"/>
+      <c r="J371" s="37"/>
     </row>
     <row r="372" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A372" s="74"/>
@@ -7188,7 +7064,7 @@
       <c r="G372" s="75"/>
       <c r="H372" s="77"/>
       <c r="I372" s="75"/>
-      <c r="J372" s="36"/>
+      <c r="J372" s="37"/>
     </row>
     <row r="373" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A373" s="74"/>
@@ -7199,18 +7075,18 @@
       <c r="G373" s="75"/>
       <c r="H373" s="77"/>
       <c r="I373" s="75"/>
-      <c r="J373" s="36"/>
+      <c r="J373" s="37"/>
     </row>
     <row r="374" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A374" s="74"/>
       <c r="C374" s="74"/>
       <c r="D374" s="75"/>
       <c r="E374" s="75"/>
-      <c r="F374" s="75"/>
-      <c r="G374" s="75"/>
+      <c r="F374" s="79"/>
+      <c r="G374" s="79"/>
       <c r="H374" s="77"/>
       <c r="I374" s="75"/>
-      <c r="J374" s="36"/>
+      <c r="J374" s="37"/>
     </row>
     <row r="375" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A375" s="74"/>
@@ -7221,7 +7097,7 @@
       <c r="G375" s="75"/>
       <c r="H375" s="77"/>
       <c r="I375" s="75"/>
-      <c r="J375" s="36"/>
+      <c r="J375" s="37"/>
     </row>
     <row r="376" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A376" s="74"/>
@@ -7232,29 +7108,29 @@
       <c r="G376" s="75"/>
       <c r="H376" s="77"/>
       <c r="I376" s="75"/>
-      <c r="J376" s="36"/>
+      <c r="J376" s="37"/>
     </row>
     <row r="377" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A377" s="74"/>
       <c r="C377" s="74"/>
       <c r="D377" s="75"/>
       <c r="E377" s="75"/>
-      <c r="F377" s="79"/>
-      <c r="G377" s="79"/>
+      <c r="F377" s="75"/>
+      <c r="G377" s="75"/>
       <c r="H377" s="77"/>
       <c r="I377" s="75"/>
-      <c r="J377" s="36"/>
+      <c r="J377" s="37"/>
     </row>
     <row r="378" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A378" s="74"/>
       <c r="C378" s="74"/>
-      <c r="D378" s="75"/>
+      <c r="D378" s="84"/>
       <c r="E378" s="75"/>
       <c r="F378" s="75"/>
       <c r="G378" s="75"/>
       <c r="H378" s="77"/>
       <c r="I378" s="75"/>
-      <c r="J378" s="36"/>
+      <c r="J378" s="37"/>
     </row>
     <row r="379" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A379" s="74"/>
@@ -7263,9 +7139,8 @@
       <c r="E379" s="75"/>
       <c r="F379" s="75"/>
       <c r="G379" s="75"/>
-      <c r="H379" s="77"/>
       <c r="I379" s="75"/>
-      <c r="J379" s="36"/>
+      <c r="J379" s="37"/>
     </row>
     <row r="380" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A380" s="74"/>
@@ -7274,20 +7149,18 @@
       <c r="E380" s="75"/>
       <c r="F380" s="75"/>
       <c r="G380" s="75"/>
-      <c r="H380" s="77"/>
       <c r="I380" s="75"/>
-      <c r="J380" s="36"/>
+      <c r="J380" s="37"/>
     </row>
     <row r="381" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A381" s="74"/>
       <c r="C381" s="74"/>
-      <c r="D381" s="84"/>
+      <c r="D381" s="75"/>
       <c r="E381" s="75"/>
       <c r="F381" s="75"/>
       <c r="G381" s="75"/>
-      <c r="H381" s="77"/>
       <c r="I381" s="75"/>
-      <c r="J381" s="36"/>
+      <c r="J381" s="37"/>
     </row>
     <row r="382" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A382" s="74"/>
@@ -7297,7 +7170,7 @@
       <c r="F382" s="75"/>
       <c r="G382" s="75"/>
       <c r="I382" s="75"/>
-      <c r="J382" s="36"/>
+      <c r="J382" s="37"/>
     </row>
     <row r="383" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A383" s="74"/>
@@ -7307,7 +7180,7 @@
       <c r="F383" s="75"/>
       <c r="G383" s="75"/>
       <c r="I383" s="75"/>
-      <c r="J383" s="36"/>
+      <c r="J383" s="37"/>
     </row>
     <row r="384" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A384" s="74"/>
@@ -7317,7 +7190,7 @@
       <c r="F384" s="75"/>
       <c r="G384" s="75"/>
       <c r="I384" s="75"/>
-      <c r="J384" s="36"/>
+      <c r="J384" s="37"/>
     </row>
     <row r="385" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A385" s="74"/>
@@ -7327,7 +7200,7 @@
       <c r="F385" s="75"/>
       <c r="G385" s="75"/>
       <c r="I385" s="75"/>
-      <c r="J385" s="36"/>
+      <c r="J385" s="37"/>
     </row>
     <row r="386" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A386" s="74"/>
@@ -7337,7 +7210,7 @@
       <c r="F386" s="75"/>
       <c r="G386" s="75"/>
       <c r="I386" s="75"/>
-      <c r="J386" s="36"/>
+      <c r="J386" s="37"/>
     </row>
     <row r="387" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A387" s="74"/>
@@ -7347,7 +7220,7 @@
       <c r="F387" s="75"/>
       <c r="G387" s="75"/>
       <c r="I387" s="75"/>
-      <c r="J387" s="36"/>
+      <c r="J387" s="37"/>
     </row>
     <row r="388" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A388" s="74"/>
@@ -7357,7 +7230,7 @@
       <c r="F388" s="75"/>
       <c r="G388" s="75"/>
       <c r="I388" s="75"/>
-      <c r="J388" s="36"/>
+      <c r="J388" s="37"/>
     </row>
     <row r="389" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A389" s="74"/>
@@ -7367,7 +7240,7 @@
       <c r="F389" s="75"/>
       <c r="G389" s="75"/>
       <c r="I389" s="75"/>
-      <c r="J389" s="36"/>
+      <c r="J389" s="37"/>
     </row>
     <row r="390" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A390" s="74"/>
@@ -7377,7 +7250,7 @@
       <c r="F390" s="75"/>
       <c r="G390" s="75"/>
       <c r="I390" s="75"/>
-      <c r="J390" s="36"/>
+      <c r="J390" s="37"/>
     </row>
     <row r="391" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A391" s="74"/>
@@ -7387,7 +7260,7 @@
       <c r="F391" s="75"/>
       <c r="G391" s="75"/>
       <c r="I391" s="75"/>
-      <c r="J391" s="36"/>
+      <c r="J391" s="37"/>
     </row>
     <row r="392" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A392" s="74"/>
@@ -7397,7 +7270,7 @@
       <c r="F392" s="75"/>
       <c r="G392" s="75"/>
       <c r="I392" s="75"/>
-      <c r="J392" s="36"/>
+      <c r="J392" s="37"/>
     </row>
     <row r="393" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A393" s="74"/>
@@ -7407,7 +7280,7 @@
       <c r="F393" s="75"/>
       <c r="G393" s="75"/>
       <c r="I393" s="75"/>
-      <c r="J393" s="36"/>
+      <c r="J393" s="37"/>
     </row>
     <row r="394" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A394" s="74"/>
@@ -7417,17 +7290,17 @@
       <c r="F394" s="75"/>
       <c r="G394" s="75"/>
       <c r="I394" s="75"/>
-      <c r="J394" s="36"/>
+      <c r="J394" s="37"/>
     </row>
     <row r="395" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A395" s="74"/>
       <c r="C395" s="74"/>
       <c r="D395" s="75"/>
       <c r="E395" s="75"/>
-      <c r="F395" s="75"/>
-      <c r="G395" s="75"/>
+      <c r="F395" s="74"/>
+      <c r="G395" s="74"/>
       <c r="I395" s="75"/>
-      <c r="J395" s="36"/>
+      <c r="J395" s="37"/>
     </row>
     <row r="396" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A396" s="74"/>
@@ -7437,7 +7310,7 @@
       <c r="F396" s="75"/>
       <c r="G396" s="75"/>
       <c r="I396" s="75"/>
-      <c r="J396" s="36"/>
+      <c r="J396" s="37"/>
     </row>
     <row r="397" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A397" s="74"/>
@@ -7447,17 +7320,17 @@
       <c r="F397" s="75"/>
       <c r="G397" s="75"/>
       <c r="I397" s="75"/>
-      <c r="J397" s="36"/>
+      <c r="J397" s="37"/>
     </row>
     <row r="398" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A398" s="74"/>
       <c r="C398" s="74"/>
       <c r="D398" s="75"/>
       <c r="E398" s="75"/>
-      <c r="F398" s="74"/>
-      <c r="G398" s="74"/>
+      <c r="F398" s="75"/>
+      <c r="G398" s="75"/>
       <c r="I398" s="75"/>
-      <c r="J398" s="36"/>
+      <c r="J398" s="37"/>
     </row>
     <row r="399" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A399" s="74"/>
@@ -7467,7 +7340,7 @@
       <c r="F399" s="75"/>
       <c r="G399" s="75"/>
       <c r="I399" s="75"/>
-      <c r="J399" s="36"/>
+      <c r="J399" s="37"/>
     </row>
     <row r="400" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A400" s="74"/>
@@ -7477,7 +7350,7 @@
       <c r="F400" s="75"/>
       <c r="G400" s="75"/>
       <c r="I400" s="75"/>
-      <c r="J400" s="36"/>
+      <c r="J400" s="37"/>
     </row>
     <row r="401" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A401" s="74"/>
@@ -7487,38 +7360,11 @@
       <c r="F401" s="75"/>
       <c r="G401" s="75"/>
       <c r="I401" s="75"/>
-      <c r="J401" s="36"/>
-    </row>
-    <row r="402" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A402" s="74"/>
-      <c r="C402" s="74"/>
-      <c r="D402" s="75"/>
-      <c r="E402" s="75"/>
-      <c r="F402" s="75"/>
-      <c r="G402" s="75"/>
-      <c r="I402" s="75"/>
-      <c r="J402" s="36"/>
-    </row>
-    <row r="403" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A403" s="74"/>
-      <c r="C403" s="74"/>
-      <c r="D403" s="75"/>
-      <c r="E403" s="75"/>
-      <c r="F403" s="75"/>
-      <c r="G403" s="75"/>
-      <c r="I403" s="75"/>
-      <c r="J403" s="36"/>
-    </row>
-    <row r="404" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A404" s="74"/>
-      <c r="C404" s="74"/>
-      <c r="D404" s="75"/>
-      <c r="E404" s="75"/>
-      <c r="F404" s="75"/>
-      <c r="G404" s="75"/>
-      <c r="I404" s="75"/>
-      <c r="J404" s="36"/>
-    </row>
+      <c r="J401" s="37"/>
+    </row>
+    <row r="402" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="403" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="404" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="405" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="406" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="407" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -7526,9 +7372,9 @@
     <row r="409" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="410" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="411" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="412" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="413" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="414" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="415" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="416" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="417" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="418" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="419" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -7539,24 +7385,24 @@
     <row r="424" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="425" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="426" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="427" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="428" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="429" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="430" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="431" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="432" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="433" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="434" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="435" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="436" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="437" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="438" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="439" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="true" sqref="C11:C12 C14 C19:C20 C22:C23 C30:C97 C208:C259 C261:C262 C264:C294 C299:C404" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="true" sqref="C10:C11 C17 C19:C20 C27:C94 C205:C256 C258:C259 C261:C291 C296:C401" type="list">
       <formula1>"Critical Error,Error,Warning"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="C2:C10 C13 C15:C18 C21 C24:C29 C98:C207 C260 C263 C295:C298" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="C2:C9 C12:C16 C18 C21:C26 C95:C204 C257 C260 C292:C295" type="list">
       <formula1>"Critical Error,Error,Warning"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -7583,170 +7429,170 @@
   <dimension ref="A1:H8"/>
   <sheetFormatPr defaultColWidth="9.14453125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="13.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="13.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="87" width="25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="23.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="26.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="23.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="12.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="26.86"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="88" width="72.14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="89" t="s">
-        <v>209</v>
+        <v>193</v>
       </c>
       <c r="B1" s="89" t="s">
-        <v>210</v>
+        <v>194</v>
       </c>
       <c r="C1" s="89" t="s">
-        <v>211</v>
+        <v>195</v>
       </c>
       <c r="D1" s="90" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="E1" s="89" t="s">
-        <v>213</v>
+        <v>197</v>
       </c>
       <c r="F1" s="89"/>
       <c r="G1" s="89" t="s">
-        <v>214</v>
+        <v>198</v>
       </c>
       <c r="H1" s="91" t="s">
-        <v>215</v>
+        <v>199</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
-        <v>216</v>
+      <c r="A2" s="1" t="s">
+        <v>200</v>
       </c>
       <c r="B2" s="92" t="n">
         <v>45580</v>
       </c>
       <c r="C2" s="92" t="s">
-        <v>217</v>
+        <v>201</v>
       </c>
       <c r="D2" s="87" t="n">
         <v>1001</v>
       </c>
-      <c r="E2" s="0" t="n">
+      <c r="E2" s="1" t="n">
         <v>1029</v>
       </c>
       <c r="G2" s="93" t="s">
-        <v>218</v>
+        <v>202</v>
       </c>
       <c r="H2" s="88" t="s">
-        <v>219</v>
+        <v>203</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
-        <v>216</v>
+      <c r="A3" s="1" t="s">
+        <v>200</v>
       </c>
       <c r="B3" s="92" t="n">
         <v>45580</v>
       </c>
-      <c r="C3" s="0" t="s">
-        <v>220</v>
+      <c r="C3" s="1" t="s">
+        <v>204</v>
       </c>
       <c r="D3" s="87" t="n">
         <v>2001</v>
       </c>
-      <c r="E3" s="0" t="n">
+      <c r="E3" s="1" t="n">
         <v>2013</v>
       </c>
       <c r="H3" s="88" t="s">
-        <v>221</v>
+        <v>205</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
-        <v>216</v>
+      <c r="A4" s="1" t="s">
+        <v>200</v>
       </c>
       <c r="B4" s="92" t="n">
         <v>45580</v>
       </c>
-      <c r="C4" s="0" t="s">
-        <v>222</v>
+      <c r="C4" s="1" t="s">
+        <v>206</v>
       </c>
       <c r="D4" s="87" t="n">
         <v>3001</v>
       </c>
-      <c r="E4" s="0" t="n">
+      <c r="E4" s="1" t="n">
         <v>3019</v>
       </c>
       <c r="H4" s="88" t="s">
-        <v>223</v>
+        <v>207</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
-        <v>216</v>
+      <c r="A5" s="1" t="s">
+        <v>200</v>
       </c>
       <c r="B5" s="92" t="n">
         <v>45580</v>
       </c>
-      <c r="C5" s="0" t="s">
-        <v>224</v>
+      <c r="C5" s="1" t="s">
+        <v>208</v>
       </c>
       <c r="D5" s="87" t="s">
-        <v>85</v>
-      </c>
-      <c r="E5" s="0" t="s">
-        <v>85</v>
+        <v>98</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>98</v>
       </c>
       <c r="H5" s="94" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
-        <v>216</v>
+      <c r="A6" s="1" t="s">
+        <v>200</v>
       </c>
       <c r="B6" s="92" t="n">
         <v>45580</v>
       </c>
-      <c r="C6" s="0" t="s">
-        <v>226</v>
+      <c r="C6" s="1" t="s">
+        <v>210</v>
       </c>
       <c r="D6" s="87" t="n">
         <v>5001</v>
       </c>
-      <c r="E6" s="0" t="n">
+      <c r="E6" s="1" t="n">
         <v>5010</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
-        <v>216</v>
+      <c r="A7" s="1" t="s">
+        <v>200</v>
       </c>
       <c r="B7" s="92" t="n">
         <v>45580</v>
       </c>
-      <c r="C7" s="0" t="s">
-        <v>227</v>
+      <c r="C7" s="1" t="s">
+        <v>211</v>
       </c>
       <c r="D7" s="87" t="n">
         <v>9001</v>
       </c>
-      <c r="E7" s="0" t="n">
+      <c r="E7" s="1" t="n">
         <v>9005</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
-        <v>228</v>
+      <c r="A8" s="1" t="s">
+        <v>212</v>
       </c>
       <c r="B8" s="92" t="n">
         <v>45614</v>
       </c>
-      <c r="C8" s="0" t="s">
-        <v>229</v>
+      <c r="C8" s="1" t="s">
+        <v>213</v>
       </c>
       <c r="D8" s="87" t="s">
-        <v>230</v>
-      </c>
-      <c r="E8" s="0" t="s">
-        <v>230</v>
+        <v>214</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>214</v>
       </c>
     </row>
   </sheetData>
